--- a/Entertainment.xlsx
+++ b/Entertainment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39775551-BBC8-4FD8-9248-EFB6F757C2D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C28629A-FC0E-4A54-95A6-440A3A467B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="4290" windowWidth="38175" windowHeight="15240" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1532,13 +1532,19 @@
     <numFmt numFmtId="165" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -1549,21 +1555,28 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -1571,20 +1584,20 @@
     <font>
       <b/>
       <u/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -1652,55 +1665,56 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3608,13 +3622,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B1669C-2C43-405D-A4FE-FB3FBD95AFDE}">
   <dimension ref="A1:AS240"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" style="23" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="4" customWidth="1"/>
+    <col min="4" max="5" width="8.85546875" style="4"/>
+    <col min="6" max="6" width="10.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.85546875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.25">
@@ -3667,7 +3684,7 @@
       <c r="AS1" s="3"/>
     </row>
     <row r="2" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="3"/>
@@ -3716,51 +3733,51 @@
       <c r="AS2" s="3"/>
     </row>
     <row r="3" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="8" t="s">
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="9"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="10"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
@@ -3785,10 +3802,10 @@
       <c r="AS3" s="3"/>
     </row>
     <row r="4" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A4" s="10">
+      <c r="A4" s="11">
         <v>1</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="12" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -3797,23 +3814,23 @@
       <c r="D4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="13">
         <f>+[1]Main!$I$3</f>
         <v>1253.22</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="14">
         <f>+[1]Main!$I$5</f>
         <v>532882.92942000006</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="14">
         <f>+[1]Main!$I$7-[1]Main!$I$6</f>
         <v>6062.6859999999997</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="14">
         <f>+F4+G4</f>
         <v>538945.61542000005</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="15" t="s">
         <v>261</v>
       </c>
       <c r="J4" s="3"/>
@@ -3856,11 +3873,11 @@
       <c r="AS4" s="3"/>
     </row>
     <row r="5" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
+      <c r="A5" s="11">
         <f>+A4+1</f>
         <v>2</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -3869,26 +3886,26 @@
       <c r="D5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="13">
         <f>+[2]Main!$K$2</f>
         <v>115.68</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="14">
         <f>+[2]Main!$K$4</f>
         <v>207984.98580144002</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="14">
         <f>+[2]Main!$K$6-[2]Main!$K$5</f>
         <v>31164</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="14">
         <f t="shared" ref="H5:H10" si="0">+F5+G5</f>
         <v>239148.98580144002</v>
       </c>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="15" t="s">
         <v>296</v>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="17">
         <v>45966</v>
       </c>
       <c r="K5" s="3"/>
@@ -3930,11 +3947,11 @@
       <c r="AS5" s="3"/>
     </row>
     <row r="6" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A6" s="10">
+      <c r="A6" s="11">
         <f t="shared" ref="A6:A69" si="1">+A5+1</f>
         <v>3</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -3943,23 +3960,23 @@
       <c r="D6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="13">
         <f>+[3]Main!$I$2</f>
         <v>34.549999999999997</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="14">
         <f>+[3]Main!$I$4</f>
         <v>129621.37067784999</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="14">
         <f>+[3]Main!$I$6-[3]Main!$I$5</f>
         <v>90529</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="14">
         <f t="shared" si="0"/>
         <v>220150.37067784998</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="15" t="s">
         <v>261</v>
       </c>
       <c r="J6" s="3"/>
@@ -4002,11 +4019,11 @@
       <c r="AS6" s="3"/>
     </row>
     <row r="7" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
+      <c r="A7" s="11">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -4015,23 +4032,23 @@
       <c r="D7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="13">
         <f>+[4]Main!$H$2</f>
         <v>3214</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="14">
         <f>+[4]Main!$H$4*FX!C2</f>
         <v>124966.1644815872</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="14">
         <f>+([4]Main!$H$6-[4]Main!$H$5)*FX!C2</f>
         <v>12550.617600000001</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="14">
         <f t="shared" si="0"/>
         <v>137516.78208158721</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="15" t="s">
         <v>243</v>
       </c>
       <c r="J7" s="3"/>
@@ -4074,11 +4091,11 @@
       <c r="AS7" s="3"/>
     </row>
     <row r="8" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A8" s="10">
+      <c r="A8" s="11">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="12" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -4087,23 +4104,23 @@
       <c r="D8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <f>+[5]Main!$H$2</f>
         <v>627.5</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="14">
         <f>+[5]Main!$H$5*FX!C3</f>
         <v>132772.605128675</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="14">
         <f>+([5]Main!$H$7-[5]Main!$H$6)*FX!C3</f>
         <v>-8594.32</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="14">
         <f t="shared" si="0"/>
         <v>124178.28512867499</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="15" t="s">
         <v>246</v>
       </c>
       <c r="J8" s="3"/>
@@ -4146,11 +4163,11 @@
       <c r="AS8" s="3"/>
     </row>
     <row r="9" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+      <c r="A9" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="12" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -4159,23 +4176,23 @@
       <c r="D9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="13">
         <f>+[6]Main!$I$2</f>
         <v>10935</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="14">
         <f>+[6]Main!$I$4*FX!C2</f>
         <v>90887.520960000009</v>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="14">
         <f>+([6]Main!$I$6-[6]Main!$I$5)*FX!C2</f>
         <v>-9499.84</v>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="14">
         <f t="shared" si="0"/>
         <v>81387.680960000012</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="15" t="s">
         <v>243</v>
       </c>
       <c r="J9" s="3"/>
@@ -4218,11 +4235,11 @@
       <c r="AS9" s="3"/>
     </row>
     <row r="10" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A10" s="10">
+      <c r="A10" s="11">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="12" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -4231,23 +4248,23 @@
       <c r="D10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="13">
         <f>+[7]Main!$I$2</f>
         <v>141.63</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="14">
         <f>+[7]Main!$I$4</f>
         <v>82151.979704910002</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="14">
         <f>+[7]Main!$I$6-[7]Main!$I$5</f>
         <v>1013.5080000000007</v>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="14">
         <f t="shared" si="0"/>
         <v>83165.487704910003</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="15" t="s">
         <v>246</v>
       </c>
       <c r="J10" s="3"/>
@@ -4288,7 +4305,7 @@
       <c r="AS10" s="3"/>
     </row>
     <row r="11" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
+      <c r="A11" s="11">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
@@ -4301,11 +4318,11 @@
       <c r="D11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="14"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="15"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -4344,7 +4361,7 @@
       <c r="AS11" s="3"/>
     </row>
     <row r="12" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
+      <c r="A12" s="11">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
@@ -4357,11 +4374,11 @@
       <c r="D12" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="14"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="15"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -4400,7 +4417,7 @@
       <c r="AS12" s="3"/>
     </row>
     <row r="13" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
+      <c r="A13" s="11">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
@@ -4413,11 +4430,11 @@
       <c r="D13" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="14"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="15"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -4456,7 +4473,7 @@
       <c r="AS13" s="3"/>
     </row>
     <row r="14" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A14" s="10">
+      <c r="A14" s="11">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
@@ -4469,11 +4486,11 @@
       <c r="D14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="12"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="14"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="15"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -4512,11 +4529,11 @@
       <c r="AS14" s="3"/>
     </row>
     <row r="15" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
+      <c r="A15" s="11">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="12" t="s">
         <v>36</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -4525,26 +4542,26 @@
       <c r="D15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="13">
         <f>+[8]Main!$I$2</f>
         <v>173.3</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="14">
         <f>+[8]Main!$I$4</f>
         <v>43360.925609900005</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="14">
         <f>+[8]Main!$I$6-[8]Main!$I$5</f>
         <v>-1230</v>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="14">
         <f>+F15+G15</f>
         <v>42130.925609900005</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="I15" s="15" t="s">
         <v>476</v>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="17">
         <v>45958</v>
       </c>
       <c r="K15" s="3"/>
@@ -4586,11 +4603,11 @@
       <c r="AS15" s="3"/>
     </row>
     <row r="16" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A16" s="10">
+      <c r="A16" s="11">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -4599,23 +4616,23 @@
       <c r="D16" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="13">
         <f>+[9]Main!$H$2</f>
         <v>58.14</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="14">
         <f>+[9]Main!$H$4</f>
         <v>38796.821127900002</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="14">
         <f>+[9]Main!$H$6-[9]Main!$H$5</f>
         <v>-1403.174</v>
       </c>
-      <c r="H16" s="13">
+      <c r="H16" s="14">
         <f>+F16+G16</f>
         <v>37393.647127900003</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="I16" s="15" t="s">
         <v>239</v>
       </c>
       <c r="J16" s="3"/>
@@ -4658,11 +4675,11 @@
       <c r="AS16" s="3"/>
     </row>
     <row r="17" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A17" s="10">
+      <c r="A17" s="11">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="12" t="s">
         <v>40</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -4671,23 +4688,23 @@
       <c r="D17" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="13">
         <f>+[10]Main!$G$2</f>
         <v>51.15</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="14">
         <f>+[10]Main!$G$4</f>
         <v>37085.089004699999</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="14">
         <f>+[10]Main!$G$6-[10]Main!$G$5</f>
         <v>9804</v>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="14">
         <f>+F17+G17</f>
         <v>46889.089004699999</v>
       </c>
-      <c r="I17" s="14" t="s">
+      <c r="I17" s="15" t="s">
         <v>239</v>
       </c>
       <c r="J17" s="3"/>
@@ -4730,7 +4747,7 @@
       <c r="AS17" s="3"/>
     </row>
     <row r="18" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A18" s="10">
+      <c r="A18" s="11">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
@@ -4744,10 +4761,10 @@
         <v>23</v>
       </c>
       <c r="E18" s="3"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="15"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
@@ -4786,11 +4803,11 @@
       <c r="AS18" s="3"/>
     </row>
     <row r="19" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A19" s="10">
+      <c r="A19" s="11">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="12" t="s">
         <v>44</v>
       </c>
       <c r="C19" s="3" t="s">
@@ -4803,19 +4820,19 @@
         <f>+[11]Main!$L$3</f>
         <v>228.01</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="14">
         <f>+[11]Main!$L$5</f>
         <v>42061.053038120001</v>
       </c>
-      <c r="G19" s="13">
+      <c r="G19" s="14">
         <f>+[11]Main!$L$7-[11]Main!$L$6</f>
         <v>1030</v>
       </c>
-      <c r="H19" s="13">
+      <c r="H19" s="14">
         <f>+F19+G19</f>
         <v>43091.053038120001</v>
       </c>
-      <c r="I19" s="14" t="s">
+      <c r="I19" s="15" t="s">
         <v>476</v>
       </c>
       <c r="J19" s="3"/>
@@ -4858,11 +4875,11 @@
       <c r="AS19" s="3"/>
     </row>
     <row r="20" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A20" s="10">
+      <c r="A20" s="11">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="12" t="s">
         <v>46</v>
       </c>
       <c r="C20" s="3" t="s">
@@ -4871,23 +4888,23 @@
       <c r="D20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="18">
         <f>+[12]Main!$H$2</f>
         <v>134.9</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="14">
         <f>+[12]Main!$H$4</f>
         <v>31344.512106500002</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="14">
         <f>+[12]Main!$H$6-[12]Main!$H$5</f>
         <v>764.97299999999996</v>
       </c>
-      <c r="H20" s="13">
+      <c r="H20" s="14">
         <f>+F20+G20</f>
         <v>32109.485106500004</v>
       </c>
-      <c r="I20" s="14" t="s">
+      <c r="I20" s="15" t="s">
         <v>239</v>
       </c>
       <c r="J20" s="3"/>
@@ -4930,11 +4947,11 @@
       <c r="AS20" s="3"/>
     </row>
     <row r="21" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A21" s="10">
+      <c r="A21" s="11">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="12" t="s">
         <v>48</v>
       </c>
       <c r="C21" s="3" t="s">
@@ -4947,19 +4964,19 @@
         <f>+[13]Main!$I$2</f>
         <v>66.67</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="14">
         <f>+[13]Main!$I$4*FX!C5</f>
         <v>26732.303286336904</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="14">
         <f>+([13]Main!$I$6-[13]Main!$I$5)*FX!C5</f>
         <v>718.45199999999988</v>
       </c>
-      <c r="H21" s="13">
+      <c r="H21" s="14">
         <f>+F21+G21</f>
         <v>27450.755286336906</v>
       </c>
-      <c r="I21" s="14" t="s">
+      <c r="I21" s="15" t="s">
         <v>246</v>
       </c>
       <c r="J21" s="3"/>
@@ -5002,11 +5019,11 @@
       <c r="AS21" s="3"/>
     </row>
     <row r="22" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A22" s="10">
+      <c r="A22" s="11">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="12" t="s">
         <v>51</v>
       </c>
       <c r="C22" s="3" t="s">
@@ -5019,22 +5036,22 @@
         <f>+[14]Main!$H$2</f>
         <v>11.87</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="14">
         <f>+[14]Main!$H$4</f>
         <v>29387.416987339999</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="14">
         <f>+[14]Main!$H$6-[14]Main!$H$5</f>
         <v>29744</v>
       </c>
-      <c r="H22" s="13">
+      <c r="H22" s="14">
         <f>+F22+G22</f>
         <v>59131.416987339995</v>
       </c>
-      <c r="I22" s="14" t="s">
+      <c r="I22" s="15" t="s">
         <v>474</v>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="17">
         <v>45967</v>
       </c>
       <c r="K22" s="3"/>
@@ -5076,11 +5093,11 @@
       <c r="AS22" s="3"/>
     </row>
     <row r="23" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A23" s="10">
+      <c r="A23" s="11">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="12" t="s">
         <v>54</v>
       </c>
       <c r="C23" s="3" t="s">
@@ -5093,19 +5110,19 @@
         <f>+[15]Main!$G$3</f>
         <v>95</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="14">
         <f>+[15]Main!$G$5</f>
         <v>23679.881450000001</v>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="14">
         <f>+[15]Main!$G$7-[15]Main!$G$6</f>
         <v>1592</v>
       </c>
-      <c r="H23" s="13">
+      <c r="H23" s="14">
         <f>+F23+G23</f>
         <v>25271.881450000001</v>
       </c>
-      <c r="I23" s="14" t="s">
+      <c r="I23" s="15" t="s">
         <v>246</v>
       </c>
       <c r="J23" s="3"/>
@@ -5148,7 +5165,7 @@
       <c r="AS23" s="3"/>
     </row>
     <row r="24" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A24" s="10">
+      <c r="A24" s="11">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
@@ -5162,10 +5179,10 @@
         <v>26</v>
       </c>
       <c r="E24" s="3"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="15"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
@@ -5204,11 +5221,11 @@
       <c r="AS24" s="3"/>
     </row>
     <row r="25" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A25" s="10">
+      <c r="A25" s="11">
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="12" t="s">
         <v>58</v>
       </c>
       <c r="C25" s="3" t="s">
@@ -5221,19 +5238,19 @@
         <f>+[16]Main!$G$2</f>
         <v>45.96</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="14">
         <f>+[16]Main!$G$4</f>
         <v>22817.764463160001</v>
       </c>
-      <c r="G25" s="13">
+      <c r="G25" s="14">
         <f>+[16]Main!$G$6-[16]Main!$G$5</f>
         <v>-669.26499999999999</v>
       </c>
-      <c r="H25" s="13">
+      <c r="H25" s="14">
         <f>+F25+G25</f>
         <v>22148.499463160002</v>
       </c>
-      <c r="I25" s="14" t="s">
+      <c r="I25" s="15" t="s">
         <v>474</v>
       </c>
       <c r="J25" s="3"/>
@@ -5276,11 +5293,11 @@
       <c r="AS25" s="3"/>
     </row>
     <row r="26" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A26" s="10">
+      <c r="A26" s="11">
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="12" t="s">
         <v>60</v>
       </c>
       <c r="C26" s="3" t="s">
@@ -5293,19 +5310,19 @@
         <f>+[17]Main!$H$2</f>
         <v>35.83</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="14">
         <f>+[17]Main!$H$4</f>
         <v>18644.53591988</v>
       </c>
-      <c r="G26" s="13">
+      <c r="G26" s="14">
         <f>+[17]Main!$H$6-[17]Main!$H$5</f>
         <v>3153</v>
       </c>
-      <c r="H26" s="13">
+      <c r="H26" s="14">
         <f>+F26+G26</f>
         <v>21797.53591988</v>
       </c>
-      <c r="I26" s="14" t="s">
+      <c r="I26" s="15" t="s">
         <v>241</v>
       </c>
       <c r="J26" s="3"/>
@@ -5348,7 +5365,7 @@
       <c r="AS26" s="3"/>
     </row>
     <row r="27" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A27" s="10">
+      <c r="A27" s="11">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
@@ -5362,10 +5379,10 @@
         <v>24</v>
       </c>
       <c r="E27" s="3"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="15"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
@@ -5404,11 +5421,11 @@
       <c r="AS27" s="3"/>
     </row>
     <row r="28" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A28" s="10">
+      <c r="A28" s="11">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="12" t="s">
         <v>64</v>
       </c>
       <c r="C28" s="3" t="s">
@@ -5417,23 +5434,23 @@
       <c r="D28" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E28" s="18">
+      <c r="E28" s="19">
         <f>+[18]Main!$I$2</f>
         <v>5241</v>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="14">
         <f>+[18]Main!$I$4*FX!C2</f>
         <v>21944.563863571202</v>
       </c>
-      <c r="G28" s="13">
+      <c r="G28" s="14">
         <f>+([18]Main!$I$6-[18]Main!$I$5)*FX!C2</f>
         <v>-2059.9551999999999</v>
       </c>
-      <c r="H28" s="13">
+      <c r="H28" s="14">
         <f>+F28+G28</f>
         <v>19884.608663571202</v>
       </c>
-      <c r="I28" s="14"/>
+      <c r="I28" s="15"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
@@ -5472,11 +5489,11 @@
       <c r="AS28" s="3"/>
     </row>
     <row r="29" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A29" s="10">
+      <c r="A29" s="11">
         <f t="shared" si="1"/>
         <v>26</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C29" s="3" t="s">
@@ -5485,23 +5502,23 @@
       <c r="D29" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E29" s="18">
+      <c r="E29" s="19">
         <f>+[19]Main!$I$2</f>
         <v>16735</v>
       </c>
-      <c r="F29" s="13">
+      <c r="F29" s="14">
         <f>+[19]Main!$I$4*FX!C2</f>
         <v>14518.749837375999</v>
       </c>
-      <c r="G29" s="13">
+      <c r="G29" s="14">
         <f>+([19]Main!$I$6-[19]Main!$I$5)*FX!C2</f>
         <v>-1445.152</v>
       </c>
-      <c r="H29" s="13">
+      <c r="H29" s="14">
         <f>+F29+G29</f>
         <v>13073.597837375999</v>
       </c>
-      <c r="I29" s="14" t="s">
+      <c r="I29" s="15" t="s">
         <v>277</v>
       </c>
       <c r="J29" s="3"/>
@@ -5542,7 +5559,7 @@
       <c r="AS29" s="3"/>
     </row>
     <row r="30" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A30" s="10">
+      <c r="A30" s="11">
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
@@ -5556,10 +5573,10 @@
         <v>23</v>
       </c>
       <c r="E30" s="3"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="15"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
@@ -5598,11 +5615,11 @@
       <c r="AS30" s="3"/>
     </row>
     <row r="31" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A31" s="10">
+      <c r="A31" s="11">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="12" t="s">
         <v>70</v>
       </c>
       <c r="C31" s="3" t="s">
@@ -5615,19 +5632,19 @@
         <f>+[20]Main!$J$2</f>
         <v>184.82</v>
       </c>
-      <c r="F31" s="13">
+      <c r="F31" s="14">
         <f>+[20]Main!$J$4</f>
         <v>15180.539270520001</v>
       </c>
-      <c r="G31" s="13">
+      <c r="G31" s="14">
         <f>+[20]Main!$J$6-[20]Main!$J$5</f>
         <v>2214.2530000000002</v>
       </c>
-      <c r="H31" s="13">
+      <c r="H31" s="14">
         <f>+F31+G31</f>
         <v>17394.79227052</v>
       </c>
-      <c r="I31" s="14" t="s">
+      <c r="I31" s="15" t="s">
         <v>474</v>
       </c>
       <c r="J31" s="3"/>
@@ -5668,7 +5685,7 @@
       <c r="AS31" s="3"/>
     </row>
     <row r="32" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A32" s="10">
+      <c r="A32" s="11">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
@@ -5682,10 +5699,10 @@
         <v>22</v>
       </c>
       <c r="E32" s="3"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="15"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -5724,7 +5741,7 @@
       <c r="AS32" s="3"/>
     </row>
     <row r="33" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A33" s="10">
+      <c r="A33" s="11">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
@@ -5738,10 +5755,10 @@
         <v>22</v>
       </c>
       <c r="E33" s="3"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="15"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
@@ -5780,7 +5797,7 @@
       <c r="AS33" s="3"/>
     </row>
     <row r="34" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A34" s="10">
+      <c r="A34" s="11">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
@@ -5794,10 +5811,10 @@
         <v>22</v>
       </c>
       <c r="E34" s="3"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="15"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
@@ -5836,7 +5853,7 @@
       <c r="AS34" s="3"/>
     </row>
     <row r="35" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A35" s="10">
+      <c r="A35" s="11">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
@@ -5850,10 +5867,10 @@
         <v>22</v>
       </c>
       <c r="E35" s="3"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="15"/>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
@@ -5892,7 +5909,7 @@
       <c r="AS35" s="3"/>
     </row>
     <row r="36" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A36" s="10">
+      <c r="A36" s="11">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
@@ -5906,10 +5923,10 @@
         <v>82</v>
       </c>
       <c r="E36" s="3"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="15"/>
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
@@ -5948,7 +5965,7 @@
       <c r="AS36" s="3"/>
     </row>
     <row r="37" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A37" s="10">
+      <c r="A37" s="11">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
@@ -5962,10 +5979,10 @@
         <v>85</v>
       </c>
       <c r="E37" s="3"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="15"/>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
@@ -6004,11 +6021,11 @@
       <c r="AS37" s="3"/>
     </row>
     <row r="38" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A38" s="10">
+      <c r="A38" s="11">
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="12" t="s">
         <v>86</v>
       </c>
       <c r="C38" s="3" t="s">
@@ -6021,19 +6038,19 @@
         <f>+[21]Main!$H$2</f>
         <v>65.319999999999993</v>
       </c>
-      <c r="F38" s="13">
+      <c r="F38" s="14">
         <f>+[21]Main!$H$4</f>
         <v>9114.1865409199982</v>
       </c>
-      <c r="G38" s="13">
+      <c r="G38" s="14">
         <f>+[21]Main!$H$6-[21]Main!$H$5</f>
         <v>2685.8</v>
       </c>
-      <c r="H38" s="13">
+      <c r="H38" s="14">
         <f>+F38+G38</f>
         <v>11799.986540919999</v>
       </c>
-      <c r="I38" s="14" t="s">
+      <c r="I38" s="15" t="s">
         <v>246</v>
       </c>
       <c r="J38" s="3"/>
@@ -6076,7 +6093,7 @@
       <c r="AS38" s="3"/>
     </row>
     <row r="39" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A39" s="10">
+      <c r="A39" s="11">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
@@ -6090,10 +6107,10 @@
         <v>22</v>
       </c>
       <c r="E39" s="3"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="15"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
@@ -6132,11 +6149,11 @@
       <c r="AS39" s="3"/>
     </row>
     <row r="40" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A40" s="10">
+      <c r="A40" s="11">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="12" t="s">
         <v>90</v>
       </c>
       <c r="C40" s="3" t="s">
@@ -6149,19 +6166,19 @@
         <f>+[22]Main!$I$2</f>
         <v>13.8</v>
       </c>
-      <c r="F40" s="13">
+      <c r="F40" s="14">
         <f>+[22]Main!$I$4</f>
         <v>9315</v>
       </c>
-      <c r="G40" s="13">
+      <c r="G40" s="14">
         <f>+[22]Main!$I$6-[22]Main!$I$5</f>
         <v>11775</v>
       </c>
-      <c r="H40" s="13">
+      <c r="H40" s="14">
         <f>+F40+G40</f>
         <v>21090</v>
       </c>
-      <c r="I40" s="14" t="s">
+      <c r="I40" s="15" t="s">
         <v>246</v>
       </c>
       <c r="J40" s="3"/>
@@ -6204,7 +6221,7 @@
       <c r="AS40" s="3"/>
     </row>
     <row r="41" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A41" s="10">
+      <c r="A41" s="11">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
@@ -6218,10 +6235,10 @@
         <v>94</v>
       </c>
       <c r="E41" s="3"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="15"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
@@ -6260,7 +6277,7 @@
       <c r="AS41" s="3"/>
     </row>
     <row r="42" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A42" s="10">
+      <c r="A42" s="11">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
@@ -6274,10 +6291,10 @@
         <v>22</v>
       </c>
       <c r="E42" s="3"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="15"/>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
@@ -6316,7 +6333,7 @@
       <c r="AS42" s="3"/>
     </row>
     <row r="43" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A43" s="10">
+      <c r="A43" s="11">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
@@ -6330,10 +6347,10 @@
         <v>25</v>
       </c>
       <c r="E43" s="3"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="15"/>
       <c r="J43" s="3"/>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
@@ -6372,7 +6389,7 @@
       <c r="AS43" s="3"/>
     </row>
     <row r="44" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A44" s="10">
+      <c r="A44" s="11">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
@@ -6386,10 +6403,10 @@
         <v>23</v>
       </c>
       <c r="E44" s="3"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="15"/>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
@@ -6428,7 +6445,7 @@
       <c r="AS44" s="3"/>
     </row>
     <row r="45" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A45" s="10">
+      <c r="A45" s="11">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
@@ -6442,10 +6459,10 @@
         <v>26</v>
       </c>
       <c r="E45" s="3"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="15"/>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
@@ -6484,11 +6501,11 @@
       <c r="AS45" s="3"/>
     </row>
     <row r="46" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A46" s="10">
+      <c r="A46" s="11">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="12" t="s">
         <v>103</v>
       </c>
       <c r="C46" s="3" t="s">
@@ -6501,19 +6518,19 @@
         <f>+[23]Main!$I$2</f>
         <v>77.77</v>
       </c>
-      <c r="F46" s="13">
+      <c r="F46" s="14">
         <f>+[23]Main!$I$4</f>
         <v>6330.7175316000003</v>
       </c>
-      <c r="G46" s="13">
+      <c r="G46" s="14">
         <f>+[23]Main!$I$6-[23]Main!$I$5</f>
         <v>3205.0709999999999</v>
       </c>
-      <c r="H46" s="13">
+      <c r="H46" s="14">
         <f>+F46+G46</f>
         <v>9535.7885315999993</v>
       </c>
-      <c r="I46" s="14" t="s">
+      <c r="I46" s="15" t="s">
         <v>261</v>
       </c>
       <c r="J46" s="3"/>
@@ -6554,7 +6571,7 @@
       <c r="AS46" s="3"/>
     </row>
     <row r="47" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A47" s="10">
+      <c r="A47" s="11">
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
@@ -6568,10 +6585,10 @@
         <v>22</v>
       </c>
       <c r="E47" s="3"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="15"/>
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
@@ -6610,7 +6627,7 @@
       <c r="AS47" s="3"/>
     </row>
     <row r="48" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A48" s="10">
+      <c r="A48" s="11">
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
@@ -6624,10 +6641,10 @@
         <v>22</v>
       </c>
       <c r="E48" s="3"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="15"/>
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
@@ -6666,11 +6683,11 @@
       <c r="AS48" s="3"/>
     </row>
     <row r="49" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A49" s="10">
+      <c r="A49" s="11">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="12" t="s">
         <v>109</v>
       </c>
       <c r="C49" s="3" t="s">
@@ -6683,19 +6700,19 @@
         <f>+[24]Main!$G$2</f>
         <v>18.07</v>
       </c>
-      <c r="F49" s="13">
+      <c r="F49" s="14">
         <f>+[24]Main!$G$4</f>
         <v>6087.7829999999994</v>
       </c>
-      <c r="G49" s="13">
+      <c r="G49" s="14">
         <f>+[24]Main!$G$6-[24]Main!$G$5</f>
         <v>1609.7280000000001</v>
       </c>
-      <c r="H49" s="13">
+      <c r="H49" s="14">
         <f>+F49+G49</f>
         <v>7697.5109999999995</v>
       </c>
-      <c r="I49" s="14" t="s">
+      <c r="I49" s="15" t="s">
         <v>239</v>
       </c>
       <c r="J49" s="3"/>
@@ -6738,7 +6755,7 @@
       <c r="AS49" s="3"/>
     </row>
     <row r="50" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A50" s="10">
+      <c r="A50" s="11">
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
@@ -6752,10 +6769,10 @@
         <v>113</v>
       </c>
       <c r="E50" s="3"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="14"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14"/>
+      <c r="H50" s="14"/>
+      <c r="I50" s="15"/>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
@@ -6794,7 +6811,7 @@
       <c r="AS50" s="3"/>
     </row>
     <row r="51" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A51" s="10">
+      <c r="A51" s="11">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
@@ -6808,10 +6825,10 @@
         <v>26</v>
       </c>
       <c r="E51" s="3"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14"/>
+      <c r="I51" s="15"/>
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
@@ -6850,7 +6867,7 @@
       <c r="AS51" s="3"/>
     </row>
     <row r="52" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A52" s="10">
+      <c r="A52" s="11">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
@@ -6864,10 +6881,10 @@
         <v>118</v>
       </c>
       <c r="E52" s="3"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14"/>
+      <c r="I52" s="15"/>
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
@@ -6906,7 +6923,7 @@
       <c r="AS52" s="3"/>
     </row>
     <row r="53" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A53" s="10">
+      <c r="A53" s="11">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
@@ -6920,10 +6937,10 @@
         <v>121</v>
       </c>
       <c r="E53" s="3"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="15"/>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
@@ -6962,24 +6979,24 @@
       <c r="AS53" s="3"/>
     </row>
     <row r="54" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A54" s="10">
+      <c r="A54" s="11">
         <f t="shared" si="1"/>
         <v>51</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C54" s="19" t="s">
+      <c r="C54" s="20" t="s">
         <v>120</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>121</v>
       </c>
       <c r="E54" s="3"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="14"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="15"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
@@ -7018,7 +7035,7 @@
       <c r="AS54" s="3"/>
     </row>
     <row r="55" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A55" s="10">
+      <c r="A55" s="11">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
@@ -7032,10 +7049,10 @@
         <v>124</v>
       </c>
       <c r="E55" s="3"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="14"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14"/>
+      <c r="I55" s="15"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
@@ -7074,11 +7091,11 @@
       <c r="AS55" s="3"/>
     </row>
     <row r="56" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A56" s="10">
+      <c r="A56" s="11">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="12" t="s">
         <v>125</v>
       </c>
       <c r="C56" s="3" t="s">
@@ -7091,19 +7108,19 @@
         <f>+[25]Main!$I$2</f>
         <v>183.2</v>
       </c>
-      <c r="F56" s="13">
+      <c r="F56" s="14">
         <f>+[25]Main!$I$4</f>
         <v>5589.2865391999994</v>
       </c>
-      <c r="G56" s="13">
+      <c r="G56" s="14">
         <f>+[25]Main!$I$6-[25]Main!$I$5</f>
         <v>6379</v>
       </c>
-      <c r="H56" s="13">
+      <c r="H56" s="14">
         <f>+F56+G56</f>
         <v>11968.286539199999</v>
       </c>
-      <c r="I56" s="14" t="s">
+      <c r="I56" s="15" t="s">
         <v>246</v>
       </c>
       <c r="J56" s="3"/>
@@ -7144,7 +7161,7 @@
       <c r="AS56" s="3"/>
     </row>
     <row r="57" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A57" s="10">
+      <c r="A57" s="11">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
@@ -7158,10 +7175,10 @@
         <v>127</v>
       </c>
       <c r="E57" s="3"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="14"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="15"/>
       <c r="J57" s="3"/>
       <c r="K57" s="3"/>
       <c r="L57" s="3"/>
@@ -7200,7 +7217,7 @@
       <c r="AS57" s="3"/>
     </row>
     <row r="58" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A58" s="10">
+      <c r="A58" s="11">
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
@@ -7214,10 +7231,10 @@
         <v>22</v>
       </c>
       <c r="E58" s="3"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="14"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="15"/>
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
       <c r="L58" s="3"/>
@@ -7256,24 +7273,24 @@
       <c r="AS58" s="3"/>
     </row>
     <row r="59" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A59" s="10">
+      <c r="A59" s="11">
         <f t="shared" si="1"/>
         <v>56</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C59" s="19" t="s">
+      <c r="C59" s="20" t="s">
         <v>133</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E59" s="3"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
-      <c r="I59" s="14"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="15"/>
       <c r="J59" s="3"/>
       <c r="K59" s="3"/>
       <c r="L59" s="3"/>
@@ -7312,7 +7329,7 @@
       <c r="AS59" s="3"/>
     </row>
     <row r="60" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A60" s="10">
+      <c r="A60" s="11">
         <f t="shared" si="1"/>
         <v>57</v>
       </c>
@@ -7326,10 +7343,10 @@
         <v>22</v>
       </c>
       <c r="E60" s="3"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="14"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="14"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="15"/>
       <c r="J60" s="3"/>
       <c r="K60" s="3"/>
       <c r="L60" s="3"/>
@@ -7368,7 +7385,7 @@
       <c r="AS60" s="3"/>
     </row>
     <row r="61" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A61" s="10">
+      <c r="A61" s="11">
         <f t="shared" si="1"/>
         <v>58</v>
       </c>
@@ -7382,10 +7399,10 @@
         <v>35</v>
       </c>
       <c r="E61" s="3"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="13"/>
-      <c r="I61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
+      <c r="H61" s="14"/>
+      <c r="I61" s="15"/>
       <c r="J61" s="3"/>
       <c r="K61" s="3"/>
       <c r="L61" s="3"/>
@@ -7424,7 +7441,7 @@
       <c r="AS61" s="3"/>
     </row>
     <row r="62" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A62" s="10">
+      <c r="A62" s="11">
         <f t="shared" si="1"/>
         <v>59</v>
       </c>
@@ -7438,10 +7455,10 @@
         <v>23</v>
       </c>
       <c r="E62" s="3"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="13"/>
-      <c r="H62" s="13"/>
-      <c r="I62" s="14"/>
+      <c r="F62" s="14"/>
+      <c r="G62" s="14"/>
+      <c r="H62" s="14"/>
+      <c r="I62" s="15"/>
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
       <c r="L62" s="3"/>
@@ -7480,7 +7497,7 @@
       <c r="AS62" s="3"/>
     </row>
     <row r="63" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A63" s="10">
+      <c r="A63" s="11">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
@@ -7494,10 +7511,10 @@
         <v>23</v>
       </c>
       <c r="E63" s="3"/>
-      <c r="F63" s="13"/>
-      <c r="G63" s="13"/>
-      <c r="H63" s="13"/>
-      <c r="I63" s="14"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="14"/>
+      <c r="H63" s="14"/>
+      <c r="I63" s="15"/>
       <c r="J63" s="3"/>
       <c r="K63" s="3"/>
       <c r="L63" s="3"/>
@@ -7536,24 +7553,24 @@
       <c r="AS63" s="3"/>
     </row>
     <row r="64" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A64" s="10">
+      <c r="A64" s="11">
         <f t="shared" si="1"/>
         <v>61</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C64" s="19" t="s">
+      <c r="C64" s="20" t="s">
         <v>144</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E64" s="3"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
-      <c r="H64" s="13"/>
-      <c r="I64" s="14"/>
+      <c r="F64" s="14"/>
+      <c r="G64" s="14"/>
+      <c r="H64" s="14"/>
+      <c r="I64" s="15"/>
       <c r="J64" s="3"/>
       <c r="K64" s="3"/>
       <c r="L64" s="3"/>
@@ -7592,7 +7609,7 @@
       <c r="AS64" s="3"/>
     </row>
     <row r="65" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A65" s="10">
+      <c r="A65" s="11">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
@@ -7606,10 +7623,10 @@
         <v>22</v>
       </c>
       <c r="E65" s="3"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
-      <c r="H65" s="13"/>
-      <c r="I65" s="14"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14"/>
+      <c r="H65" s="14"/>
+      <c r="I65" s="15"/>
       <c r="J65" s="3"/>
       <c r="K65" s="3"/>
       <c r="L65" s="3"/>
@@ -7648,7 +7665,7 @@
       <c r="AS65" s="3"/>
     </row>
     <row r="66" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A66" s="10">
+      <c r="A66" s="11">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
@@ -7662,10 +7679,10 @@
         <v>23</v>
       </c>
       <c r="E66" s="3"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13"/>
-      <c r="I66" s="14"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14"/>
+      <c r="H66" s="14"/>
+      <c r="I66" s="15"/>
       <c r="J66" s="3"/>
       <c r="K66" s="3"/>
       <c r="L66" s="3"/>
@@ -7704,7 +7721,7 @@
       <c r="AS66" s="3"/>
     </row>
     <row r="67" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A67" s="10">
+      <c r="A67" s="11">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
@@ -7718,10 +7735,10 @@
         <v>24</v>
       </c>
       <c r="E67" s="3"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
-      <c r="H67" s="13"/>
-      <c r="I67" s="14"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14"/>
+      <c r="H67" s="14"/>
+      <c r="I67" s="15"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
@@ -7760,7 +7777,7 @@
       <c r="AS67" s="3"/>
     </row>
     <row r="68" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A68" s="10">
+      <c r="A68" s="11">
         <f t="shared" si="1"/>
         <v>65</v>
       </c>
@@ -7774,10 +7791,10 @@
         <v>153</v>
       </c>
       <c r="E68" s="3"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="14"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
+      <c r="H68" s="14"/>
+      <c r="I68" s="15"/>
       <c r="J68" s="3"/>
       <c r="K68" s="3"/>
       <c r="L68" s="3"/>
@@ -7816,7 +7833,7 @@
       <c r="AS68" s="3"/>
     </row>
     <row r="69" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A69" s="10">
+      <c r="A69" s="11">
         <f t="shared" si="1"/>
         <v>66</v>
       </c>
@@ -7830,10 +7847,10 @@
         <v>23</v>
       </c>
       <c r="E69" s="3"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="14"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="14"/>
+      <c r="H69" s="14"/>
+      <c r="I69" s="15"/>
       <c r="J69" s="3"/>
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
@@ -7872,24 +7889,24 @@
       <c r="AS69" s="3"/>
     </row>
     <row r="70" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A70" s="10">
+      <c r="A70" s="11">
         <f t="shared" ref="A70:A112" si="2">+A69+1</f>
         <v>67</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C70" s="19" t="s">
+      <c r="C70" s="20" t="s">
         <v>157</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E70" s="3"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="14"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="14"/>
+      <c r="H70" s="14"/>
+      <c r="I70" s="15"/>
       <c r="J70" s="3"/>
       <c r="K70" s="3"/>
       <c r="L70" s="3"/>
@@ -7928,7 +7945,7 @@
       <c r="AS70" s="3"/>
     </row>
     <row r="71" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A71" s="10">
+      <c r="A71" s="11">
         <f t="shared" si="2"/>
         <v>68</v>
       </c>
@@ -7942,10 +7959,10 @@
         <v>160</v>
       </c>
       <c r="E71" s="3"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="15"/>
       <c r="J71" s="3"/>
       <c r="K71" s="3"/>
       <c r="L71" s="3"/>
@@ -7984,7 +8001,7 @@
       <c r="AS71" s="3"/>
     </row>
     <row r="72" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A72" s="10">
+      <c r="A72" s="11">
         <f t="shared" si="2"/>
         <v>69</v>
       </c>
@@ -7998,10 +8015,10 @@
         <v>163</v>
       </c>
       <c r="E72" s="3"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14"/>
+      <c r="H72" s="14"/>
+      <c r="I72" s="15"/>
       <c r="J72" s="3"/>
       <c r="K72" s="3"/>
       <c r="L72" s="3"/>
@@ -8040,7 +8057,7 @@
       <c r="AS72" s="3"/>
     </row>
     <row r="73" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A73" s="10">
+      <c r="A73" s="11">
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
@@ -8054,10 +8071,10 @@
         <v>166</v>
       </c>
       <c r="E73" s="3"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
+      <c r="I73" s="15"/>
       <c r="J73" s="3"/>
       <c r="K73" s="3"/>
       <c r="L73" s="3"/>
@@ -8096,7 +8113,7 @@
       <c r="AS73" s="3"/>
     </row>
     <row r="74" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A74" s="10">
+      <c r="A74" s="11">
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
@@ -8110,10 +8127,10 @@
         <v>22</v>
       </c>
       <c r="E74" s="3"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="14"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="14"/>
+      <c r="H74" s="14"/>
+      <c r="I74" s="15"/>
       <c r="J74" s="3"/>
       <c r="K74" s="3"/>
       <c r="L74" s="3"/>
@@ -8152,7 +8169,7 @@
       <c r="AS74" s="3"/>
     </row>
     <row r="75" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A75" s="10">
+      <c r="A75" s="11">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
@@ -8166,10 +8183,10 @@
         <v>22</v>
       </c>
       <c r="E75" s="3"/>
-      <c r="F75" s="13"/>
-      <c r="G75" s="13"/>
-      <c r="H75" s="13"/>
-      <c r="I75" s="14"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="14"/>
+      <c r="H75" s="14"/>
+      <c r="I75" s="15"/>
       <c r="J75" s="3"/>
       <c r="K75" s="3"/>
       <c r="L75" s="3"/>
@@ -8208,7 +8225,7 @@
       <c r="AS75" s="3"/>
     </row>
     <row r="76" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A76" s="10">
+      <c r="A76" s="11">
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
@@ -8222,10 +8239,10 @@
         <v>22</v>
       </c>
       <c r="E76" s="3"/>
-      <c r="F76" s="13"/>
-      <c r="G76" s="13"/>
-      <c r="H76" s="13"/>
-      <c r="I76" s="14"/>
+      <c r="F76" s="14"/>
+      <c r="G76" s="14"/>
+      <c r="H76" s="14"/>
+      <c r="I76" s="15"/>
       <c r="J76" s="3"/>
       <c r="K76" s="3"/>
       <c r="L76" s="3"/>
@@ -8264,7 +8281,7 @@
       <c r="AS76" s="3"/>
     </row>
     <row r="77" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A77" s="10">
+      <c r="A77" s="11">
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
@@ -8278,10 +8295,10 @@
         <v>94</v>
       </c>
       <c r="E77" s="3"/>
-      <c r="F77" s="13"/>
-      <c r="G77" s="13"/>
-      <c r="H77" s="13"/>
-      <c r="I77" s="14"/>
+      <c r="F77" s="14"/>
+      <c r="G77" s="14"/>
+      <c r="H77" s="14"/>
+      <c r="I77" s="15"/>
       <c r="J77" s="3"/>
       <c r="K77" s="3"/>
       <c r="L77" s="3"/>
@@ -8320,7 +8337,7 @@
       <c r="AS77" s="3"/>
     </row>
     <row r="78" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A78" s="10">
+      <c r="A78" s="11">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
@@ -8334,10 +8351,10 @@
         <v>121</v>
       </c>
       <c r="E78" s="3"/>
-      <c r="F78" s="13"/>
-      <c r="G78" s="13"/>
-      <c r="H78" s="13"/>
-      <c r="I78" s="14"/>
+      <c r="F78" s="14"/>
+      <c r="G78" s="14"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="15"/>
       <c r="J78" s="3"/>
       <c r="K78" s="3"/>
       <c r="L78" s="3"/>
@@ -8376,7 +8393,7 @@
       <c r="AS78" s="3"/>
     </row>
     <row r="79" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A79" s="10">
+      <c r="A79" s="11">
         <f t="shared" si="2"/>
         <v>76</v>
       </c>
@@ -8390,10 +8407,10 @@
         <v>163</v>
       </c>
       <c r="E79" s="3"/>
-      <c r="F79" s="13"/>
-      <c r="G79" s="13"/>
-      <c r="H79" s="13"/>
-      <c r="I79" s="14"/>
+      <c r="F79" s="14"/>
+      <c r="G79" s="14"/>
+      <c r="H79" s="14"/>
+      <c r="I79" s="15"/>
       <c r="J79" s="3"/>
       <c r="K79" s="3"/>
       <c r="L79" s="3"/>
@@ -8432,7 +8449,7 @@
       <c r="AS79" s="3"/>
     </row>
     <row r="80" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A80" s="10">
+      <c r="A80" s="11">
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
@@ -8446,10 +8463,10 @@
         <v>26</v>
       </c>
       <c r="E80" s="3"/>
-      <c r="F80" s="13"/>
-      <c r="G80" s="13"/>
-      <c r="H80" s="13"/>
-      <c r="I80" s="14"/>
+      <c r="F80" s="14"/>
+      <c r="G80" s="14"/>
+      <c r="H80" s="14"/>
+      <c r="I80" s="15"/>
       <c r="J80" s="3"/>
       <c r="K80" s="3"/>
       <c r="L80" s="3"/>
@@ -8488,24 +8505,24 @@
       <c r="AS80" s="3"/>
     </row>
     <row r="81" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A81" s="10">
+      <c r="A81" s="11">
         <f t="shared" si="2"/>
         <v>78</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C81" s="19" t="s">
+      <c r="C81" s="20" t="s">
         <v>182</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E81" s="3"/>
-      <c r="F81" s="13"/>
-      <c r="G81" s="13"/>
-      <c r="H81" s="13"/>
-      <c r="I81" s="14"/>
+      <c r="F81" s="14"/>
+      <c r="G81" s="14"/>
+      <c r="H81" s="14"/>
+      <c r="I81" s="15"/>
       <c r="J81" s="3"/>
       <c r="K81" s="3"/>
       <c r="L81" s="3"/>
@@ -8544,7 +8561,7 @@
       <c r="AS81" s="3"/>
     </row>
     <row r="82" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A82" s="10">
+      <c r="A82" s="11">
         <f t="shared" si="2"/>
         <v>79</v>
       </c>
@@ -8558,10 +8575,10 @@
         <v>118</v>
       </c>
       <c r="E82" s="3"/>
-      <c r="F82" s="13"/>
-      <c r="G82" s="13"/>
-      <c r="H82" s="13"/>
-      <c r="I82" s="14"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="14"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="15"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
@@ -8600,7 +8617,7 @@
       <c r="AS82" s="3"/>
     </row>
     <row r="83" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A83" s="10">
+      <c r="A83" s="11">
         <f t="shared" si="2"/>
         <v>80</v>
       </c>
@@ -8614,10 +8631,10 @@
         <v>23</v>
       </c>
       <c r="E83" s="3"/>
-      <c r="F83" s="13"/>
-      <c r="G83" s="13"/>
-      <c r="H83" s="13"/>
-      <c r="I83" s="14"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="14"/>
+      <c r="H83" s="14"/>
+      <c r="I83" s="15"/>
       <c r="J83" s="3"/>
       <c r="K83" s="3"/>
       <c r="L83" s="3"/>
@@ -8656,7 +8673,7 @@
       <c r="AS83" s="3"/>
     </row>
     <row r="84" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A84" s="10">
+      <c r="A84" s="11">
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
@@ -8670,10 +8687,10 @@
         <v>35</v>
       </c>
       <c r="E84" s="3"/>
-      <c r="F84" s="13"/>
-      <c r="G84" s="13"/>
-      <c r="H84" s="13"/>
-      <c r="I84" s="14"/>
+      <c r="F84" s="14"/>
+      <c r="G84" s="14"/>
+      <c r="H84" s="14"/>
+      <c r="I84" s="15"/>
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
       <c r="L84" s="3"/>
@@ -8712,7 +8729,7 @@
       <c r="AS84" s="3"/>
     </row>
     <row r="85" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A85" s="10">
+      <c r="A85" s="11">
         <f t="shared" si="2"/>
         <v>82</v>
       </c>
@@ -8726,10 +8743,10 @@
         <v>191</v>
       </c>
       <c r="E85" s="3"/>
-      <c r="F85" s="13"/>
-      <c r="G85" s="13"/>
-      <c r="H85" s="13"/>
-      <c r="I85" s="14"/>
+      <c r="F85" s="14"/>
+      <c r="G85" s="14"/>
+      <c r="H85" s="14"/>
+      <c r="I85" s="15"/>
       <c r="J85" s="3"/>
       <c r="K85" s="3"/>
       <c r="L85" s="3"/>
@@ -8768,7 +8785,7 @@
       <c r="AS85" s="3"/>
     </row>
     <row r="86" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A86" s="10">
+      <c r="A86" s="11">
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
@@ -8782,10 +8799,10 @@
         <v>194</v>
       </c>
       <c r="E86" s="3"/>
-      <c r="F86" s="13"/>
-      <c r="G86" s="13"/>
-      <c r="H86" s="13"/>
-      <c r="I86" s="14"/>
+      <c r="F86" s="14"/>
+      <c r="G86" s="14"/>
+      <c r="H86" s="14"/>
+      <c r="I86" s="15"/>
       <c r="J86" s="3"/>
       <c r="K86" s="3"/>
       <c r="L86" s="3"/>
@@ -8824,7 +8841,7 @@
       <c r="AS86" s="3"/>
     </row>
     <row r="87" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A87" s="10">
+      <c r="A87" s="11">
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
@@ -8838,10 +8855,10 @@
         <v>121</v>
       </c>
       <c r="E87" s="3"/>
-      <c r="F87" s="13"/>
-      <c r="G87" s="13"/>
-      <c r="H87" s="13"/>
-      <c r="I87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="H87" s="14"/>
+      <c r="I87" s="15"/>
       <c r="J87" s="3"/>
       <c r="K87" s="3"/>
       <c r="L87" s="3"/>
@@ -8880,24 +8897,24 @@
       <c r="AS87" s="3"/>
     </row>
     <row r="88" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A88" s="10">
+      <c r="A88" s="11">
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="C88" s="19" t="s">
+      <c r="C88" s="20" t="s">
         <v>198</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>121</v>
       </c>
       <c r="E88" s="3"/>
-      <c r="F88" s="13"/>
-      <c r="G88" s="13"/>
-      <c r="H88" s="13"/>
-      <c r="I88" s="14"/>
+      <c r="F88" s="14"/>
+      <c r="G88" s="14"/>
+      <c r="H88" s="14"/>
+      <c r="I88" s="15"/>
       <c r="J88" s="3"/>
       <c r="K88" s="3"/>
       <c r="L88" s="3"/>
@@ -8936,24 +8953,24 @@
       <c r="AS88" s="3"/>
     </row>
     <row r="89" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A89" s="10">
+      <c r="A89" s="11">
         <f t="shared" si="2"/>
         <v>86</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="C89" s="19" t="s">
+      <c r="C89" s="20" t="s">
         <v>200</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>201</v>
       </c>
       <c r="E89" s="3"/>
-      <c r="F89" s="13"/>
-      <c r="G89" s="13"/>
-      <c r="H89" s="13"/>
-      <c r="I89" s="14"/>
+      <c r="F89" s="14"/>
+      <c r="G89" s="14"/>
+      <c r="H89" s="14"/>
+      <c r="I89" s="15"/>
       <c r="J89" s="3"/>
       <c r="K89" s="3"/>
       <c r="L89" s="3"/>
@@ -8992,7 +9009,7 @@
       <c r="AS89" s="3"/>
     </row>
     <row r="90" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A90" s="10">
+      <c r="A90" s="11">
         <f t="shared" si="2"/>
         <v>87</v>
       </c>
@@ -9006,9 +9023,9 @@
         <v>201</v>
       </c>
       <c r="E90" s="3"/>
-      <c r="F90" s="13"/>
-      <c r="G90" s="13"/>
-      <c r="H90" s="13"/>
+      <c r="F90" s="14"/>
+      <c r="G90" s="14"/>
+      <c r="H90" s="14"/>
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
@@ -9048,7 +9065,7 @@
       <c r="AS90" s="3"/>
     </row>
     <row r="91" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A91" s="10">
+      <c r="A91" s="11">
         <f t="shared" si="2"/>
         <v>88</v>
       </c>
@@ -9062,9 +9079,9 @@
         <v>206</v>
       </c>
       <c r="E91" s="3"/>
-      <c r="F91" s="13"/>
-      <c r="G91" s="13"/>
-      <c r="H91" s="13"/>
+      <c r="F91" s="14"/>
+      <c r="G91" s="14"/>
+      <c r="H91" s="14"/>
       <c r="I91" s="3"/>
       <c r="J91" s="3"/>
       <c r="K91" s="3"/>
@@ -9104,7 +9121,7 @@
       <c r="AS91" s="3"/>
     </row>
     <row r="92" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A92" s="10">
+      <c r="A92" s="11">
         <f t="shared" si="2"/>
         <v>89</v>
       </c>
@@ -9118,9 +9135,9 @@
         <v>23</v>
       </c>
       <c r="E92" s="3"/>
-      <c r="F92" s="13"/>
-      <c r="G92" s="13"/>
-      <c r="H92" s="13"/>
+      <c r="F92" s="14"/>
+      <c r="G92" s="14"/>
+      <c r="H92" s="14"/>
       <c r="I92" s="3"/>
       <c r="J92" s="3"/>
       <c r="K92" s="3"/>
@@ -9160,7 +9177,7 @@
       <c r="AS92" s="3"/>
     </row>
     <row r="93" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A93" s="10">
+      <c r="A93" s="11">
         <f t="shared" si="2"/>
         <v>90</v>
       </c>
@@ -9174,9 +9191,9 @@
         <v>23</v>
       </c>
       <c r="E93" s="3"/>
-      <c r="F93" s="13"/>
-      <c r="G93" s="13"/>
-      <c r="H93" s="13"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
+      <c r="H93" s="14"/>
       <c r="I93" s="3"/>
       <c r="J93" s="3"/>
       <c r="K93" s="3"/>
@@ -9216,7 +9233,7 @@
       <c r="AS93" s="3"/>
     </row>
     <row r="94" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A94" s="10">
+      <c r="A94" s="11">
         <f t="shared" si="2"/>
         <v>91</v>
       </c>
@@ -9230,9 +9247,9 @@
         <v>22</v>
       </c>
       <c r="E94" s="3"/>
-      <c r="F94" s="13"/>
-      <c r="G94" s="13"/>
-      <c r="H94" s="13"/>
+      <c r="F94" s="14"/>
+      <c r="G94" s="14"/>
+      <c r="H94" s="14"/>
       <c r="I94" s="3"/>
       <c r="J94" s="3"/>
       <c r="K94" s="3"/>
@@ -9272,23 +9289,23 @@
       <c r="AS94" s="3"/>
     </row>
     <row r="95" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A95" s="10">
+      <c r="A95" s="11">
         <f t="shared" si="2"/>
         <v>92</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C95" s="19" t="s">
+      <c r="C95" s="20" t="s">
         <v>214</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>121</v>
       </c>
       <c r="E95" s="3"/>
-      <c r="F95" s="13"/>
-      <c r="G95" s="13"/>
-      <c r="H95" s="13"/>
+      <c r="F95" s="14"/>
+      <c r="G95" s="14"/>
+      <c r="H95" s="14"/>
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
@@ -9328,7 +9345,7 @@
       <c r="AS95" s="3"/>
     </row>
     <row r="96" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A96" s="10">
+      <c r="A96" s="11">
         <f t="shared" si="2"/>
         <v>93</v>
       </c>
@@ -9342,9 +9359,9 @@
         <v>26</v>
       </c>
       <c r="E96" s="3"/>
-      <c r="F96" s="13"/>
-      <c r="G96" s="13"/>
-      <c r="H96" s="13"/>
+      <c r="F96" s="14"/>
+      <c r="G96" s="14"/>
+      <c r="H96" s="14"/>
       <c r="I96" s="3"/>
       <c r="J96" s="3"/>
       <c r="K96" s="3"/>
@@ -9384,7 +9401,7 @@
       <c r="AS96" s="3"/>
     </row>
     <row r="97" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A97" s="10">
+      <c r="A97" s="11">
         <f t="shared" si="2"/>
         <v>94</v>
       </c>
@@ -9398,9 +9415,9 @@
         <v>26</v>
       </c>
       <c r="E97" s="3"/>
-      <c r="F97" s="13"/>
-      <c r="G97" s="13"/>
-      <c r="H97" s="13"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="H97" s="14"/>
       <c r="I97" s="3"/>
       <c r="J97" s="3"/>
       <c r="K97" s="3"/>
@@ -9440,7 +9457,7 @@
       <c r="AS97" s="3"/>
     </row>
     <row r="98" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A98" s="10">
+      <c r="A98" s="11">
         <f t="shared" si="2"/>
         <v>95</v>
       </c>
@@ -9454,9 +9471,9 @@
         <v>160</v>
       </c>
       <c r="E98" s="3"/>
-      <c r="F98" s="13"/>
-      <c r="G98" s="13"/>
-      <c r="H98" s="13"/>
+      <c r="F98" s="14"/>
+      <c r="G98" s="14"/>
+      <c r="H98" s="14"/>
       <c r="I98" s="3"/>
       <c r="J98" s="3"/>
       <c r="K98" s="3"/>
@@ -9496,7 +9513,7 @@
       <c r="AS98" s="3"/>
     </row>
     <row r="99" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A99" s="10">
+      <c r="A99" s="11">
         <f t="shared" si="2"/>
         <v>96</v>
       </c>
@@ -9510,9 +9527,9 @@
         <v>24</v>
       </c>
       <c r="E99" s="3"/>
-      <c r="F99" s="13"/>
-      <c r="G99" s="13"/>
-      <c r="H99" s="13"/>
+      <c r="F99" s="14"/>
+      <c r="G99" s="14"/>
+      <c r="H99" s="14"/>
       <c r="I99" s="3"/>
       <c r="J99" s="3"/>
       <c r="K99" s="3"/>
@@ -9552,7 +9569,7 @@
       <c r="AS99" s="3"/>
     </row>
     <row r="100" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A100" s="10">
+      <c r="A100" s="11">
         <f t="shared" si="2"/>
         <v>97</v>
       </c>
@@ -9566,9 +9583,9 @@
         <v>26</v>
       </c>
       <c r="E100" s="3"/>
-      <c r="F100" s="13"/>
-      <c r="G100" s="13"/>
-      <c r="H100" s="13"/>
+      <c r="F100" s="14"/>
+      <c r="G100" s="14"/>
+      <c r="H100" s="14"/>
       <c r="I100" s="3"/>
       <c r="J100" s="3"/>
       <c r="K100" s="3"/>
@@ -9608,7 +9625,7 @@
       <c r="AS100" s="3"/>
     </row>
     <row r="101" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A101" s="10">
+      <c r="A101" s="11">
         <f t="shared" si="2"/>
         <v>98</v>
       </c>
@@ -9622,9 +9639,9 @@
         <v>24</v>
       </c>
       <c r="E101" s="3"/>
-      <c r="F101" s="13"/>
-      <c r="G101" s="13"/>
-      <c r="H101" s="13"/>
+      <c r="F101" s="14"/>
+      <c r="G101" s="14"/>
+      <c r="H101" s="14"/>
       <c r="I101" s="3"/>
       <c r="J101" s="3"/>
       <c r="K101" s="3"/>
@@ -9664,7 +9681,7 @@
       <c r="AS101" s="3"/>
     </row>
     <row r="102" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A102" s="10">
+      <c r="A102" s="11">
         <f t="shared" si="2"/>
         <v>99</v>
       </c>
@@ -9678,9 +9695,9 @@
         <v>94</v>
       </c>
       <c r="E102" s="3"/>
-      <c r="F102" s="13"/>
-      <c r="G102" s="13"/>
-      <c r="H102" s="13"/>
+      <c r="F102" s="14"/>
+      <c r="G102" s="14"/>
+      <c r="H102" s="14"/>
       <c r="I102" s="3"/>
       <c r="J102" s="3"/>
       <c r="K102" s="3"/>
@@ -9720,7 +9737,7 @@
       <c r="AS102" s="3"/>
     </row>
     <row r="103" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A103" s="10">
+      <c r="A103" s="11">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
@@ -9734,9 +9751,9 @@
         <v>22</v>
       </c>
       <c r="E103" s="3"/>
-      <c r="F103" s="13"/>
-      <c r="G103" s="13"/>
-      <c r="H103" s="13"/>
+      <c r="F103" s="14"/>
+      <c r="G103" s="14"/>
+      <c r="H103" s="14"/>
       <c r="I103" s="3"/>
       <c r="J103" s="3"/>
       <c r="K103" s="3"/>
@@ -9776,11 +9793,11 @@
       <c r="AS103" s="3"/>
     </row>
     <row r="104" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A104" s="10">
+      <c r="A104" s="11">
         <f t="shared" si="2"/>
         <v>101</v>
       </c>
-      <c r="B104" s="11" t="s">
+      <c r="B104" s="12" t="s">
         <v>237</v>
       </c>
       <c r="C104" s="3" t="s">
@@ -9793,19 +9810,19 @@
         <f>+[26]Main!$I$2</f>
         <v>33.76</v>
       </c>
-      <c r="F104" s="13">
+      <c r="F104" s="14">
         <f>+[26]Main!$I$4</f>
         <v>1615.1327198399999</v>
       </c>
-      <c r="G104" s="13">
+      <c r="G104" s="14">
         <f>+[26]Main!$I$6-[26]Main!$I$5</f>
         <v>553.85699999999997</v>
       </c>
-      <c r="H104" s="13">
+      <c r="H104" s="14">
         <f>+F104+G104</f>
         <v>2168.9897198399999</v>
       </c>
-      <c r="I104" s="14" t="s">
+      <c r="I104" s="15" t="s">
         <v>240</v>
       </c>
       <c r="J104" s="3"/>
@@ -9846,7 +9863,7 @@
       <c r="AS104" s="3"/>
     </row>
     <row r="105" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A105" s="10">
+      <c r="A105" s="11">
         <f t="shared" si="2"/>
         <v>102</v>
       </c>
@@ -9860,9 +9877,9 @@
         <v>206</v>
       </c>
       <c r="E105" s="3"/>
-      <c r="F105" s="13"/>
-      <c r="G105" s="13"/>
-      <c r="H105" s="13"/>
+      <c r="F105" s="14"/>
+      <c r="G105" s="14"/>
+      <c r="H105" s="14"/>
       <c r="I105" s="3"/>
       <c r="J105" s="3"/>
       <c r="K105" s="3"/>
@@ -9902,7 +9919,7 @@
       <c r="AS105" s="3"/>
     </row>
     <row r="106" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A106" s="10">
+      <c r="A106" s="11">
         <f t="shared" si="2"/>
         <v>103</v>
       </c>
@@ -9916,9 +9933,9 @@
         <v>85</v>
       </c>
       <c r="E106" s="3"/>
-      <c r="F106" s="13"/>
-      <c r="G106" s="13"/>
-      <c r="H106" s="13"/>
+      <c r="F106" s="14"/>
+      <c r="G106" s="14"/>
+      <c r="H106" s="14"/>
       <c r="I106" s="3"/>
       <c r="J106" s="3"/>
       <c r="K106" s="3"/>
@@ -9958,11 +9975,11 @@
       <c r="AS106" s="3"/>
     </row>
     <row r="107" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A107" s="10">
+      <c r="A107" s="11">
         <f t="shared" si="2"/>
         <v>104</v>
       </c>
-      <c r="B107" s="11" t="s">
+      <c r="B107" s="12" t="s">
         <v>247</v>
       </c>
       <c r="C107" s="3" t="s">
@@ -9975,19 +9992,19 @@
         <f>+[27]Main!$H$2</f>
         <v>15.92</v>
       </c>
-      <c r="F107" s="13">
+      <c r="F107" s="14">
         <f>+[27]Main!$H$5*FX!C4</f>
         <v>2707.3869572160002</v>
       </c>
-      <c r="G107" s="13">
+      <c r="G107" s="14">
         <f>+([27]Main!$H$7-[27]Main!$H$6)*FX!C4</f>
         <v>699.94651999999996</v>
       </c>
-      <c r="H107" s="13">
+      <c r="H107" s="14">
         <f>+F107+G107</f>
         <v>3407.3334772160001</v>
       </c>
-      <c r="I107" s="14" t="s">
+      <c r="I107" s="15" t="s">
         <v>261</v>
       </c>
       <c r="J107" s="3"/>
@@ -10030,7 +10047,7 @@
       <c r="AS107" s="3"/>
     </row>
     <row r="108" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A108" s="10">
+      <c r="A108" s="11">
         <f t="shared" si="2"/>
         <v>105</v>
       </c>
@@ -10044,9 +10061,9 @@
         <v>160</v>
       </c>
       <c r="E108" s="3"/>
-      <c r="F108" s="13"/>
-      <c r="G108" s="13"/>
-      <c r="H108" s="13"/>
+      <c r="F108" s="14"/>
+      <c r="G108" s="14"/>
+      <c r="H108" s="14"/>
       <c r="I108" s="3"/>
       <c r="J108" s="3"/>
       <c r="K108" s="3"/>
@@ -10086,11 +10103,11 @@
       <c r="AS108" s="3"/>
     </row>
     <row r="109" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A109" s="10">
+      <c r="A109" s="11">
         <f t="shared" si="2"/>
         <v>106</v>
       </c>
-      <c r="B109" s="11" t="s">
+      <c r="B109" s="12" t="s">
         <v>251</v>
       </c>
       <c r="C109" s="3" t="s">
@@ -10103,19 +10120,19 @@
         <f>+[28]Main!$I$2</f>
         <v>3.28</v>
       </c>
-      <c r="F109" s="13">
+      <c r="F109" s="14">
         <f>+[28]Main!$I$4*FX!C3</f>
         <v>372.96258964800001</v>
       </c>
-      <c r="G109" s="13">
+      <c r="G109" s="14">
         <f>+([28]Main!$I$6-[28]Main!$I$5)*FX!C3</f>
         <v>50.842859999999995</v>
       </c>
-      <c r="H109" s="13">
+      <c r="H109" s="14">
         <f>+F109+G109</f>
         <v>423.80544964799998</v>
       </c>
-      <c r="I109" s="14" t="s">
+      <c r="I109" s="15" t="s">
         <v>241</v>
       </c>
       <c r="J109" s="3"/>
@@ -10158,7 +10175,7 @@
       <c r="AS109" s="3"/>
     </row>
     <row r="110" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A110" s="10">
+      <c r="A110" s="11">
         <f t="shared" si="2"/>
         <v>107</v>
       </c>
@@ -10172,9 +10189,9 @@
         <v>94</v>
       </c>
       <c r="E110" s="3"/>
-      <c r="F110" s="20"/>
-      <c r="G110" s="20"/>
-      <c r="H110" s="20"/>
+      <c r="F110" s="21"/>
+      <c r="G110" s="21"/>
+      <c r="H110" s="21"/>
       <c r="I110" s="3"/>
       <c r="J110" s="3"/>
       <c r="K110" s="3"/>
@@ -10214,7 +10231,7 @@
       <c r="AS110" s="3"/>
     </row>
     <row r="111" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A111" s="10">
+      <c r="A111" s="11">
         <f t="shared" si="2"/>
         <v>108</v>
       </c>
@@ -10228,9 +10245,9 @@
         <v>153</v>
       </c>
       <c r="E111" s="3"/>
-      <c r="F111" s="20"/>
-      <c r="G111" s="20"/>
-      <c r="H111" s="20"/>
+      <c r="F111" s="21"/>
+      <c r="G111" s="21"/>
+      <c r="H111" s="21"/>
       <c r="I111" s="3"/>
       <c r="J111" s="3"/>
       <c r="K111" s="3"/>
@@ -10270,7 +10287,7 @@
       <c r="AS111" s="3"/>
     </row>
     <row r="112" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A112" s="10">
+      <c r="A112" s="11">
         <f t="shared" si="2"/>
         <v>109</v>
       </c>
@@ -10284,9 +10301,9 @@
         <v>259</v>
       </c>
       <c r="E112" s="3"/>
-      <c r="F112" s="20"/>
-      <c r="G112" s="20"/>
-      <c r="H112" s="20"/>
+      <c r="F112" s="21"/>
+      <c r="G112" s="21"/>
+      <c r="H112" s="21"/>
       <c r="I112" s="3"/>
       <c r="J112" s="3"/>
       <c r="K112" s="3"/>
@@ -10326,14 +10343,14 @@
       <c r="AS112" s="3"/>
     </row>
     <row r="113" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A113" s="10"/>
+      <c r="A113" s="11"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
-      <c r="F113" s="20"/>
-      <c r="G113" s="20"/>
-      <c r="H113" s="20"/>
+      <c r="F113" s="21"/>
+      <c r="G113" s="21"/>
+      <c r="H113" s="21"/>
       <c r="I113" s="3"/>
       <c r="J113" s="3"/>
       <c r="K113" s="3"/>
@@ -10373,14 +10390,14 @@
       <c r="AS113" s="3"/>
     </row>
     <row r="114" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A114" s="10"/>
+      <c r="A114" s="11"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
-      <c r="F114" s="20"/>
-      <c r="G114" s="20"/>
-      <c r="H114" s="20"/>
+      <c r="F114" s="21"/>
+      <c r="G114" s="21"/>
+      <c r="H114" s="21"/>
       <c r="I114" s="3"/>
       <c r="J114" s="3"/>
       <c r="K114" s="3"/>
@@ -10420,16 +10437,16 @@
       <c r="AS114" s="3"/>
     </row>
     <row r="115" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A115" s="10"/>
-      <c r="B115" s="21" t="s">
+      <c r="A115" s="11"/>
+      <c r="B115" s="22" t="s">
         <v>477</v>
       </c>
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
-      <c r="F115" s="20"/>
-      <c r="G115" s="20"/>
-      <c r="H115" s="20"/>
+      <c r="F115" s="21"/>
+      <c r="G115" s="21"/>
+      <c r="H115" s="21"/>
       <c r="I115" s="3"/>
       <c r="J115" s="3"/>
       <c r="K115" s="3"/>
@@ -10469,16 +10486,16 @@
       <c r="AS115" s="3"/>
     </row>
     <row r="116" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A116" s="10"/>
+      <c r="A116" s="11"/>
       <c r="B116" s="3" t="s">
         <v>478</v>
       </c>
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
-      <c r="F116" s="20"/>
-      <c r="G116" s="20"/>
-      <c r="H116" s="20"/>
+      <c r="F116" s="21"/>
+      <c r="G116" s="21"/>
+      <c r="H116" s="21"/>
       <c r="I116" s="3"/>
       <c r="J116" s="3"/>
       <c r="K116" s="3"/>
@@ -10518,14 +10535,14 @@
       <c r="AS116" s="3"/>
     </row>
     <row r="117" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A117" s="10"/>
+      <c r="A117" s="11"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
-      <c r="F117" s="20"/>
-      <c r="G117" s="20"/>
-      <c r="H117" s="20"/>
+      <c r="F117" s="21"/>
+      <c r="G117" s="21"/>
+      <c r="H117" s="21"/>
       <c r="I117" s="3"/>
       <c r="J117" s="3"/>
       <c r="K117" s="3"/>
@@ -10565,14 +10582,14 @@
       <c r="AS117" s="3"/>
     </row>
     <row r="118" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A118" s="10"/>
+      <c r="A118" s="11"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
-      <c r="F118" s="20"/>
-      <c r="G118" s="20"/>
-      <c r="H118" s="20"/>
+      <c r="F118" s="21"/>
+      <c r="G118" s="21"/>
+      <c r="H118" s="21"/>
       <c r="I118" s="3"/>
       <c r="J118" s="3"/>
       <c r="K118" s="3"/>
@@ -10612,14 +10629,14 @@
       <c r="AS118" s="3"/>
     </row>
     <row r="119" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A119" s="10"/>
+      <c r="A119" s="11"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
-      <c r="F119" s="20"/>
-      <c r="G119" s="20"/>
-      <c r="H119" s="20"/>
+      <c r="F119" s="21"/>
+      <c r="G119" s="21"/>
+      <c r="H119" s="21"/>
       <c r="I119" s="3"/>
       <c r="J119" s="3"/>
       <c r="K119" s="3"/>
@@ -10659,14 +10676,14 @@
       <c r="AS119" s="3"/>
     </row>
     <row r="120" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A120" s="10"/>
+      <c r="A120" s="11"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
-      <c r="F120" s="20"/>
-      <c r="G120" s="20"/>
-      <c r="H120" s="20"/>
+      <c r="F120" s="21"/>
+      <c r="G120" s="21"/>
+      <c r="H120" s="21"/>
       <c r="I120" s="3"/>
       <c r="J120" s="3"/>
       <c r="K120" s="3"/>
@@ -10706,14 +10723,14 @@
       <c r="AS120" s="3"/>
     </row>
     <row r="121" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A121" s="10"/>
+      <c r="A121" s="11"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
-      <c r="F121" s="20"/>
-      <c r="G121" s="20"/>
-      <c r="H121" s="20"/>
+      <c r="F121" s="21"/>
+      <c r="G121" s="21"/>
+      <c r="H121" s="21"/>
       <c r="I121" s="3"/>
       <c r="J121" s="3"/>
       <c r="K121" s="3"/>
@@ -10753,14 +10770,14 @@
       <c r="AS121" s="3"/>
     </row>
     <row r="122" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A122" s="10"/>
+      <c r="A122" s="11"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
-      <c r="F122" s="20"/>
-      <c r="G122" s="20"/>
-      <c r="H122" s="20"/>
+      <c r="F122" s="21"/>
+      <c r="G122" s="21"/>
+      <c r="H122" s="21"/>
       <c r="I122" s="3"/>
       <c r="J122" s="3"/>
       <c r="K122" s="3"/>
@@ -10800,14 +10817,14 @@
       <c r="AS122" s="3"/>
     </row>
     <row r="123" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A123" s="10"/>
+      <c r="A123" s="11"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
-      <c r="F123" s="20"/>
-      <c r="G123" s="20"/>
-      <c r="H123" s="20"/>
+      <c r="F123" s="21"/>
+      <c r="G123" s="21"/>
+      <c r="H123" s="21"/>
       <c r="I123" s="3"/>
       <c r="J123" s="3"/>
       <c r="K123" s="3"/>
@@ -10847,14 +10864,14 @@
       <c r="AS123" s="3"/>
     </row>
     <row r="124" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A124" s="10"/>
+      <c r="A124" s="11"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
-      <c r="F124" s="20"/>
-      <c r="G124" s="20"/>
-      <c r="H124" s="20"/>
+      <c r="F124" s="21"/>
+      <c r="G124" s="21"/>
+      <c r="H124" s="21"/>
       <c r="I124" s="3"/>
       <c r="J124" s="3"/>
       <c r="K124" s="3"/>
@@ -10894,14 +10911,14 @@
       <c r="AS124" s="3"/>
     </row>
     <row r="125" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A125" s="10"/>
+      <c r="A125" s="11"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
-      <c r="F125" s="20"/>
-      <c r="G125" s="20"/>
-      <c r="H125" s="20"/>
+      <c r="F125" s="21"/>
+      <c r="G125" s="21"/>
+      <c r="H125" s="21"/>
       <c r="I125" s="3"/>
       <c r="J125" s="3"/>
       <c r="K125" s="3"/>
@@ -10941,14 +10958,14 @@
       <c r="AS125" s="3"/>
     </row>
     <row r="126" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A126" s="10"/>
+      <c r="A126" s="11"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
-      <c r="F126" s="20"/>
-      <c r="G126" s="20"/>
-      <c r="H126" s="20"/>
+      <c r="F126" s="21"/>
+      <c r="G126" s="21"/>
+      <c r="H126" s="21"/>
       <c r="I126" s="3"/>
       <c r="J126" s="3"/>
       <c r="K126" s="3"/>
@@ -10988,14 +11005,14 @@
       <c r="AS126" s="3"/>
     </row>
     <row r="127" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A127" s="10"/>
+      <c r="A127" s="11"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
-      <c r="F127" s="20"/>
-      <c r="G127" s="20"/>
-      <c r="H127" s="20"/>
+      <c r="F127" s="21"/>
+      <c r="G127" s="21"/>
+      <c r="H127" s="21"/>
       <c r="I127" s="3"/>
       <c r="J127" s="3"/>
       <c r="K127" s="3"/>
@@ -11035,14 +11052,14 @@
       <c r="AS127" s="3"/>
     </row>
     <row r="128" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A128" s="10"/>
+      <c r="A128" s="11"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
-      <c r="F128" s="20"/>
-      <c r="G128" s="20"/>
-      <c r="H128" s="20"/>
+      <c r="F128" s="21"/>
+      <c r="G128" s="21"/>
+      <c r="H128" s="21"/>
       <c r="I128" s="3"/>
       <c r="J128" s="3"/>
       <c r="K128" s="3"/>
@@ -11082,14 +11099,14 @@
       <c r="AS128" s="3"/>
     </row>
     <row r="129" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A129" s="10"/>
+      <c r="A129" s="11"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
-      <c r="F129" s="20"/>
-      <c r="G129" s="20"/>
-      <c r="H129" s="20"/>
+      <c r="F129" s="21"/>
+      <c r="G129" s="21"/>
+      <c r="H129" s="21"/>
       <c r="I129" s="3"/>
       <c r="J129" s="3"/>
       <c r="K129" s="3"/>
@@ -11129,14 +11146,14 @@
       <c r="AS129" s="3"/>
     </row>
     <row r="130" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A130" s="10"/>
+      <c r="A130" s="11"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
-      <c r="F130" s="20"/>
-      <c r="G130" s="20"/>
-      <c r="H130" s="20"/>
+      <c r="F130" s="21"/>
+      <c r="G130" s="21"/>
+      <c r="H130" s="21"/>
       <c r="I130" s="3"/>
       <c r="J130" s="3"/>
       <c r="K130" s="3"/>
@@ -11176,14 +11193,14 @@
       <c r="AS130" s="3"/>
     </row>
     <row r="131" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A131" s="10"/>
+      <c r="A131" s="11"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
-      <c r="F131" s="20"/>
-      <c r="G131" s="20"/>
-      <c r="H131" s="20"/>
+      <c r="F131" s="21"/>
+      <c r="G131" s="21"/>
+      <c r="H131" s="21"/>
       <c r="I131" s="3"/>
       <c r="J131" s="3"/>
       <c r="K131" s="3"/>
@@ -11223,14 +11240,14 @@
       <c r="AS131" s="3"/>
     </row>
     <row r="132" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A132" s="10"/>
+      <c r="A132" s="11"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
-      <c r="F132" s="20"/>
-      <c r="G132" s="20"/>
-      <c r="H132" s="20"/>
+      <c r="F132" s="21"/>
+      <c r="G132" s="21"/>
+      <c r="H132" s="21"/>
       <c r="I132" s="3"/>
       <c r="J132" s="3"/>
       <c r="K132" s="3"/>
@@ -11270,14 +11287,14 @@
       <c r="AS132" s="3"/>
     </row>
     <row r="133" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A133" s="10"/>
+      <c r="A133" s="11"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
-      <c r="F133" s="20"/>
-      <c r="G133" s="20"/>
-      <c r="H133" s="20"/>
+      <c r="F133" s="21"/>
+      <c r="G133" s="21"/>
+      <c r="H133" s="21"/>
       <c r="I133" s="3"/>
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
@@ -11317,14 +11334,14 @@
       <c r="AS133" s="3"/>
     </row>
     <row r="134" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A134" s="10"/>
+      <c r="A134" s="11"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
-      <c r="F134" s="20"/>
-      <c r="G134" s="20"/>
-      <c r="H134" s="20"/>
+      <c r="F134" s="21"/>
+      <c r="G134" s="21"/>
+      <c r="H134" s="21"/>
       <c r="I134" s="3"/>
       <c r="J134" s="3"/>
       <c r="K134" s="3"/>
@@ -11364,14 +11381,14 @@
       <c r="AS134" s="3"/>
     </row>
     <row r="135" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A135" s="10"/>
+      <c r="A135" s="11"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
-      <c r="F135" s="20"/>
-      <c r="G135" s="20"/>
-      <c r="H135" s="20"/>
+      <c r="F135" s="21"/>
+      <c r="G135" s="21"/>
+      <c r="H135" s="21"/>
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
@@ -11411,14 +11428,14 @@
       <c r="AS135" s="3"/>
     </row>
     <row r="136" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A136" s="10"/>
+      <c r="A136" s="11"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
-      <c r="F136" s="20"/>
-      <c r="G136" s="20"/>
-      <c r="H136" s="20"/>
+      <c r="F136" s="21"/>
+      <c r="G136" s="21"/>
+      <c r="H136" s="21"/>
       <c r="I136" s="3"/>
       <c r="J136" s="3"/>
       <c r="K136" s="3"/>
@@ -11458,14 +11475,14 @@
       <c r="AS136" s="3"/>
     </row>
     <row r="137" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A137" s="10"/>
+      <c r="A137" s="11"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
-      <c r="F137" s="20"/>
-      <c r="G137" s="20"/>
-      <c r="H137" s="20"/>
+      <c r="F137" s="21"/>
+      <c r="G137" s="21"/>
+      <c r="H137" s="21"/>
       <c r="I137" s="3"/>
       <c r="J137" s="3"/>
       <c r="K137" s="3"/>
@@ -11505,14 +11522,14 @@
       <c r="AS137" s="3"/>
     </row>
     <row r="138" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A138" s="10"/>
+      <c r="A138" s="11"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
-      <c r="F138" s="20"/>
-      <c r="G138" s="20"/>
-      <c r="H138" s="20"/>
+      <c r="F138" s="21"/>
+      <c r="G138" s="21"/>
+      <c r="H138" s="21"/>
       <c r="I138" s="3"/>
       <c r="J138" s="3"/>
       <c r="K138" s="3"/>
@@ -11552,14 +11569,14 @@
       <c r="AS138" s="3"/>
     </row>
     <row r="139" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A139" s="10"/>
+      <c r="A139" s="11"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
-      <c r="F139" s="20"/>
-      <c r="G139" s="20"/>
-      <c r="H139" s="20"/>
+      <c r="F139" s="21"/>
+      <c r="G139" s="21"/>
+      <c r="H139" s="21"/>
       <c r="I139" s="3"/>
       <c r="J139" s="3"/>
       <c r="K139" s="3"/>
@@ -11599,14 +11616,14 @@
       <c r="AS139" s="3"/>
     </row>
     <row r="140" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A140" s="10"/>
+      <c r="A140" s="11"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
-      <c r="F140" s="20"/>
-      <c r="G140" s="20"/>
-      <c r="H140" s="20"/>
+      <c r="F140" s="21"/>
+      <c r="G140" s="21"/>
+      <c r="H140" s="21"/>
       <c r="I140" s="3"/>
       <c r="J140" s="3"/>
       <c r="K140" s="3"/>
@@ -11646,14 +11663,14 @@
       <c r="AS140" s="3"/>
     </row>
     <row r="141" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A141" s="10"/>
+      <c r="A141" s="11"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
-      <c r="F141" s="20"/>
-      <c r="G141" s="20"/>
-      <c r="H141" s="20"/>
+      <c r="F141" s="21"/>
+      <c r="G141" s="21"/>
+      <c r="H141" s="21"/>
       <c r="I141" s="3"/>
       <c r="J141" s="3"/>
       <c r="K141" s="3"/>
@@ -11693,14 +11710,14 @@
       <c r="AS141" s="3"/>
     </row>
     <row r="142" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A142" s="10"/>
+      <c r="A142" s="11"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
-      <c r="F142" s="20"/>
-      <c r="G142" s="20"/>
-      <c r="H142" s="20"/>
+      <c r="F142" s="21"/>
+      <c r="G142" s="21"/>
+      <c r="H142" s="21"/>
       <c r="I142" s="3"/>
       <c r="J142" s="3"/>
       <c r="K142" s="3"/>
@@ -11740,14 +11757,14 @@
       <c r="AS142" s="3"/>
     </row>
     <row r="143" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A143" s="10"/>
+      <c r="A143" s="11"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
-      <c r="F143" s="20"/>
-      <c r="G143" s="20"/>
-      <c r="H143" s="20"/>
+      <c r="F143" s="21"/>
+      <c r="G143" s="21"/>
+      <c r="H143" s="21"/>
       <c r="I143" s="3"/>
       <c r="J143" s="3"/>
       <c r="K143" s="3"/>
@@ -11787,14 +11804,14 @@
       <c r="AS143" s="3"/>
     </row>
     <row r="144" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A144" s="10"/>
+      <c r="A144" s="11"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
-      <c r="F144" s="20"/>
-      <c r="G144" s="20"/>
-      <c r="H144" s="20"/>
+      <c r="F144" s="21"/>
+      <c r="G144" s="21"/>
+      <c r="H144" s="21"/>
       <c r="I144" s="3"/>
       <c r="J144" s="3"/>
       <c r="K144" s="3"/>
@@ -11834,14 +11851,14 @@
       <c r="AS144" s="3"/>
     </row>
     <row r="145" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A145" s="10"/>
+      <c r="A145" s="11"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
-      <c r="F145" s="20"/>
-      <c r="G145" s="20"/>
-      <c r="H145" s="20"/>
+      <c r="F145" s="21"/>
+      <c r="G145" s="21"/>
+      <c r="H145" s="21"/>
       <c r="I145" s="3"/>
       <c r="J145" s="3"/>
       <c r="K145" s="3"/>
@@ -11881,14 +11898,14 @@
       <c r="AS145" s="3"/>
     </row>
     <row r="146" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A146" s="10"/>
+      <c r="A146" s="11"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
-      <c r="F146" s="20"/>
-      <c r="G146" s="20"/>
-      <c r="H146" s="20"/>
+      <c r="F146" s="21"/>
+      <c r="G146" s="21"/>
+      <c r="H146" s="21"/>
       <c r="I146" s="3"/>
       <c r="J146" s="3"/>
       <c r="K146" s="3"/>
@@ -11928,14 +11945,14 @@
       <c r="AS146" s="3"/>
     </row>
     <row r="147" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A147" s="10"/>
+      <c r="A147" s="11"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
-      <c r="F147" s="20"/>
-      <c r="G147" s="20"/>
-      <c r="H147" s="20"/>
+      <c r="F147" s="21"/>
+      <c r="G147" s="21"/>
+      <c r="H147" s="21"/>
       <c r="I147" s="3"/>
       <c r="J147" s="3"/>
       <c r="K147" s="3"/>
@@ -11975,14 +11992,14 @@
       <c r="AS147" s="3"/>
     </row>
     <row r="148" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A148" s="10"/>
+      <c r="A148" s="11"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
-      <c r="F148" s="20"/>
-      <c r="G148" s="20"/>
-      <c r="H148" s="20"/>
+      <c r="F148" s="21"/>
+      <c r="G148" s="21"/>
+      <c r="H148" s="21"/>
       <c r="I148" s="3"/>
       <c r="J148" s="3"/>
       <c r="K148" s="3"/>
@@ -12022,14 +12039,14 @@
       <c r="AS148" s="3"/>
     </row>
     <row r="149" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A149" s="10"/>
+      <c r="A149" s="11"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
-      <c r="F149" s="20"/>
-      <c r="G149" s="20"/>
-      <c r="H149" s="20"/>
+      <c r="F149" s="21"/>
+      <c r="G149" s="21"/>
+      <c r="H149" s="21"/>
       <c r="I149" s="3"/>
       <c r="J149" s="3"/>
       <c r="K149" s="3"/>
@@ -12069,14 +12086,14 @@
       <c r="AS149" s="3"/>
     </row>
     <row r="150" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A150" s="10"/>
+      <c r="A150" s="11"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
-      <c r="F150" s="20"/>
-      <c r="G150" s="20"/>
-      <c r="H150" s="20"/>
+      <c r="F150" s="21"/>
+      <c r="G150" s="21"/>
+      <c r="H150" s="21"/>
       <c r="I150" s="3"/>
       <c r="J150" s="3"/>
       <c r="K150" s="3"/>
@@ -12116,14 +12133,14 @@
       <c r="AS150" s="3"/>
     </row>
     <row r="151" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A151" s="10"/>
+      <c r="A151" s="11"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
-      <c r="F151" s="20"/>
-      <c r="G151" s="20"/>
-      <c r="H151" s="20"/>
+      <c r="F151" s="21"/>
+      <c r="G151" s="21"/>
+      <c r="H151" s="21"/>
       <c r="I151" s="3"/>
       <c r="J151" s="3"/>
       <c r="K151" s="3"/>
@@ -12163,14 +12180,14 @@
       <c r="AS151" s="3"/>
     </row>
     <row r="152" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A152" s="10"/>
+      <c r="A152" s="11"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
-      <c r="F152" s="20"/>
-      <c r="G152" s="20"/>
-      <c r="H152" s="20"/>
+      <c r="F152" s="21"/>
+      <c r="G152" s="21"/>
+      <c r="H152" s="21"/>
       <c r="I152" s="3"/>
       <c r="J152" s="3"/>
       <c r="K152" s="3"/>
@@ -12210,14 +12227,14 @@
       <c r="AS152" s="3"/>
     </row>
     <row r="153" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A153" s="10"/>
+      <c r="A153" s="11"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
-      <c r="F153" s="20"/>
-      <c r="G153" s="20"/>
-      <c r="H153" s="20"/>
+      <c r="F153" s="21"/>
+      <c r="G153" s="21"/>
+      <c r="H153" s="21"/>
       <c r="I153" s="3"/>
       <c r="J153" s="3"/>
       <c r="K153" s="3"/>
@@ -12257,14 +12274,14 @@
       <c r="AS153" s="3"/>
     </row>
     <row r="154" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A154" s="10"/>
+      <c r="A154" s="11"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
-      <c r="F154" s="20"/>
-      <c r="G154" s="20"/>
-      <c r="H154" s="20"/>
+      <c r="F154" s="21"/>
+      <c r="G154" s="21"/>
+      <c r="H154" s="21"/>
       <c r="I154" s="3"/>
       <c r="J154" s="3"/>
       <c r="K154" s="3"/>
@@ -12304,14 +12321,14 @@
       <c r="AS154" s="3"/>
     </row>
     <row r="155" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A155" s="10"/>
+      <c r="A155" s="11"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
-      <c r="F155" s="20"/>
-      <c r="G155" s="20"/>
-      <c r="H155" s="20"/>
+      <c r="F155" s="21"/>
+      <c r="G155" s="21"/>
+      <c r="H155" s="21"/>
       <c r="I155" s="3"/>
       <c r="J155" s="3"/>
       <c r="K155" s="3"/>
@@ -12351,14 +12368,14 @@
       <c r="AS155" s="3"/>
     </row>
     <row r="156" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A156" s="10"/>
+      <c r="A156" s="11"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
-      <c r="F156" s="20"/>
-      <c r="G156" s="20"/>
-      <c r="H156" s="20"/>
+      <c r="F156" s="21"/>
+      <c r="G156" s="21"/>
+      <c r="H156" s="21"/>
       <c r="I156" s="3"/>
       <c r="J156" s="3"/>
       <c r="K156" s="3"/>
@@ -12398,14 +12415,14 @@
       <c r="AS156" s="3"/>
     </row>
     <row r="157" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A157" s="10"/>
+      <c r="A157" s="11"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
-      <c r="F157" s="20"/>
-      <c r="G157" s="20"/>
-      <c r="H157" s="20"/>
+      <c r="F157" s="21"/>
+      <c r="G157" s="21"/>
+      <c r="H157" s="21"/>
       <c r="I157" s="3"/>
       <c r="J157" s="3"/>
       <c r="K157" s="3"/>
@@ -12445,14 +12462,14 @@
       <c r="AS157" s="3"/>
     </row>
     <row r="158" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A158" s="10"/>
+      <c r="A158" s="11"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
-      <c r="F158" s="20"/>
-      <c r="G158" s="20"/>
-      <c r="H158" s="20"/>
+      <c r="F158" s="21"/>
+      <c r="G158" s="21"/>
+      <c r="H158" s="21"/>
       <c r="I158" s="3"/>
       <c r="J158" s="3"/>
       <c r="K158" s="3"/>
@@ -12492,14 +12509,14 @@
       <c r="AS158" s="3"/>
     </row>
     <row r="159" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A159" s="10"/>
+      <c r="A159" s="11"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
-      <c r="F159" s="20"/>
-      <c r="G159" s="20"/>
-      <c r="H159" s="20"/>
+      <c r="F159" s="21"/>
+      <c r="G159" s="21"/>
+      <c r="H159" s="21"/>
       <c r="I159" s="3"/>
       <c r="J159" s="3"/>
       <c r="K159" s="3"/>
@@ -12539,14 +12556,14 @@
       <c r="AS159" s="3"/>
     </row>
     <row r="160" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A160" s="10"/>
+      <c r="A160" s="11"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
-      <c r="F160" s="20"/>
-      <c r="G160" s="20"/>
-      <c r="H160" s="20"/>
+      <c r="F160" s="21"/>
+      <c r="G160" s="21"/>
+      <c r="H160" s="21"/>
       <c r="I160" s="3"/>
       <c r="J160" s="3"/>
       <c r="K160" s="3"/>
@@ -12586,14 +12603,14 @@
       <c r="AS160" s="3"/>
     </row>
     <row r="161" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A161" s="10"/>
+      <c r="A161" s="11"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
-      <c r="F161" s="20"/>
-      <c r="G161" s="20"/>
-      <c r="H161" s="20"/>
+      <c r="F161" s="21"/>
+      <c r="G161" s="21"/>
+      <c r="H161" s="21"/>
       <c r="I161" s="3"/>
       <c r="J161" s="3"/>
       <c r="K161" s="3"/>
@@ -12633,14 +12650,14 @@
       <c r="AS161" s="3"/>
     </row>
     <row r="162" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A162" s="10"/>
+      <c r="A162" s="11"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
-      <c r="F162" s="20"/>
-      <c r="G162" s="20"/>
-      <c r="H162" s="20"/>
+      <c r="F162" s="21"/>
+      <c r="G162" s="21"/>
+      <c r="H162" s="21"/>
       <c r="I162" s="3"/>
       <c r="J162" s="3"/>
       <c r="K162" s="3"/>
@@ -12680,14 +12697,14 @@
       <c r="AS162" s="3"/>
     </row>
     <row r="163" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A163" s="10"/>
+      <c r="A163" s="11"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
-      <c r="F163" s="20"/>
-      <c r="G163" s="20"/>
-      <c r="H163" s="20"/>
+      <c r="F163" s="21"/>
+      <c r="G163" s="21"/>
+      <c r="H163" s="21"/>
       <c r="I163" s="3"/>
       <c r="J163" s="3"/>
       <c r="K163" s="3"/>
@@ -12727,14 +12744,14 @@
       <c r="AS163" s="3"/>
     </row>
     <row r="164" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A164" s="10"/>
+      <c r="A164" s="11"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
-      <c r="F164" s="20"/>
-      <c r="G164" s="20"/>
-      <c r="H164" s="20"/>
+      <c r="F164" s="21"/>
+      <c r="G164" s="21"/>
+      <c r="H164" s="21"/>
       <c r="I164" s="3"/>
       <c r="J164" s="3"/>
       <c r="K164" s="3"/>
@@ -12774,14 +12791,14 @@
       <c r="AS164" s="3"/>
     </row>
     <row r="165" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A165" s="10"/>
+      <c r="A165" s="11"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
-      <c r="F165" s="20"/>
-      <c r="G165" s="20"/>
-      <c r="H165" s="20"/>
+      <c r="F165" s="21"/>
+      <c r="G165" s="21"/>
+      <c r="H165" s="21"/>
       <c r="I165" s="3"/>
       <c r="J165" s="3"/>
       <c r="K165" s="3"/>
@@ -12821,14 +12838,14 @@
       <c r="AS165" s="3"/>
     </row>
     <row r="166" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A166" s="10"/>
+      <c r="A166" s="11"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
-      <c r="F166" s="20"/>
-      <c r="G166" s="20"/>
-      <c r="H166" s="20"/>
+      <c r="F166" s="21"/>
+      <c r="G166" s="21"/>
+      <c r="H166" s="21"/>
       <c r="I166" s="3"/>
       <c r="J166" s="3"/>
       <c r="K166" s="3"/>
@@ -12868,14 +12885,14 @@
       <c r="AS166" s="3"/>
     </row>
     <row r="167" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A167" s="10"/>
+      <c r="A167" s="11"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
-      <c r="F167" s="20"/>
-      <c r="G167" s="20"/>
-      <c r="H167" s="20"/>
+      <c r="F167" s="21"/>
+      <c r="G167" s="21"/>
+      <c r="H167" s="21"/>
       <c r="I167" s="3"/>
       <c r="J167" s="3"/>
       <c r="K167" s="3"/>
@@ -12915,14 +12932,14 @@
       <c r="AS167" s="3"/>
     </row>
     <row r="168" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A168" s="10"/>
+      <c r="A168" s="11"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
-      <c r="F168" s="20"/>
-      <c r="G168" s="20"/>
-      <c r="H168" s="20"/>
+      <c r="F168" s="21"/>
+      <c r="G168" s="21"/>
+      <c r="H168" s="21"/>
       <c r="I168" s="3"/>
       <c r="J168" s="3"/>
       <c r="K168" s="3"/>
@@ -12962,14 +12979,14 @@
       <c r="AS168" s="3"/>
     </row>
     <row r="169" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A169" s="10"/>
+      <c r="A169" s="11"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
-      <c r="F169" s="20"/>
-      <c r="G169" s="20"/>
-      <c r="H169" s="20"/>
+      <c r="F169" s="21"/>
+      <c r="G169" s="21"/>
+      <c r="H169" s="21"/>
       <c r="I169" s="3"/>
       <c r="J169" s="3"/>
       <c r="K169" s="3"/>
@@ -13009,14 +13026,14 @@
       <c r="AS169" s="3"/>
     </row>
     <row r="170" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A170" s="10"/>
+      <c r="A170" s="11"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
-      <c r="F170" s="20"/>
-      <c r="G170" s="20"/>
-      <c r="H170" s="20"/>
+      <c r="F170" s="21"/>
+      <c r="G170" s="21"/>
+      <c r="H170" s="21"/>
       <c r="I170" s="3"/>
       <c r="J170" s="3"/>
       <c r="K170" s="3"/>
@@ -13056,14 +13073,14 @@
       <c r="AS170" s="3"/>
     </row>
     <row r="171" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A171" s="10"/>
+      <c r="A171" s="11"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
-      <c r="F171" s="20"/>
-      <c r="G171" s="20"/>
-      <c r="H171" s="20"/>
+      <c r="F171" s="21"/>
+      <c r="G171" s="21"/>
+      <c r="H171" s="21"/>
       <c r="I171" s="3"/>
       <c r="J171" s="3"/>
       <c r="K171" s="3"/>
@@ -13103,14 +13120,14 @@
       <c r="AS171" s="3"/>
     </row>
     <row r="172" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A172" s="10"/>
+      <c r="A172" s="11"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
-      <c r="F172" s="20"/>
-      <c r="G172" s="20"/>
-      <c r="H172" s="20"/>
+      <c r="F172" s="21"/>
+      <c r="G172" s="21"/>
+      <c r="H172" s="21"/>
       <c r="I172" s="3"/>
       <c r="J172" s="3"/>
       <c r="K172" s="3"/>
@@ -13150,14 +13167,14 @@
       <c r="AS172" s="3"/>
     </row>
     <row r="173" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A173" s="10"/>
+      <c r="A173" s="11"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
-      <c r="F173" s="20"/>
-      <c r="G173" s="20"/>
-      <c r="H173" s="20"/>
+      <c r="F173" s="21"/>
+      <c r="G173" s="21"/>
+      <c r="H173" s="21"/>
       <c r="I173" s="3"/>
       <c r="J173" s="3"/>
       <c r="K173" s="3"/>
@@ -13197,14 +13214,14 @@
       <c r="AS173" s="3"/>
     </row>
     <row r="174" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A174" s="10"/>
+      <c r="A174" s="11"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
-      <c r="F174" s="20"/>
-      <c r="G174" s="20"/>
-      <c r="H174" s="20"/>
+      <c r="F174" s="21"/>
+      <c r="G174" s="21"/>
+      <c r="H174" s="21"/>
       <c r="I174" s="3"/>
       <c r="J174" s="3"/>
       <c r="K174" s="3"/>
@@ -13244,14 +13261,14 @@
       <c r="AS174" s="3"/>
     </row>
     <row r="175" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A175" s="10"/>
+      <c r="A175" s="11"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
-      <c r="F175" s="20"/>
-      <c r="G175" s="20"/>
-      <c r="H175" s="20"/>
+      <c r="F175" s="21"/>
+      <c r="G175" s="21"/>
+      <c r="H175" s="21"/>
       <c r="I175" s="3"/>
       <c r="J175" s="3"/>
       <c r="K175" s="3"/>
@@ -13291,14 +13308,14 @@
       <c r="AS175" s="3"/>
     </row>
     <row r="176" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A176" s="10"/>
+      <c r="A176" s="11"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
-      <c r="F176" s="20"/>
-      <c r="G176" s="20"/>
-      <c r="H176" s="20"/>
+      <c r="F176" s="21"/>
+      <c r="G176" s="21"/>
+      <c r="H176" s="21"/>
       <c r="I176" s="3"/>
       <c r="J176" s="3"/>
       <c r="K176" s="3"/>
@@ -13338,14 +13355,14 @@
       <c r="AS176" s="3"/>
     </row>
     <row r="177" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A177" s="10"/>
+      <c r="A177" s="11"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
-      <c r="F177" s="20"/>
-      <c r="G177" s="20"/>
-      <c r="H177" s="20"/>
+      <c r="F177" s="21"/>
+      <c r="G177" s="21"/>
+      <c r="H177" s="21"/>
       <c r="I177" s="3"/>
       <c r="J177" s="3"/>
       <c r="K177" s="3"/>
@@ -13385,14 +13402,14 @@
       <c r="AS177" s="3"/>
     </row>
     <row r="178" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A178" s="10"/>
+      <c r="A178" s="11"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
-      <c r="F178" s="20"/>
-      <c r="G178" s="20"/>
-      <c r="H178" s="20"/>
+      <c r="F178" s="21"/>
+      <c r="G178" s="21"/>
+      <c r="H178" s="21"/>
       <c r="I178" s="3"/>
       <c r="J178" s="3"/>
       <c r="K178" s="3"/>
@@ -13432,14 +13449,14 @@
       <c r="AS178" s="3"/>
     </row>
     <row r="179" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A179" s="10"/>
+      <c r="A179" s="11"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
-      <c r="F179" s="20"/>
-      <c r="G179" s="20"/>
-      <c r="H179" s="20"/>
+      <c r="F179" s="21"/>
+      <c r="G179" s="21"/>
+      <c r="H179" s="21"/>
       <c r="I179" s="3"/>
       <c r="J179" s="3"/>
       <c r="K179" s="3"/>
@@ -13479,14 +13496,14 @@
       <c r="AS179" s="3"/>
     </row>
     <row r="180" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A180" s="10"/>
+      <c r="A180" s="11"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
-      <c r="F180" s="20"/>
-      <c r="G180" s="20"/>
-      <c r="H180" s="20"/>
+      <c r="F180" s="21"/>
+      <c r="G180" s="21"/>
+      <c r="H180" s="21"/>
       <c r="I180" s="3"/>
       <c r="J180" s="3"/>
       <c r="K180" s="3"/>
@@ -13526,14 +13543,14 @@
       <c r="AS180" s="3"/>
     </row>
     <row r="181" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A181" s="10"/>
+      <c r="A181" s="11"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
-      <c r="F181" s="20"/>
-      <c r="G181" s="20"/>
-      <c r="H181" s="20"/>
+      <c r="F181" s="21"/>
+      <c r="G181" s="21"/>
+      <c r="H181" s="21"/>
       <c r="I181" s="3"/>
       <c r="J181" s="3"/>
       <c r="K181" s="3"/>
@@ -13573,14 +13590,14 @@
       <c r="AS181" s="3"/>
     </row>
     <row r="182" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A182" s="10"/>
+      <c r="A182" s="11"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
-      <c r="F182" s="20"/>
-      <c r="G182" s="20"/>
-      <c r="H182" s="20"/>
+      <c r="F182" s="21"/>
+      <c r="G182" s="21"/>
+      <c r="H182" s="21"/>
       <c r="I182" s="3"/>
       <c r="J182" s="3"/>
       <c r="K182" s="3"/>
@@ -13620,14 +13637,14 @@
       <c r="AS182" s="3"/>
     </row>
     <row r="183" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A183" s="10"/>
+      <c r="A183" s="11"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
-      <c r="F183" s="20"/>
-      <c r="G183" s="20"/>
-      <c r="H183" s="20"/>
+      <c r="F183" s="21"/>
+      <c r="G183" s="21"/>
+      <c r="H183" s="21"/>
       <c r="I183" s="3"/>
       <c r="J183" s="3"/>
       <c r="K183" s="3"/>
@@ -13667,14 +13684,14 @@
       <c r="AS183" s="3"/>
     </row>
     <row r="184" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A184" s="10"/>
+      <c r="A184" s="11"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
-      <c r="F184" s="20"/>
-      <c r="G184" s="20"/>
-      <c r="H184" s="20"/>
+      <c r="F184" s="21"/>
+      <c r="G184" s="21"/>
+      <c r="H184" s="21"/>
       <c r="I184" s="3"/>
       <c r="J184" s="3"/>
       <c r="K184" s="3"/>
@@ -13714,14 +13731,14 @@
       <c r="AS184" s="3"/>
     </row>
     <row r="185" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A185" s="10"/>
+      <c r="A185" s="11"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
-      <c r="F185" s="20"/>
-      <c r="G185" s="20"/>
-      <c r="H185" s="20"/>
+      <c r="F185" s="21"/>
+      <c r="G185" s="21"/>
+      <c r="H185" s="21"/>
       <c r="I185" s="3"/>
       <c r="J185" s="3"/>
       <c r="K185" s="3"/>
@@ -13761,14 +13778,14 @@
       <c r="AS185" s="3"/>
     </row>
     <row r="186" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A186" s="10"/>
+      <c r="A186" s="11"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
-      <c r="F186" s="20"/>
-      <c r="G186" s="20"/>
-      <c r="H186" s="20"/>
+      <c r="F186" s="21"/>
+      <c r="G186" s="21"/>
+      <c r="H186" s="21"/>
       <c r="I186" s="3"/>
       <c r="J186" s="3"/>
       <c r="K186" s="3"/>
@@ -13808,14 +13825,14 @@
       <c r="AS186" s="3"/>
     </row>
     <row r="187" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A187" s="10"/>
+      <c r="A187" s="11"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
-      <c r="F187" s="20"/>
-      <c r="G187" s="20"/>
-      <c r="H187" s="20"/>
+      <c r="F187" s="21"/>
+      <c r="G187" s="21"/>
+      <c r="H187" s="21"/>
       <c r="I187" s="3"/>
       <c r="J187" s="3"/>
       <c r="K187" s="3"/>
@@ -13855,14 +13872,14 @@
       <c r="AS187" s="3"/>
     </row>
     <row r="188" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A188" s="10"/>
+      <c r="A188" s="11"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
-      <c r="F188" s="20"/>
-      <c r="G188" s="20"/>
-      <c r="H188" s="20"/>
+      <c r="F188" s="21"/>
+      <c r="G188" s="21"/>
+      <c r="H188" s="21"/>
       <c r="I188" s="3"/>
       <c r="J188" s="3"/>
       <c r="K188" s="3"/>
@@ -13902,14 +13919,14 @@
       <c r="AS188" s="3"/>
     </row>
     <row r="189" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A189" s="10"/>
+      <c r="A189" s="11"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
-      <c r="F189" s="20"/>
-      <c r="G189" s="20"/>
-      <c r="H189" s="20"/>
+      <c r="F189" s="21"/>
+      <c r="G189" s="21"/>
+      <c r="H189" s="21"/>
       <c r="I189" s="3"/>
       <c r="J189" s="3"/>
       <c r="K189" s="3"/>
@@ -13949,14 +13966,14 @@
       <c r="AS189" s="3"/>
     </row>
     <row r="190" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A190" s="10"/>
+      <c r="A190" s="11"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
-      <c r="F190" s="20"/>
-      <c r="G190" s="20"/>
-      <c r="H190" s="20"/>
+      <c r="F190" s="21"/>
+      <c r="G190" s="21"/>
+      <c r="H190" s="21"/>
       <c r="I190" s="3"/>
       <c r="J190" s="3"/>
       <c r="K190" s="3"/>
@@ -13996,14 +14013,14 @@
       <c r="AS190" s="3"/>
     </row>
     <row r="191" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A191" s="10"/>
+      <c r="A191" s="11"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
-      <c r="F191" s="20"/>
-      <c r="G191" s="20"/>
-      <c r="H191" s="20"/>
+      <c r="F191" s="21"/>
+      <c r="G191" s="21"/>
+      <c r="H191" s="21"/>
       <c r="I191" s="3"/>
       <c r="J191" s="3"/>
       <c r="K191" s="3"/>
@@ -14043,14 +14060,14 @@
       <c r="AS191" s="3"/>
     </row>
     <row r="192" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A192" s="10"/>
+      <c r="A192" s="11"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
-      <c r="F192" s="20"/>
-      <c r="G192" s="20"/>
-      <c r="H192" s="20"/>
+      <c r="F192" s="21"/>
+      <c r="G192" s="21"/>
+      <c r="H192" s="21"/>
       <c r="I192" s="3"/>
       <c r="J192" s="3"/>
       <c r="K192" s="3"/>
@@ -14090,14 +14107,14 @@
       <c r="AS192" s="3"/>
     </row>
     <row r="193" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A193" s="10"/>
+      <c r="A193" s="11"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
-      <c r="F193" s="20"/>
-      <c r="G193" s="20"/>
-      <c r="H193" s="20"/>
+      <c r="F193" s="21"/>
+      <c r="G193" s="21"/>
+      <c r="H193" s="21"/>
       <c r="I193" s="3"/>
       <c r="J193" s="3"/>
       <c r="K193" s="3"/>
@@ -14137,14 +14154,14 @@
       <c r="AS193" s="3"/>
     </row>
     <row r="194" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A194" s="10"/>
+      <c r="A194" s="11"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
-      <c r="F194" s="20"/>
-      <c r="G194" s="20"/>
-      <c r="H194" s="20"/>
+      <c r="F194" s="21"/>
+      <c r="G194" s="21"/>
+      <c r="H194" s="21"/>
       <c r="I194" s="3"/>
       <c r="J194" s="3"/>
       <c r="K194" s="3"/>
@@ -14184,14 +14201,14 @@
       <c r="AS194" s="3"/>
     </row>
     <row r="195" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A195" s="10"/>
+      <c r="A195" s="11"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
-      <c r="F195" s="20"/>
-      <c r="G195" s="20"/>
-      <c r="H195" s="20"/>
+      <c r="F195" s="21"/>
+      <c r="G195" s="21"/>
+      <c r="H195" s="21"/>
       <c r="I195" s="3"/>
       <c r="J195" s="3"/>
       <c r="K195" s="3"/>
@@ -14231,14 +14248,14 @@
       <c r="AS195" s="3"/>
     </row>
     <row r="196" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A196" s="10"/>
+      <c r="A196" s="11"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
-      <c r="F196" s="20"/>
-      <c r="G196" s="20"/>
-      <c r="H196" s="20"/>
+      <c r="F196" s="21"/>
+      <c r="G196" s="21"/>
+      <c r="H196" s="21"/>
       <c r="I196" s="3"/>
       <c r="J196" s="3"/>
       <c r="K196" s="3"/>
@@ -14278,14 +14295,14 @@
       <c r="AS196" s="3"/>
     </row>
     <row r="197" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A197" s="10"/>
+      <c r="A197" s="11"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
-      <c r="F197" s="20"/>
-      <c r="G197" s="20"/>
-      <c r="H197" s="20"/>
+      <c r="F197" s="21"/>
+      <c r="G197" s="21"/>
+      <c r="H197" s="21"/>
       <c r="I197" s="3"/>
       <c r="J197" s="3"/>
       <c r="K197" s="3"/>
@@ -14325,14 +14342,14 @@
       <c r="AS197" s="3"/>
     </row>
     <row r="198" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A198" s="10"/>
+      <c r="A198" s="11"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
-      <c r="F198" s="20"/>
-      <c r="G198" s="20"/>
-      <c r="H198" s="20"/>
+      <c r="F198" s="21"/>
+      <c r="G198" s="21"/>
+      <c r="H198" s="21"/>
       <c r="I198" s="3"/>
       <c r="J198" s="3"/>
       <c r="K198" s="3"/>
@@ -14372,14 +14389,14 @@
       <c r="AS198" s="3"/>
     </row>
     <row r="199" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A199" s="10"/>
+      <c r="A199" s="11"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
-      <c r="F199" s="20"/>
-      <c r="G199" s="20"/>
-      <c r="H199" s="20"/>
+      <c r="F199" s="21"/>
+      <c r="G199" s="21"/>
+      <c r="H199" s="21"/>
       <c r="I199" s="3"/>
       <c r="J199" s="3"/>
       <c r="K199" s="3"/>
@@ -14419,14 +14436,14 @@
       <c r="AS199" s="3"/>
     </row>
     <row r="200" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A200" s="10"/>
+      <c r="A200" s="11"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
-      <c r="F200" s="20"/>
-      <c r="G200" s="20"/>
-      <c r="H200" s="20"/>
+      <c r="F200" s="21"/>
+      <c r="G200" s="21"/>
+      <c r="H200" s="21"/>
       <c r="I200" s="3"/>
       <c r="J200" s="3"/>
       <c r="K200" s="3"/>
@@ -14466,14 +14483,14 @@
       <c r="AS200" s="3"/>
     </row>
     <row r="201" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A201" s="10"/>
+      <c r="A201" s="11"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
-      <c r="F201" s="20"/>
-      <c r="G201" s="20"/>
-      <c r="H201" s="20"/>
+      <c r="F201" s="21"/>
+      <c r="G201" s="21"/>
+      <c r="H201" s="21"/>
       <c r="I201" s="3"/>
       <c r="J201" s="3"/>
       <c r="K201" s="3"/>
@@ -14513,14 +14530,14 @@
       <c r="AS201" s="3"/>
     </row>
     <row r="202" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A202" s="10"/>
+      <c r="A202" s="11"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
-      <c r="F202" s="20"/>
-      <c r="G202" s="20"/>
-      <c r="H202" s="20"/>
+      <c r="F202" s="21"/>
+      <c r="G202" s="21"/>
+      <c r="H202" s="21"/>
       <c r="I202" s="3"/>
       <c r="J202" s="3"/>
       <c r="K202" s="3"/>
@@ -14560,14 +14577,14 @@
       <c r="AS202" s="3"/>
     </row>
     <row r="203" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A203" s="10"/>
+      <c r="A203" s="11"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
       <c r="E203" s="3"/>
-      <c r="F203" s="20"/>
-      <c r="G203" s="20"/>
-      <c r="H203" s="20"/>
+      <c r="F203" s="21"/>
+      <c r="G203" s="21"/>
+      <c r="H203" s="21"/>
       <c r="I203" s="3"/>
       <c r="J203" s="3"/>
       <c r="K203" s="3"/>
@@ -14607,14 +14624,14 @@
       <c r="AS203" s="3"/>
     </row>
     <row r="204" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A204" s="10"/>
+      <c r="A204" s="11"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
-      <c r="F204" s="20"/>
-      <c r="G204" s="20"/>
-      <c r="H204" s="20"/>
+      <c r="F204" s="21"/>
+      <c r="G204" s="21"/>
+      <c r="H204" s="21"/>
       <c r="I204" s="3"/>
       <c r="J204" s="3"/>
       <c r="K204" s="3"/>
@@ -14654,14 +14671,14 @@
       <c r="AS204" s="3"/>
     </row>
     <row r="205" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A205" s="10"/>
+      <c r="A205" s="11"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="3"/>
-      <c r="F205" s="20"/>
-      <c r="G205" s="20"/>
-      <c r="H205" s="20"/>
+      <c r="F205" s="21"/>
+      <c r="G205" s="21"/>
+      <c r="H205" s="21"/>
       <c r="I205" s="3"/>
       <c r="J205" s="3"/>
       <c r="K205" s="3"/>
@@ -14701,14 +14718,14 @@
       <c r="AS205" s="3"/>
     </row>
     <row r="206" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A206" s="10"/>
+      <c r="A206" s="11"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
-      <c r="F206" s="20"/>
-      <c r="G206" s="20"/>
-      <c r="H206" s="20"/>
+      <c r="F206" s="21"/>
+      <c r="G206" s="21"/>
+      <c r="H206" s="21"/>
       <c r="I206" s="3"/>
       <c r="J206" s="3"/>
       <c r="K206" s="3"/>
@@ -14748,14 +14765,14 @@
       <c r="AS206" s="3"/>
     </row>
     <row r="207" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A207" s="10"/>
+      <c r="A207" s="11"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
-      <c r="F207" s="20"/>
-      <c r="G207" s="20"/>
-      <c r="H207" s="20"/>
+      <c r="F207" s="21"/>
+      <c r="G207" s="21"/>
+      <c r="H207" s="21"/>
       <c r="I207" s="3"/>
       <c r="J207" s="3"/>
       <c r="K207" s="3"/>
@@ -14795,14 +14812,14 @@
       <c r="AS207" s="3"/>
     </row>
     <row r="208" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A208" s="10"/>
+      <c r="A208" s="11"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
-      <c r="F208" s="20"/>
-      <c r="G208" s="20"/>
-      <c r="H208" s="20"/>
+      <c r="F208" s="21"/>
+      <c r="G208" s="21"/>
+      <c r="H208" s="21"/>
       <c r="I208" s="3"/>
       <c r="J208" s="3"/>
       <c r="K208" s="3"/>
@@ -14842,14 +14859,14 @@
       <c r="AS208" s="3"/>
     </row>
     <row r="209" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A209" s="10"/>
+      <c r="A209" s="11"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3"/>
-      <c r="F209" s="20"/>
-      <c r="G209" s="20"/>
-      <c r="H209" s="20"/>
+      <c r="F209" s="21"/>
+      <c r="G209" s="21"/>
+      <c r="H209" s="21"/>
       <c r="I209" s="3"/>
       <c r="J209" s="3"/>
       <c r="K209" s="3"/>
@@ -14889,14 +14906,14 @@
       <c r="AS209" s="3"/>
     </row>
     <row r="210" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A210" s="10"/>
+      <c r="A210" s="11"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
-      <c r="F210" s="20"/>
-      <c r="G210" s="20"/>
-      <c r="H210" s="20"/>
+      <c r="F210" s="21"/>
+      <c r="G210" s="21"/>
+      <c r="H210" s="21"/>
       <c r="I210" s="3"/>
       <c r="J210" s="3"/>
       <c r="K210" s="3"/>
@@ -14936,14 +14953,14 @@
       <c r="AS210" s="3"/>
     </row>
     <row r="211" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A211" s="10"/>
+      <c r="A211" s="11"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
       <c r="E211" s="3"/>
-      <c r="F211" s="20"/>
-      <c r="G211" s="20"/>
-      <c r="H211" s="20"/>
+      <c r="F211" s="21"/>
+      <c r="G211" s="21"/>
+      <c r="H211" s="21"/>
       <c r="I211" s="3"/>
       <c r="J211" s="3"/>
       <c r="K211" s="3"/>
@@ -14983,14 +15000,14 @@
       <c r="AS211" s="3"/>
     </row>
     <row r="212" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A212" s="10"/>
+      <c r="A212" s="11"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
-      <c r="F212" s="20"/>
-      <c r="G212" s="20"/>
-      <c r="H212" s="20"/>
+      <c r="F212" s="21"/>
+      <c r="G212" s="21"/>
+      <c r="H212" s="21"/>
       <c r="I212" s="3"/>
       <c r="J212" s="3"/>
       <c r="K212" s="3"/>
@@ -15030,14 +15047,14 @@
       <c r="AS212" s="3"/>
     </row>
     <row r="213" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A213" s="10"/>
+      <c r="A213" s="11"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
       <c r="E213" s="3"/>
-      <c r="F213" s="20"/>
-      <c r="G213" s="20"/>
-      <c r="H213" s="20"/>
+      <c r="F213" s="21"/>
+      <c r="G213" s="21"/>
+      <c r="H213" s="21"/>
       <c r="I213" s="3"/>
       <c r="J213" s="3"/>
       <c r="K213" s="3"/>
@@ -15077,14 +15094,14 @@
       <c r="AS213" s="3"/>
     </row>
     <row r="214" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A214" s="10"/>
+      <c r="A214" s="11"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
-      <c r="F214" s="20"/>
-      <c r="G214" s="20"/>
-      <c r="H214" s="20"/>
+      <c r="F214" s="21"/>
+      <c r="G214" s="21"/>
+      <c r="H214" s="21"/>
       <c r="I214" s="3"/>
       <c r="J214" s="3"/>
       <c r="K214" s="3"/>
@@ -15124,14 +15141,14 @@
       <c r="AS214" s="3"/>
     </row>
     <row r="215" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A215" s="10"/>
+      <c r="A215" s="11"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
-      <c r="F215" s="20"/>
-      <c r="G215" s="20"/>
-      <c r="H215" s="20"/>
+      <c r="F215" s="21"/>
+      <c r="G215" s="21"/>
+      <c r="H215" s="21"/>
       <c r="I215" s="3"/>
       <c r="J215" s="3"/>
       <c r="K215" s="3"/>
@@ -15171,14 +15188,14 @@
       <c r="AS215" s="3"/>
     </row>
     <row r="216" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A216" s="10"/>
+      <c r="A216" s="11"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
-      <c r="F216" s="20"/>
-      <c r="G216" s="20"/>
-      <c r="H216" s="20"/>
+      <c r="F216" s="21"/>
+      <c r="G216" s="21"/>
+      <c r="H216" s="21"/>
       <c r="I216" s="3"/>
       <c r="J216" s="3"/>
       <c r="K216" s="3"/>
@@ -15218,14 +15235,14 @@
       <c r="AS216" s="3"/>
     </row>
     <row r="217" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A217" s="10"/>
+      <c r="A217" s="11"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
-      <c r="F217" s="20"/>
-      <c r="G217" s="20"/>
-      <c r="H217" s="20"/>
+      <c r="F217" s="21"/>
+      <c r="G217" s="21"/>
+      <c r="H217" s="21"/>
       <c r="I217" s="3"/>
       <c r="J217" s="3"/>
       <c r="K217" s="3"/>
@@ -15265,14 +15282,14 @@
       <c r="AS217" s="3"/>
     </row>
     <row r="218" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A218" s="10"/>
+      <c r="A218" s="11"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
       <c r="E218" s="3"/>
-      <c r="F218" s="20"/>
-      <c r="G218" s="20"/>
-      <c r="H218" s="20"/>
+      <c r="F218" s="21"/>
+      <c r="G218" s="21"/>
+      <c r="H218" s="21"/>
       <c r="I218" s="3"/>
       <c r="J218" s="3"/>
       <c r="K218" s="3"/>
@@ -15312,14 +15329,14 @@
       <c r="AS218" s="3"/>
     </row>
     <row r="219" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A219" s="10"/>
+      <c r="A219" s="11"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
       <c r="E219" s="3"/>
-      <c r="F219" s="20"/>
-      <c r="G219" s="20"/>
-      <c r="H219" s="20"/>
+      <c r="F219" s="21"/>
+      <c r="G219" s="21"/>
+      <c r="H219" s="21"/>
       <c r="I219" s="3"/>
       <c r="J219" s="3"/>
       <c r="K219" s="3"/>
@@ -15359,14 +15376,14 @@
       <c r="AS219" s="3"/>
     </row>
     <row r="220" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A220" s="10"/>
+      <c r="A220" s="11"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
-      <c r="F220" s="20"/>
-      <c r="G220" s="20"/>
-      <c r="H220" s="20"/>
+      <c r="F220" s="21"/>
+      <c r="G220" s="21"/>
+      <c r="H220" s="21"/>
       <c r="I220" s="3"/>
       <c r="J220" s="3"/>
       <c r="K220" s="3"/>
@@ -15406,14 +15423,14 @@
       <c r="AS220" s="3"/>
     </row>
     <row r="221" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A221" s="10"/>
+      <c r="A221" s="11"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
-      <c r="F221" s="20"/>
-      <c r="G221" s="20"/>
-      <c r="H221" s="20"/>
+      <c r="F221" s="21"/>
+      <c r="G221" s="21"/>
+      <c r="H221" s="21"/>
       <c r="I221" s="3"/>
       <c r="J221" s="3"/>
       <c r="K221" s="3"/>
@@ -15453,14 +15470,14 @@
       <c r="AS221" s="3"/>
     </row>
     <row r="222" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A222" s="10"/>
+      <c r="A222" s="11"/>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
       <c r="E222" s="3"/>
-      <c r="F222" s="20"/>
-      <c r="G222" s="20"/>
-      <c r="H222" s="20"/>
+      <c r="F222" s="21"/>
+      <c r="G222" s="21"/>
+      <c r="H222" s="21"/>
       <c r="I222" s="3"/>
       <c r="J222" s="3"/>
       <c r="K222" s="3"/>
@@ -15500,14 +15517,14 @@
       <c r="AS222" s="3"/>
     </row>
     <row r="223" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A223" s="10"/>
+      <c r="A223" s="11"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
       <c r="E223" s="3"/>
-      <c r="F223" s="20"/>
-      <c r="G223" s="20"/>
-      <c r="H223" s="20"/>
+      <c r="F223" s="21"/>
+      <c r="G223" s="21"/>
+      <c r="H223" s="21"/>
       <c r="I223" s="3"/>
       <c r="J223" s="3"/>
       <c r="K223" s="3"/>
@@ -15547,14 +15564,14 @@
       <c r="AS223" s="3"/>
     </row>
     <row r="224" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A224" s="10"/>
+      <c r="A224" s="11"/>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
       <c r="E224" s="3"/>
-      <c r="F224" s="20"/>
-      <c r="G224" s="20"/>
-      <c r="H224" s="20"/>
+      <c r="F224" s="21"/>
+      <c r="G224" s="21"/>
+      <c r="H224" s="21"/>
       <c r="I224" s="3"/>
       <c r="J224" s="3"/>
       <c r="K224" s="3"/>
@@ -15594,7 +15611,7 @@
       <c r="AS224" s="3"/>
     </row>
     <row r="225" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A225" s="10"/>
+      <c r="A225" s="11"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
@@ -15641,7 +15658,7 @@
       <c r="AS225" s="3"/>
     </row>
     <row r="226" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A226" s="10"/>
+      <c r="A226" s="11"/>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
@@ -15688,7 +15705,7 @@
       <c r="AS226" s="3"/>
     </row>
     <row r="227" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A227" s="10"/>
+      <c r="A227" s="11"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
@@ -15735,7 +15752,7 @@
       <c r="AS227" s="3"/>
     </row>
     <row r="228" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A228" s="10"/>
+      <c r="A228" s="11"/>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
@@ -15782,7 +15799,7 @@
       <c r="AS228" s="3"/>
     </row>
     <row r="229" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A229" s="10"/>
+      <c r="A229" s="11"/>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
@@ -15829,7 +15846,7 @@
       <c r="AS229" s="3"/>
     </row>
     <row r="230" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A230" s="10"/>
+      <c r="A230" s="11"/>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
@@ -15876,7 +15893,7 @@
       <c r="AS230" s="3"/>
     </row>
     <row r="231" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A231" s="10"/>
+      <c r="A231" s="11"/>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
@@ -15923,7 +15940,7 @@
       <c r="AS231" s="3"/>
     </row>
     <row r="232" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A232" s="10"/>
+      <c r="A232" s="11"/>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
@@ -15970,7 +15987,7 @@
       <c r="AS232" s="3"/>
     </row>
     <row r="233" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A233" s="10"/>
+      <c r="A233" s="11"/>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
@@ -16017,7 +16034,7 @@
       <c r="AS233" s="3"/>
     </row>
     <row r="234" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A234" s="10"/>
+      <c r="A234" s="11"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
@@ -16064,7 +16081,7 @@
       <c r="AS234" s="3"/>
     </row>
     <row r="235" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A235" s="10"/>
+      <c r="A235" s="11"/>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
@@ -16111,7 +16128,7 @@
       <c r="AS235" s="3"/>
     </row>
     <row r="236" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A236" s="10"/>
+      <c r="A236" s="11"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
@@ -16158,7 +16175,7 @@
       <c r="AS236" s="3"/>
     </row>
     <row r="237" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A237" s="10"/>
+      <c r="A237" s="11"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
@@ -16205,7 +16222,7 @@
       <c r="AS237" s="3"/>
     </row>
     <row r="238" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A238" s="10"/>
+      <c r="A238" s="11"/>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
@@ -16252,7 +16269,7 @@
       <c r="AS238" s="3"/>
     </row>
     <row r="239" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A239" s="10"/>
+      <c r="A239" s="11"/>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
@@ -16299,7 +16316,7 @@
       <c r="AS239" s="3"/>
     </row>
     <row r="240" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A240" s="10"/>
+      <c r="A240" s="11"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
@@ -16383,18 +16400,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9CC9CA2-CEEF-4FD9-95A4-95A07D05EBFE}">
   <dimension ref="A1:BR147"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.42578125" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.42578125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.140625" style="4"/>
+    <col min="5" max="5" width="9.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>471</v>
       </c>
       <c r="B1" s="3"/>
@@ -16542,35 +16561,35 @@
       <c r="BR2" s="3"/>
     </row>
     <row r="3" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="J3" s="23"/>
-      <c r="K3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="25"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
@@ -16633,18 +16652,18 @@
     </row>
     <row r="4" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="25" t="s">
         <v>284</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="12"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -16706,39 +16725,39 @@
       <c r="BR4" s="3"/>
     </row>
     <row r="5" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
+      <c r="A5" s="11">
         <v>1</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="26">
         <f>+[29]Main!$H$2</f>
         <v>559.02</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="26">
         <f>+[29]Main!$H$4</f>
         <v>4155288.66918858</v>
       </c>
-      <c r="G5" s="25">
+      <c r="G5" s="26">
         <f>+[29]Main!$H$6-[29]Main!$H$5</f>
         <v>-54413</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="26">
         <f t="shared" ref="H5:H18" si="0">+F5+G5</f>
         <v>4100875.66918858</v>
       </c>
-      <c r="I5" s="26" t="s">
+      <c r="I5" s="27" t="s">
         <v>240</v>
       </c>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
@@ -16800,11 +16819,11 @@
       <c r="BR5" s="3"/>
     </row>
     <row r="6" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A6" s="10">
+      <c r="A6" s="11">
         <f>+A5+1</f>
         <v>2</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>287</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -16813,23 +16832,23 @@
       <c r="D6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <f>+[30]Main!$G$2</f>
         <v>373.4</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="26">
         <f>+[30]Main!$G$4*FX!C6</f>
         <v>475516.08776000002</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="26">
         <f>+([30]Main!$G$6-[30]Main!$G$5)*FX!C6</f>
         <v>-20873.440000000002</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="26">
         <f t="shared" si="0"/>
         <v>454642.64776000002</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="15" t="s">
         <v>239</v>
       </c>
       <c r="J6" s="3"/>
@@ -16895,11 +16914,11 @@
       <c r="BR6" s="3"/>
     </row>
     <row r="7" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
+      <c r="A7" s="11">
         <f t="shared" ref="A7:A18" si="1">+A6+1</f>
         <v>3</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -16908,23 +16927,23 @@
       <c r="D7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <f>+[4]Main!$H$2</f>
         <v>3214</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="26">
         <f>+[4]Main!$H$4*FX!C2</f>
         <v>124966.1644815872</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="26">
         <f>+([4]Main!$H$6-[4]Main!$H$5)*FX!C2</f>
         <v>12550.617600000001</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="26">
         <f t="shared" si="0"/>
         <v>137516.78208158721</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="15" t="s">
         <v>243</v>
       </c>
       <c r="J7" s="3"/>
@@ -16990,11 +17009,11 @@
       <c r="BR7" s="3"/>
     </row>
     <row r="8" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A8" s="10">
+      <c r="A8" s="11">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="12" t="s">
         <v>289</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -17003,23 +17022,23 @@
       <c r="D8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <f>+[6]Main!$I$2</f>
         <v>10935</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="26">
         <f>+[6]Main!$I$4*FX!C2</f>
         <v>90887.520960000009</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="26">
         <f>+([6]Main!$I$6-[6]Main!$I$5)*FX!C2</f>
         <v>-9499.84</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="26">
         <f t="shared" si="0"/>
         <v>81387.680960000012</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="15" t="s">
         <v>291</v>
       </c>
       <c r="J8" s="3"/>
@@ -17085,11 +17104,11 @@
       <c r="BR8" s="3"/>
     </row>
     <row r="9" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+      <c r="A9" s="11">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="12" t="s">
         <v>292</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -17098,23 +17117,23 @@
       <c r="D9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="26">
         <f>+[31]Main!$I$2</f>
         <v>2123</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="26">
         <f>+[32]Main!$H$5*FX!C6</f>
         <v>65131.275185760009</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="26">
         <f>+([32]Main!$H$7-[32]Main!$H$6)*FX!C6</f>
         <v>-16042.82638</v>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="26">
         <f t="shared" si="0"/>
         <v>49088.44880576001</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="15" t="s">
         <v>246</v>
       </c>
       <c r="J9" s="3"/>
@@ -17180,11 +17199,11 @@
       <c r="BR9" s="3"/>
     </row>
     <row r="10" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A10" s="10">
+      <c r="A10" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="12" t="s">
         <v>17</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -17193,23 +17212,23 @@
       <c r="D10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="26">
         <f>+[7]Main!$I$2</f>
         <v>141.63</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="26">
         <f>+[7]Main!$I$4</f>
         <v>82151.979704910002</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="26">
         <f>+[7]Main!$I$6-[7]Main!$I$5</f>
         <v>1013.5080000000007</v>
       </c>
-      <c r="H10" s="25">
+      <c r="H10" s="26">
         <f t="shared" si="0"/>
         <v>83165.487704910003</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="15" t="s">
         <v>246</v>
       </c>
       <c r="J10" s="3"/>
@@ -17275,11 +17294,11 @@
       <c r="BR10" s="3"/>
     </row>
     <row r="11" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
+      <c r="A11" s="11">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="12" t="s">
         <v>36</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -17288,23 +17307,23 @@
       <c r="D11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <f>+[8]Main!$I$2</f>
         <v>173.3</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="26">
         <f>+[8]Main!$I$4</f>
         <v>43360.925609900005</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="26">
         <f>+[8]Main!$I$6-[8]Main!$I$5</f>
         <v>-1230</v>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="26">
         <f t="shared" si="0"/>
         <v>42130.925609900005</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="15" t="s">
         <v>240</v>
       </c>
       <c r="J11" s="3"/>
@@ -17370,11 +17389,11 @@
       <c r="BR11" s="3"/>
     </row>
     <row r="12" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
+      <c r="A12" s="11">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="12" t="s">
         <v>293</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -17383,23 +17402,23 @@
       <c r="D12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="26">
         <f>+[11]Main!$L$3</f>
         <v>228.01</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="26">
         <f>+[11]Main!$L$5</f>
         <v>42061.053038120001</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="26">
         <f>+[11]Main!$L$7-[11]Main!$L$6</f>
         <v>1030</v>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="26">
         <f t="shared" si="0"/>
         <v>43091.053038120001</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="I12" s="15" t="s">
         <v>240</v>
       </c>
       <c r="J12" s="3"/>
@@ -17465,11 +17484,11 @@
       <c r="BR12" s="3"/>
     </row>
     <row r="13" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
+      <c r="A13" s="11">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="12" t="s">
         <v>38</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -17478,23 +17497,23 @@
       <c r="D13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <f>+[9]Main!$H$2</f>
         <v>58.14</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="26">
         <f>+[9]Main!$H$4</f>
         <v>38796.821127900002</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="26">
         <f>+[9]Main!$H$6-[9]Main!$H$5</f>
         <v>-1403.174</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="26">
         <f t="shared" si="0"/>
         <v>37393.647127900003</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="I13" s="15" t="s">
         <v>294</v>
       </c>
       <c r="J13" s="3"/>
@@ -17560,11 +17579,11 @@
       <c r="BR13" s="3"/>
     </row>
     <row r="14" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A14" s="10">
+      <c r="A14" s="11">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="12" t="s">
         <v>295</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -17573,23 +17592,23 @@
       <c r="D14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="26">
         <f>+[13]Main!$I$2</f>
         <v>66.67</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="26">
         <f>+[13]Main!$I$4*FX!C5</f>
         <v>26732.303286336904</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="26">
         <f>+([13]Main!$I$6-[13]Main!$I$5)*FX!C5</f>
         <v>718.45199999999988</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="26">
         <f t="shared" si="0"/>
         <v>27450.755286336906</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="I14" s="15" t="s">
         <v>246</v>
       </c>
       <c r="J14" s="3"/>
@@ -17655,11 +17674,11 @@
       <c r="BR14" s="3"/>
     </row>
     <row r="15" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
+      <c r="A15" s="11">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="12" t="s">
         <v>67</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -17668,23 +17687,23 @@
       <c r="D15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="26">
         <f>+[31]Main!$I$2</f>
         <v>2123</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="26">
         <f>+[31]Main!$I$4*FX!C2</f>
         <v>11429.0165977856</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="26">
         <f>+([31]Main!$I$6-[31]Main!$I$5)*FX!C2</f>
         <v>-2117.3888000000002</v>
       </c>
-      <c r="H15" s="25">
+      <c r="H15" s="26">
         <f t="shared" si="0"/>
         <v>9311.6277977855989</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="I15" s="15" t="s">
         <v>246</v>
       </c>
       <c r="J15" s="3"/>
@@ -17750,11 +17769,11 @@
       <c r="BR15" s="3"/>
     </row>
     <row r="16" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A16" s="10">
+      <c r="A16" s="11">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="12" t="s">
         <v>64</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -17763,23 +17782,23 @@
       <c r="D16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="26">
         <f>+[18]Main!$I$2</f>
         <v>5241</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="26">
         <f>+[18]Main!$I$4*FX!C2</f>
         <v>21944.563863571202</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="26">
         <f>+([18]Main!$I$6-[18]Main!$I$5)*FX!C2</f>
         <v>-2059.9551999999999</v>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="26">
         <f t="shared" si="0"/>
         <v>19884.608663571202</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="I16" s="15" t="s">
         <v>296</v>
       </c>
       <c r="J16" s="3"/>
@@ -17845,11 +17864,11 @@
       <c r="BR16" s="3"/>
     </row>
     <row r="17" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A17" s="10">
+      <c r="A17" s="11">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -17858,23 +17877,23 @@
       <c r="D17" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="26">
         <f>+[19]Main!$I$2</f>
         <v>16735</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="26">
         <f>+[19]Main!$I$4*FX!C2</f>
         <v>14518.749837375999</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="26">
         <f>+([19]Main!$I$6-[19]Main!$I$5)*FX!C2</f>
         <v>-1445.152</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="26">
         <f t="shared" si="0"/>
         <v>13073.597837375999</v>
       </c>
-      <c r="I17" s="14" t="s">
+      <c r="I17" s="15" t="s">
         <v>296</v>
       </c>
       <c r="J17" s="3"/>
@@ -17940,11 +17959,11 @@
       <c r="BR17" s="3"/>
     </row>
     <row r="18" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A18" s="10">
+      <c r="A18" s="11">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="12" t="s">
         <v>227</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -17953,23 +17972,23 @@
       <c r="D18" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="26">
         <f>+[33]Main!$H$2</f>
         <v>12.11</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="26">
         <f>+[33]Main!$H$4*FX!C3</f>
         <v>1601.5717199999999</v>
       </c>
-      <c r="G18" s="25">
+      <c r="G18" s="26">
         <f>+([33]Main!$H$6-[33]Main!$H$5)*FX!C3</f>
         <v>1343.7380000000003</v>
       </c>
-      <c r="H18" s="25">
+      <c r="H18" s="26">
         <f t="shared" si="0"/>
         <v>2945.3097200000002</v>
       </c>
-      <c r="I18" s="14" t="s">
+      <c r="I18" s="15" t="s">
         <v>246</v>
       </c>
       <c r="J18" s="3"/>
@@ -18035,15 +18054,15 @@
       <c r="BR18" s="3"/>
     </row>
     <row r="19" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A19" s="10"/>
+      <c r="A19" s="11"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="14"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="15"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
@@ -18107,17 +18126,17 @@
       <c r="BR19" s="3"/>
     </row>
     <row r="20" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
-      <c r="B20" s="24" t="s">
+      <c r="A20" s="11"/>
+      <c r="B20" s="25" t="s">
         <v>297</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="14"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="15"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
@@ -18181,8 +18200,8 @@
       <c r="BR20" s="3"/>
     </row>
     <row r="21" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A21" s="10"/>
-      <c r="B21" s="11" t="s">
+      <c r="A21" s="11"/>
+      <c r="B21" s="12" t="s">
         <v>298</v>
       </c>
       <c r="C21" s="3" t="s">
@@ -18191,23 +18210,23 @@
       <c r="D21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="26">
         <f>+[34]Main!$J$2</f>
         <v>21.7</v>
       </c>
-      <c r="F21" s="25">
+      <c r="F21" s="26">
         <f>+[34]Main!$J$4</f>
         <v>9701.7223876999997</v>
       </c>
-      <c r="G21" s="25">
+      <c r="G21" s="26">
         <f>+[34]Main!$J$6-[34]Main!$J$5</f>
         <v>-4758</v>
       </c>
-      <c r="H21" s="25">
+      <c r="H21" s="26">
         <f>+F21+G21</f>
         <v>4943.7223876999997</v>
       </c>
-      <c r="I21" s="14" t="s">
+      <c r="I21" s="15" t="s">
         <v>246</v>
       </c>
       <c r="J21" s="3"/>
@@ -18273,15 +18292,15 @@
       <c r="BR21" s="3"/>
     </row>
     <row r="22" spans="1:70" x14ac:dyDescent="0.25">
-      <c r="A22" s="10"/>
+      <c r="A22" s="11"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="14"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="15"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
@@ -27370,15 +27389,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{987B8BB7-A6AF-4603-BAFA-28C123C35E62}">
   <dimension ref="A1:Y93"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.42578125" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.42578125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>471</v>
       </c>
       <c r="B1" s="3"/>
@@ -27436,39 +27456,39 @@
       <c r="Y2" s="3"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="27"/>
-      <c r="N3" s="27"/>
-      <c r="O3" s="23"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="24"/>
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
@@ -27481,10 +27501,10 @@
       <c r="Y3" s="3"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="10">
+      <c r="A4" s="11">
         <v>1</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="12" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -27493,28 +27513,28 @@
       <c r="D4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="14">
         <f>+[3]Main!$I$2</f>
         <v>34.549999999999997</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="14">
         <f>+[3]Main!$I$4</f>
         <v>129621.37067784999</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="14">
         <f>+[3]Main!$I$6-[3]Main!$I$5</f>
         <v>90529</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="14">
         <f>+F4+G4</f>
         <v>220150.37067784998</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
@@ -27530,7 +27550,7 @@
       <c r="Y4" s="3"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
+      <c r="A5" s="11">
         <f>+A4+1</f>
         <v>2</v>
       </c>
@@ -27543,14 +27563,14 @@
       <c r="D5" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
@@ -27566,7 +27586,7 @@
       <c r="Y5" s="3"/>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A6" s="10">
+      <c r="A6" s="11">
         <f t="shared" ref="A6:A69" si="0">+A5+1</f>
         <v>3</v>
       </c>
@@ -27579,14 +27599,14 @@
       <c r="D6" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
@@ -27602,11 +27622,11 @@
       <c r="Y6" s="3"/>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
+      <c r="A7" s="11">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="12" t="s">
         <v>307</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -27615,28 +27635,28 @@
       <c r="D7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="14">
         <f>+[14]Main!$H$2</f>
         <v>11.87</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="14">
         <f>+[14]Main!$H$4</f>
         <v>29387.416987339999</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="14">
         <f>+[14]Main!$H$6-[14]Main!$H$5</f>
         <v>29744</v>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="14">
         <f>+F7+G7</f>
         <v>59131.416987339995</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
@@ -27652,11 +27672,11 @@
       <c r="Y7" s="3"/>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A8" s="10">
+      <c r="A8" s="11">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="12" t="s">
         <v>308</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -27665,28 +27685,28 @@
       <c r="D8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="14">
         <f>+[35]Main!$I$2</f>
         <v>50.5</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="14">
         <f>+[35]Main!$I$4</f>
         <v>22898.106829</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="14">
         <f>+[35]Main!$I$6-[35]Main!$I$5</f>
         <v>3878</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="14">
         <f>+F8+G8</f>
         <v>26776.106829</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
@@ -27702,7 +27722,7 @@
       <c r="Y8" s="3"/>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+      <c r="A9" s="11">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
@@ -27715,14 +27735,14 @@
       <c r="D9" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
@@ -27738,7 +27758,7 @@
       <c r="Y9" s="3"/>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A10" s="10">
+      <c r="A10" s="11">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -27751,14 +27771,14 @@
       <c r="D10" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
@@ -27774,11 +27794,11 @@
       <c r="Y10" s="3"/>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
+      <c r="A11" s="11">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="12" t="s">
         <v>313</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -27787,28 +27807,28 @@
       <c r="D11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="14">
         <f>+[36]Main!$I$2</f>
         <v>30.44</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="14">
         <f>+[36]Main!$I$4</f>
         <v>17310.539416759999</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="14">
         <f>+[36]Main!$I$6-[36]Main!$I$5</f>
         <v>1122</v>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="14">
         <f>+F11+G11</f>
         <v>18432.539416759999</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
@@ -27824,7 +27844,7 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
+      <c r="A12" s="11">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
@@ -27837,14 +27857,14 @@
       <c r="D12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
@@ -27860,11 +27880,11 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
+      <c r="A13" s="11">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="12" t="s">
         <v>317</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -27873,28 +27893,28 @@
       <c r="D13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="14">
         <f>+[37]Main!$H$2</f>
         <v>41.21</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="14">
         <f>+[37]Main!$H$4</f>
         <v>8939.4565020800001</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="14">
         <f>+[37]Main!$H$6-[37]Main!$H$5</f>
         <v>-663.44470000000001</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="14">
         <f>+F13+G13</f>
         <v>8276.0118020800001</v>
       </c>
-      <c r="I13" s="14" t="s">
+      <c r="I13" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
@@ -27910,11 +27930,11 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="10">
+      <c r="A14" s="11">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="12" t="s">
         <v>319</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -27923,28 +27943,28 @@
       <c r="D14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="14">
         <f>+[38]Main!$H$2</f>
         <v>52.09</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="14">
         <f>+[38]Main!$H$4</f>
         <v>8540.3870921399994</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="14">
         <f>+[38]Main!$H$6-[38]Main!$H$5</f>
         <v>-492.94499999999999</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="14">
         <f>+F14+G14</f>
         <v>8047.4420921399997</v>
       </c>
-      <c r="I14" s="14" t="s">
+      <c r="I14" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
@@ -27960,11 +27980,11 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
+      <c r="A15" s="11">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="12" t="s">
         <v>321</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -27973,28 +27993,28 @@
       <c r="D15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="14">
         <f>+[22]Main!$I$2</f>
         <v>13.8</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="14">
         <f>+[22]Main!$I$4</f>
         <v>9315</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="14">
         <f>+[22]Main!$I$6-[22]Main!$I$5</f>
         <v>11775</v>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="14">
         <f>+F15+G15</f>
         <v>21090</v>
       </c>
-      <c r="I15" s="14" t="s">
+      <c r="I15" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
@@ -28010,7 +28030,7 @@
       <c r="Y15" s="3"/>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="10">
+      <c r="A16" s="11">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
@@ -28023,10 +28043,10 @@
       <c r="D16" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -28046,11 +28066,11 @@
       <c r="Y16" s="3"/>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A17" s="10">
+      <c r="A17" s="11">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="12" t="s">
         <v>325</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -28059,23 +28079,23 @@
       <c r="D17" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="14">
         <f>+[39]Main!$K$2</f>
         <v>78.55</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="14">
         <f>+[39]Main!$K$4</f>
         <v>7215.2325581999994</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="14">
         <f>+[39]Main!$K$6-[39]Main!$K$5</f>
         <v>1417</v>
       </c>
-      <c r="H17" s="13">
+      <c r="H17" s="14">
         <f>+F17+G17</f>
         <v>8632.2325581999994</v>
       </c>
-      <c r="I17" s="14" t="s">
+      <c r="I17" s="15" t="s">
         <v>261</v>
       </c>
       <c r="J17" s="3"/>
@@ -28096,7 +28116,7 @@
       <c r="Y17" s="3"/>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A18" s="10">
+      <c r="A18" s="11">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -28109,10 +28129,10 @@
       <c r="D18" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
@@ -28132,7 +28152,7 @@
       <c r="Y18" s="3"/>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A19" s="10">
+      <c r="A19" s="11">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -28145,10 +28165,10 @@
       <c r="D19" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
@@ -28168,7 +28188,7 @@
       <c r="Y19" s="3"/>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A20" s="10">
+      <c r="A20" s="11">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
@@ -28181,10 +28201,10 @@
       <c r="D20" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
@@ -28204,7 +28224,7 @@
       <c r="Y20" s="3"/>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A21" s="10">
+      <c r="A21" s="11">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
@@ -28217,10 +28237,10 @@
       <c r="D21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
@@ -28240,7 +28260,7 @@
       <c r="Y21" s="3"/>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A22" s="10">
+      <c r="A22" s="11">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
@@ -28253,10 +28273,10 @@
       <c r="D22" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
@@ -28276,7 +28296,7 @@
       <c r="Y22" s="3"/>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A23" s="10">
+      <c r="A23" s="11">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -28289,10 +28309,10 @@
       <c r="D23" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
@@ -28312,7 +28332,7 @@
       <c r="Y23" s="3"/>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A24" s="10">
+      <c r="A24" s="11">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
@@ -28325,10 +28345,10 @@
       <c r="D24" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
@@ -28348,7 +28368,7 @@
       <c r="Y24" s="3"/>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A25" s="10">
+      <c r="A25" s="11">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
@@ -28361,10 +28381,10 @@
       <c r="D25" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
@@ -28384,7 +28404,7 @@
       <c r="Y25" s="3"/>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A26" s="10">
+      <c r="A26" s="11">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
@@ -28397,10 +28417,10 @@
       <c r="D26" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
@@ -28420,7 +28440,7 @@
       <c r="Y26" s="3"/>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A27" s="10">
+      <c r="A27" s="11">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
@@ -28433,10 +28453,10 @@
       <c r="D27" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
@@ -28456,7 +28476,7 @@
       <c r="Y27" s="3"/>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A28" s="10">
+      <c r="A28" s="11">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
@@ -28469,10 +28489,10 @@
       <c r="D28" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
@@ -28492,7 +28512,7 @@
       <c r="Y28" s="3"/>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A29" s="10">
+      <c r="A29" s="11">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
@@ -28505,10 +28525,10 @@
       <c r="D29" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
@@ -28528,7 +28548,7 @@
       <c r="Y29" s="3"/>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A30" s="10">
+      <c r="A30" s="11">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
@@ -28541,10 +28561,10 @@
       <c r="D30" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
@@ -28564,7 +28584,7 @@
       <c r="Y30" s="3"/>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A31" s="10">
+      <c r="A31" s="11">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
@@ -28577,10 +28597,10 @@
       <c r="D31" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
@@ -28600,7 +28620,7 @@
       <c r="Y31" s="3"/>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A32" s="10">
+      <c r="A32" s="11">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
@@ -28613,10 +28633,10 @@
       <c r="D32" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
@@ -28636,7 +28656,7 @@
       <c r="Y32" s="3"/>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A33" s="10">
+      <c r="A33" s="11">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -28649,10 +28669,10 @@
       <c r="D33" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
@@ -28672,7 +28692,7 @@
       <c r="Y33" s="3"/>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A34" s="10">
+      <c r="A34" s="11">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
@@ -28685,10 +28705,10 @@
       <c r="D34" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
@@ -28708,7 +28728,7 @@
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A35" s="10">
+      <c r="A35" s="11">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
@@ -28717,10 +28737,10 @@
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
       <c r="K35" s="3"/>
@@ -28740,7 +28760,7 @@
       <c r="Y35" s="3"/>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A36" s="10">
+      <c r="A36" s="11">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
@@ -28753,10 +28773,10 @@
       <c r="D36" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
@@ -28776,7 +28796,7 @@
       <c r="Y36" s="3"/>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A37" s="10">
+      <c r="A37" s="11">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
@@ -28789,10 +28809,10 @@
       <c r="D37" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
@@ -28812,7 +28832,7 @@
       <c r="Y37" s="3"/>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A38" s="10">
+      <c r="A38" s="11">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
@@ -28825,10 +28845,10 @@
       <c r="D38" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
@@ -28848,7 +28868,7 @@
       <c r="Y38" s="3"/>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A39" s="10">
+      <c r="A39" s="11">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
@@ -28861,10 +28881,10 @@
       <c r="D39" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
@@ -28884,7 +28904,7 @@
       <c r="Y39" s="3"/>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A40" s="10">
+      <c r="A40" s="11">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
@@ -28897,10 +28917,10 @@
       <c r="D40" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
@@ -28920,7 +28940,7 @@
       <c r="Y40" s="3"/>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A41" s="10">
+      <c r="A41" s="11">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
@@ -28933,10 +28953,10 @@
       <c r="D41" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
@@ -28956,7 +28976,7 @@
       <c r="Y41" s="3"/>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A42" s="10">
+      <c r="A42" s="11">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
@@ -28969,10 +28989,10 @@
       <c r="D42" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
@@ -28992,7 +29012,7 @@
       <c r="Y42" s="3"/>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A43" s="10">
+      <c r="A43" s="11">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
@@ -29005,10 +29025,10 @@
       <c r="D43" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
       <c r="I43" s="3"/>
       <c r="J43" s="3"/>
       <c r="K43" s="3"/>
@@ -29028,7 +29048,7 @@
       <c r="Y43" s="3"/>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A44" s="10">
+      <c r="A44" s="11">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
@@ -29041,10 +29061,10 @@
       <c r="D44" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3"/>
       <c r="K44" s="3"/>
@@ -29064,7 +29084,7 @@
       <c r="Y44" s="3"/>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A45" s="10">
+      <c r="A45" s="11">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
@@ -29077,10 +29097,10 @@
       <c r="D45" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14"/>
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
       <c r="K45" s="3"/>
@@ -29100,7 +29120,7 @@
       <c r="Y45" s="3"/>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A46" s="10">
+      <c r="A46" s="11">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
@@ -29113,10 +29133,10 @@
       <c r="D46" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
@@ -29136,7 +29156,7 @@
       <c r="Y46" s="3"/>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A47" s="10">
+      <c r="A47" s="11">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
@@ -29149,10 +29169,10 @@
       <c r="D47" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
       <c r="I47" s="3"/>
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
@@ -29172,7 +29192,7 @@
       <c r="Y47" s="3"/>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A48" s="10">
+      <c r="A48" s="11">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
@@ -29185,10 +29205,10 @@
       <c r="D48" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14"/>
       <c r="I48" s="3"/>
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
@@ -29208,7 +29228,7 @@
       <c r="Y48" s="3"/>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A49" s="10">
+      <c r="A49" s="11">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
@@ -29221,10 +29241,10 @@
       <c r="D49" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
@@ -29244,7 +29264,7 @@
       <c r="Y49" s="3"/>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A50" s="10">
+      <c r="A50" s="11">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
@@ -29257,10 +29277,10 @@
       <c r="D50" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
+      <c r="E50" s="14"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14"/>
+      <c r="H50" s="14"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
@@ -29280,7 +29300,7 @@
       <c r="Y50" s="3"/>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A51" s="10">
+      <c r="A51" s="11">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
@@ -29293,10 +29313,10 @@
       <c r="D51" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
+      <c r="H51" s="14"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
@@ -29316,7 +29336,7 @@
       <c r="Y51" s="3"/>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A52" s="10">
+      <c r="A52" s="11">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
@@ -29329,10 +29349,10 @@
       <c r="D52" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
+      <c r="H52" s="14"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
@@ -29352,7 +29372,7 @@
       <c r="Y52" s="3"/>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A53" s="10">
+      <c r="A53" s="11">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
@@ -29365,10 +29385,10 @@
       <c r="D53" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
+      <c r="H53" s="14"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
@@ -29388,7 +29408,7 @@
       <c r="Y53" s="3"/>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A54" s="10">
+      <c r="A54" s="11">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
@@ -29401,10 +29421,10 @@
       <c r="D54" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
+      <c r="G54" s="14"/>
+      <c r="H54" s="14"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
@@ -29424,7 +29444,7 @@
       <c r="Y54" s="3"/>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A55" s="10">
+      <c r="A55" s="11">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
@@ -29437,10 +29457,10 @@
       <c r="D55" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
+      <c r="H55" s="14"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
@@ -29460,7 +29480,7 @@
       <c r="Y55" s="3"/>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A56" s="10">
+      <c r="A56" s="11">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
@@ -29473,10 +29493,10 @@
       <c r="D56" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
@@ -29496,7 +29516,7 @@
       <c r="Y56" s="3"/>
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A57" s="10">
+      <c r="A57" s="11">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
@@ -29509,10 +29529,10 @@
       <c r="D57" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
+      <c r="H57" s="14"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3"/>
       <c r="K57" s="3"/>
@@ -29532,7 +29552,7 @@
       <c r="Y57" s="3"/>
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A58" s="10">
+      <c r="A58" s="11">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
@@ -29545,10 +29565,10 @@
       <c r="D58" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
+      <c r="E58" s="14"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14"/>
+      <c r="H58" s="14"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
@@ -29568,7 +29588,7 @@
       <c r="Y58" s="3"/>
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A59" s="10">
+      <c r="A59" s="11">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
@@ -29581,10 +29601,10 @@
       <c r="D59" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3"/>
       <c r="K59" s="3"/>
@@ -29604,7 +29624,7 @@
       <c r="Y59" s="3"/>
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A60" s="10">
+      <c r="A60" s="11">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
@@ -29617,10 +29637,10 @@
       <c r="D60" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="14"/>
+      <c r="H60" s="14"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3"/>
       <c r="K60" s="3"/>
@@ -29640,7 +29660,7 @@
       <c r="Y60" s="3"/>
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A61" s="10">
+      <c r="A61" s="11">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
@@ -29653,10 +29673,10 @@
       <c r="D61" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E61" s="13"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="13"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
+      <c r="H61" s="14"/>
       <c r="I61" s="3"/>
       <c r="J61" s="3"/>
       <c r="K61" s="3"/>
@@ -29676,7 +29696,7 @@
       <c r="Y61" s="3"/>
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A62" s="10">
+      <c r="A62" s="11">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
@@ -29689,10 +29709,10 @@
       <c r="D62" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E62" s="13"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="13"/>
-      <c r="H62" s="13"/>
+      <c r="E62" s="14"/>
+      <c r="F62" s="14"/>
+      <c r="G62" s="14"/>
+      <c r="H62" s="14"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
@@ -29712,7 +29732,7 @@
       <c r="Y62" s="3"/>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A63" s="10">
+      <c r="A63" s="11">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
@@ -29725,10 +29745,10 @@
       <c r="D63" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E63" s="13"/>
-      <c r="F63" s="13"/>
-      <c r="G63" s="13"/>
-      <c r="H63" s="13"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="14"/>
+      <c r="H63" s="14"/>
       <c r="I63" s="3"/>
       <c r="J63" s="3"/>
       <c r="K63" s="3"/>
@@ -29748,7 +29768,7 @@
       <c r="Y63" s="3"/>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A64" s="10">
+      <c r="A64" s="11">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
@@ -29761,10 +29781,10 @@
       <c r="D64" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
-      <c r="H64" s="13"/>
+      <c r="E64" s="14"/>
+      <c r="F64" s="14"/>
+      <c r="G64" s="14"/>
+      <c r="H64" s="14"/>
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
       <c r="K64" s="3"/>
@@ -29784,7 +29804,7 @@
       <c r="Y64" s="3"/>
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A65" s="10">
+      <c r="A65" s="11">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
@@ -29797,10 +29817,10 @@
       <c r="D65" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
-      <c r="H65" s="13"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14"/>
+      <c r="H65" s="14"/>
       <c r="I65" s="3"/>
       <c r="J65" s="3"/>
       <c r="K65" s="3"/>
@@ -29820,7 +29840,7 @@
       <c r="Y65" s="3"/>
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A66" s="10">
+      <c r="A66" s="11">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
@@ -29833,10 +29853,10 @@
       <c r="D66" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14"/>
+      <c r="H66" s="14"/>
       <c r="I66" s="3"/>
       <c r="J66" s="3"/>
       <c r="K66" s="3"/>
@@ -29856,7 +29876,7 @@
       <c r="Y66" s="3"/>
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A67" s="10">
+      <c r="A67" s="11">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
@@ -29869,10 +29889,10 @@
       <c r="D67" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
-      <c r="H67" s="13"/>
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14"/>
+      <c r="H67" s="14"/>
       <c r="I67" s="3"/>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
@@ -29892,7 +29912,7 @@
       <c r="Y67" s="3"/>
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A68" s="10">
+      <c r="A68" s="11">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
@@ -29905,10 +29925,10 @@
       <c r="D68" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
+      <c r="H68" s="14"/>
       <c r="I68" s="3"/>
       <c r="J68" s="3"/>
       <c r="K68" s="3"/>
@@ -29928,7 +29948,7 @@
       <c r="Y68" s="3"/>
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A69" s="10">
+      <c r="A69" s="11">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
@@ -29941,10 +29961,10 @@
       <c r="D69" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
+      <c r="E69" s="14"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="14"/>
+      <c r="H69" s="14"/>
       <c r="I69" s="3"/>
       <c r="J69" s="3"/>
       <c r="K69" s="3"/>
@@ -29964,7 +29984,7 @@
       <c r="Y69" s="3"/>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A70" s="10">
+      <c r="A70" s="11">
         <f t="shared" ref="A70:A93" si="1">+A69+1</f>
         <v>67</v>
       </c>
@@ -29977,10 +29997,10 @@
       <c r="D70" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
+      <c r="E70" s="14"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="14"/>
+      <c r="H70" s="14"/>
       <c r="I70" s="3"/>
       <c r="J70" s="3"/>
       <c r="K70" s="3"/>
@@ -30000,7 +30020,7 @@
       <c r="Y70" s="3"/>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A71" s="10">
+      <c r="A71" s="11">
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
@@ -30013,10 +30033,10 @@
       <c r="D71" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14"/>
       <c r="I71" s="3"/>
       <c r="J71" s="3"/>
       <c r="K71" s="3"/>
@@ -30036,7 +30056,7 @@
       <c r="Y71" s="3"/>
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A72" s="10">
+      <c r="A72" s="11">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
@@ -30049,10 +30069,10 @@
       <c r="D72" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14"/>
+      <c r="H72" s="14"/>
       <c r="I72" s="3"/>
       <c r="J72" s="3"/>
       <c r="K72" s="3"/>
@@ -30072,7 +30092,7 @@
       <c r="Y72" s="3"/>
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A73" s="10">
+      <c r="A73" s="11">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
@@ -30085,10 +30105,10 @@
       <c r="D73" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
+      <c r="H73" s="14"/>
       <c r="I73" s="3"/>
       <c r="J73" s="3"/>
       <c r="K73" s="3"/>
@@ -30108,7 +30128,7 @@
       <c r="Y73" s="3"/>
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A74" s="10">
+      <c r="A74" s="11">
         <f t="shared" si="1"/>
         <v>71</v>
       </c>
@@ -30121,10 +30141,10 @@
       <c r="D74" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="14"/>
+      <c r="H74" s="14"/>
       <c r="I74" s="3"/>
       <c r="J74" s="3"/>
       <c r="K74" s="3"/>
@@ -30144,7 +30164,7 @@
       <c r="Y74" s="3"/>
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A75" s="10">
+      <c r="A75" s="11">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
@@ -30157,10 +30177,10 @@
       <c r="D75" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E75" s="13"/>
-      <c r="F75" s="13"/>
-      <c r="G75" s="13"/>
-      <c r="H75" s="13"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="14"/>
+      <c r="H75" s="14"/>
       <c r="I75" s="3"/>
       <c r="J75" s="3"/>
       <c r="K75" s="3"/>
@@ -30180,7 +30200,7 @@
       <c r="Y75" s="3"/>
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A76" s="10">
+      <c r="A76" s="11">
         <f t="shared" si="1"/>
         <v>73</v>
       </c>
@@ -30193,10 +30213,10 @@
       <c r="D76" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E76" s="13"/>
-      <c r="F76" s="13"/>
-      <c r="G76" s="13"/>
-      <c r="H76" s="13"/>
+      <c r="E76" s="14"/>
+      <c r="F76" s="14"/>
+      <c r="G76" s="14"/>
+      <c r="H76" s="14"/>
       <c r="I76" s="3"/>
       <c r="J76" s="3"/>
       <c r="K76" s="3"/>
@@ -30216,7 +30236,7 @@
       <c r="Y76" s="3"/>
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A77" s="10">
+      <c r="A77" s="11">
         <f t="shared" si="1"/>
         <v>74</v>
       </c>
@@ -30229,10 +30249,10 @@
       <c r="D77" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="E77" s="13"/>
-      <c r="F77" s="13"/>
-      <c r="G77" s="13"/>
-      <c r="H77" s="13"/>
+      <c r="E77" s="14"/>
+      <c r="F77" s="14"/>
+      <c r="G77" s="14"/>
+      <c r="H77" s="14"/>
       <c r="I77" s="3"/>
       <c r="J77" s="3"/>
       <c r="K77" s="3"/>
@@ -30252,11 +30272,11 @@
       <c r="Y77" s="3"/>
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A78" s="10">
+      <c r="A78" s="11">
         <f t="shared" si="1"/>
         <v>75</v>
       </c>
-      <c r="B78" s="11" t="s">
+      <c r="B78" s="12" t="s">
         <v>449</v>
       </c>
       <c r="C78" s="3" t="s">
@@ -30265,28 +30285,28 @@
       <c r="D78" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E78" s="13">
+      <c r="E78" s="14">
         <f>+[40]Main!$H$2</f>
         <v>1.2</v>
       </c>
-      <c r="F78" s="13">
+      <c r="F78" s="14">
         <f>+[40]Main!$H$4</f>
         <v>112.4964828</v>
       </c>
-      <c r="G78" s="13">
+      <c r="G78" s="14">
         <f>+[40]Main!$H$6-[40]Main!$H$5</f>
         <v>145.571</v>
       </c>
-      <c r="H78" s="13">
+      <c r="H78" s="14">
         <f>+F78+G78</f>
         <v>258.06748279999999</v>
       </c>
-      <c r="I78" s="14" t="s">
+      <c r="I78" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="J78" s="14"/>
-      <c r="K78" s="14"/>
-      <c r="L78" s="14"/>
+      <c r="J78" s="15"/>
+      <c r="K78" s="15"/>
+      <c r="L78" s="15"/>
       <c r="M78" s="3"/>
       <c r="N78" s="3"/>
       <c r="O78" s="3"/>
@@ -30302,7 +30322,7 @@
       <c r="Y78" s="3"/>
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A79" s="10">
+      <c r="A79" s="11">
         <f t="shared" si="1"/>
         <v>76</v>
       </c>
@@ -30315,10 +30335,10 @@
       <c r="D79" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E79" s="13"/>
-      <c r="F79" s="13"/>
-      <c r="G79" s="13"/>
-      <c r="H79" s="13"/>
+      <c r="E79" s="14"/>
+      <c r="F79" s="14"/>
+      <c r="G79" s="14"/>
+      <c r="H79" s="14"/>
       <c r="I79" s="3"/>
       <c r="J79" s="3"/>
       <c r="K79" s="3"/>
@@ -30338,7 +30358,7 @@
       <c r="Y79" s="3"/>
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A80" s="10">
+      <c r="A80" s="11">
         <f t="shared" si="1"/>
         <v>77</v>
       </c>
@@ -30351,10 +30371,10 @@
       <c r="D80" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="E80" s="13"/>
-      <c r="F80" s="13"/>
-      <c r="G80" s="13"/>
-      <c r="H80" s="13"/>
+      <c r="E80" s="14"/>
+      <c r="F80" s="14"/>
+      <c r="G80" s="14"/>
+      <c r="H80" s="14"/>
       <c r="I80" s="3"/>
       <c r="J80" s="3"/>
       <c r="K80" s="3"/>
@@ -30374,7 +30394,7 @@
       <c r="Y80" s="3"/>
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A81" s="10">
+      <c r="A81" s="11">
         <f t="shared" si="1"/>
         <v>78</v>
       </c>
@@ -30387,10 +30407,10 @@
       <c r="D81" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="E81" s="13"/>
-      <c r="F81" s="13"/>
-      <c r="G81" s="13"/>
-      <c r="H81" s="13"/>
+      <c r="E81" s="14"/>
+      <c r="F81" s="14"/>
+      <c r="G81" s="14"/>
+      <c r="H81" s="14"/>
       <c r="I81" s="3"/>
       <c r="J81" s="3"/>
       <c r="K81" s="3"/>
@@ -30410,7 +30430,7 @@
       <c r="Y81" s="3"/>
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A82" s="10">
+      <c r="A82" s="11">
         <f t="shared" si="1"/>
         <v>79</v>
       </c>
@@ -30423,10 +30443,10 @@
       <c r="D82" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E82" s="13"/>
-      <c r="F82" s="13"/>
-      <c r="G82" s="13"/>
-      <c r="H82" s="13"/>
+      <c r="E82" s="14"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="14"/>
+      <c r="H82" s="14"/>
       <c r="I82" s="3"/>
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
@@ -30446,7 +30466,7 @@
       <c r="Y82" s="3"/>
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A83" s="10">
+      <c r="A83" s="11">
         <f t="shared" si="1"/>
         <v>80</v>
       </c>
@@ -30459,10 +30479,10 @@
       <c r="D83" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="E83" s="13"/>
-      <c r="F83" s="13"/>
-      <c r="G83" s="13"/>
-      <c r="H83" s="13"/>
+      <c r="E83" s="14"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="14"/>
+      <c r="H83" s="14"/>
       <c r="I83" s="3"/>
       <c r="J83" s="3"/>
       <c r="K83" s="3"/>
@@ -30482,7 +30502,7 @@
       <c r="Y83" s="3"/>
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A84" s="10">
+      <c r="A84" s="11">
         <f t="shared" si="1"/>
         <v>81</v>
       </c>
@@ -30495,10 +30515,10 @@
       <c r="D84" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E84" s="13"/>
-      <c r="F84" s="13"/>
-      <c r="G84" s="13"/>
-      <c r="H84" s="13"/>
+      <c r="E84" s="14"/>
+      <c r="F84" s="14"/>
+      <c r="G84" s="14"/>
+      <c r="H84" s="14"/>
       <c r="I84" s="3"/>
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
@@ -30518,7 +30538,7 @@
       <c r="Y84" s="3"/>
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A85" s="10">
+      <c r="A85" s="11">
         <f t="shared" si="1"/>
         <v>82</v>
       </c>
@@ -30531,10 +30551,10 @@
       <c r="D85" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E85" s="13"/>
-      <c r="F85" s="13"/>
-      <c r="G85" s="13"/>
-      <c r="H85" s="13"/>
+      <c r="E85" s="14"/>
+      <c r="F85" s="14"/>
+      <c r="G85" s="14"/>
+      <c r="H85" s="14"/>
       <c r="I85" s="3"/>
       <c r="J85" s="3"/>
       <c r="K85" s="3"/>
@@ -30554,7 +30574,7 @@
       <c r="Y85" s="3"/>
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A86" s="10">
+      <c r="A86" s="11">
         <f t="shared" si="1"/>
         <v>83</v>
       </c>
@@ -30563,10 +30583,10 @@
       </c>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
-      <c r="E86" s="13"/>
-      <c r="F86" s="13"/>
-      <c r="G86" s="13"/>
-      <c r="H86" s="13"/>
+      <c r="E86" s="14"/>
+      <c r="F86" s="14"/>
+      <c r="G86" s="14"/>
+      <c r="H86" s="14"/>
       <c r="I86" s="3"/>
       <c r="J86" s="3"/>
       <c r="K86" s="3"/>
@@ -30586,7 +30606,7 @@
       <c r="Y86" s="3"/>
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A87" s="10">
+      <c r="A87" s="11">
         <f t="shared" si="1"/>
         <v>84</v>
       </c>
@@ -30599,10 +30619,10 @@
       <c r="D87" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E87" s="13"/>
-      <c r="F87" s="13"/>
-      <c r="G87" s="13"/>
-      <c r="H87" s="13"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="H87" s="14"/>
       <c r="I87" s="3"/>
       <c r="J87" s="3"/>
       <c r="K87" s="3"/>
@@ -30622,7 +30642,7 @@
       <c r="Y87" s="3"/>
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A88" s="10">
+      <c r="A88" s="11">
         <f t="shared" si="1"/>
         <v>85</v>
       </c>
@@ -30635,10 +30655,10 @@
       <c r="D88" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="E88" s="13"/>
-      <c r="F88" s="13"/>
-      <c r="G88" s="13"/>
-      <c r="H88" s="13"/>
+      <c r="E88" s="14"/>
+      <c r="F88" s="14"/>
+      <c r="G88" s="14"/>
+      <c r="H88" s="14"/>
       <c r="I88" s="3"/>
       <c r="J88" s="3"/>
       <c r="K88" s="3"/>
@@ -30658,17 +30678,17 @@
       <c r="Y88" s="3"/>
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A89" s="10">
+      <c r="A89" s="11">
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
-      <c r="E89" s="13"/>
-      <c r="F89" s="13"/>
-      <c r="G89" s="13"/>
-      <c r="H89" s="13"/>
+      <c r="E89" s="14"/>
+      <c r="F89" s="14"/>
+      <c r="G89" s="14"/>
+      <c r="H89" s="14"/>
       <c r="I89" s="3"/>
       <c r="J89" s="3"/>
       <c r="K89" s="3"/>
@@ -30688,17 +30708,17 @@
       <c r="Y89" s="3"/>
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A90" s="10">
+      <c r="A90" s="11">
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
-      <c r="E90" s="13"/>
-      <c r="F90" s="13"/>
-      <c r="G90" s="13"/>
-      <c r="H90" s="13"/>
+      <c r="E90" s="14"/>
+      <c r="F90" s="14"/>
+      <c r="G90" s="14"/>
+      <c r="H90" s="14"/>
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
@@ -30718,17 +30738,17 @@
       <c r="Y90" s="3"/>
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A91" s="10">
+      <c r="A91" s="11">
         <f t="shared" si="1"/>
         <v>88</v>
       </c>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
-      <c r="E91" s="13"/>
-      <c r="F91" s="13"/>
-      <c r="G91" s="13"/>
-      <c r="H91" s="13"/>
+      <c r="E91" s="14"/>
+      <c r="F91" s="14"/>
+      <c r="G91" s="14"/>
+      <c r="H91" s="14"/>
       <c r="I91" s="3"/>
       <c r="J91" s="3"/>
       <c r="K91" s="3"/>
@@ -30748,17 +30768,17 @@
       <c r="Y91" s="3"/>
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A92" s="10">
+      <c r="A92" s="11">
         <f t="shared" si="1"/>
         <v>89</v>
       </c>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
-      <c r="E92" s="13"/>
-      <c r="F92" s="13"/>
-      <c r="G92" s="13"/>
-      <c r="H92" s="13"/>
+      <c r="E92" s="14"/>
+      <c r="F92" s="14"/>
+      <c r="G92" s="14"/>
+      <c r="H92" s="14"/>
       <c r="I92" s="3"/>
       <c r="J92" s="3"/>
       <c r="K92" s="3"/>
@@ -30778,17 +30798,17 @@
       <c r="Y92" s="3"/>
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A93" s="10">
+      <c r="A93" s="11">
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
-      <c r="E93" s="13"/>
-      <c r="F93" s="13"/>
-      <c r="G93" s="13"/>
-      <c r="H93" s="13"/>
+      <c r="E93" s="14"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
+      <c r="H93" s="14"/>
       <c r="I93" s="3"/>
       <c r="J93" s="3"/>
       <c r="K93" s="3"/>
@@ -30834,10 +30854,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
@@ -30846,8 +30866,8 @@
       <c r="C2" s="3">
         <v>6.4000000000000003E-3</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
@@ -30856,8 +30876,8 @@
       <c r="C3" s="3">
         <v>1.03</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
@@ -30866,8 +30886,8 @@
       <c r="C4" s="3">
         <v>1.24</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
@@ -30876,8 +30896,8 @@
       <c r="C5" s="3">
         <v>0.63</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
@@ -30886,44 +30906,44 @@
       <c r="C6" s="3">
         <v>0.14000000000000001</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Entertainment.xlsx
+++ b/Entertainment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C28629A-FC0E-4A54-95A6-440A3A467B10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31785A62-21DC-44CD-89DA-4D626DF23AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
+    <workbookView xWindow="225" yWindow="1950" windowWidth="38175" windowHeight="15240" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1532,13 +1532,25 @@
     <numFmt numFmtId="165" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1665,56 +1677,62 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2387,26 +2405,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="G2">
-            <v>18.07</v>
+            <v>18.649999999999999</v>
           </cell>
         </row>
         <row r="4">
           <cell r="G4">
-            <v>6087.7829999999994</v>
+            <v>6195.53</v>
           </cell>
         </row>
         <row r="5">
           <cell r="G5">
-            <v>723.53200000000004</v>
+            <v>870.452</v>
           </cell>
         </row>
         <row r="6">
           <cell r="G6">
-            <v>2333.2600000000002</v>
+            <v>2336.5330000000004</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2623,22 +2641,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>34.549999999999997</v>
+            <v>33.840000000000003</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>129621.37067784999</v>
+            <v>124944.26802768001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>8593</v>
+            <v>9687</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>99122</v>
+            <v>101528</v>
           </cell>
         </row>
       </sheetData>
@@ -3830,8 +3848,8 @@
         <f>+F4+G4</f>
         <v>538945.61542000005</v>
       </c>
-      <c r="I4" s="15" t="s">
-        <v>261</v>
+      <c r="I4" s="29" t="s">
+        <v>474</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -3962,22 +3980,22 @@
       </c>
       <c r="E6" s="13">
         <f>+[3]Main!$I$2</f>
-        <v>34.549999999999997</v>
+        <v>33.840000000000003</v>
       </c>
       <c r="F6" s="14">
         <f>+[3]Main!$I$4</f>
-        <v>129621.37067784999</v>
+        <v>124944.26802768001</v>
       </c>
       <c r="G6" s="14">
         <f>+[3]Main!$I$6-[3]Main!$I$5</f>
-        <v>90529</v>
+        <v>91841</v>
       </c>
       <c r="H6" s="14">
         <f t="shared" si="0"/>
-        <v>220150.37067784998</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>261</v>
+        <v>216785.26802767999</v>
+      </c>
+      <c r="I6" s="30" t="s">
+        <v>474</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -6698,19 +6716,19 @@
       </c>
       <c r="E49" s="3">
         <f>+[24]Main!$G$2</f>
-        <v>18.07</v>
+        <v>18.649999999999999</v>
       </c>
       <c r="F49" s="14">
         <f>+[24]Main!$G$4</f>
-        <v>6087.7829999999994</v>
+        <v>6195.53</v>
       </c>
       <c r="G49" s="14">
         <f>+[24]Main!$G$6-[24]Main!$G$5</f>
-        <v>1609.7280000000001</v>
+        <v>1466.0810000000004</v>
       </c>
       <c r="H49" s="14">
         <f>+F49+G49</f>
-        <v>7697.5109999999995</v>
+        <v>7661.6109999999999</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>239</v>
@@ -27515,19 +27533,19 @@
       </c>
       <c r="E4" s="14">
         <f>+[3]Main!$I$2</f>
-        <v>34.549999999999997</v>
+        <v>33.840000000000003</v>
       </c>
       <c r="F4" s="14">
         <f>+[3]Main!$I$4</f>
-        <v>129621.37067784999</v>
+        <v>124944.26802768001</v>
       </c>
       <c r="G4" s="14">
         <f>+[3]Main!$I$6-[3]Main!$I$5</f>
-        <v>90529</v>
+        <v>91841</v>
       </c>
       <c r="H4" s="14">
         <f>+F4+G4</f>
-        <v>220150.37067784998</v>
+        <v>216785.26802767999</v>
       </c>
       <c r="I4" s="15" t="s">
         <v>239</v>

--- a/Entertainment.xlsx
+++ b/Entertainment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31785A62-21DC-44CD-89DA-4D626DF23AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE40600-820C-46AD-8B4F-67B37E912AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="1950" windowWidth="38175" windowHeight="15240" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1532,13 +1532,19 @@
     <numFmt numFmtId="165" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1677,56 +1683,59 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -2424,7 +2433,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2680,22 +2689,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="G2">
-            <v>373.4</v>
+            <v>617.5</v>
           </cell>
         </row>
         <row r="4">
           <cell r="G4">
-            <v>3396543.4839999997</v>
+            <v>9097</v>
           </cell>
         </row>
         <row r="5">
           <cell r="G5">
-            <v>343463</v>
+            <v>5168005.7</v>
           </cell>
         </row>
         <row r="6">
           <cell r="G6">
-            <v>194367</v>
+            <v>351480</v>
           </cell>
         </row>
       </sheetData>
@@ -3160,7 +3169,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3297,26 +3306,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>58.14</v>
+            <v>127.88</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>38796.821127900002</v>
+            <v>82486.819144840003</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>2409.5450000000001</v>
+            <v>2627.1959999999999</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>1006.371</v>
+            <v>992.37699999999995</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4138,8 +4147,8 @@
         <f t="shared" si="0"/>
         <v>124178.28512867499</v>
       </c>
-      <c r="I8" s="15" t="s">
-        <v>246</v>
+      <c r="I8" s="31" t="s">
+        <v>474</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -4636,22 +4645,22 @@
       </c>
       <c r="E16" s="13">
         <f>+[9]Main!$H$2</f>
-        <v>58.14</v>
+        <v>127.88</v>
       </c>
       <c r="F16" s="14">
         <f>+[9]Main!$H$4</f>
-        <v>38796.821127900002</v>
+        <v>82486.819144840003</v>
       </c>
       <c r="G16" s="14">
         <f>+[9]Main!$H$6-[9]Main!$H$5</f>
-        <v>-1403.174</v>
+        <v>-1634.819</v>
       </c>
       <c r="H16" s="14">
         <f>+F16+G16</f>
-        <v>37393.647127900003</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>239</v>
+        <v>80852.00014484</v>
+      </c>
+      <c r="I16" s="31" t="s">
+        <v>474</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -16852,19 +16861,19 @@
       </c>
       <c r="E6" s="26">
         <f>+[30]Main!$G$2</f>
-        <v>373.4</v>
+        <v>617.5</v>
       </c>
       <c r="F6" s="26">
         <f>+[30]Main!$G$4*FX!C6</f>
-        <v>475516.08776000002</v>
+        <v>1273.5800000000002</v>
       </c>
       <c r="G6" s="26">
         <f>+([30]Main!$G$6-[30]Main!$G$5)*FX!C6</f>
-        <v>-20873.440000000002</v>
+        <v>-674313.59800000011</v>
       </c>
       <c r="H6" s="26">
         <f t="shared" si="0"/>
-        <v>454642.64776000002</v>
+        <v>-673040.01800000016</v>
       </c>
       <c r="I6" s="15" t="s">
         <v>239</v>
@@ -17517,19 +17526,19 @@
       </c>
       <c r="E13" s="26">
         <f>+[9]Main!$H$2</f>
-        <v>58.14</v>
+        <v>127.88</v>
       </c>
       <c r="F13" s="26">
         <f>+[9]Main!$H$4</f>
-        <v>38796.821127900002</v>
+        <v>82486.819144840003</v>
       </c>
       <c r="G13" s="26">
         <f>+[9]Main!$H$6-[9]Main!$H$5</f>
-        <v>-1403.174</v>
+        <v>-1634.819</v>
       </c>
       <c r="H13" s="26">
         <f t="shared" si="0"/>
-        <v>37393.647127900003</v>
+        <v>80852.00014484</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>294</v>

--- a/Entertainment.xlsx
+++ b/Entertainment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE40600-820C-46AD-8B4F-67B37E912AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F7B6B3-0564-44EA-B6E3-45542878D864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
+    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="481">
   <si>
     <t>Name</t>
   </si>
@@ -1521,6 +1521,12 @@
   </si>
   <si>
     <t>Lego</t>
+  </si>
+  <si>
+    <t>Pop Mart</t>
+  </si>
+  <si>
+    <t>9992.HK</t>
   </si>
 </sst>
 </file>
@@ -1532,13 +1538,19 @@
     <numFmt numFmtId="165" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1683,65 +1695,66 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3169,7 +3182,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3325,7 +3338,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -7917,7 +7930,7 @@
     </row>
     <row r="70" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A70" s="11">
-        <f t="shared" ref="A70:A112" si="2">+A69+1</f>
+        <f t="shared" ref="A70:A113" si="2">+A69+1</f>
         <v>67</v>
       </c>
       <c r="B70" s="3" t="s">
@@ -10370,10 +10383,19 @@
       <c r="AS112" s="3"/>
     </row>
     <row r="113" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A113" s="11"/>
-      <c r="B113" s="3"/>
-      <c r="C113" s="3"/>
-      <c r="D113" s="3"/>
+      <c r="A113" s="11">
+        <f t="shared" si="2"/>
+        <v>110</v>
+      </c>
+      <c r="B113" s="32" t="s">
+        <v>479</v>
+      </c>
+      <c r="C113" s="32" t="s">
+        <v>480</v>
+      </c>
+      <c r="D113" s="32" t="s">
+        <v>26</v>
+      </c>
       <c r="E113" s="3"/>
       <c r="F113" s="21"/>
       <c r="G113" s="21"/>

--- a/Entertainment.xlsx
+++ b/Entertainment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F7B6B3-0564-44EA-B6E3-45542878D864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8698638F-2AF4-44B0-B18C-D16BC7A03E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -59,9 +59,10 @@
     <externalReference r:id="rId42"/>
     <externalReference r:id="rId43"/>
     <externalReference r:id="rId44"/>
+    <externalReference r:id="rId45"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$A$1:$J$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$A$1:$J$113</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -84,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="481">
   <si>
     <t>Name</t>
   </si>
@@ -1538,13 +1539,19 @@
     <numFmt numFmtId="165" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1695,66 +1702,69 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2602,7 +2612,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3149,6 +3159,45 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>256.39999999999998</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>340780.2144</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>13765.710999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -3988,7 +4037,7 @@
     </row>
     <row r="6" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <f t="shared" ref="A6:A69" si="1">+A5+1</f>
+        <f t="shared" ref="A6:A70" si="1">+A5+1</f>
         <v>3</v>
       </c>
       <c r="B6" s="12" t="s">
@@ -4791,20 +4840,34 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15"/>
+      <c r="B18" s="12" t="s">
+        <v>479</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>480</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="3">
+        <f>+[41]Main!$I$2</f>
+        <v>256.39999999999998</v>
+      </c>
+      <c r="F18" s="21">
+        <f>+[41]Main!$I$4*FX!C6</f>
+        <v>47709.230016000001</v>
+      </c>
+      <c r="G18" s="14">
+        <f>+([41]Main!$I$6-[41]Main!$I$5)*FX!C6</f>
+        <v>-1927.1995400000001</v>
+      </c>
+      <c r="H18" s="14">
+        <f>+F18+G18</f>
+        <v>45782.030476</v>
+      </c>
+      <c r="I18" s="33" t="s">
+        <v>474</v>
+      </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
@@ -4847,34 +4910,20 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="B19" s="12" t="s">
-        <v>44</v>
+      <c r="B19" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" s="3">
-        <f>+[11]Main!$L$3</f>
-        <v>228.01</v>
-      </c>
-      <c r="F19" s="14">
-        <f>+[11]Main!$L$5</f>
-        <v>42061.053038120001</v>
-      </c>
-      <c r="G19" s="14">
-        <f>+[11]Main!$L$7-[11]Main!$L$6</f>
-        <v>1030</v>
-      </c>
-      <c r="H19" s="14">
-        <f>+F19+G19</f>
-        <v>43091.053038120001</v>
-      </c>
-      <c r="I19" s="15" t="s">
-        <v>476</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="E19" s="3"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="15"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
@@ -4884,9 +4933,7 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-      <c r="S19" s="3" t="s">
-        <v>266</v>
-      </c>
+      <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
@@ -4920,32 +4967,32 @@
         <v>17</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="18">
-        <f>+[12]Main!$H$2</f>
-        <v>134.9</v>
+      <c r="E20" s="3">
+        <f>+[11]Main!$L$3</f>
+        <v>228.01</v>
       </c>
       <c r="F20" s="14">
-        <f>+[12]Main!$H$4</f>
-        <v>31344.512106500002</v>
+        <f>+[11]Main!$L$5</f>
+        <v>42061.053038120001</v>
       </c>
       <c r="G20" s="14">
-        <f>+[12]Main!$H$6-[12]Main!$H$5</f>
-        <v>764.97299999999996</v>
+        <f>+[11]Main!$L$7-[11]Main!$L$6</f>
+        <v>1030</v>
       </c>
       <c r="H20" s="14">
         <f>+F20+G20</f>
-        <v>32109.485106500004</v>
+        <v>43091.053038120001</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>239</v>
+        <v>476</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
@@ -4957,7 +5004,7 @@
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
       <c r="S20" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
@@ -4992,32 +5039,32 @@
         <v>18</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21" s="3">
-        <f>+[13]Main!$I$2</f>
-        <v>66.67</v>
+        <v>22</v>
+      </c>
+      <c r="E21" s="18">
+        <f>+[12]Main!$H$2</f>
+        <v>134.9</v>
       </c>
       <c r="F21" s="14">
-        <f>+[13]Main!$I$4*FX!C5</f>
-        <v>26732.303286336904</v>
+        <f>+[12]Main!$H$4</f>
+        <v>31344.512106500002</v>
       </c>
       <c r="G21" s="14">
-        <f>+([13]Main!$I$6-[13]Main!$I$5)*FX!C5</f>
-        <v>718.45199999999988</v>
+        <f>+[12]Main!$H$6-[12]Main!$H$5</f>
+        <v>764.97299999999996</v>
       </c>
       <c r="H21" s="14">
         <f>+F21+G21</f>
-        <v>27450.755286336906</v>
+        <v>32109.485106500004</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
@@ -5029,7 +5076,7 @@
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
       <c r="S21" s="3" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
@@ -5064,36 +5111,34 @@
         <v>19</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="E22" s="3">
-        <f>+[14]Main!$H$2</f>
-        <v>11.87</v>
+        <f>+[13]Main!$I$2</f>
+        <v>66.67</v>
       </c>
       <c r="F22" s="14">
-        <f>+[14]Main!$H$4</f>
-        <v>29387.416987339999</v>
+        <f>+[13]Main!$I$4*FX!C5</f>
+        <v>26732.303286336904</v>
       </c>
       <c r="G22" s="14">
-        <f>+[14]Main!$H$6-[14]Main!$H$5</f>
-        <v>29744</v>
+        <f>+([13]Main!$I$6-[13]Main!$I$5)*FX!C5</f>
+        <v>718.45199999999988</v>
       </c>
       <c r="H22" s="14">
         <f>+F22+G22</f>
-        <v>59131.416987339995</v>
+        <v>27450.755286336906</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>474</v>
-      </c>
-      <c r="J22" s="17">
-        <v>45967</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
@@ -5103,7 +5148,7 @@
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
       <c r="S22" s="3" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
@@ -5138,34 +5183,36 @@
         <v>20</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E23" s="3">
-        <f>+[15]Main!$G$3</f>
-        <v>95</v>
+        <f>+[14]Main!$H$2</f>
+        <v>11.87</v>
       </c>
       <c r="F23" s="14">
-        <f>+[15]Main!$G$5</f>
-        <v>23679.881450000001</v>
+        <f>+[14]Main!$H$4</f>
+        <v>29387.416987339999</v>
       </c>
       <c r="G23" s="14">
-        <f>+[15]Main!$G$7-[15]Main!$G$6</f>
-        <v>1592</v>
+        <f>+[14]Main!$H$6-[14]Main!$H$5</f>
+        <v>29744</v>
       </c>
       <c r="H23" s="14">
         <f>+F23+G23</f>
-        <v>25271.881450000001</v>
+        <v>59131.416987339995</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>246</v>
-      </c>
-      <c r="J23" s="3"/>
+        <v>474</v>
+      </c>
+      <c r="J23" s="17">
+        <v>45967</v>
+      </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
@@ -5175,7 +5222,7 @@
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
       <c r="S23" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
@@ -5209,20 +5256,34 @@
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>56</v>
+      <c r="B24" s="12" t="s">
+        <v>54</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15"/>
+        <v>22</v>
+      </c>
+      <c r="E24" s="3">
+        <f>+[15]Main!$G$3</f>
+        <v>95</v>
+      </c>
+      <c r="F24" s="14">
+        <f>+[15]Main!$G$5</f>
+        <v>23679.881450000001</v>
+      </c>
+      <c r="G24" s="14">
+        <f>+[15]Main!$G$7-[15]Main!$G$6</f>
+        <v>1592</v>
+      </c>
+      <c r="H24" s="14">
+        <f>+F24+G24</f>
+        <v>25271.881450000001</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>246</v>
+      </c>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
@@ -5232,7 +5293,9 @@
       <c r="P24" s="3"/>
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
+      <c r="S24" s="3" t="s">
+        <v>270</v>
+      </c>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
@@ -5265,34 +5328,20 @@
         <f t="shared" si="1"/>
         <v>22</v>
       </c>
-      <c r="B25" s="12" t="s">
-        <v>58</v>
+      <c r="B25" s="3" t="s">
+        <v>56</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25" s="3">
-        <f>+[16]Main!$G$2</f>
-        <v>45.96</v>
-      </c>
-      <c r="F25" s="14">
-        <f>+[16]Main!$G$4</f>
-        <v>22817.764463160001</v>
-      </c>
-      <c r="G25" s="14">
-        <f>+[16]Main!$G$6-[16]Main!$G$5</f>
-        <v>-669.26499999999999</v>
-      </c>
-      <c r="H25" s="14">
-        <f>+F25+G25</f>
-        <v>22148.499463160002</v>
-      </c>
-      <c r="I25" s="15" t="s">
-        <v>474</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="15"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
@@ -5302,9 +5351,7 @@
       <c r="P25" s="3"/>
       <c r="Q25" s="3"/>
       <c r="R25" s="3"/>
-      <c r="S25" s="3" t="s">
-        <v>267</v>
-      </c>
+      <c r="S25" s="3"/>
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
@@ -5338,32 +5385,32 @@
         <v>23</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E26" s="3">
-        <f>+[17]Main!$H$2</f>
-        <v>35.83</v>
+        <f>+[16]Main!$G$2</f>
+        <v>45.96</v>
       </c>
       <c r="F26" s="14">
-        <f>+[17]Main!$H$4</f>
-        <v>18644.53591988</v>
+        <f>+[16]Main!$G$4</f>
+        <v>22817.764463160001</v>
       </c>
       <c r="G26" s="14">
-        <f>+[17]Main!$H$6-[17]Main!$H$5</f>
-        <v>3153</v>
+        <f>+[16]Main!$G$6-[16]Main!$G$5</f>
+        <v>-669.26499999999999</v>
       </c>
       <c r="H26" s="14">
         <f>+F26+G26</f>
-        <v>21797.53591988</v>
+        <v>22148.499463160002</v>
       </c>
       <c r="I26" s="15" t="s">
-        <v>241</v>
+        <v>474</v>
       </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
@@ -5375,7 +5422,7 @@
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
       <c r="S26" s="3" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
@@ -5409,20 +5456,34 @@
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>62</v>
+      <c r="B27" s="12" t="s">
+        <v>60</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15"/>
+        <v>22</v>
+      </c>
+      <c r="E27" s="3">
+        <f>+[17]Main!$H$2</f>
+        <v>35.83</v>
+      </c>
+      <c r="F27" s="14">
+        <f>+[17]Main!$H$4</f>
+        <v>18644.53591988</v>
+      </c>
+      <c r="G27" s="14">
+        <f>+[17]Main!$H$6-[17]Main!$H$5</f>
+        <v>3153</v>
+      </c>
+      <c r="H27" s="14">
+        <f>+F27+G27</f>
+        <v>21797.53591988</v>
+      </c>
+      <c r="I27" s="15" t="s">
+        <v>241</v>
+      </c>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
@@ -5432,7 +5493,9 @@
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
-      <c r="S27" s="3"/>
+      <c r="S27" s="3" t="s">
+        <v>271</v>
+      </c>
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
@@ -5465,31 +5528,19 @@
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="B28" s="12" t="s">
-        <v>64</v>
+      <c r="B28" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" s="19">
-        <f>+[18]Main!$I$2</f>
-        <v>5241</v>
-      </c>
-      <c r="F28" s="14">
-        <f>+[18]Main!$I$4*FX!C2</f>
-        <v>21944.563863571202</v>
-      </c>
-      <c r="G28" s="14">
-        <f>+([18]Main!$I$6-[18]Main!$I$5)*FX!C2</f>
-        <v>-2059.9551999999999</v>
-      </c>
-      <c r="H28" s="14">
-        <f>+F28+G28</f>
-        <v>19884.608663571202</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="E28" s="3"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
       <c r="I28" s="15"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
@@ -5534,33 +5585,31 @@
         <v>26</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E29" s="19">
-        <f>+[19]Main!$I$2</f>
-        <v>16735</v>
+        <f>+[18]Main!$I$2</f>
+        <v>5241</v>
       </c>
       <c r="F29" s="14">
-        <f>+[19]Main!$I$4*FX!C2</f>
-        <v>14518.749837375999</v>
+        <f>+[18]Main!$I$4*FX!C2</f>
+        <v>21944.563863571202</v>
       </c>
       <c r="G29" s="14">
-        <f>+([19]Main!$I$6-[19]Main!$I$5)*FX!C2</f>
-        <v>-1445.152</v>
+        <f>+([18]Main!$I$6-[18]Main!$I$5)*FX!C2</f>
+        <v>-2059.9551999999999</v>
       </c>
       <c r="H29" s="14">
         <f>+F29+G29</f>
-        <v>13073.597837375999</v>
-      </c>
-      <c r="I29" s="15" t="s">
-        <v>277</v>
-      </c>
+        <v>19884.608663571202</v>
+      </c>
+      <c r="I29" s="15"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
@@ -5603,20 +5652,34 @@
         <f t="shared" si="1"/>
         <v>27</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>67</v>
+      <c r="B30" s="12" t="s">
+        <v>66</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15"/>
+      <c r="E30" s="19">
+        <f>+[19]Main!$I$2</f>
+        <v>16735</v>
+      </c>
+      <c r="F30" s="14">
+        <f>+[19]Main!$I$4*FX!C2</f>
+        <v>14518.749837375999</v>
+      </c>
+      <c r="G30" s="14">
+        <f>+([19]Main!$I$6-[19]Main!$I$5)*FX!C2</f>
+        <v>-1445.152</v>
+      </c>
+      <c r="H30" s="14">
+        <f>+F30+G30</f>
+        <v>13073.597837375999</v>
+      </c>
+      <c r="I30" s="15" t="s">
+        <v>277</v>
+      </c>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
@@ -5659,34 +5722,20 @@
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="B31" s="12" t="s">
-        <v>70</v>
+      <c r="B31" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E31" s="3">
-        <f>+[20]Main!$J$2</f>
-        <v>184.82</v>
-      </c>
-      <c r="F31" s="14">
-        <f>+[20]Main!$J$4</f>
-        <v>15180.539270520001</v>
-      </c>
-      <c r="G31" s="14">
-        <f>+[20]Main!$J$6-[20]Main!$J$5</f>
-        <v>2214.2530000000002</v>
-      </c>
-      <c r="H31" s="14">
-        <f>+F31+G31</f>
-        <v>17394.79227052</v>
-      </c>
-      <c r="I31" s="15" t="s">
-        <v>474</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="E31" s="3"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="15"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
@@ -5729,20 +5778,34 @@
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>72</v>
+      <c r="B32" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15"/>
+      <c r="E32" s="3">
+        <f>+[20]Main!$J$2</f>
+        <v>184.82</v>
+      </c>
+      <c r="F32" s="14">
+        <f>+[20]Main!$J$4</f>
+        <v>15180.539270520001</v>
+      </c>
+      <c r="G32" s="14">
+        <f>+[20]Main!$J$6-[20]Main!$J$5</f>
+        <v>2214.2530000000002</v>
+      </c>
+      <c r="H32" s="14">
+        <f>+F32+G32</f>
+        <v>17394.79227052</v>
+      </c>
+      <c r="I32" s="15" t="s">
+        <v>474</v>
+      </c>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
@@ -5786,10 +5849,10 @@
         <v>30</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>22</v>
@@ -5842,10 +5905,10 @@
         <v>31</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>22</v>
@@ -5898,10 +5961,10 @@
         <v>32</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>22</v>
@@ -5954,13 +6017,13 @@
         <v>33</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>82</v>
+        <v>22</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="14"/>
@@ -6010,13 +6073,13 @@
         <v>34</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="14"/>
@@ -6065,34 +6128,20 @@
         <f t="shared" si="1"/>
         <v>35</v>
       </c>
-      <c r="B38" s="12" t="s">
-        <v>86</v>
+      <c r="B38" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E38" s="3">
-        <f>+[21]Main!$H$2</f>
-        <v>65.319999999999993</v>
-      </c>
-      <c r="F38" s="14">
-        <f>+[21]Main!$H$4</f>
-        <v>9114.1865409199982</v>
-      </c>
-      <c r="G38" s="14">
-        <f>+[21]Main!$H$6-[21]Main!$H$5</f>
-        <v>2685.8</v>
-      </c>
-      <c r="H38" s="14">
-        <f>+F38+G38</f>
-        <v>11799.986540919999</v>
-      </c>
-      <c r="I38" s="15" t="s">
-        <v>246</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="E38" s="3"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="15"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
@@ -6102,9 +6151,7 @@
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
-      <c r="S38" s="3" t="s">
-        <v>272</v>
-      </c>
+      <c r="S38" s="3"/>
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
@@ -6137,20 +6184,34 @@
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>88</v>
+      <c r="B39" s="12" t="s">
+        <v>86</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E39" s="3"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15"/>
+      <c r="E39" s="3">
+        <f>+[21]Main!$H$2</f>
+        <v>65.319999999999993</v>
+      </c>
+      <c r="F39" s="14">
+        <f>+[21]Main!$H$4</f>
+        <v>9114.1865409199982</v>
+      </c>
+      <c r="G39" s="14">
+        <f>+[21]Main!$H$6-[21]Main!$H$5</f>
+        <v>2685.8</v>
+      </c>
+      <c r="H39" s="14">
+        <f>+F39+G39</f>
+        <v>11799.986540919999</v>
+      </c>
+      <c r="I39" s="15" t="s">
+        <v>246</v>
+      </c>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
@@ -6160,7 +6221,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-      <c r="S39" s="3"/>
+      <c r="S39" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
@@ -6193,34 +6256,20 @@
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
-      <c r="B40" s="12" t="s">
-        <v>90</v>
+      <c r="B40" s="3" t="s">
+        <v>88</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>475</v>
+        <v>89</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E40" s="3">
-        <f>+[22]Main!$I$2</f>
-        <v>13.8</v>
-      </c>
-      <c r="F40" s="14">
-        <f>+[22]Main!$I$4</f>
-        <v>9315</v>
-      </c>
-      <c r="G40" s="14">
-        <f>+[22]Main!$I$6-[22]Main!$I$5</f>
-        <v>11775</v>
-      </c>
-      <c r="H40" s="14">
-        <f>+F40+G40</f>
-        <v>21090</v>
-      </c>
-      <c r="I40" s="15" t="s">
-        <v>246</v>
-      </c>
+      <c r="E40" s="3"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="15"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
@@ -6230,9 +6279,7 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-      <c r="S40" s="3" t="s">
-        <v>274</v>
-      </c>
+      <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
@@ -6265,20 +6312,34 @@
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>92</v>
+      <c r="B41" s="12" t="s">
+        <v>90</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>93</v>
+        <v>475</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15"/>
+        <v>22</v>
+      </c>
+      <c r="E41" s="3">
+        <f>+[22]Main!$I$2</f>
+        <v>13.8</v>
+      </c>
+      <c r="F41" s="14">
+        <f>+[22]Main!$I$4</f>
+        <v>9315</v>
+      </c>
+      <c r="G41" s="14">
+        <f>+[22]Main!$I$6-[22]Main!$I$5</f>
+        <v>11775</v>
+      </c>
+      <c r="H41" s="14">
+        <f>+F41+G41</f>
+        <v>21090</v>
+      </c>
+      <c r="I41" s="15" t="s">
+        <v>246</v>
+      </c>
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
@@ -6288,7 +6349,9 @@
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
-      <c r="S41" s="3"/>
+      <c r="S41" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
@@ -6322,13 +6385,13 @@
         <v>39</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="14"/>
@@ -6378,13 +6441,13 @@
         <v>40</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="14"/>
@@ -6434,13 +6497,13 @@
         <v>41</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="14"/>
@@ -6490,13 +6553,13 @@
         <v>42</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="14"/>
@@ -6545,34 +6608,20 @@
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
-      <c r="B46" s="12" t="s">
-        <v>103</v>
+      <c r="B46" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E46" s="3">
-        <f>+[23]Main!$I$2</f>
-        <v>77.77</v>
-      </c>
-      <c r="F46" s="14">
-        <f>+[23]Main!$I$4</f>
-        <v>6330.7175316000003</v>
-      </c>
-      <c r="G46" s="14">
-        <f>+[23]Main!$I$6-[23]Main!$I$5</f>
-        <v>3205.0709999999999</v>
-      </c>
-      <c r="H46" s="14">
-        <f>+F46+G46</f>
-        <v>9535.7885315999993</v>
-      </c>
-      <c r="I46" s="15" t="s">
-        <v>261</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="E46" s="3"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="15"/>
       <c r="J46" s="3"/>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
@@ -6615,20 +6664,34 @@
         <f t="shared" si="1"/>
         <v>44</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>105</v>
+      <c r="B47" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E47" s="3"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15"/>
+      <c r="E47" s="3">
+        <f>+[23]Main!$I$2</f>
+        <v>77.77</v>
+      </c>
+      <c r="F47" s="14">
+        <f>+[23]Main!$I$4</f>
+        <v>6330.7175316000003</v>
+      </c>
+      <c r="G47" s="14">
+        <f>+[23]Main!$I$6-[23]Main!$I$5</f>
+        <v>3205.0709999999999</v>
+      </c>
+      <c r="H47" s="14">
+        <f>+F47+G47</f>
+        <v>9535.7885315999993</v>
+      </c>
+      <c r="I47" s="15" t="s">
+        <v>261</v>
+      </c>
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
@@ -6672,10 +6735,10 @@
         <v>45</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>22</v>
@@ -6727,34 +6790,20 @@
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
-      <c r="B49" s="12" t="s">
-        <v>109</v>
+      <c r="B49" s="3" t="s">
+        <v>107</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E49" s="3">
-        <f>+[24]Main!$G$2</f>
-        <v>18.649999999999999</v>
-      </c>
-      <c r="F49" s="14">
-        <f>+[24]Main!$G$4</f>
-        <v>6195.53</v>
-      </c>
-      <c r="G49" s="14">
-        <f>+[24]Main!$G$6-[24]Main!$G$5</f>
-        <v>1466.0810000000004</v>
-      </c>
-      <c r="H49" s="14">
-        <f>+F49+G49</f>
-        <v>7661.6109999999999</v>
-      </c>
-      <c r="I49" s="15" t="s">
-        <v>239</v>
-      </c>
+      <c r="E49" s="3"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
+      <c r="H49" s="14"/>
+      <c r="I49" s="15"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
@@ -6764,9 +6813,7 @@
       <c r="P49" s="3"/>
       <c r="Q49" s="3"/>
       <c r="R49" s="3"/>
-      <c r="S49" s="3" t="s">
-        <v>275</v>
-      </c>
+      <c r="S49" s="3"/>
       <c r="T49" s="3"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3"/>
@@ -6799,20 +6846,34 @@
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>111</v>
+      <c r="B50" s="12" t="s">
+        <v>109</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E50" s="3"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15"/>
+        <v>22</v>
+      </c>
+      <c r="E50" s="3">
+        <f>+[24]Main!$G$2</f>
+        <v>18.649999999999999</v>
+      </c>
+      <c r="F50" s="14">
+        <f>+[24]Main!$G$4</f>
+        <v>6195.53</v>
+      </c>
+      <c r="G50" s="14">
+        <f>+[24]Main!$G$6-[24]Main!$G$5</f>
+        <v>1466.0810000000004</v>
+      </c>
+      <c r="H50" s="14">
+        <f>+F50+G50</f>
+        <v>7661.6109999999999</v>
+      </c>
+      <c r="I50" s="15" t="s">
+        <v>239</v>
+      </c>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
@@ -6822,7 +6883,9 @@
       <c r="P50" s="3"/>
       <c r="Q50" s="3"/>
       <c r="R50" s="3"/>
-      <c r="S50" s="3"/>
+      <c r="S50" s="3" t="s">
+        <v>275</v>
+      </c>
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3"/>
@@ -6856,13 +6919,13 @@
         <v>48</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="14"/>
@@ -6912,13 +6975,13 @@
         <v>49</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>118</v>
+        <v>26</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="14"/>
@@ -6968,13 +7031,13 @@
         <v>50</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>231</v>
+        <v>116</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>232</v>
+        <v>117</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="14"/>
@@ -7024,10 +7087,10 @@
         <v>51</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C54" s="20" t="s">
-        <v>120</v>
+        <v>231</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>232</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>121</v>
@@ -7080,13 +7143,13 @@
         <v>52</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
+      </c>
+      <c r="C55" s="20" t="s">
+        <v>120</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="14"/>
@@ -7135,34 +7198,20 @@
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
-      <c r="B56" s="12" t="s">
-        <v>125</v>
+      <c r="B56" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E56" s="3">
-        <f>+[25]Main!$I$2</f>
-        <v>183.2</v>
-      </c>
-      <c r="F56" s="14">
-        <f>+[25]Main!$I$4</f>
-        <v>5589.2865391999994</v>
-      </c>
-      <c r="G56" s="14">
-        <f>+[25]Main!$I$6-[25]Main!$I$5</f>
-        <v>6379</v>
-      </c>
-      <c r="H56" s="14">
-        <f>+F56+G56</f>
-        <v>11968.286539199999</v>
-      </c>
-      <c r="I56" s="15" t="s">
-        <v>246</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="E56" s="3"/>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="15"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
@@ -7205,20 +7254,34 @@
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>128</v>
+      <c r="B57" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E57" s="3"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15"/>
+        <v>22</v>
+      </c>
+      <c r="E57" s="3">
+        <f>+[25]Main!$I$2</f>
+        <v>183.2</v>
+      </c>
+      <c r="F57" s="14">
+        <f>+[25]Main!$I$4</f>
+        <v>5589.2865391999994</v>
+      </c>
+      <c r="G57" s="14">
+        <f>+[25]Main!$I$6-[25]Main!$I$5</f>
+        <v>6379</v>
+      </c>
+      <c r="H57" s="14">
+        <f>+F57+G57</f>
+        <v>11968.286539199999</v>
+      </c>
+      <c r="I57" s="15" t="s">
+        <v>246</v>
+      </c>
       <c r="J57" s="3"/>
       <c r="K57" s="3"/>
       <c r="L57" s="3"/>
@@ -7262,13 +7325,13 @@
         <v>55</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>22</v>
+        <v>127</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="14"/>
@@ -7318,13 +7381,13 @@
         <v>56</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C59" s="20" t="s">
-        <v>133</v>
+        <v>130</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>131</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="14"/>
@@ -7374,13 +7437,13 @@
         <v>57</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
+      </c>
+      <c r="C60" s="20" t="s">
+        <v>133</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="14"/>
@@ -7430,13 +7493,13 @@
         <v>58</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="14"/>
@@ -7486,13 +7549,13 @@
         <v>59</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="14"/>
@@ -7542,10 +7605,10 @@
         <v>60</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>23</v>
@@ -7598,13 +7661,13 @@
         <v>61</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C64" s="20" t="s">
-        <v>144</v>
+        <v>141</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="14"/>
@@ -7654,13 +7717,13 @@
         <v>62</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
+      </c>
+      <c r="C65" s="20" t="s">
+        <v>144</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="14"/>
@@ -7710,13 +7773,13 @@
         <v>63</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="14"/>
@@ -7766,13 +7829,13 @@
         <v>64</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="14"/>
@@ -7822,13 +7885,13 @@
         <v>65</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>153</v>
+        <v>24</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="14"/>
@@ -7878,13 +7941,13 @@
         <v>66</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>23</v>
+        <v>153</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="14"/>
@@ -7930,17 +7993,17 @@
     </row>
     <row r="70" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A70" s="11">
-        <f t="shared" ref="A70:A113" si="2">+A69+1</f>
+        <f t="shared" si="1"/>
         <v>67</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C70" s="20" t="s">
-        <v>157</v>
+        <v>154</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>155</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="14"/>
@@ -7986,17 +8049,17 @@
     </row>
     <row r="71" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A71" s="11">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A71:A113" si="2">+A70+1</f>
         <v>68</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
+      </c>
+      <c r="C71" s="20" t="s">
+        <v>157</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>160</v>
+        <v>26</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="14"/>
@@ -8046,13 +8109,13 @@
         <v>69</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="14"/>
@@ -8102,13 +8165,13 @@
         <v>70</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="14"/>
@@ -8158,13 +8221,13 @@
         <v>71</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>22</v>
+        <v>166</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="14"/>
@@ -8214,10 +8277,10 @@
         <v>72</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>22</v>
@@ -8270,10 +8333,10 @@
         <v>73</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>22</v>
@@ -8326,13 +8389,13 @@
         <v>74</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="14"/>
@@ -8382,13 +8445,13 @@
         <v>75</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="14"/>
@@ -8438,13 +8501,13 @@
         <v>76</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>163</v>
+        <v>121</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="14"/>
@@ -8494,13 +8557,13 @@
         <v>77</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>26</v>
+        <v>163</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="14"/>
@@ -8550,10 +8613,10 @@
         <v>78</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C81" s="20" t="s">
-        <v>182</v>
+        <v>179</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>180</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>26</v>
@@ -8606,13 +8669,13 @@
         <v>79</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
+      </c>
+      <c r="C82" s="20" t="s">
+        <v>182</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>118</v>
+        <v>26</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="14"/>
@@ -8662,13 +8725,13 @@
         <v>80</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="14"/>
@@ -8718,13 +8781,13 @@
         <v>81</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="14"/>
@@ -8774,13 +8837,13 @@
         <v>82</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>191</v>
+        <v>35</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="14"/>
@@ -8830,13 +8893,13 @@
         <v>83</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="14"/>
@@ -8886,13 +8949,13 @@
         <v>84</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>121</v>
+        <v>194</v>
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="14"/>
@@ -8942,10 +9005,10 @@
         <v>85</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C88" s="20" t="s">
-        <v>198</v>
+        <v>195</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>196</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>121</v>
@@ -8998,13 +9061,13 @@
         <v>86</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C89" s="20" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>201</v>
+        <v>121</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="14"/>
@@ -9054,10 +9117,10 @@
         <v>87</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>203</v>
+        <v>199</v>
+      </c>
+      <c r="C90" s="20" t="s">
+        <v>200</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>201</v>
@@ -9066,7 +9129,7 @@
       <c r="F90" s="14"/>
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
-      <c r="I90" s="3"/>
+      <c r="I90" s="15"/>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
@@ -9110,13 +9173,13 @@
         <v>88</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="14"/>
@@ -9166,13 +9229,13 @@
         <v>89</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>23</v>
+        <v>206</v>
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="14"/>
@@ -9222,10 +9285,10 @@
         <v>90</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>23</v>
@@ -9278,13 +9341,13 @@
         <v>91</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="14"/>
@@ -9334,13 +9397,13 @@
         <v>92</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C95" s="20" t="s">
-        <v>214</v>
+        <v>211</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>121</v>
+        <v>22</v>
       </c>
       <c r="E95" s="3"/>
       <c r="F95" s="14"/>
@@ -9390,13 +9453,13 @@
         <v>93</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
+      </c>
+      <c r="C96" s="20" t="s">
+        <v>214</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
       <c r="E96" s="3"/>
       <c r="F96" s="14"/>
@@ -9446,10 +9509,10 @@
         <v>94</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>26</v>
@@ -9502,13 +9565,13 @@
         <v>95</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>160</v>
+        <v>26</v>
       </c>
       <c r="E98" s="3"/>
       <c r="F98" s="14"/>
@@ -9558,13 +9621,13 @@
         <v>96</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="E99" s="3"/>
       <c r="F99" s="14"/>
@@ -9614,13 +9677,13 @@
         <v>97</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E100" s="3"/>
       <c r="F100" s="14"/>
@@ -9670,13 +9733,13 @@
         <v>98</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E101" s="3"/>
       <c r="F101" s="14"/>
@@ -9726,13 +9789,13 @@
         <v>99</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>94</v>
+        <v>24</v>
       </c>
       <c r="E102" s="3"/>
       <c r="F102" s="14"/>
@@ -9782,13 +9845,13 @@
         <v>100</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="E103" s="3"/>
       <c r="F103" s="14"/>
@@ -9837,34 +9900,20 @@
         <f t="shared" si="2"/>
         <v>101</v>
       </c>
-      <c r="B104" s="12" t="s">
-        <v>237</v>
+      <c r="B104" s="3" t="s">
+        <v>229</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E104" s="3">
-        <f>+[26]Main!$I$2</f>
-        <v>33.76</v>
-      </c>
-      <c r="F104" s="14">
-        <f>+[26]Main!$I$4</f>
-        <v>1615.1327198399999</v>
-      </c>
-      <c r="G104" s="14">
-        <f>+[26]Main!$I$6-[26]Main!$I$5</f>
-        <v>553.85699999999997</v>
-      </c>
-      <c r="H104" s="14">
-        <f>+F104+G104</f>
-        <v>2168.9897198399999</v>
-      </c>
-      <c r="I104" s="15" t="s">
-        <v>240</v>
-      </c>
+      <c r="E104" s="3"/>
+      <c r="F104" s="14"/>
+      <c r="G104" s="14"/>
+      <c r="H104" s="14"/>
+      <c r="I104" s="3"/>
       <c r="J104" s="3"/>
       <c r="K104" s="3"/>
       <c r="L104" s="3"/>
@@ -9907,20 +9956,34 @@
         <f t="shared" si="2"/>
         <v>102</v>
       </c>
-      <c r="B105" s="3" t="s">
-        <v>235</v>
+      <c r="B105" s="12" t="s">
+        <v>237</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E105" s="3"/>
-      <c r="F105" s="14"/>
-      <c r="G105" s="14"/>
-      <c r="H105" s="14"/>
-      <c r="I105" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="E105" s="3">
+        <f>+[26]Main!$I$2</f>
+        <v>33.76</v>
+      </c>
+      <c r="F105" s="14">
+        <f>+[26]Main!$I$4</f>
+        <v>1615.1327198399999</v>
+      </c>
+      <c r="G105" s="14">
+        <f>+[26]Main!$I$6-[26]Main!$I$5</f>
+        <v>553.85699999999997</v>
+      </c>
+      <c r="H105" s="14">
+        <f>+F105+G105</f>
+        <v>2168.9897198399999</v>
+      </c>
+      <c r="I105" s="15" t="s">
+        <v>240</v>
+      </c>
       <c r="J105" s="3"/>
       <c r="K105" s="3"/>
       <c r="L105" s="3"/>
@@ -9964,13 +10027,13 @@
         <v>103</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="E106" s="3"/>
       <c r="F106" s="14"/>
@@ -10019,34 +10082,20 @@
         <f t="shared" si="2"/>
         <v>104</v>
       </c>
-      <c r="B107" s="12" t="s">
-        <v>247</v>
+      <c r="B107" s="3" t="s">
+        <v>234</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E107" s="3">
-        <f>+[27]Main!$H$2</f>
-        <v>15.92</v>
-      </c>
-      <c r="F107" s="14">
-        <f>+[27]Main!$H$5*FX!C4</f>
-        <v>2707.3869572160002</v>
-      </c>
-      <c r="G107" s="14">
-        <f>+([27]Main!$H$7-[27]Main!$H$6)*FX!C4</f>
-        <v>699.94651999999996</v>
-      </c>
-      <c r="H107" s="14">
-        <f>+F107+G107</f>
-        <v>3407.3334772160001</v>
-      </c>
-      <c r="I107" s="15" t="s">
-        <v>261</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="E107" s="3"/>
+      <c r="F107" s="14"/>
+      <c r="G107" s="14"/>
+      <c r="H107" s="14"/>
+      <c r="I107" s="3"/>
       <c r="J107" s="3"/>
       <c r="K107" s="3"/>
       <c r="L107" s="3"/>
@@ -10056,9 +10105,7 @@
       <c r="P107" s="3"/>
       <c r="Q107" s="3"/>
       <c r="R107" s="3"/>
-      <c r="S107" s="3" t="s">
-        <v>276</v>
-      </c>
+      <c r="S107" s="3"/>
       <c r="T107" s="3"/>
       <c r="U107" s="3"/>
       <c r="V107" s="3"/>
@@ -10091,20 +10138,34 @@
         <f t="shared" si="2"/>
         <v>105</v>
       </c>
-      <c r="B108" s="3" t="s">
-        <v>249</v>
+      <c r="B108" s="12" t="s">
+        <v>247</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="E108" s="3"/>
-      <c r="F108" s="14"/>
-      <c r="G108" s="14"/>
-      <c r="H108" s="14"/>
-      <c r="I108" s="3"/>
+        <v>153</v>
+      </c>
+      <c r="E108" s="3">
+        <f>+[27]Main!$H$2</f>
+        <v>15.92</v>
+      </c>
+      <c r="F108" s="14">
+        <f>+[27]Main!$H$5*FX!C4</f>
+        <v>2707.3869572160002</v>
+      </c>
+      <c r="G108" s="14">
+        <f>+([27]Main!$H$7-[27]Main!$H$6)*FX!C4</f>
+        <v>699.94651999999996</v>
+      </c>
+      <c r="H108" s="14">
+        <f>+F108+G108</f>
+        <v>3407.3334772160001</v>
+      </c>
+      <c r="I108" s="15" t="s">
+        <v>261</v>
+      </c>
       <c r="J108" s="3"/>
       <c r="K108" s="3"/>
       <c r="L108" s="3"/>
@@ -10114,7 +10175,9 @@
       <c r="P108" s="3"/>
       <c r="Q108" s="3"/>
       <c r="R108" s="3"/>
-      <c r="S108" s="3"/>
+      <c r="S108" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="T108" s="3"/>
       <c r="U108" s="3"/>
       <c r="V108" s="3"/>
@@ -10147,34 +10210,20 @@
         <f t="shared" si="2"/>
         <v>106</v>
       </c>
-      <c r="B109" s="12" t="s">
-        <v>251</v>
+      <c r="B109" s="3" t="s">
+        <v>249</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E109" s="3">
-        <f>+[28]Main!$I$2</f>
-        <v>3.28</v>
-      </c>
-      <c r="F109" s="14">
-        <f>+[28]Main!$I$4*FX!C3</f>
-        <v>372.96258964800001</v>
-      </c>
-      <c r="G109" s="14">
-        <f>+([28]Main!$I$6-[28]Main!$I$5)*FX!C3</f>
-        <v>50.842859999999995</v>
-      </c>
-      <c r="H109" s="14">
-        <f>+F109+G109</f>
-        <v>423.80544964799998</v>
-      </c>
-      <c r="I109" s="15" t="s">
-        <v>241</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="E109" s="3"/>
+      <c r="F109" s="14"/>
+      <c r="G109" s="14"/>
+      <c r="H109" s="14"/>
+      <c r="I109" s="3"/>
       <c r="J109" s="3"/>
       <c r="K109" s="3"/>
       <c r="L109" s="3"/>
@@ -10184,9 +10233,7 @@
       <c r="P109" s="3"/>
       <c r="Q109" s="3"/>
       <c r="R109" s="3"/>
-      <c r="S109" s="3" t="s">
-        <v>276</v>
-      </c>
+      <c r="S109" s="3"/>
       <c r="T109" s="3"/>
       <c r="U109" s="3"/>
       <c r="V109" s="3"/>
@@ -10219,20 +10266,34 @@
         <f t="shared" si="2"/>
         <v>107</v>
       </c>
-      <c r="B110" s="3" t="s">
-        <v>253</v>
+      <c r="B110" s="12" t="s">
+        <v>251</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E110" s="3"/>
-      <c r="F110" s="21"/>
-      <c r="G110" s="21"/>
-      <c r="H110" s="21"/>
-      <c r="I110" s="3"/>
+        <v>85</v>
+      </c>
+      <c r="E110" s="3">
+        <f>+[28]Main!$I$2</f>
+        <v>3.28</v>
+      </c>
+      <c r="F110" s="14">
+        <f>+[28]Main!$I$4*FX!C3</f>
+        <v>372.96258964800001</v>
+      </c>
+      <c r="G110" s="14">
+        <f>+([28]Main!$I$6-[28]Main!$I$5)*FX!C3</f>
+        <v>50.842859999999995</v>
+      </c>
+      <c r="H110" s="14">
+        <f>+F110+G110</f>
+        <v>423.80544964799998</v>
+      </c>
+      <c r="I110" s="15" t="s">
+        <v>241</v>
+      </c>
       <c r="J110" s="3"/>
       <c r="K110" s="3"/>
       <c r="L110" s="3"/>
@@ -10242,7 +10303,9 @@
       <c r="P110" s="3"/>
       <c r="Q110" s="3"/>
       <c r="R110" s="3"/>
-      <c r="S110" s="3"/>
+      <c r="S110" s="3" t="s">
+        <v>276</v>
+      </c>
       <c r="T110" s="3"/>
       <c r="U110" s="3"/>
       <c r="V110" s="3"/>
@@ -10276,13 +10339,13 @@
         <v>108</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>153</v>
+        <v>94</v>
       </c>
       <c r="E111" s="3"/>
       <c r="F111" s="21"/>
@@ -10332,13 +10395,13 @@
         <v>109</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>259</v>
+        <v>153</v>
       </c>
       <c r="E112" s="3"/>
       <c r="F112" s="21"/>
@@ -10387,14 +10450,14 @@
         <f t="shared" si="2"/>
         <v>110</v>
       </c>
-      <c r="B113" s="32" t="s">
-        <v>479</v>
-      </c>
-      <c r="C113" s="32" t="s">
-        <v>480</v>
-      </c>
-      <c r="D113" s="32" t="s">
-        <v>26</v>
+      <c r="B113" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>259</v>
       </c>
       <c r="E113" s="3"/>
       <c r="F113" s="21"/>
@@ -16415,32 +16478,33 @@
   <hyperlinks>
     <hyperlink ref="B5" r:id="rId1" xr:uid="{28DCB031-FE72-4DDD-A270-8F54C33B0D07}"/>
     <hyperlink ref="B4" r:id="rId2" xr:uid="{26E5ABC1-BB04-437E-9206-F1C20901DED0}"/>
-    <hyperlink ref="B23" r:id="rId3" xr:uid="{90530EB5-2052-4CB4-AF13-B31111EBF67A}"/>
-    <hyperlink ref="B22" r:id="rId4" xr:uid="{7F153815-6E43-4099-8156-DC87E23678F8}"/>
-    <hyperlink ref="B19" r:id="rId5" xr:uid="{5DC12985-47BA-47C6-AD3C-158905087A9F}"/>
+    <hyperlink ref="B24" r:id="rId3" xr:uid="{90530EB5-2052-4CB4-AF13-B31111EBF67A}"/>
+    <hyperlink ref="B23" r:id="rId4" xr:uid="{7F153815-6E43-4099-8156-DC87E23678F8}"/>
+    <hyperlink ref="B20" r:id="rId5" xr:uid="{5DC12985-47BA-47C6-AD3C-158905087A9F}"/>
     <hyperlink ref="B16" r:id="rId6" xr:uid="{EF84B852-0E40-42BE-B540-DAB2CF38A7D8}"/>
-    <hyperlink ref="B25" r:id="rId7" xr:uid="{0B1A5131-7333-432D-A872-CF71A7AC0540}"/>
+    <hyperlink ref="B26" r:id="rId7" xr:uid="{0B1A5131-7333-432D-A872-CF71A7AC0540}"/>
     <hyperlink ref="B17" r:id="rId8" xr:uid="{B0DA5556-145A-4727-8860-850C98EAB410}"/>
-    <hyperlink ref="B26" r:id="rId9" xr:uid="{1C45EE99-8D08-4692-8B5C-4824C1CCC008}"/>
+    <hyperlink ref="B27" r:id="rId9" xr:uid="{1C45EE99-8D08-4692-8B5C-4824C1CCC008}"/>
     <hyperlink ref="B15" r:id="rId10" xr:uid="{6B4B6886-7033-490D-8BAB-89F16B58D022}"/>
-    <hyperlink ref="B40" r:id="rId11" xr:uid="{01B4B332-C402-42FD-907A-B7441FE22791}"/>
+    <hyperlink ref="B41" r:id="rId11" xr:uid="{01B4B332-C402-42FD-907A-B7441FE22791}"/>
     <hyperlink ref="B6" r:id="rId12" xr:uid="{29A8336F-7A8A-440D-81B6-8D61FB9E952D}"/>
-    <hyperlink ref="B20" r:id="rId13" xr:uid="{34693E39-C404-4A29-AF6E-04DFA48973B1}"/>
+    <hyperlink ref="B21" r:id="rId13" xr:uid="{34693E39-C404-4A29-AF6E-04DFA48973B1}"/>
     <hyperlink ref="B7" r:id="rId14" xr:uid="{AEC84F4B-AC96-4B2C-9742-70964CE88355}"/>
     <hyperlink ref="B8" r:id="rId15" xr:uid="{555CADF4-767E-4280-A32C-DE081D369605}"/>
     <hyperlink ref="B9" r:id="rId16" xr:uid="{ED0367BF-991D-42F3-9917-454450529D69}"/>
-    <hyperlink ref="B49" r:id="rId17" xr:uid="{A2CCB87B-50A6-4FAC-A784-BCC99C531A0C}"/>
-    <hyperlink ref="B107" r:id="rId18" xr:uid="{924ECF37-F972-4517-97AA-A46CB7071D84}"/>
-    <hyperlink ref="B109" r:id="rId19" xr:uid="{32F77D75-54CA-47B0-850A-36529751389F}"/>
-    <hyperlink ref="B38" r:id="rId20" xr:uid="{56071FD0-D9F8-4DBC-B271-5B6B3208455E}"/>
+    <hyperlink ref="B50" r:id="rId17" xr:uid="{A2CCB87B-50A6-4FAC-A784-BCC99C531A0C}"/>
+    <hyperlink ref="B108" r:id="rId18" xr:uid="{924ECF37-F972-4517-97AA-A46CB7071D84}"/>
+    <hyperlink ref="B110" r:id="rId19" xr:uid="{32F77D75-54CA-47B0-850A-36529751389F}"/>
+    <hyperlink ref="B39" r:id="rId20" xr:uid="{56071FD0-D9F8-4DBC-B271-5B6B3208455E}"/>
     <hyperlink ref="B10" r:id="rId21" xr:uid="{4E90805E-1BC8-4B3F-BBEA-AFE55F664C5A}"/>
-    <hyperlink ref="B29" r:id="rId22" xr:uid="{C7A221F5-614C-4C4A-B853-965FC1172BC6}"/>
-    <hyperlink ref="B21" r:id="rId23" xr:uid="{36029B94-59A5-4E11-BE00-520EEA9982EA}"/>
-    <hyperlink ref="B31" r:id="rId24" xr:uid="{456E081E-4795-42B4-A042-215BC3BDE8AD}"/>
-    <hyperlink ref="B104" r:id="rId25" xr:uid="{6D51229C-82B9-4B3B-8BCD-7E2D8D8D1697}"/>
-    <hyperlink ref="B28" r:id="rId26" xr:uid="{725EC800-EAC4-45CD-844A-DCF52C2E49D3}"/>
-    <hyperlink ref="B56" r:id="rId27" xr:uid="{34044582-871E-46CA-BEE4-6F8CE2992A03}"/>
-    <hyperlink ref="B46" r:id="rId28" xr:uid="{373784ED-2071-41B3-AA12-4F7A1FE107EB}"/>
+    <hyperlink ref="B30" r:id="rId22" xr:uid="{C7A221F5-614C-4C4A-B853-965FC1172BC6}"/>
+    <hyperlink ref="B22" r:id="rId23" xr:uid="{36029B94-59A5-4E11-BE00-520EEA9982EA}"/>
+    <hyperlink ref="B32" r:id="rId24" xr:uid="{456E081E-4795-42B4-A042-215BC3BDE8AD}"/>
+    <hyperlink ref="B105" r:id="rId25" xr:uid="{6D51229C-82B9-4B3B-8BCD-7E2D8D8D1697}"/>
+    <hyperlink ref="B29" r:id="rId26" xr:uid="{725EC800-EAC4-45CD-844A-DCF52C2E49D3}"/>
+    <hyperlink ref="B57" r:id="rId27" xr:uid="{34044582-871E-46CA-BEE4-6F8CE2992A03}"/>
+    <hyperlink ref="B47" r:id="rId28" xr:uid="{373784ED-2071-41B3-AA12-4F7A1FE107EB}"/>
+    <hyperlink ref="B18" r:id="rId29" xr:uid="{23A47D69-4386-4E38-8AD5-1AC2221DA4C3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Entertainment.xlsx
+++ b/Entertainment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8698638F-2AF4-44B0-B18C-D16BC7A03E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F27B40CC-A606-45B6-9D44-DEE6CC6ADE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
+    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -60,6 +60,8 @@
     <externalReference r:id="rId43"/>
     <externalReference r:id="rId44"/>
     <externalReference r:id="rId45"/>
+    <externalReference r:id="rId46"/>
+    <externalReference r:id="rId47"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$A$1:$J$113</definedName>
@@ -85,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="481">
   <si>
     <t>Name</t>
   </si>
@@ -819,9 +821,6 @@
     <t>FQ224</t>
   </si>
   <si>
-    <t>Market Cap</t>
-  </si>
-  <si>
     <t>EUR/USD</t>
   </si>
   <si>
@@ -1528,6 +1527,9 @@
   </si>
   <si>
     <t>9992.HK</t>
+  </si>
+  <si>
+    <t>Q126</t>
   </si>
 </sst>
 </file>
@@ -1539,13 +1541,25 @@
     <numFmt numFmtId="165" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1702,69 +1716,73 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1871,6 +1889,45 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>256.39999999999998</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>340780.2144</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>13765.710999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
       <sheetName val="Financials"/>
     </sheetNames>
     <sheetDataSet>
@@ -1902,7 +1959,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1941,7 +1998,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1980,7 +2037,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2019,7 +2076,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2058,7 +2115,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2097,7 +2154,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2111,32 +2168,32 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>35.83</v>
+            <v>33.81</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>18644.53591988</v>
+            <v>17624.033178990001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>802</v>
+            <v>527</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>3955</v>
+            <v>4363</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2166,45 +2223,6 @@
         <row r="6">
           <cell r="I6">
             <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>16735</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>2268554.6620899998</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>285700</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>59895</v>
           </cell>
         </row>
       </sheetData>
@@ -2280,6 +2298,45 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
+          <cell r="I2">
+            <v>16735</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>2268554.6620899998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>285700</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>59895</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
           <cell r="J2">
             <v>184.82</v>
           </cell>
@@ -2306,7 +2363,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2345,7 +2402,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2384,7 +2441,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2423,7 +2480,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2437,12 +2494,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="G2">
-            <v>18.649999999999999</v>
+            <v>17.309999999999999</v>
           </cell>
         </row>
         <row r="4">
           <cell r="G4">
-            <v>6195.53</v>
+            <v>5750.3819999999996</v>
           </cell>
         </row>
         <row r="5">
@@ -2462,7 +2519,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2501,7 +2558,46 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>5310</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>328662.32786999998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>104775</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>12486</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2540,7 +2636,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2574,86 +2670,6 @@
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>3.28</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>362.09960159999997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>4.45</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>53.811999999999998</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>559.02</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>4155288.66918858</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>94565</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>40152</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2711,6 +2727,86 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
+          <cell r="I2">
+            <v>3.28</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>362.09960159999997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>4.45</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>53.811999999999998</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>559.02</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>4155288.66918858</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>94565</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>40152</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
           <cell r="G2">
             <v>617.5</v>
           </cell>
@@ -2737,7 +2833,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2776,7 +2872,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2810,7 +2906,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2849,7 +2945,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2888,7 +2984,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2927,7 +3023,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2966,7 +3062,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3000,82 +3096,6 @@
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>52.09</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>8540.3870921399994</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>492.94499999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>78.55</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="K4">
-            <v>7215.2325581999994</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="K5">
-            <v>3147</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="K6">
-            <v>4564</v>
-          </cell>
-        </row>
-      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3134,6 +3154,82 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
+            <v>52.09</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>8540.3870921399994</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>492.94499999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>78.55</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="K4">
+            <v>7215.2325581999994</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="K5">
+            <v>3147</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="K6">
+            <v>4564</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
             <v>1.2</v>
           </cell>
         </row>
@@ -3159,7 +3255,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3172,23 +3268,23 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="I2">
-            <v>256.39999999999998</v>
+          <cell r="J2">
+            <v>3555</v>
           </cell>
         </row>
         <row r="4">
-          <cell r="I4">
-            <v>340780.2144</v>
+          <cell r="J4">
+            <v>520979.16739500005</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="I5">
-            <v>13765.710999999999</v>
+          <cell r="J5">
+            <v>133399</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="I6">
-            <v>0</v>
+          <cell r="J6">
+            <v>26577</v>
           </cell>
         </row>
       </sheetData>
@@ -3231,7 +3327,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3251,17 +3347,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>10935</v>
+            <v>12800</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>14201175.15</v>
+            <v>16623232</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>1484350</v>
+            <v>1586275</v>
           </cell>
         </row>
         <row r="6">
@@ -3270,7 +3366,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3725,7 +3821,7 @@
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -3837,20 +3933,20 @@
       <c r="E3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="G3" s="7" t="s">
+      <c r="F3" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>53</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>5</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
@@ -3861,7 +3957,7 @@
       <c r="Q3" s="8"/>
       <c r="R3" s="8"/>
       <c r="S3" s="9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="T3" s="7"/>
       <c r="U3" s="7"/>
@@ -3920,7 +4016,7 @@
         <v>538945.61542000005</v>
       </c>
       <c r="I4" s="29" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -3932,7 +4028,7 @@
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="S4" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
@@ -3992,7 +4088,7 @@
         <v>239148.98580144002</v>
       </c>
       <c r="I5" s="15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J5" s="17">
         <v>45966</v>
@@ -4006,7 +4102,7 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="S5" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
@@ -4066,7 +4162,7 @@
         <v>216785.26802767999</v>
       </c>
       <c r="I6" s="30" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -4078,7 +4174,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="S6" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
@@ -4150,7 +4246,7 @@
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
       <c r="S7" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
@@ -4210,7 +4306,7 @@
         <v>124178.28512867499</v>
       </c>
       <c r="I8" s="31" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -4222,7 +4318,7 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
@@ -4267,19 +4363,19 @@
       </c>
       <c r="E9" s="13">
         <f>+[6]Main!$I$2</f>
-        <v>10935</v>
+        <v>12800</v>
       </c>
       <c r="F9" s="14">
         <f>+[6]Main!$I$4*FX!C2</f>
-        <v>90887.520960000009</v>
+        <v>106388.6848</v>
       </c>
       <c r="G9" s="14">
         <f>+([6]Main!$I$6-[6]Main!$I$5)*FX!C2</f>
-        <v>-9499.84</v>
+        <v>-10152.16</v>
       </c>
       <c r="H9" s="14">
         <f t="shared" si="0"/>
-        <v>81387.680960000012</v>
+        <v>96236.524799999999</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>243</v>
@@ -4294,7 +4390,7 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="S9" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
@@ -4354,7 +4450,7 @@
         <v>83165.487704910003</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -4648,7 +4744,7 @@
         <v>42130.925609900005</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="J15" s="17">
         <v>45958</v>
@@ -4662,7 +4758,7 @@
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
       <c r="S15" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
@@ -4722,7 +4818,7 @@
         <v>80852.00014484</v>
       </c>
       <c r="I16" s="31" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -4734,7 +4830,7 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
@@ -4806,7 +4902,7 @@
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
       <c r="S17" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
@@ -4841,24 +4937,24 @@
         <v>15</v>
       </c>
       <c r="B18" s="12" t="s">
+        <v>478</v>
+      </c>
+      <c r="C18" s="32" t="s">
         <v>479</v>
-      </c>
-      <c r="C18" s="32" t="s">
-        <v>480</v>
       </c>
       <c r="D18" s="32" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="3">
-        <f>+[41]Main!$I$2</f>
+        <f>+[11]Main!$I$2</f>
         <v>256.39999999999998</v>
       </c>
       <c r="F18" s="21">
-        <f>+[41]Main!$I$4*FX!C6</f>
+        <f>+[11]Main!$I$4*FX!C6</f>
         <v>47709.230016000001</v>
       </c>
       <c r="G18" s="14">
-        <f>+([41]Main!$I$6-[41]Main!$I$5)*FX!C6</f>
+        <f>+([11]Main!$I$6-[11]Main!$I$5)*FX!C6</f>
         <v>-1927.1995400000001</v>
       </c>
       <c r="H18" s="14">
@@ -4866,7 +4962,7 @@
         <v>45782.030476</v>
       </c>
       <c r="I18" s="33" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
@@ -4976,15 +5072,15 @@
         <v>22</v>
       </c>
       <c r="E20" s="3">
-        <f>+[11]Main!$L$3</f>
+        <f>+[12]Main!$L$3</f>
         <v>228.01</v>
       </c>
       <c r="F20" s="14">
-        <f>+[11]Main!$L$5</f>
+        <f>+[12]Main!$L$5</f>
         <v>42061.053038120001</v>
       </c>
       <c r="G20" s="14">
-        <f>+[11]Main!$L$7-[11]Main!$L$6</f>
+        <f>+[12]Main!$L$7-[12]Main!$L$6</f>
         <v>1030</v>
       </c>
       <c r="H20" s="14">
@@ -4992,7 +5088,7 @@
         <v>43091.053038120001</v>
       </c>
       <c r="I20" s="15" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
@@ -5004,7 +5100,7 @@
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
       <c r="S20" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
@@ -5048,15 +5144,15 @@
         <v>22</v>
       </c>
       <c r="E21" s="18">
-        <f>+[12]Main!$H$2</f>
+        <f>+[13]Main!$H$2</f>
         <v>134.9</v>
       </c>
       <c r="F21" s="14">
-        <f>+[12]Main!$H$4</f>
+        <f>+[13]Main!$H$4</f>
         <v>31344.512106500002</v>
       </c>
       <c r="G21" s="14">
-        <f>+[12]Main!$H$6-[12]Main!$H$5</f>
+        <f>+[13]Main!$H$6-[13]Main!$H$5</f>
         <v>764.97299999999996</v>
       </c>
       <c r="H21" s="14">
@@ -5076,7 +5172,7 @@
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
       <c r="S21" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
@@ -5120,15 +5216,15 @@
         <v>50</v>
       </c>
       <c r="E22" s="3">
-        <f>+[13]Main!$I$2</f>
+        <f>+[14]Main!$I$2</f>
         <v>66.67</v>
       </c>
       <c r="F22" s="14">
-        <f>+[13]Main!$I$4*FX!C5</f>
+        <f>+[14]Main!$I$4*FX!C5</f>
         <v>26732.303286336904</v>
       </c>
       <c r="G22" s="14">
-        <f>+([13]Main!$I$6-[13]Main!$I$5)*FX!C5</f>
+        <f>+([14]Main!$I$6-[14]Main!$I$5)*FX!C5</f>
         <v>718.45199999999988</v>
       </c>
       <c r="H22" s="14">
@@ -5136,7 +5232,7 @@
         <v>27450.755286336906</v>
       </c>
       <c r="I22" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
@@ -5148,7 +5244,7 @@
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
       <c r="S22" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
@@ -5192,15 +5288,15 @@
         <v>22</v>
       </c>
       <c r="E23" s="3">
-        <f>+[14]Main!$H$2</f>
+        <f>+[15]Main!$H$2</f>
         <v>11.87</v>
       </c>
       <c r="F23" s="14">
-        <f>+[14]Main!$H$4</f>
+        <f>+[15]Main!$H$4</f>
         <v>29387.416987339999</v>
       </c>
       <c r="G23" s="14">
-        <f>+[14]Main!$H$6-[14]Main!$H$5</f>
+        <f>+[15]Main!$H$6-[15]Main!$H$5</f>
         <v>29744</v>
       </c>
       <c r="H23" s="14">
@@ -5208,7 +5304,7 @@
         <v>59131.416987339995</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J23" s="17">
         <v>45967</v>
@@ -5222,7 +5318,7 @@
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
       <c r="S23" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
@@ -5266,15 +5362,15 @@
         <v>22</v>
       </c>
       <c r="E24" s="3">
-        <f>+[15]Main!$G$3</f>
+        <f>+[16]Main!$G$3</f>
         <v>95</v>
       </c>
       <c r="F24" s="14">
-        <f>+[15]Main!$G$5</f>
+        <f>+[16]Main!$G$5</f>
         <v>23679.881450000001</v>
       </c>
       <c r="G24" s="14">
-        <f>+[15]Main!$G$7-[15]Main!$G$6</f>
+        <f>+[16]Main!$G$7-[16]Main!$G$6</f>
         <v>1592</v>
       </c>
       <c r="H24" s="14">
@@ -5282,7 +5378,7 @@
         <v>25271.881450000001</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
@@ -5294,7 +5390,7 @@
       <c r="Q24" s="3"/>
       <c r="R24" s="3"/>
       <c r="S24" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
@@ -5394,15 +5490,15 @@
         <v>22</v>
       </c>
       <c r="E26" s="3">
-        <f>+[16]Main!$G$2</f>
+        <f>+[17]Main!$G$2</f>
         <v>45.96</v>
       </c>
       <c r="F26" s="14">
-        <f>+[16]Main!$G$4</f>
+        <f>+[17]Main!$G$4</f>
         <v>22817.764463160001</v>
       </c>
       <c r="G26" s="14">
-        <f>+[16]Main!$G$6-[16]Main!$G$5</f>
+        <f>+[17]Main!$G$6-[17]Main!$G$5</f>
         <v>-669.26499999999999</v>
       </c>
       <c r="H26" s="14">
@@ -5410,7 +5506,7 @@
         <v>22148.499463160002</v>
       </c>
       <c r="I26" s="15" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
@@ -5422,7 +5518,7 @@
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
       <c r="S26" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
@@ -5466,20 +5562,20 @@
         <v>22</v>
       </c>
       <c r="E27" s="3">
-        <f>+[17]Main!$H$2</f>
-        <v>35.83</v>
+        <f>+[18]Main!$H$2</f>
+        <v>33.81</v>
       </c>
       <c r="F27" s="14">
-        <f>+[17]Main!$H$4</f>
-        <v>18644.53591988</v>
+        <f>+[18]Main!$H$4</f>
+        <v>17624.033178990001</v>
       </c>
       <c r="G27" s="14">
-        <f>+[17]Main!$H$6-[17]Main!$H$5</f>
-        <v>3153</v>
+        <f>+[18]Main!$H$6-[18]Main!$H$5</f>
+        <v>3836</v>
       </c>
       <c r="H27" s="14">
         <f>+F27+G27</f>
-        <v>21797.53591988</v>
+        <v>21460.033178990001</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>241</v>
@@ -5494,7 +5590,7 @@
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
       <c r="S27" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
@@ -5594,15 +5690,15 @@
         <v>23</v>
       </c>
       <c r="E29" s="19">
-        <f>+[18]Main!$I$2</f>
+        <f>+[19]Main!$I$2</f>
         <v>5241</v>
       </c>
       <c r="F29" s="14">
-        <f>+[18]Main!$I$4*FX!C2</f>
+        <f>+[19]Main!$I$4*FX!C2</f>
         <v>21944.563863571202</v>
       </c>
       <c r="G29" s="14">
-        <f>+([18]Main!$I$6-[18]Main!$I$5)*FX!C2</f>
+        <f>+([19]Main!$I$6-[19]Main!$I$5)*FX!C2</f>
         <v>-2059.9551999999999</v>
       </c>
       <c r="H29" s="14">
@@ -5662,15 +5758,15 @@
         <v>23</v>
       </c>
       <c r="E30" s="19">
-        <f>+[19]Main!$I$2</f>
+        <f>+[20]Main!$I$2</f>
         <v>16735</v>
       </c>
       <c r="F30" s="14">
-        <f>+[19]Main!$I$4*FX!C2</f>
+        <f>+[20]Main!$I$4*FX!C2</f>
         <v>14518.749837375999</v>
       </c>
       <c r="G30" s="14">
-        <f>+([19]Main!$I$6-[19]Main!$I$5)*FX!C2</f>
+        <f>+([20]Main!$I$6-[20]Main!$I$5)*FX!C2</f>
         <v>-1445.152</v>
       </c>
       <c r="H30" s="14">
@@ -5678,7 +5774,7 @@
         <v>13073.597837375999</v>
       </c>
       <c r="I30" s="15" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
@@ -5788,15 +5884,15 @@
         <v>22</v>
       </c>
       <c r="E32" s="3">
-        <f>+[20]Main!$J$2</f>
+        <f>+[21]Main!$J$2</f>
         <v>184.82</v>
       </c>
       <c r="F32" s="14">
-        <f>+[20]Main!$J$4</f>
+        <f>+[21]Main!$J$4</f>
         <v>15180.539270520001</v>
       </c>
       <c r="G32" s="14">
-        <f>+[20]Main!$J$6-[20]Main!$J$5</f>
+        <f>+[21]Main!$J$6-[21]Main!$J$5</f>
         <v>2214.2530000000002</v>
       </c>
       <c r="H32" s="14">
@@ -5804,7 +5900,7 @@
         <v>17394.79227052</v>
       </c>
       <c r="I32" s="15" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
@@ -6194,15 +6290,15 @@
         <v>22</v>
       </c>
       <c r="E39" s="3">
-        <f>+[21]Main!$H$2</f>
+        <f>+[22]Main!$H$2</f>
         <v>65.319999999999993</v>
       </c>
       <c r="F39" s="14">
-        <f>+[21]Main!$H$4</f>
+        <f>+[22]Main!$H$4</f>
         <v>9114.1865409199982</v>
       </c>
       <c r="G39" s="14">
-        <f>+[21]Main!$H$6-[21]Main!$H$5</f>
+        <f>+[22]Main!$H$6-[22]Main!$H$5</f>
         <v>2685.8</v>
       </c>
       <c r="H39" s="14">
@@ -6210,7 +6306,7 @@
         <v>11799.986540919999</v>
       </c>
       <c r="I39" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
@@ -6222,7 +6318,7 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
@@ -6316,29 +6412,29 @@
         <v>90</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E41" s="3">
-        <f>+[22]Main!$I$2</f>
+        <f>+[23]Main!$I$2</f>
         <v>13.8</v>
       </c>
       <c r="F41" s="14">
-        <f>+[22]Main!$I$4</f>
+        <f>+[23]Main!$I$4</f>
         <v>9315</v>
       </c>
       <c r="G41" s="14">
-        <f>+[22]Main!$I$6-[22]Main!$I$5</f>
+        <f>+[23]Main!$I$6-[23]Main!$I$5</f>
         <v>11775</v>
       </c>
       <c r="H41" s="14">
         <f>+F41+G41</f>
         <v>21090</v>
       </c>
-      <c r="I41" s="15" t="s">
-        <v>246</v>
+      <c r="I41" s="34" t="s">
+        <v>473</v>
       </c>
       <c r="J41" s="3"/>
       <c r="K41" s="3"/>
@@ -6350,7 +6446,7 @@
       <c r="Q41" s="3"/>
       <c r="R41" s="3"/>
       <c r="S41" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T41" s="3"/>
       <c r="U41" s="3"/>
@@ -6674,15 +6770,15 @@
         <v>22</v>
       </c>
       <c r="E47" s="3">
-        <f>+[23]Main!$I$2</f>
+        <f>+[24]Main!$I$2</f>
         <v>77.77</v>
       </c>
       <c r="F47" s="14">
-        <f>+[23]Main!$I$4</f>
+        <f>+[24]Main!$I$4</f>
         <v>6330.7175316000003</v>
       </c>
       <c r="G47" s="14">
-        <f>+[23]Main!$I$6-[23]Main!$I$5</f>
+        <f>+[24]Main!$I$6-[24]Main!$I$5</f>
         <v>3205.0709999999999</v>
       </c>
       <c r="H47" s="14">
@@ -6690,7 +6786,7 @@
         <v>9535.7885315999993</v>
       </c>
       <c r="I47" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
@@ -6856,23 +6952,23 @@
         <v>22</v>
       </c>
       <c r="E50" s="3">
-        <f>+[24]Main!$G$2</f>
-        <v>18.649999999999999</v>
+        <f>+[25]Main!$G$2</f>
+        <v>17.309999999999999</v>
       </c>
       <c r="F50" s="14">
-        <f>+[24]Main!$G$4</f>
-        <v>6195.53</v>
+        <f>+[25]Main!$G$4</f>
+        <v>5750.3819999999996</v>
       </c>
       <c r="G50" s="14">
-        <f>+[24]Main!$G$6-[24]Main!$G$5</f>
+        <f>+[25]Main!$G$6-[25]Main!$G$5</f>
         <v>1466.0810000000004</v>
       </c>
       <c r="H50" s="14">
         <f>+F50+G50</f>
-        <v>7661.6109999999999</v>
-      </c>
-      <c r="I50" s="15" t="s">
-        <v>239</v>
+        <v>7216.4629999999997</v>
+      </c>
+      <c r="I50" s="34" t="s">
+        <v>473</v>
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
@@ -6884,7 +6980,7 @@
       <c r="Q50" s="3"/>
       <c r="R50" s="3"/>
       <c r="S50" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="T50" s="3"/>
       <c r="U50" s="3"/>
@@ -7264,15 +7360,15 @@
         <v>22</v>
       </c>
       <c r="E57" s="3">
-        <f>+[25]Main!$I$2</f>
+        <f>+[26]Main!$I$2</f>
         <v>183.2</v>
       </c>
       <c r="F57" s="14">
-        <f>+[25]Main!$I$4</f>
+        <f>+[26]Main!$I$4</f>
         <v>5589.2865391999994</v>
       </c>
       <c r="G57" s="14">
-        <f>+[25]Main!$I$6-[25]Main!$I$5</f>
+        <f>+[26]Main!$I$6-[26]Main!$I$5</f>
         <v>6379</v>
       </c>
       <c r="H57" s="14">
@@ -7280,7 +7376,7 @@
         <v>11968.286539199999</v>
       </c>
       <c r="I57" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J57" s="3"/>
       <c r="K57" s="3"/>
@@ -8780,7 +8876,7 @@
         <f t="shared" si="2"/>
         <v>81</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B84" s="12" t="s">
         <v>185</v>
       </c>
       <c r="C84" s="3" t="s">
@@ -8789,11 +8885,25 @@
       <c r="D84" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E84" s="3"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
-      <c r="H84" s="14"/>
-      <c r="I84" s="15"/>
+      <c r="E84" s="35">
+        <f>+[43]Main!$J$2</f>
+        <v>3555</v>
+      </c>
+      <c r="F84" s="14">
+        <f>+[43]Main!$J$4*FX!C2</f>
+        <v>3334.2666713280005</v>
+      </c>
+      <c r="G84" s="14">
+        <f>+([43]Main!$J$6-[43]Main!$J$5)*FX!C2</f>
+        <v>-683.66079999999999</v>
+      </c>
+      <c r="H84" s="14">
+        <f>+F84+G84</f>
+        <v>2650.6058713280004</v>
+      </c>
+      <c r="I84" s="34" t="s">
+        <v>480</v>
+      </c>
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
       <c r="L84" s="3"/>
@@ -9284,7 +9394,7 @@
         <f t="shared" si="2"/>
         <v>90</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B93" s="12" t="s">
         <v>207</v>
       </c>
       <c r="C93" s="3" t="s">
@@ -9293,11 +9403,25 @@
       <c r="D93" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E93" s="3"/>
-      <c r="F93" s="14"/>
-      <c r="G93" s="14"/>
-      <c r="H93" s="14"/>
-      <c r="I93" s="3"/>
+      <c r="E93" s="3">
+        <f>+[27]Main!$I$2</f>
+        <v>5310</v>
+      </c>
+      <c r="F93" s="14">
+        <f>+[27]Main!$I$4*FX!C2</f>
+        <v>2103.4388983680001</v>
+      </c>
+      <c r="G93" s="14">
+        <f>+([27]Main!$I$6-[27]Main!$I$5)*FX!C2</f>
+        <v>-590.64960000000008</v>
+      </c>
+      <c r="H93" s="14">
+        <f>+F93+G93</f>
+        <v>1512.7892983679999</v>
+      </c>
+      <c r="I93" s="34" t="s">
+        <v>480</v>
+      </c>
       <c r="J93" s="3"/>
       <c r="K93" s="3"/>
       <c r="L93" s="3"/>
@@ -9844,7 +9968,7 @@
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="B103" s="3" t="s">
+      <c r="B103" s="12" t="s">
         <v>227</v>
       </c>
       <c r="C103" s="3" t="s">
@@ -9966,15 +10090,15 @@
         <v>22</v>
       </c>
       <c r="E105" s="3">
-        <f>+[26]Main!$I$2</f>
+        <f>+[28]Main!$I$2</f>
         <v>33.76</v>
       </c>
       <c r="F105" s="14">
-        <f>+[26]Main!$I$4</f>
+        <f>+[28]Main!$I$4</f>
         <v>1615.1327198399999</v>
       </c>
       <c r="G105" s="14">
-        <f>+[26]Main!$I$6-[26]Main!$I$5</f>
+        <f>+[28]Main!$I$6-[28]Main!$I$5</f>
         <v>553.85699999999997</v>
       </c>
       <c r="H105" s="14">
@@ -10139,24 +10263,24 @@
         <v>105</v>
       </c>
       <c r="B108" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="C108" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="C108" s="3" t="s">
-        <v>248</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>153</v>
       </c>
       <c r="E108" s="3">
-        <f>+[27]Main!$H$2</f>
+        <f>+[29]Main!$H$2</f>
         <v>15.92</v>
       </c>
       <c r="F108" s="14">
-        <f>+[27]Main!$H$5*FX!C4</f>
+        <f>+[29]Main!$H$5*FX!C4</f>
         <v>2707.3869572160002</v>
       </c>
       <c r="G108" s="14">
-        <f>+([27]Main!$H$7-[27]Main!$H$6)*FX!C4</f>
+        <f>+([29]Main!$H$7-[29]Main!$H$6)*FX!C4</f>
         <v>699.94651999999996</v>
       </c>
       <c r="H108" s="14">
@@ -10164,7 +10288,7 @@
         <v>3407.3334772160001</v>
       </c>
       <c r="I108" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J108" s="3"/>
       <c r="K108" s="3"/>
@@ -10176,7 +10300,7 @@
       <c r="Q108" s="3"/>
       <c r="R108" s="3"/>
       <c r="S108" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="T108" s="3"/>
       <c r="U108" s="3"/>
@@ -10211,10 +10335,10 @@
         <v>106</v>
       </c>
       <c r="B109" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C109" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="C109" s="3" t="s">
-        <v>250</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>160</v>
@@ -10267,24 +10391,24 @@
         <v>107</v>
       </c>
       <c r="B110" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="C110" s="3" t="s">
         <v>251</v>
-      </c>
-      <c r="C110" s="3" t="s">
-        <v>252</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>85</v>
       </c>
       <c r="E110" s="3">
-        <f>+[28]Main!$I$2</f>
+        <f>+[30]Main!$I$2</f>
         <v>3.28</v>
       </c>
       <c r="F110" s="14">
-        <f>+[28]Main!$I$4*FX!C3</f>
+        <f>+[30]Main!$I$4*FX!C3</f>
         <v>372.96258964800001</v>
       </c>
       <c r="G110" s="14">
-        <f>+([28]Main!$I$6-[28]Main!$I$5)*FX!C3</f>
+        <f>+([30]Main!$I$6-[30]Main!$I$5)*FX!C3</f>
         <v>50.842859999999995</v>
       </c>
       <c r="H110" s="14">
@@ -10304,7 +10428,7 @@
       <c r="Q110" s="3"/>
       <c r="R110" s="3"/>
       <c r="S110" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="T110" s="3"/>
       <c r="U110" s="3"/>
@@ -10339,10 +10463,10 @@
         <v>108</v>
       </c>
       <c r="B111" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C111" s="3" t="s">
         <v>253</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>254</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>94</v>
@@ -10395,10 +10519,10 @@
         <v>109</v>
       </c>
       <c r="B112" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C112" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="C112" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>153</v>
@@ -10451,13 +10575,13 @@
         <v>110</v>
       </c>
       <c r="B113" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C113" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="C113" s="3" t="s">
+      <c r="D113" s="3" t="s">
         <v>258</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>259</v>
       </c>
       <c r="E113" s="3"/>
       <c r="F113" s="21"/>
@@ -10551,7 +10675,7 @@
     <row r="115" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A115" s="11"/>
       <c r="B115" s="22" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
@@ -10600,7 +10724,7 @@
     <row r="116" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A116" s="11"/>
       <c r="B116" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
@@ -16505,6 +16629,9 @@
     <hyperlink ref="B57" r:id="rId27" xr:uid="{34044582-871E-46CA-BEE4-6F8CE2992A03}"/>
     <hyperlink ref="B47" r:id="rId28" xr:uid="{373784ED-2071-41B3-AA12-4F7A1FE107EB}"/>
     <hyperlink ref="B18" r:id="rId29" xr:uid="{23A47D69-4386-4E38-8AD5-1AC2221DA4C3}"/>
+    <hyperlink ref="B103" r:id="rId30" xr:uid="{99A434BF-F5F7-467F-AB02-447D8D64F5FB}"/>
+    <hyperlink ref="B93" r:id="rId31" xr:uid="{04B6A34E-7F7B-490D-8880-75C12621EECA}"/>
+    <hyperlink ref="B84" r:id="rId32" xr:uid="{56024696-67B2-4803-B0DF-95A89BDC0A77}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16527,7 +16654,7 @@
   <sheetData>
     <row r="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -16601,7 +16728,7 @@
     </row>
     <row r="2" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -16681,7 +16808,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>21</v>
@@ -16690,7 +16817,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>53</v>
@@ -16699,7 +16826,7 @@
         <v>5</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J3" s="24"/>
       <c r="K3" s="25"/>
@@ -16766,7 +16893,7 @@
     <row r="4" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="25" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -16842,24 +16969,24 @@
         <v>1</v>
       </c>
       <c r="B5" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>285</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>286</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>22</v>
       </c>
       <c r="E5" s="26">
-        <f>+[29]Main!$H$2</f>
+        <f>+[31]Main!$H$2</f>
         <v>559.02</v>
       </c>
       <c r="F5" s="26">
-        <f>+[29]Main!$H$4</f>
+        <f>+[31]Main!$H$4</f>
         <v>4155288.66918858</v>
       </c>
       <c r="G5" s="26">
-        <f>+[29]Main!$H$6-[29]Main!$H$5</f>
+        <f>+[31]Main!$H$6-[31]Main!$H$5</f>
         <v>-54413</v>
       </c>
       <c r="H5" s="26">
@@ -16937,24 +17064,24 @@
         <v>2</v>
       </c>
       <c r="B6" s="12" t="s">
+        <v>286</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>288</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="26">
-        <f>+[30]Main!$G$2</f>
+        <f>+[32]Main!$G$2</f>
         <v>617.5</v>
       </c>
       <c r="F6" s="26">
-        <f>+[30]Main!$G$4*FX!C6</f>
+        <f>+[32]Main!$G$4*FX!C6</f>
         <v>1273.5800000000002</v>
       </c>
       <c r="G6" s="26">
-        <f>+([30]Main!$G$6-[30]Main!$G$5)*FX!C6</f>
+        <f>+([32]Main!$G$6-[32]Main!$G$5)*FX!C6</f>
         <v>-674313.59800000011</v>
       </c>
       <c r="H6" s="26">
@@ -17127,32 +17254,32 @@
         <v>4</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>289</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>290</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E8" s="26">
         <f>+[6]Main!$I$2</f>
-        <v>10935</v>
+        <v>12800</v>
       </c>
       <c r="F8" s="26">
         <f>+[6]Main!$I$4*FX!C2</f>
-        <v>90887.520960000009</v>
+        <v>106388.6848</v>
       </c>
       <c r="G8" s="26">
         <f>+([6]Main!$I$6-[6]Main!$I$5)*FX!C2</f>
-        <v>-9499.84</v>
+        <v>-10152.16</v>
       </c>
       <c r="H8" s="26">
         <f t="shared" si="0"/>
-        <v>81387.680960000012</v>
+        <v>96236.524799999999</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -17222,7 +17349,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>20</v>
@@ -17231,15 +17358,15 @@
         <v>26</v>
       </c>
       <c r="E9" s="26">
-        <f>+[31]Main!$I$2</f>
+        <f>+[33]Main!$I$2</f>
         <v>2123</v>
       </c>
       <c r="F9" s="26">
-        <f>+[32]Main!$H$5*FX!C6</f>
+        <f>+[34]Main!$H$5*FX!C6</f>
         <v>65131.275185760009</v>
       </c>
       <c r="G9" s="26">
-        <f>+([32]Main!$H$7-[32]Main!$H$6)*FX!C6</f>
+        <f>+([34]Main!$H$7-[34]Main!$H$6)*FX!C6</f>
         <v>-16042.82638</v>
       </c>
       <c r="H9" s="26">
@@ -17247,7 +17374,7 @@
         <v>49088.44880576001</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -17342,7 +17469,7 @@
         <v>83165.487704910003</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -17507,7 +17634,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>45</v>
@@ -17516,15 +17643,15 @@
         <v>22</v>
       </c>
       <c r="E12" s="26">
-        <f>+[11]Main!$L$3</f>
+        <f>+[12]Main!$L$3</f>
         <v>228.01</v>
       </c>
       <c r="F12" s="26">
-        <f>+[11]Main!$L$5</f>
+        <f>+[12]Main!$L$5</f>
         <v>42061.053038120001</v>
       </c>
       <c r="G12" s="26">
-        <f>+[11]Main!$L$7-[11]Main!$L$6</f>
+        <f>+[12]Main!$L$7-[12]Main!$L$6</f>
         <v>1030</v>
       </c>
       <c r="H12" s="26">
@@ -17627,7 +17754,7 @@
         <v>80852.00014484</v>
       </c>
       <c r="I13" s="15" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -17697,7 +17824,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>49</v>
@@ -17706,15 +17833,15 @@
         <v>50</v>
       </c>
       <c r="E14" s="26">
-        <f>+[13]Main!$I$2</f>
+        <f>+[14]Main!$I$2</f>
         <v>66.67</v>
       </c>
       <c r="F14" s="26">
-        <f>+[13]Main!$I$4*FX!C5</f>
+        <f>+[14]Main!$I$4*FX!C5</f>
         <v>26732.303286336904</v>
       </c>
       <c r="G14" s="26">
-        <f>+([13]Main!$I$6-[13]Main!$I$5)*FX!C5</f>
+        <f>+([14]Main!$I$6-[14]Main!$I$5)*FX!C5</f>
         <v>718.45199999999988</v>
       </c>
       <c r="H14" s="26">
@@ -17722,7 +17849,7 @@
         <v>27450.755286336906</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
@@ -17801,15 +17928,15 @@
         <v>23</v>
       </c>
       <c r="E15" s="26">
-        <f>+[31]Main!$I$2</f>
+        <f>+[33]Main!$I$2</f>
         <v>2123</v>
       </c>
       <c r="F15" s="26">
-        <f>+[31]Main!$I$4*FX!C2</f>
+        <f>+[33]Main!$I$4*FX!C2</f>
         <v>11429.0165977856</v>
       </c>
       <c r="G15" s="26">
-        <f>+([31]Main!$I$6-[31]Main!$I$5)*FX!C2</f>
+        <f>+([33]Main!$I$6-[33]Main!$I$5)*FX!C2</f>
         <v>-2117.3888000000002</v>
       </c>
       <c r="H15" s="26">
@@ -17817,7 +17944,7 @@
         <v>9311.6277977855989</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -17896,15 +18023,15 @@
         <v>23</v>
       </c>
       <c r="E16" s="26">
-        <f>+[18]Main!$I$2</f>
+        <f>+[19]Main!$I$2</f>
         <v>5241</v>
       </c>
       <c r="F16" s="26">
-        <f>+[18]Main!$I$4*FX!C2</f>
+        <f>+[19]Main!$I$4*FX!C2</f>
         <v>21944.563863571202</v>
       </c>
       <c r="G16" s="26">
-        <f>+([18]Main!$I$6-[18]Main!$I$5)*FX!C2</f>
+        <f>+([19]Main!$I$6-[19]Main!$I$5)*FX!C2</f>
         <v>-2059.9551999999999</v>
       </c>
       <c r="H16" s="26">
@@ -17912,7 +18039,7 @@
         <v>19884.608663571202</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -17991,15 +18118,15 @@
         <v>23</v>
       </c>
       <c r="E17" s="26">
-        <f>+[19]Main!$I$2</f>
+        <f>+[20]Main!$I$2</f>
         <v>16735</v>
       </c>
       <c r="F17" s="26">
-        <f>+[19]Main!$I$4*FX!C2</f>
+        <f>+[20]Main!$I$4*FX!C2</f>
         <v>14518.749837375999</v>
       </c>
       <c r="G17" s="26">
-        <f>+([19]Main!$I$6-[19]Main!$I$5)*FX!C2</f>
+        <f>+([20]Main!$I$6-[20]Main!$I$5)*FX!C2</f>
         <v>-1445.152</v>
       </c>
       <c r="H17" s="26">
@@ -18007,7 +18134,7 @@
         <v>13073.597837375999</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
@@ -18086,15 +18213,15 @@
         <v>94</v>
       </c>
       <c r="E18" s="26">
-        <f>+[33]Main!$H$2</f>
+        <f>+[35]Main!$H$2</f>
         <v>12.11</v>
       </c>
       <c r="F18" s="26">
-        <f>+[33]Main!$H$4*FX!C3</f>
+        <f>+[35]Main!$H$4*FX!C3</f>
         <v>1601.5717199999999</v>
       </c>
       <c r="G18" s="26">
-        <f>+([33]Main!$H$6-[33]Main!$H$5)*FX!C3</f>
+        <f>+([35]Main!$H$6-[35]Main!$H$5)*FX!C3</f>
         <v>1343.7380000000003</v>
       </c>
       <c r="H18" s="26">
@@ -18102,7 +18229,7 @@
         <v>2945.3097200000002</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
@@ -18241,7 +18368,7 @@
     <row r="20" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A20" s="11"/>
       <c r="B20" s="25" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -18315,24 +18442,24 @@
     <row r="21" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A21" s="11"/>
       <c r="B21" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>299</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E21" s="26">
-        <f>+[34]Main!$J$2</f>
+        <f>+[36]Main!$J$2</f>
         <v>21.7</v>
       </c>
       <c r="F21" s="26">
-        <f>+[34]Main!$J$4</f>
+        <f>+[36]Main!$J$4</f>
         <v>9701.7223876999997</v>
       </c>
       <c r="G21" s="26">
-        <f>+[34]Main!$J$6-[34]Main!$J$5</f>
+        <f>+[36]Main!$J$6-[36]Main!$J$5</f>
         <v>-4758</v>
       </c>
       <c r="H21" s="26">
@@ -18340,7 +18467,7 @@
         <v>4943.7223876999997</v>
       </c>
       <c r="I21" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
@@ -27512,7 +27639,7 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -27541,7 +27668,7 @@
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -27576,7 +27703,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>21</v>
@@ -27585,7 +27712,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>53</v>
@@ -27594,7 +27721,7 @@
         <v>5</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
@@ -27668,13 +27795,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>304</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>305</v>
       </c>
       <c r="E5" s="14"/>
       <c r="F5" s="14"/>
@@ -27710,7 +27837,7 @@
         <v>34</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E6" s="14"/>
       <c r="F6" s="14"/>
@@ -27740,7 +27867,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>52</v>
@@ -27749,15 +27876,15 @@
         <v>22</v>
       </c>
       <c r="E7" s="14">
-        <f>+[14]Main!$H$2</f>
+        <f>+[15]Main!$H$2</f>
         <v>11.87</v>
       </c>
       <c r="F7" s="14">
-        <f>+[14]Main!$H$4</f>
+        <f>+[15]Main!$H$4</f>
         <v>29387.416987339999</v>
       </c>
       <c r="G7" s="14">
-        <f>+[14]Main!$H$6-[14]Main!$H$5</f>
+        <f>+[15]Main!$H$6-[15]Main!$H$5</f>
         <v>29744</v>
       </c>
       <c r="H7" s="14">
@@ -27790,24 +27917,24 @@
         <v>5</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>307</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>308</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>309</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E8" s="14">
-        <f>+[35]Main!$I$2</f>
+        <f>+[37]Main!$I$2</f>
         <v>50.5</v>
       </c>
       <c r="F8" s="14">
-        <f>+[35]Main!$I$4</f>
+        <f>+[37]Main!$I$4</f>
         <v>22898.106829</v>
       </c>
       <c r="G8" s="14">
-        <f>+[35]Main!$I$6-[35]Main!$I$5</f>
+        <f>+[37]Main!$I$6-[37]Main!$I$5</f>
         <v>3878</v>
       </c>
       <c r="H8" s="14">
@@ -27840,13 +27967,13 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E9" s="14"/>
       <c r="F9" s="14"/>
@@ -27876,13 +28003,13 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>312</v>
-      </c>
       <c r="D10" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E10" s="14"/>
       <c r="F10" s="14"/>
@@ -27912,24 +28039,24 @@
         <v>8</v>
       </c>
       <c r="B11" s="12" t="s">
+        <v>312</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>313</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>314</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="14">
-        <f>+[36]Main!$I$2</f>
+        <f>+[38]Main!$I$2</f>
         <v>30.44</v>
       </c>
       <c r="F11" s="14">
-        <f>+[36]Main!$I$4</f>
+        <f>+[38]Main!$I$4</f>
         <v>17310.539416759999</v>
       </c>
       <c r="G11" s="14">
-        <f>+[36]Main!$I$6-[36]Main!$I$5</f>
+        <f>+[38]Main!$I$6-[38]Main!$I$5</f>
         <v>1122</v>
       </c>
       <c r="H11" s="14">
@@ -27962,10 +28089,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>315</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>316</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>22</v>
@@ -27998,24 +28125,24 @@
         <v>10</v>
       </c>
       <c r="B13" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>317</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>318</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E13" s="14">
-        <f>+[37]Main!$H$2</f>
+        <f>+[39]Main!$H$2</f>
         <v>41.21</v>
       </c>
       <c r="F13" s="14">
-        <f>+[37]Main!$H$4</f>
+        <f>+[39]Main!$H$4</f>
         <v>8939.4565020800001</v>
       </c>
       <c r="G13" s="14">
-        <f>+[37]Main!$H$6-[37]Main!$H$5</f>
+        <f>+[39]Main!$H$6-[39]Main!$H$5</f>
         <v>-663.44470000000001</v>
       </c>
       <c r="H13" s="14">
@@ -28048,24 +28175,24 @@
         <v>11</v>
       </c>
       <c r="B14" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>319</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>320</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E14" s="14">
-        <f>+[38]Main!$H$2</f>
+        <f>+[40]Main!$H$2</f>
         <v>52.09</v>
       </c>
       <c r="F14" s="14">
-        <f>+[38]Main!$H$4</f>
+        <f>+[40]Main!$H$4</f>
         <v>8540.3870921399994</v>
       </c>
       <c r="G14" s="14">
-        <f>+[38]Main!$H$6-[38]Main!$H$5</f>
+        <f>+[40]Main!$H$6-[40]Main!$H$5</f>
         <v>-492.94499999999999</v>
       </c>
       <c r="H14" s="14">
@@ -28098,7 +28225,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>91</v>
@@ -28107,15 +28234,15 @@
         <v>22</v>
       </c>
       <c r="E15" s="14">
-        <f>+[22]Main!$I$2</f>
+        <f>+[23]Main!$I$2</f>
         <v>13.8</v>
       </c>
       <c r="F15" s="14">
-        <f>+[22]Main!$I$4</f>
+        <f>+[23]Main!$I$4</f>
         <v>9315</v>
       </c>
       <c r="G15" s="14">
-        <f>+[22]Main!$I$6-[22]Main!$I$5</f>
+        <f>+[23]Main!$I$6-[23]Main!$I$5</f>
         <v>11775</v>
       </c>
       <c r="H15" s="14">
@@ -28123,7 +28250,7 @@
         <v>21090</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
@@ -28148,13 +28275,13 @@
         <v>13</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>323</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>324</v>
       </c>
       <c r="E16" s="14"/>
       <c r="F16" s="14"/>
@@ -28184,7 +28311,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>108</v>
@@ -28193,15 +28320,15 @@
         <v>22</v>
       </c>
       <c r="E17" s="14">
-        <f>+[39]Main!$K$2</f>
+        <f>+[41]Main!$K$2</f>
         <v>78.55</v>
       </c>
       <c r="F17" s="14">
-        <f>+[39]Main!$K$4</f>
+        <f>+[41]Main!$K$4</f>
         <v>7215.2325581999994</v>
       </c>
       <c r="G17" s="14">
-        <f>+[39]Main!$K$6-[39]Main!$K$5</f>
+        <f>+[41]Main!$K$6-[41]Main!$K$5</f>
         <v>1417</v>
       </c>
       <c r="H17" s="14">
@@ -28209,7 +28336,7 @@
         <v>8632.2325581999994</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
@@ -28234,13 +28361,13 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>327</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>328</v>
       </c>
       <c r="E18" s="14"/>
       <c r="F18" s="14"/>
@@ -28270,13 +28397,13 @@
         <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>330</v>
-      </c>
       <c r="D19" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E19" s="14"/>
       <c r="F19" s="14"/>
@@ -28306,7 +28433,7 @@
         <v>17</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>137</v>
@@ -28342,7 +28469,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>126</v>
@@ -28378,13 +28505,13 @@
         <v>19</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>334</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>335</v>
       </c>
       <c r="E22" s="14"/>
       <c r="F22" s="14"/>
@@ -28414,10 +28541,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>336</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>337</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>23</v>
@@ -28450,13 +28577,13 @@
         <v>21</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>339</v>
-      </c>
       <c r="D24" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E24" s="14"/>
       <c r="F24" s="14"/>
@@ -28486,10 +28613,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>340</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>341</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>22</v>
@@ -28522,10 +28649,10 @@
         <v>23</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>22</v>
@@ -28558,10 +28685,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>22</v>
@@ -28594,10 +28721,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>345</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>346</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>153</v>
@@ -28630,10 +28757,10 @@
         <v>26</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>347</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>348</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>22</v>
@@ -28702,13 +28829,13 @@
         <v>28</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="3" t="s">
         <v>350</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>351</v>
       </c>
       <c r="E31" s="14"/>
       <c r="F31" s="14"/>
@@ -28738,13 +28865,13 @@
         <v>29</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>174</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E32" s="14"/>
       <c r="F32" s="14"/>
@@ -28774,10 +28901,10 @@
         <v>30</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>354</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>355</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>22</v>
@@ -28810,13 +28937,13 @@
         <v>31</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>188</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E34" s="14"/>
       <c r="F34" s="14"/>
@@ -28846,7 +28973,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
@@ -28878,10 +29005,10 @@
         <v>33</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>358</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>359</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>22</v>
@@ -28914,13 +29041,13 @@
         <v>34</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>361</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>362</v>
       </c>
       <c r="E37" s="14"/>
       <c r="F37" s="14"/>
@@ -28950,13 +29077,13 @@
         <v>35</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>364</v>
-      </c>
       <c r="D38" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E38" s="14"/>
       <c r="F38" s="14"/>
@@ -28989,7 +29116,7 @@
         <v>219</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>160</v>
@@ -29022,13 +29149,13 @@
         <v>37</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>367</v>
-      </c>
       <c r="D40" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E40" s="14"/>
       <c r="F40" s="14"/>
@@ -29058,13 +29185,13 @@
         <v>38</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>369</v>
-      </c>
       <c r="D41" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E41" s="14"/>
       <c r="F41" s="14"/>
@@ -29094,13 +29221,13 @@
         <v>39</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>371</v>
-      </c>
       <c r="D42" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E42" s="14"/>
       <c r="F42" s="14"/>
@@ -29130,13 +29257,13 @@
         <v>40</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>373</v>
-      </c>
       <c r="D43" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E43" s="14"/>
       <c r="F43" s="14"/>
@@ -29166,10 +29293,10 @@
         <v>41</v>
       </c>
       <c r="B44" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>374</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>375</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>22</v>
@@ -29202,13 +29329,13 @@
         <v>42</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="D45" s="3" t="s">
         <v>377</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>378</v>
       </c>
       <c r="E45" s="14"/>
       <c r="F45" s="14"/>
@@ -29238,13 +29365,13 @@
         <v>43</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="D46" s="3" t="s">
         <v>380</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>381</v>
       </c>
       <c r="E46" s="14"/>
       <c r="F46" s="14"/>
@@ -29274,13 +29401,13 @@
         <v>44</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="D47" s="3" t="s">
         <v>383</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>384</v>
       </c>
       <c r="E47" s="14"/>
       <c r="F47" s="14"/>
@@ -29310,10 +29437,10 @@
         <v>45</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>385</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>386</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>153</v>
@@ -29346,13 +29473,13 @@
         <v>46</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>233</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E49" s="14"/>
       <c r="F49" s="14"/>
@@ -29382,10 +29509,10 @@
         <v>47</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>389</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>390</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>22</v>
@@ -29418,13 +29545,13 @@
         <v>48</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="D51" s="3" t="s">
         <v>392</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>393</v>
       </c>
       <c r="E51" s="14"/>
       <c r="F51" s="14"/>
@@ -29454,13 +29581,13 @@
         <v>49</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="D52" s="3" t="s">
         <v>395</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>396</v>
       </c>
       <c r="E52" s="14"/>
       <c r="F52" s="14"/>
@@ -29490,13 +29617,13 @@
         <v>50</v>
       </c>
       <c r="B53" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C53" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="D53" s="3" t="s">
         <v>398</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>399</v>
       </c>
       <c r="E53" s="14"/>
       <c r="F53" s="14"/>
@@ -29526,13 +29653,13 @@
         <v>51</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>401</v>
-      </c>
       <c r="D54" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E54" s="14"/>
       <c r="F54" s="14"/>
@@ -29562,10 +29689,10 @@
         <v>52</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>402</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>403</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>22</v>
@@ -29598,10 +29725,10 @@
         <v>53</v>
       </c>
       <c r="B56" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>404</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>405</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>22</v>
@@ -29634,10 +29761,10 @@
         <v>54</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C57" s="3" t="s">
         <v>406</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>407</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>22</v>
@@ -29670,10 +29797,10 @@
         <v>55</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>408</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>409</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>23</v>
@@ -29706,10 +29833,10 @@
         <v>56</v>
       </c>
       <c r="B59" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C59" s="3" t="s">
         <v>410</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>411</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>23</v>
@@ -29742,10 +29869,10 @@
         <v>57</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>412</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>413</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>22</v>
@@ -29778,10 +29905,10 @@
         <v>58</v>
       </c>
       <c r="B61" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>414</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>415</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>23</v>
@@ -29814,10 +29941,10 @@
         <v>59</v>
       </c>
       <c r="B62" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="C62" s="3" t="s">
         <v>416</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>417</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>160</v>
@@ -29850,10 +29977,10 @@
         <v>60</v>
       </c>
       <c r="B63" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C63" s="3" t="s">
         <v>418</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>419</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>22</v>
@@ -29886,10 +30013,10 @@
         <v>61</v>
       </c>
       <c r="B64" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>420</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>421</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>22</v>
@@ -29922,13 +30049,13 @@
         <v>62</v>
       </c>
       <c r="B65" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="C65" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>423</v>
-      </c>
       <c r="D65" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E65" s="14"/>
       <c r="F65" s="14"/>
@@ -29958,10 +30085,10 @@
         <v>63</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>424</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>425</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>160</v>
@@ -29994,10 +30121,10 @@
         <v>64</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="C67" s="3" t="s">
         <v>426</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>427</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>22</v>
@@ -30030,10 +30157,10 @@
         <v>65</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>428</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>429</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>24</v>
@@ -30066,10 +30193,10 @@
         <v>66</v>
       </c>
       <c r="B69" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>430</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>431</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>22</v>
@@ -30102,10 +30229,10 @@
         <v>67</v>
       </c>
       <c r="B70" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>432</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>433</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>23</v>
@@ -30138,10 +30265,10 @@
         <v>68</v>
       </c>
       <c r="B71" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="C71" s="3" t="s">
         <v>434</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>435</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>22</v>
@@ -30174,13 +30301,13 @@
         <v>69</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="C72" s="3" t="s">
-        <v>437</v>
-      </c>
       <c r="D72" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E72" s="14"/>
       <c r="F72" s="14"/>
@@ -30210,13 +30337,13 @@
         <v>70</v>
       </c>
       <c r="B73" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C73" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="C73" s="3" t="s">
-        <v>439</v>
-      </c>
       <c r="D73" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E73" s="14"/>
       <c r="F73" s="14"/>
@@ -30246,10 +30373,10 @@
         <v>71</v>
       </c>
       <c r="B74" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>440</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>441</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>201</v>
@@ -30282,10 +30409,10 @@
         <v>72</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>442</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>443</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>23</v>
@@ -30318,13 +30445,13 @@
         <v>73</v>
       </c>
       <c r="B76" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="C76" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="D76" s="3" t="s">
         <v>445</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>446</v>
       </c>
       <c r="E76" s="14"/>
       <c r="F76" s="14"/>
@@ -30354,13 +30481,13 @@
         <v>74</v>
       </c>
       <c r="B77" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>448</v>
-      </c>
       <c r="D77" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E77" s="14"/>
       <c r="F77" s="14"/>
@@ -30390,24 +30517,24 @@
         <v>75</v>
       </c>
       <c r="B78" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>449</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>450</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E78" s="14">
-        <f>+[40]Main!$H$2</f>
+        <f>+[42]Main!$H$2</f>
         <v>1.2</v>
       </c>
       <c r="F78" s="14">
-        <f>+[40]Main!$H$4</f>
+        <f>+[42]Main!$H$4</f>
         <v>112.4964828</v>
       </c>
       <c r="G78" s="14">
-        <f>+[40]Main!$H$6-[40]Main!$H$5</f>
+        <f>+[42]Main!$H$6-[42]Main!$H$5</f>
         <v>145.571</v>
       </c>
       <c r="H78" s="14">
@@ -30440,10 +30567,10 @@
         <v>76</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>451</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>452</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>22</v>
@@ -30476,13 +30603,13 @@
         <v>77</v>
       </c>
       <c r="B80" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="C80" s="3" t="s">
-        <v>454</v>
-      </c>
       <c r="D80" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E80" s="14"/>
       <c r="F80" s="14"/>
@@ -30512,13 +30639,13 @@
         <v>78</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C81" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="C81" s="3" t="s">
-        <v>456</v>
-      </c>
       <c r="D81" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E81" s="14"/>
       <c r="F81" s="14"/>
@@ -30548,10 +30675,10 @@
         <v>79</v>
       </c>
       <c r="B82" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>457</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>458</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>85</v>
@@ -30584,13 +30711,13 @@
         <v>80</v>
       </c>
       <c r="B83" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="C83" s="3" t="s">
+      <c r="D83" s="3" t="s">
         <v>460</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>461</v>
       </c>
       <c r="E83" s="14"/>
       <c r="F83" s="14"/>
@@ -30620,10 +30747,10 @@
         <v>81</v>
       </c>
       <c r="B84" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>462</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>463</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>22</v>
@@ -30656,10 +30783,10 @@
         <v>82</v>
       </c>
       <c r="B85" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C85" s="3" t="s">
         <v>464</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>465</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>22</v>
@@ -30692,7 +30819,7 @@
         <v>83</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
@@ -30724,10 +30851,10 @@
         <v>84</v>
       </c>
       <c r="B87" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>467</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>468</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>22</v>
@@ -30760,13 +30887,13 @@
         <v>85</v>
       </c>
       <c r="B88" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="C88" s="3" t="s">
-        <v>470</v>
-      </c>
       <c r="D88" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E88" s="14"/>
       <c r="F88" s="14"/>
@@ -30984,7 +31111,7 @@
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C3" s="3">
         <v>1.03</v>
@@ -30994,7 +31121,7 @@
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C4" s="3">
         <v>1.24</v>
@@ -31004,7 +31131,7 @@
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C5" s="3">
         <v>0.63</v>
@@ -31014,7 +31141,7 @@
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C6" s="3">
         <v>0.14000000000000001</v>

--- a/Entertainment.xlsx
+++ b/Entertainment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F27B40CC-A606-45B6-9D44-DEE6CC6ADE6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79FB2DD3-B7C6-40C2-B1F9-6928E3E7988F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
   </bookViews>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="483">
   <si>
     <t>Name</t>
   </si>
@@ -1530,6 +1530,12 @@
   </si>
   <si>
     <t>Q126</t>
+  </si>
+  <si>
+    <t>n.a.</t>
+  </si>
+  <si>
+    <t>DEN</t>
   </si>
 </sst>
 </file>
@@ -1541,13 +1547,19 @@
     <numFmt numFmtId="165" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1716,72 +1728,73 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -2187,7 +2200,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2571,6 +2584,45 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
+          <cell r="J2">
+            <v>3555</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>520979.16739500005</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>133399</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>26577</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
           <cell r="I2">
             <v>5310</v>
           </cell>
@@ -2597,7 +2649,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2627,45 +2679,6 @@
         <row r="6">
           <cell r="I6">
             <v>609.07600000000002</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>15.92</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>2183.3765784000002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>149.55799999999999</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="H7">
-            <v>714.03099999999995</v>
           </cell>
         </row>
       </sheetData>
@@ -2727,6 +2740,45 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
+          <cell r="H2">
+            <v>15.92</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>2183.3765784000002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>149.55799999999999</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="H7">
+            <v>714.03099999999995</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
           <cell r="I2">
             <v>3.28</v>
           </cell>
@@ -2753,7 +2805,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2794,7 +2846,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2833,7 +2885,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2872,7 +2924,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2906,7 +2958,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2945,7 +2997,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2984,7 +3036,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3023,7 +3075,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3053,45 +3105,6 @@
         <row r="6">
           <cell r="I6">
             <v>2900</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>41.21</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>8939.4565020800001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>672.87819999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>9.4335000000000004</v>
           </cell>
         </row>
       </sheetData>
@@ -3154,6 +3167,45 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
+            <v>41.21</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>8939.4565020800001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>672.87819999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>9.4335000000000004</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
             <v>52.09</v>
           </cell>
         </row>
@@ -3179,7 +3231,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3216,7 +3268,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3246,45 +3298,6 @@
         <row r="6">
           <cell r="H6">
             <v>176.57499999999999</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>3555</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>520979.16739500005</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>133399</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>26577</v>
           </cell>
         </row>
       </sheetData>
@@ -3327,7 +3340,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3366,7 +3379,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -8886,15 +8899,15 @@
         <v>23</v>
       </c>
       <c r="E84" s="35">
-        <f>+[43]Main!$J$2</f>
+        <f>+[27]Main!$J$2</f>
         <v>3555</v>
       </c>
       <c r="F84" s="14">
-        <f>+[43]Main!$J$4*FX!C2</f>
+        <f>+[27]Main!$J$4*FX!C2</f>
         <v>3334.2666713280005</v>
       </c>
       <c r="G84" s="14">
-        <f>+([43]Main!$J$6-[43]Main!$J$5)*FX!C2</f>
+        <f>+([27]Main!$J$6-[27]Main!$J$5)*FX!C2</f>
         <v>-683.66079999999999</v>
       </c>
       <c r="H84" s="14">
@@ -9404,15 +9417,15 @@
         <v>23</v>
       </c>
       <c r="E93" s="3">
-        <f>+[27]Main!$I$2</f>
+        <f>+[28]Main!$I$2</f>
         <v>5310</v>
       </c>
       <c r="F93" s="14">
-        <f>+[27]Main!$I$4*FX!C2</f>
+        <f>+[28]Main!$I$4*FX!C2</f>
         <v>2103.4388983680001</v>
       </c>
       <c r="G93" s="14">
-        <f>+([27]Main!$I$6-[27]Main!$I$5)*FX!C2</f>
+        <f>+([28]Main!$I$6-[28]Main!$I$5)*FX!C2</f>
         <v>-590.64960000000008</v>
       </c>
       <c r="H93" s="14">
@@ -10090,15 +10103,15 @@
         <v>22</v>
       </c>
       <c r="E105" s="3">
-        <f>+[28]Main!$I$2</f>
+        <f>+[29]Main!$I$2</f>
         <v>33.76</v>
       </c>
       <c r="F105" s="14">
-        <f>+[28]Main!$I$4</f>
+        <f>+[29]Main!$I$4</f>
         <v>1615.1327198399999</v>
       </c>
       <c r="G105" s="14">
-        <f>+[28]Main!$I$6-[28]Main!$I$5</f>
+        <f>+[29]Main!$I$6-[29]Main!$I$5</f>
         <v>553.85699999999997</v>
       </c>
       <c r="H105" s="14">
@@ -10272,15 +10285,15 @@
         <v>153</v>
       </c>
       <c r="E108" s="3">
-        <f>+[29]Main!$H$2</f>
+        <f>+[30]Main!$H$2</f>
         <v>15.92</v>
       </c>
       <c r="F108" s="14">
-        <f>+[29]Main!$H$5*FX!C4</f>
+        <f>+[30]Main!$H$5*FX!C4</f>
         <v>2707.3869572160002</v>
       </c>
       <c r="G108" s="14">
-        <f>+([29]Main!$H$7-[29]Main!$H$6)*FX!C4</f>
+        <f>+([30]Main!$H$7-[30]Main!$H$6)*FX!C4</f>
         <v>699.94651999999996</v>
       </c>
       <c r="H108" s="14">
@@ -10400,15 +10413,15 @@
         <v>85</v>
       </c>
       <c r="E110" s="3">
-        <f>+[30]Main!$I$2</f>
+        <f>+[31]Main!$I$2</f>
         <v>3.28</v>
       </c>
       <c r="F110" s="14">
-        <f>+[30]Main!$I$4*FX!C3</f>
+        <f>+[31]Main!$I$4*FX!C3</f>
         <v>372.96258964800001</v>
       </c>
       <c r="G110" s="14">
-        <f>+([30]Main!$I$6-[30]Main!$I$5)*FX!C3</f>
+        <f>+([31]Main!$I$6-[31]Main!$I$5)*FX!C3</f>
         <v>50.842859999999995</v>
       </c>
       <c r="H110" s="14">
@@ -10723,11 +10736,15 @@
     </row>
     <row r="116" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A116" s="11"/>
-      <c r="B116" s="3" t="s">
+      <c r="B116" s="12" t="s">
         <v>477</v>
       </c>
-      <c r="C116" s="3"/>
-      <c r="D116" s="3"/>
+      <c r="C116" s="36" t="s">
+        <v>481</v>
+      </c>
+      <c r="D116" s="36" t="s">
+        <v>482</v>
+      </c>
       <c r="E116" s="3"/>
       <c r="F116" s="21"/>
       <c r="G116" s="21"/>
@@ -16632,6 +16649,7 @@
     <hyperlink ref="B103" r:id="rId30" xr:uid="{99A434BF-F5F7-467F-AB02-447D8D64F5FB}"/>
     <hyperlink ref="B93" r:id="rId31" xr:uid="{04B6A34E-7F7B-490D-8880-75C12621EECA}"/>
     <hyperlink ref="B84" r:id="rId32" xr:uid="{56024696-67B2-4803-B0DF-95A89BDC0A77}"/>
+    <hyperlink ref="B116" r:id="rId33" xr:uid="{165C2902-BD53-4337-94C5-A6EDD7D0D481}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16978,15 +16996,15 @@
         <v>22</v>
       </c>
       <c r="E5" s="26">
-        <f>+[31]Main!$H$2</f>
+        <f>+[32]Main!$H$2</f>
         <v>559.02</v>
       </c>
       <c r="F5" s="26">
-        <f>+[31]Main!$H$4</f>
+        <f>+[32]Main!$H$4</f>
         <v>4155288.66918858</v>
       </c>
       <c r="G5" s="26">
-        <f>+[31]Main!$H$6-[31]Main!$H$5</f>
+        <f>+[32]Main!$H$6-[32]Main!$H$5</f>
         <v>-54413</v>
       </c>
       <c r="H5" s="26">
@@ -17073,15 +17091,15 @@
         <v>26</v>
       </c>
       <c r="E6" s="26">
-        <f>+[32]Main!$G$2</f>
+        <f>+[33]Main!$G$2</f>
         <v>617.5</v>
       </c>
       <c r="F6" s="26">
-        <f>+[32]Main!$G$4*FX!C6</f>
+        <f>+[33]Main!$G$4*FX!C6</f>
         <v>1273.5800000000002</v>
       </c>
       <c r="G6" s="26">
-        <f>+([32]Main!$G$6-[32]Main!$G$5)*FX!C6</f>
+        <f>+([33]Main!$G$6-[33]Main!$G$5)*FX!C6</f>
         <v>-674313.59800000011</v>
       </c>
       <c r="H6" s="26">
@@ -17358,15 +17376,15 @@
         <v>26</v>
       </c>
       <c r="E9" s="26">
-        <f>+[33]Main!$I$2</f>
+        <f>+[34]Main!$I$2</f>
         <v>2123</v>
       </c>
       <c r="F9" s="26">
-        <f>+[34]Main!$H$5*FX!C6</f>
+        <f>+[35]Main!$H$5*FX!C6</f>
         <v>65131.275185760009</v>
       </c>
       <c r="G9" s="26">
-        <f>+([34]Main!$H$7-[34]Main!$H$6)*FX!C6</f>
+        <f>+([35]Main!$H$7-[35]Main!$H$6)*FX!C6</f>
         <v>-16042.82638</v>
       </c>
       <c r="H9" s="26">
@@ -17928,15 +17946,15 @@
         <v>23</v>
       </c>
       <c r="E15" s="26">
-        <f>+[33]Main!$I$2</f>
+        <f>+[34]Main!$I$2</f>
         <v>2123</v>
       </c>
       <c r="F15" s="26">
-        <f>+[33]Main!$I$4*FX!C2</f>
+        <f>+[34]Main!$I$4*FX!C2</f>
         <v>11429.0165977856</v>
       </c>
       <c r="G15" s="26">
-        <f>+([33]Main!$I$6-[33]Main!$I$5)*FX!C2</f>
+        <f>+([34]Main!$I$6-[34]Main!$I$5)*FX!C2</f>
         <v>-2117.3888000000002</v>
       </c>
       <c r="H15" s="26">
@@ -18213,15 +18231,15 @@
         <v>94</v>
       </c>
       <c r="E18" s="26">
-        <f>+[35]Main!$H$2</f>
+        <f>+[36]Main!$H$2</f>
         <v>12.11</v>
       </c>
       <c r="F18" s="26">
-        <f>+[35]Main!$H$4*FX!C3</f>
+        <f>+[36]Main!$H$4*FX!C3</f>
         <v>1601.5717199999999</v>
       </c>
       <c r="G18" s="26">
-        <f>+([35]Main!$H$6-[35]Main!$H$5)*FX!C3</f>
+        <f>+([36]Main!$H$6-[36]Main!$H$5)*FX!C3</f>
         <v>1343.7380000000003</v>
       </c>
       <c r="H18" s="26">
@@ -18451,15 +18469,15 @@
         <v>22</v>
       </c>
       <c r="E21" s="26">
-        <f>+[36]Main!$J$2</f>
+        <f>+[37]Main!$J$2</f>
         <v>21.7</v>
       </c>
       <c r="F21" s="26">
-        <f>+[36]Main!$J$4</f>
+        <f>+[37]Main!$J$4</f>
         <v>9701.7223876999997</v>
       </c>
       <c r="G21" s="26">
-        <f>+[36]Main!$J$6-[36]Main!$J$5</f>
+        <f>+[37]Main!$J$6-[37]Main!$J$5</f>
         <v>-4758</v>
       </c>
       <c r="H21" s="26">
@@ -27926,15 +27944,15 @@
         <v>22</v>
       </c>
       <c r="E8" s="14">
-        <f>+[37]Main!$I$2</f>
+        <f>+[38]Main!$I$2</f>
         <v>50.5</v>
       </c>
       <c r="F8" s="14">
-        <f>+[37]Main!$I$4</f>
+        <f>+[38]Main!$I$4</f>
         <v>22898.106829</v>
       </c>
       <c r="G8" s="14">
-        <f>+[37]Main!$I$6-[37]Main!$I$5</f>
+        <f>+[38]Main!$I$6-[38]Main!$I$5</f>
         <v>3878</v>
       </c>
       <c r="H8" s="14">
@@ -28048,15 +28066,15 @@
         <v>22</v>
       </c>
       <c r="E11" s="14">
-        <f>+[38]Main!$I$2</f>
+        <f>+[39]Main!$I$2</f>
         <v>30.44</v>
       </c>
       <c r="F11" s="14">
-        <f>+[38]Main!$I$4</f>
+        <f>+[39]Main!$I$4</f>
         <v>17310.539416759999</v>
       </c>
       <c r="G11" s="14">
-        <f>+[38]Main!$I$6-[38]Main!$I$5</f>
+        <f>+[39]Main!$I$6-[39]Main!$I$5</f>
         <v>1122</v>
       </c>
       <c r="H11" s="14">
@@ -28134,15 +28152,15 @@
         <v>22</v>
       </c>
       <c r="E13" s="14">
-        <f>+[39]Main!$H$2</f>
+        <f>+[40]Main!$H$2</f>
         <v>41.21</v>
       </c>
       <c r="F13" s="14">
-        <f>+[39]Main!$H$4</f>
+        <f>+[40]Main!$H$4</f>
         <v>8939.4565020800001</v>
       </c>
       <c r="G13" s="14">
-        <f>+[39]Main!$H$6-[39]Main!$H$5</f>
+        <f>+[40]Main!$H$6-[40]Main!$H$5</f>
         <v>-663.44470000000001</v>
       </c>
       <c r="H13" s="14">
@@ -28184,15 +28202,15 @@
         <v>22</v>
       </c>
       <c r="E14" s="14">
-        <f>+[40]Main!$H$2</f>
+        <f>+[41]Main!$H$2</f>
         <v>52.09</v>
       </c>
       <c r="F14" s="14">
-        <f>+[40]Main!$H$4</f>
+        <f>+[41]Main!$H$4</f>
         <v>8540.3870921399994</v>
       </c>
       <c r="G14" s="14">
-        <f>+[40]Main!$H$6-[40]Main!$H$5</f>
+        <f>+[41]Main!$H$6-[41]Main!$H$5</f>
         <v>-492.94499999999999</v>
       </c>
       <c r="H14" s="14">
@@ -28320,15 +28338,15 @@
         <v>22</v>
       </c>
       <c r="E17" s="14">
-        <f>+[41]Main!$K$2</f>
+        <f>+[42]Main!$K$2</f>
         <v>78.55</v>
       </c>
       <c r="F17" s="14">
-        <f>+[41]Main!$K$4</f>
+        <f>+[42]Main!$K$4</f>
         <v>7215.2325581999994</v>
       </c>
       <c r="G17" s="14">
-        <f>+[41]Main!$K$6-[41]Main!$K$5</f>
+        <f>+[42]Main!$K$6-[42]Main!$K$5</f>
         <v>1417</v>
       </c>
       <c r="H17" s="14">
@@ -30526,15 +30544,15 @@
         <v>22</v>
       </c>
       <c r="E78" s="14">
-        <f>+[42]Main!$H$2</f>
+        <f>+[43]Main!$H$2</f>
         <v>1.2</v>
       </c>
       <c r="F78" s="14">
-        <f>+[42]Main!$H$4</f>
+        <f>+[43]Main!$H$4</f>
         <v>112.4964828</v>
       </c>
       <c r="G78" s="14">
-        <f>+[42]Main!$H$6-[42]Main!$H$5</f>
+        <f>+[43]Main!$H$6-[43]Main!$H$5</f>
         <v>145.571</v>
       </c>
       <c r="H78" s="14">

--- a/Entertainment.xlsx
+++ b/Entertainment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79FB2DD3-B7C6-40C2-B1F9-6928E3E7988F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EBF0615-6F10-4EBE-B671-EB2BCC86C743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1927,7 +1927,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>

--- a/Entertainment.xlsx
+++ b/Entertainment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EBF0615-6F10-4EBE-B671-EB2BCC86C743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8152984-9C49-445E-B619-52764AAE1201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
+    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1927,7 +1927,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3438,12 +3438,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>173.3</v>
+            <v>202.53</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>43360.925609900005</v>
+            <v>50674.485076589997</v>
           </cell>
         </row>
         <row r="5">
@@ -3457,7 +3457,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -4742,11 +4742,11 @@
       </c>
       <c r="E15" s="13">
         <f>+[8]Main!$I$2</f>
-        <v>173.3</v>
+        <v>202.53</v>
       </c>
       <c r="F15" s="14">
         <f>+[8]Main!$I$4</f>
-        <v>43360.925609900005</v>
+        <v>50674.485076589997</v>
       </c>
       <c r="G15" s="14">
         <f>+[8]Main!$I$6-[8]Main!$I$5</f>
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H15" s="14">
         <f>+F15+G15</f>
-        <v>42130.925609900005</v>
+        <v>49444.485076589997</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>475</v>
@@ -17567,11 +17567,11 @@
       </c>
       <c r="E11" s="26">
         <f>+[8]Main!$I$2</f>
-        <v>173.3</v>
+        <v>202.53</v>
       </c>
       <c r="F11" s="26">
         <f>+[8]Main!$I$4</f>
-        <v>43360.925609900005</v>
+        <v>50674.485076589997</v>
       </c>
       <c r="G11" s="26">
         <f>+[8]Main!$I$6-[8]Main!$I$5</f>
@@ -17579,7 +17579,7 @@
       </c>
       <c r="H11" s="26">
         <f t="shared" si="0"/>
-        <v>42130.925609900005</v>
+        <v>49444.485076589997</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>240</v>

--- a/Entertainment.xlsx
+++ b/Entertainment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8152984-9C49-445E-B619-52764AAE1201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C64C37-85FC-4D2A-8F21-F95E569B3F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
   </bookViews>
@@ -3457,7 +3457,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>

--- a/Entertainment.xlsx
+++ b/Entertainment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C64C37-85FC-4D2A-8F21-F95E569B3F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214CFF0C-A9EC-49B8-A4E8-9987AF640C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3510" windowWidth="38175" windowHeight="15240" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
+    <workbookView xWindow="225" yWindow="3855" windowWidth="38175" windowHeight="15240" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1829,27 +1829,27 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="I3">
-            <v>1253.22</v>
+            <v>1123</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>532882.92942000006</v>
+            <v>475851.41108200001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>8390.52</v>
+            <v>9324.3919999999998</v>
           </cell>
         </row>
         <row r="7">
           <cell r="I7">
-            <v>14453.206</v>
+            <v>14463.02</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1908,12 +1908,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>256.39999999999998</v>
+            <v>266.8</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>340780.2144</v>
+            <v>354602.81280000001</v>
           </cell>
         </row>
         <row r="5">
@@ -2064,12 +2064,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>11.87</v>
+            <v>25.88</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>29387.416987339999</v>
+            <v>64072.986658159993</v>
           </cell>
         </row>
         <row r="5">
@@ -2820,22 +2820,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>559.02</v>
+            <v>516.99</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>4155288.66918858</v>
+            <v>3842464.9238584503</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>94565</v>
+            <v>102012</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>40152</v>
+            <v>43208</v>
           </cell>
         </row>
       </sheetData>
@@ -4014,19 +4014,19 @@
       </c>
       <c r="E4" s="13">
         <f>+[1]Main!$I$3</f>
-        <v>1253.22</v>
+        <v>1123</v>
       </c>
       <c r="F4" s="14">
         <f>+[1]Main!$I$5</f>
-        <v>532882.92942000006</v>
+        <v>475851.41108200001</v>
       </c>
       <c r="G4" s="14">
         <f>+[1]Main!$I$7-[1]Main!$I$6</f>
-        <v>6062.6859999999997</v>
+        <v>5138.6280000000006</v>
       </c>
       <c r="H4" s="14">
         <f>+F4+G4</f>
-        <v>538945.61542000005</v>
+        <v>480990.03908200003</v>
       </c>
       <c r="I4" s="29" t="s">
         <v>473</v>
@@ -4960,11 +4960,11 @@
       </c>
       <c r="E18" s="3">
         <f>+[11]Main!$I$2</f>
-        <v>256.39999999999998</v>
+        <v>266.8</v>
       </c>
       <c r="F18" s="21">
         <f>+[11]Main!$I$4*FX!C6</f>
-        <v>47709.230016000001</v>
+        <v>49644.39379200001</v>
       </c>
       <c r="G18" s="14">
         <f>+([11]Main!$I$6-[11]Main!$I$5)*FX!C6</f>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="H18" s="14">
         <f>+F18+G18</f>
-        <v>45782.030476</v>
+        <v>47717.194252000008</v>
       </c>
       <c r="I18" s="33" t="s">
         <v>473</v>
@@ -5302,11 +5302,11 @@
       </c>
       <c r="E23" s="3">
         <f>+[15]Main!$H$2</f>
-        <v>11.87</v>
+        <v>25.88</v>
       </c>
       <c r="F23" s="14">
         <f>+[15]Main!$H$4</f>
-        <v>29387.416987339999</v>
+        <v>64072.986658159993</v>
       </c>
       <c r="G23" s="14">
         <f>+[15]Main!$H$6-[15]Main!$H$5</f>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="H23" s="14">
         <f>+F23+G23</f>
-        <v>59131.416987339995</v>
+        <v>93816.986658159993</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>473</v>
@@ -16997,19 +16997,19 @@
       </c>
       <c r="E5" s="26">
         <f>+[32]Main!$H$2</f>
-        <v>559.02</v>
+        <v>516.99</v>
       </c>
       <c r="F5" s="26">
         <f>+[32]Main!$H$4</f>
-        <v>4155288.66918858</v>
+        <v>3842464.9238584503</v>
       </c>
       <c r="G5" s="26">
         <f>+[32]Main!$H$6-[32]Main!$H$5</f>
-        <v>-54413</v>
+        <v>-58804</v>
       </c>
       <c r="H5" s="26">
         <f t="shared" ref="H5:H18" si="0">+F5+G5</f>
-        <v>4100875.66918858</v>
+        <v>3783660.9238584503</v>
       </c>
       <c r="I5" s="27" t="s">
         <v>240</v>
@@ -27895,11 +27895,11 @@
       </c>
       <c r="E7" s="14">
         <f>+[15]Main!$H$2</f>
-        <v>11.87</v>
+        <v>25.88</v>
       </c>
       <c r="F7" s="14">
         <f>+[15]Main!$H$4</f>
-        <v>29387.416987339999</v>
+        <v>64072.986658159993</v>
       </c>
       <c r="G7" s="14">
         <f>+[15]Main!$H$6-[15]Main!$H$5</f>
@@ -27907,7 +27907,7 @@
       </c>
       <c r="H7" s="14">
         <f>+F7+G7</f>
-        <v>59131.416987339995</v>
+        <v>93816.986658159993</v>
       </c>
       <c r="I7" s="15" t="s">
         <v>239</v>

--- a/Entertainment.xlsx
+++ b/Entertainment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214CFF0C-A9EC-49B8-A4E8-9987AF640C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F25DD3A-2568-4552-A5F9-1A5A5F735D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3855" windowWidth="38175" windowHeight="15240" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
+    <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" activeTab="2" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1547,13 +1547,25 @@
     <numFmt numFmtId="165" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1728,74 +1740,80 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1848,8 +1866,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2702,26 +2720,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="I2">
-            <v>33.840000000000003</v>
+            <v>29.6</v>
           </cell>
         </row>
         <row r="4">
           <cell r="I4">
-            <v>124944.26802768001</v>
+            <v>107859.27734800002</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>9687</v>
+            <v>9325</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>101528</v>
+            <v>99063</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3206,17 +3224,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>52.09</v>
+            <v>69.87</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>8540.3870921399994</v>
+            <v>11343.32525883</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>492.94499999999999</v>
+            <v>617.35199999999998</v>
           </cell>
         </row>
         <row r="6">
@@ -4160,19 +4178,19 @@
       </c>
       <c r="E6" s="13">
         <f>+[3]Main!$I$2</f>
-        <v>33.840000000000003</v>
+        <v>29.6</v>
       </c>
       <c r="F6" s="14">
         <f>+[3]Main!$I$4</f>
-        <v>124944.26802768001</v>
+        <v>107859.27734800002</v>
       </c>
       <c r="G6" s="14">
         <f>+[3]Main!$I$6-[3]Main!$I$5</f>
-        <v>91841</v>
+        <v>89738</v>
       </c>
       <c r="H6" s="14">
         <f t="shared" si="0"/>
-        <v>216785.26802767999</v>
+        <v>197597.27734800003</v>
       </c>
       <c r="I6" s="30" t="s">
         <v>473</v>
@@ -27773,22 +27791,22 @@
       </c>
       <c r="E4" s="14">
         <f>+[3]Main!$I$2</f>
-        <v>33.840000000000003</v>
+        <v>29.6</v>
       </c>
       <c r="F4" s="14">
         <f>+[3]Main!$I$4</f>
-        <v>124944.26802768001</v>
+        <v>107859.27734800002</v>
       </c>
       <c r="G4" s="14">
         <f>+[3]Main!$I$6-[3]Main!$I$5</f>
-        <v>91841</v>
+        <v>89738</v>
       </c>
       <c r="H4" s="14">
         <f>+F4+G4</f>
-        <v>216785.26802767999</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>239</v>
+        <v>197597.27734800003</v>
+      </c>
+      <c r="I4" s="38" t="s">
+        <v>295</v>
       </c>
       <c r="J4" s="15"/>
       <c r="K4" s="15"/>
@@ -28203,22 +28221,22 @@
       </c>
       <c r="E14" s="14">
         <f>+[41]Main!$H$2</f>
-        <v>52.09</v>
+        <v>69.87</v>
       </c>
       <c r="F14" s="14">
         <f>+[41]Main!$H$4</f>
-        <v>8540.3870921399994</v>
+        <v>11343.32525883</v>
       </c>
       <c r="G14" s="14">
         <f>+[41]Main!$H$6-[41]Main!$H$5</f>
-        <v>-492.94499999999999</v>
+        <v>-617.35199999999998</v>
       </c>
       <c r="H14" s="14">
         <f>+F14+G14</f>
-        <v>8047.4420921399997</v>
-      </c>
-      <c r="I14" s="15" t="s">
-        <v>239</v>
+        <v>10725.973258829999</v>
+      </c>
+      <c r="I14" s="37" t="s">
+        <v>295</v>
       </c>
       <c r="J14" s="15"/>
       <c r="K14" s="15"/>

--- a/Entertainment.xlsx
+++ b/Entertainment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F25DD3A-2568-4552-A5F9-1A5A5F735D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963B41F2-D580-44D4-8C73-3137BEAC6EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" activeTab="2" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
   </bookViews>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="485">
   <si>
     <t>Name</t>
   </si>
@@ -1536,6 +1536,12 @@
   </si>
   <si>
     <t>DEN</t>
+  </si>
+  <si>
+    <t>Versant</t>
+  </si>
+  <si>
+    <t>VSNT</t>
   </si>
 </sst>
 </file>
@@ -1547,13 +1553,19 @@
     <numFmt numFmtId="165" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1740,80 +1752,81 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2739,7 +2752,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -30958,9 +30971,15 @@
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
-      <c r="B89" s="3"/>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3"/>
+      <c r="B89" s="39" t="s">
+        <v>483</v>
+      </c>
+      <c r="C89" s="39" t="s">
+        <v>484</v>
+      </c>
+      <c r="D89" s="39" t="s">
+        <v>22</v>
+      </c>
       <c r="E89" s="14"/>
       <c r="F89" s="14"/>
       <c r="G89" s="14"/>

--- a/Entertainment.xlsx
+++ b/Entertainment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{963B41F2-D580-44D4-8C73-3137BEAC6EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F24729-491A-4450-8F57-3777C2C194E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" activeTab="2" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="486">
   <si>
     <t>Name</t>
   </si>
@@ -1542,6 +1542,9 @@
   </si>
   <si>
     <t>VSNT</t>
+  </si>
+  <si>
+    <t>Q425</t>
   </si>
 </sst>
 </file>
@@ -1808,25 +1811,25 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1850,6 +1853,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -1860,27 +1864,27 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="I3">
-            <v>1123</v>
+            <v>97.5</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>475851.41108200001</v>
+            <v>411660.80962499999</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>9324.3919999999998</v>
+            <v>9062.3590000000004</v>
           </cell>
         </row>
         <row r="7">
           <cell r="I7">
-            <v>14463.02</v>
+            <v>14462.835999999999</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1891,6 +1895,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -1930,6 +1935,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -1969,6 +1975,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2008,6 +2015,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2047,6 +2055,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2086,6 +2095,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2125,6 +2135,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2164,6 +2175,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2203,6 +2215,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2242,6 +2255,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2281,6 +2295,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2334,6 +2349,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2373,6 +2389,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2412,6 +2429,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2451,6 +2469,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2490,6 +2509,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2529,6 +2549,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2568,6 +2589,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2607,6 +2629,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2646,6 +2669,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2685,6 +2709,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2724,6 +2749,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2763,6 +2789,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2802,6 +2829,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2841,6 +2869,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2851,22 +2880,22 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>516.99</v>
+            <v>432.32</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>3842464.9238584503</v>
+            <v>3210247.9621363198</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>102012</v>
+            <v>89462</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>43208</v>
+            <v>40262</v>
           </cell>
         </row>
       </sheetData>
@@ -2882,6 +2911,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2921,6 +2951,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2960,6 +2991,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -2994,6 +3026,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3033,6 +3066,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3072,6 +3106,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3111,6 +3146,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3150,6 +3186,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3189,6 +3226,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3228,6 +3266,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3256,7 +3295,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3267,6 +3306,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3304,6 +3344,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3313,26 +3354,26 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>1.2</v>
+            <v>1.7</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>112.4964828</v>
+            <v>183.18753240000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>31.004000000000001</v>
+            <v>27.463000000000001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="H6">
-            <v>176.57499999999999</v>
+            <v>176.79499999999999</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3343,6 +3384,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3382,6 +3424,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3421,6 +3464,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3460,6 +3504,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -3499,6 +3544,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -4045,22 +4091,22 @@
       </c>
       <c r="E4" s="13">
         <f>+[1]Main!$I$3</f>
-        <v>1123</v>
+        <v>97.5</v>
       </c>
       <c r="F4" s="14">
         <f>+[1]Main!$I$5</f>
-        <v>475851.41108200001</v>
+        <v>411660.80962499999</v>
       </c>
       <c r="G4" s="14">
         <f>+[1]Main!$I$7-[1]Main!$I$6</f>
-        <v>5138.6280000000006</v>
+        <v>5400.476999999999</v>
       </c>
       <c r="H4" s="14">
         <f>+F4+G4</f>
-        <v>480990.03908200003</v>
-      </c>
-      <c r="I4" s="29" t="s">
-        <v>473</v>
+        <v>417061.28662500001</v>
+      </c>
+      <c r="I4" s="39" t="s">
+        <v>485</v>
       </c>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
@@ -4205,7 +4251,7 @@
         <f t="shared" si="0"/>
         <v>197597.27734800003</v>
       </c>
-      <c r="I6" s="30" t="s">
+      <c r="I6" s="29" t="s">
         <v>473</v>
       </c>
       <c r="J6" s="3"/>
@@ -4349,7 +4395,7 @@
         <f t="shared" si="0"/>
         <v>124178.28512867499</v>
       </c>
-      <c r="I8" s="31" t="s">
+      <c r="I8" s="30" t="s">
         <v>473</v>
       </c>
       <c r="J8" s="3"/>
@@ -4861,7 +4907,7 @@
         <f>+F16+G16</f>
         <v>80852.00014484</v>
       </c>
-      <c r="I16" s="31" t="s">
+      <c r="I16" s="30" t="s">
         <v>473</v>
       </c>
       <c r="J16" s="3"/>
@@ -4983,10 +5029,10 @@
       <c r="B18" s="12" t="s">
         <v>478</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="31" t="s">
         <v>479</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="31" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="3">
@@ -5005,7 +5051,7 @@
         <f>+F18+G18</f>
         <v>47717.194252000008</v>
       </c>
-      <c r="I18" s="33" t="s">
+      <c r="I18" s="32" t="s">
         <v>473</v>
       </c>
       <c r="J18" s="3"/>
@@ -6477,7 +6523,7 @@
         <f>+F41+G41</f>
         <v>21090</v>
       </c>
-      <c r="I41" s="34" t="s">
+      <c r="I41" s="33" t="s">
         <v>473</v>
       </c>
       <c r="J41" s="3"/>
@@ -7011,7 +7057,7 @@
         <f>+F50+G50</f>
         <v>7216.4629999999997</v>
       </c>
-      <c r="I50" s="34" t="s">
+      <c r="I50" s="33" t="s">
         <v>473</v>
       </c>
       <c r="J50" s="3"/>
@@ -8929,7 +8975,7 @@
       <c r="D84" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E84" s="35">
+      <c r="E84" s="34">
         <f>+[27]Main!$J$2</f>
         <v>3555</v>
       </c>
@@ -8945,7 +8991,7 @@
         <f>+F84+G84</f>
         <v>2650.6058713280004</v>
       </c>
-      <c r="I84" s="34" t="s">
+      <c r="I84" s="33" t="s">
         <v>480</v>
       </c>
       <c r="J84" s="3"/>
@@ -9463,7 +9509,7 @@
         <f>+F93+G93</f>
         <v>1512.7892983679999</v>
       </c>
-      <c r="I93" s="34" t="s">
+      <c r="I93" s="33" t="s">
         <v>480</v>
       </c>
       <c r="J93" s="3"/>
@@ -10770,10 +10816,10 @@
       <c r="B116" s="12" t="s">
         <v>477</v>
       </c>
-      <c r="C116" s="36" t="s">
+      <c r="C116" s="35" t="s">
         <v>481</v>
       </c>
-      <c r="D116" s="36" t="s">
+      <c r="D116" s="35" t="s">
         <v>482</v>
       </c>
       <c r="E116" s="3"/>
@@ -17028,19 +17074,19 @@
       </c>
       <c r="E5" s="26">
         <f>+[32]Main!$H$2</f>
-        <v>516.99</v>
+        <v>432.32</v>
       </c>
       <c r="F5" s="26">
         <f>+[32]Main!$H$4</f>
-        <v>3842464.9238584503</v>
+        <v>3210247.9621363198</v>
       </c>
       <c r="G5" s="26">
         <f>+[32]Main!$H$6-[32]Main!$H$5</f>
-        <v>-58804</v>
+        <v>-49200</v>
       </c>
       <c r="H5" s="26">
         <f t="shared" ref="H5:H18" si="0">+F5+G5</f>
-        <v>3783660.9238584503</v>
+        <v>3161047.9621363198</v>
       </c>
       <c r="I5" s="27" t="s">
         <v>240</v>
@@ -27818,7 +27864,7 @@
         <f>+F4+G4</f>
         <v>197597.27734800003</v>
       </c>
-      <c r="I4" s="38" t="s">
+      <c r="I4" s="37" t="s">
         <v>295</v>
       </c>
       <c r="J4" s="15"/>
@@ -28248,7 +28294,7 @@
         <f>+F14+G14</f>
         <v>10725.973258829999</v>
       </c>
-      <c r="I14" s="37" t="s">
+      <c r="I14" s="36" t="s">
         <v>295</v>
       </c>
       <c r="J14" s="15"/>
@@ -30576,19 +30622,19 @@
       </c>
       <c r="E78" s="14">
         <f>+[43]Main!$H$2</f>
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="F78" s="14">
         <f>+[43]Main!$H$4</f>
-        <v>112.4964828</v>
+        <v>183.18753240000001</v>
       </c>
       <c r="G78" s="14">
         <f>+[43]Main!$H$6-[43]Main!$H$5</f>
-        <v>145.571</v>
+        <v>149.33199999999999</v>
       </c>
       <c r="H78" s="14">
         <f>+F78+G78</f>
-        <v>258.06748279999999</v>
+        <v>332.5195324</v>
       </c>
       <c r="I78" s="15" t="s">
         <v>239</v>
@@ -30971,13 +31017,13 @@
         <f t="shared" si="1"/>
         <v>86</v>
       </c>
-      <c r="B89" s="39" t="s">
+      <c r="B89" s="38" t="s">
         <v>483</v>
       </c>
-      <c r="C89" s="39" t="s">
+      <c r="C89" s="38" t="s">
         <v>484</v>
       </c>
-      <c r="D89" s="39" t="s">
+      <c r="D89" s="38" t="s">
         <v>22</v>
       </c>
       <c r="E89" s="14"/>

--- a/Entertainment.xlsx
+++ b/Entertainment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F24729-491A-4450-8F57-3777C2C194E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2A42D9-09FB-4AF4-A81F-935840CACC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
   </bookViews>
@@ -1883,8 +1883,8 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3295,7 +3295,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3373,7 +3373,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>

--- a/Entertainment.xlsx
+++ b/Entertainment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2A42D9-09FB-4AF4-A81F-935840CACC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BDF368F-C9A2-4D25-B17B-DA2FAF5B1D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
   </bookViews>

--- a/Entertainment.xlsx
+++ b/Entertainment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BDF368F-C9A2-4D25-B17B-DA2FAF5B1D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B7F779-362B-4E09-BC98-68EDC1B0C74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="2" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -62,6 +62,7 @@
     <externalReference r:id="rId45"/>
     <externalReference r:id="rId46"/>
     <externalReference r:id="rId47"/>
+    <externalReference r:id="rId48"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$A$1:$J$113</definedName>
@@ -87,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="488">
   <si>
     <t>Name</t>
   </si>
@@ -1545,6 +1546,12 @@
   </si>
   <si>
     <t>Q425</t>
+  </si>
+  <si>
+    <t>Springer Nature</t>
+  </si>
+  <si>
+    <t>SPG.F</t>
   </si>
 </sst>
 </file>
@@ -1637,12 +1644,10 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1755,17 +1760,17 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1779,60 +1784,64 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2926,17 +2935,17 @@
         </row>
         <row r="4">
           <cell r="G4">
-            <v>9097</v>
+            <v>9081</v>
           </cell>
         </row>
         <row r="5">
           <cell r="G5">
-            <v>5168005.7</v>
+            <v>5158916.1000000006</v>
           </cell>
         </row>
         <row r="6">
           <cell r="G6">
-            <v>351480</v>
+            <v>386128</v>
           </cell>
         </row>
       </sheetData>
@@ -3370,6 +3379,46 @@
         <row r="6">
           <cell r="H6">
             <v>176.79499999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>17.72</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="K4">
+            <v>3524.5079999999998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="K5">
+            <v>269.7</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="K6">
+            <v>1426.6</v>
           </cell>
         </row>
       </sheetData>
@@ -17173,15 +17222,15 @@
       </c>
       <c r="F6" s="26">
         <f>+[33]Main!$G$4*FX!C6</f>
-        <v>1273.5800000000002</v>
+        <v>1271.3400000000001</v>
       </c>
       <c r="G6" s="26">
         <f>+([33]Main!$G$6-[33]Main!$G$5)*FX!C6</f>
-        <v>-674313.59800000011</v>
+        <v>-668190.33400000015</v>
       </c>
       <c r="H6" s="26">
         <f t="shared" si="0"/>
-        <v>-673040.01800000016</v>
+        <v>-666918.99400000018</v>
       </c>
       <c r="I6" s="15" t="s">
         <v>239</v>
@@ -31053,14 +31102,34 @@
         <f t="shared" si="1"/>
         <v>87</v>
       </c>
-      <c r="B90" s="3"/>
-      <c r="C90" s="3"/>
-      <c r="D90" s="3"/>
-      <c r="E90" s="14"/>
-      <c r="F90" s="14"/>
-      <c r="G90" s="14"/>
-      <c r="H90" s="14"/>
-      <c r="I90" s="3"/>
+      <c r="B90" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="C90" s="40" t="s">
+        <v>487</v>
+      </c>
+      <c r="D90" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="E90" s="14">
+        <f>+[44]Main!$K$2</f>
+        <v>17.72</v>
+      </c>
+      <c r="F90" s="14">
+        <f>+[44]Main!$K$4*FX!C3</f>
+        <v>3630.2432399999998</v>
+      </c>
+      <c r="G90" s="14">
+        <f>+([44]Main!$K$6-[44]Main!$K$5)*FX!C3</f>
+        <v>1191.607</v>
+      </c>
+      <c r="H90" s="14">
+        <f>+F90+G90</f>
+        <v>4821.8502399999998</v>
+      </c>
+      <c r="I90" s="41" t="s">
+        <v>485</v>
+      </c>
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
@@ -31180,6 +31249,7 @@
     <hyperlink ref="B8" r:id="rId8" xr:uid="{5881067F-840F-4EE3-A6A6-49A5D5599E05}"/>
     <hyperlink ref="A1" location="Main!A1" display="Main" xr:uid="{AE554250-8BDC-41F6-B028-39BB218027C1}"/>
     <hyperlink ref="B17" r:id="rId9" xr:uid="{C10C3CEA-F36C-41AB-B9D5-0C29F9468CCE}"/>
+    <hyperlink ref="B90" r:id="rId10" xr:uid="{4A76E0B4-C24B-4D6F-9A4C-CD6DAE096C4C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Entertainment.xlsx
+++ b/Entertainment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B7F779-362B-4E09-BC98-68EDC1B0C74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6EC6EC6-4507-435B-A959-83FE01A41A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" activeTab="2" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
+    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1787,13 +1787,13 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="16" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1867,6 +1867,86 @@
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>29.6</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>107859.27734800002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>9325</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>99063</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>17.72</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="K4">
+            <v>3524.5079999999998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="K5">
+            <v>269.7</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="K6">
+            <v>1426.6</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
       <sheetName val="Streaming"/>
     </sheetNames>
     <sheetDataSet>
@@ -1899,407 +1979,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="G2">
-            <v>51.15</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="G4">
-            <v>37085.089004699999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="G5">
-            <v>4208</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="G6">
-            <v>14012</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink11.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>266.8</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>354602.81280000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>13765.710999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Financials"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="L3">
-            <v>228.01</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="L5">
-            <v>42061.053038120001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="L6">
-            <v>2035.1</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="L7">
-            <v>3065.1</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>134.9</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>31344.512106500002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>5489.9189999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>6254.8919999999998</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>66.67</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>42432.227438630005</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>943.8</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>2084.1999999999998</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>25.88</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>64072.986658159993</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>4888</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>34632</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="G3">
-            <v>95</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="G5">
-            <v>23679.881450000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="G6">
-            <v>2956</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="G7">
-            <v>4548</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="G2">
-            <v>45.96</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="G4">
-            <v>22817.764463160001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="G5">
-            <v>1261.9690000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="G6">
-            <v>592.70400000000006</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>33.81</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>17624.033178990001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>527</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>4363</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>5241</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>3428838.103683</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>321868</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2353,7 +2033,647 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>3214</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>19525963.200247999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>2127399</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>4088433</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>627.5</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>128905.4418725</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>8344</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="H7">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>12800</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>16623232</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1586275</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>141.63</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>82151.979704910002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>4060.3239999999996</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>5073.8320000000003</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>202.53</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>50674.485076589997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1630</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>400</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>127.88</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>82486.819144840003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>2627.1959999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>992.37699999999995</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="G2">
+            <v>51.15</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="G4">
+            <v>37085.089004699999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="G5">
+            <v>4208</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="G6">
+            <v>14012</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>25.88</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>64072.986658159993</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>4888</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>34632</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>266.8</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>354602.81280000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>13765.710999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Financials"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="L3">
+            <v>228.01</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="L5">
+            <v>42061.053038120001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="L6">
+            <v>2035.1</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="L7">
+            <v>3065.1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>134.9</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>31344.512106500002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>5489.9189999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>6254.8919999999998</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>66.67</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>42432.227438630005</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>943.8</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>2084.1999999999998</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="G3">
+            <v>95</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="G5">
+            <v>23679.881450000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="G6">
+            <v>2956</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="G7">
+            <v>4548</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="G2">
+            <v>45.96</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="G4">
+            <v>22817.764463160001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="G5">
+            <v>1261.9690000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="G6">
+            <v>592.70400000000006</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>33.81</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>17624.033178990001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>527</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>4363</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>5241</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>3428838.103683</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>321868</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2393,7 +2713,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2433,7 +2753,47 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>50.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>22898.106829</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>3322</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>7200</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2473,47 +2833,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>13.8</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>9315</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>2739</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>14514</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2553,7 +2873,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2593,7 +2913,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2633,7 +2953,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2673,7 +2993,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2713,7 +3033,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2753,47 +3073,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>29.6</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>107859.27734800002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>9325</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>99063</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2833,7 +3113,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2873,7 +3153,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2915,7 +3195,47 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>30.44</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>17310.539416759999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1778</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>2900</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2955,7 +3275,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2995,7 +3315,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3030,7 +3350,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3070,7 +3390,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3110,127 +3430,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>50.5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>22898.106829</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>3322</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>7200</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>30.44</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>17310.539416759999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1778</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>2900</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>3214</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>19525963.200247999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>2127399</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>4088433</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3270,7 +3470,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3285,17 +3485,17 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="H2">
-            <v>69.87</v>
+            <v>80.5</v>
           </cell>
         </row>
         <row r="4">
           <cell r="H4">
-            <v>11343.32525883</v>
+            <v>12979.714142500001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="H5">
-            <v>617.35199999999998</v>
+            <v>642.15699999999993</v>
           </cell>
         </row>
         <row r="6">
@@ -3310,7 +3510,47 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>13.8</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>9315</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>2739</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>14514</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3348,7 +3588,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3379,246 +3619,6 @@
         <row r="6">
           <cell r="H6">
             <v>176.79499999999999</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>17.72</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="K4">
-            <v>3524.5079999999998</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="K5">
-            <v>269.7</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="K6">
-            <v>1426.6</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>627.5</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>128905.4418725</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>8344</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="H7">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>12800</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>16623232</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1586275</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>141.63</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>82151.979704910002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>4060.3239999999996</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>5073.8320000000003</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>202.53</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>50674.485076589997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1630</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>400</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>127.88</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>82486.819144840003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>2627.1959999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>992.37699999999995</v>
           </cell>
         </row>
       </sheetData>
@@ -4139,15 +4139,15 @@
         <v>22</v>
       </c>
       <c r="E4" s="13">
-        <f>+[1]Main!$I$3</f>
+        <f>+[11]Main!$I$3</f>
         <v>97.5</v>
       </c>
       <c r="F4" s="14">
-        <f>+[1]Main!$I$5</f>
+        <f>+[11]Main!$I$5</f>
         <v>411660.80962499999</v>
       </c>
       <c r="G4" s="14">
-        <f>+[1]Main!$I$7-[1]Main!$I$6</f>
+        <f>+[11]Main!$I$7-[11]Main!$I$6</f>
         <v>5400.476999999999</v>
       </c>
       <c r="H4" s="14">
@@ -4211,15 +4211,15 @@
         <v>22</v>
       </c>
       <c r="E5" s="13">
-        <f>+[2]Main!$K$2</f>
+        <f>+[12]Main!$K$2</f>
         <v>115.68</v>
       </c>
       <c r="F5" s="14">
-        <f>+[2]Main!$K$4</f>
+        <f>+[12]Main!$K$4</f>
         <v>207984.98580144002</v>
       </c>
       <c r="G5" s="14">
-        <f>+[2]Main!$K$6-[2]Main!$K$5</f>
+        <f>+[12]Main!$K$6-[12]Main!$K$5</f>
         <v>31164</v>
       </c>
       <c r="H5" s="14">
@@ -4285,15 +4285,15 @@
         <v>22</v>
       </c>
       <c r="E6" s="13">
-        <f>+[3]Main!$I$2</f>
+        <f>+[1]Main!$I$2</f>
         <v>29.6</v>
       </c>
       <c r="F6" s="14">
-        <f>+[3]Main!$I$4</f>
+        <f>+[1]Main!$I$4</f>
         <v>107859.27734800002</v>
       </c>
       <c r="G6" s="14">
-        <f>+[3]Main!$I$6-[3]Main!$I$5</f>
+        <f>+[1]Main!$I$6-[1]Main!$I$5</f>
         <v>89738</v>
       </c>
       <c r="H6" s="14">
@@ -4357,15 +4357,15 @@
         <v>23</v>
       </c>
       <c r="E7" s="13">
-        <f>+[4]Main!$H$2</f>
+        <f>+[13]Main!$H$2</f>
         <v>3214</v>
       </c>
       <c r="F7" s="14">
-        <f>+[4]Main!$H$4*FX!C2</f>
+        <f>+[13]Main!$H$4*FX!C2</f>
         <v>124966.1644815872</v>
       </c>
       <c r="G7" s="14">
-        <f>+([4]Main!$H$6-[4]Main!$H$5)*FX!C2</f>
+        <f>+([13]Main!$H$6-[13]Main!$H$5)*FX!C2</f>
         <v>12550.617600000001</v>
       </c>
       <c r="H7" s="14">
@@ -4429,15 +4429,15 @@
         <v>24</v>
       </c>
       <c r="E8" s="13">
-        <f>+[5]Main!$H$2</f>
+        <f>+[14]Main!$H$2</f>
         <v>627.5</v>
       </c>
       <c r="F8" s="14">
-        <f>+[5]Main!$H$5*FX!C3</f>
+        <f>+[14]Main!$H$5*FX!C3</f>
         <v>132772.605128675</v>
       </c>
       <c r="G8" s="14">
-        <f>+([5]Main!$H$7-[5]Main!$H$6)*FX!C3</f>
+        <f>+([14]Main!$H$7-[14]Main!$H$6)*FX!C3</f>
         <v>-8594.32</v>
       </c>
       <c r="H8" s="14">
@@ -4501,15 +4501,15 @@
         <v>23</v>
       </c>
       <c r="E9" s="13">
-        <f>+[6]Main!$I$2</f>
+        <f>+[15]Main!$I$2</f>
         <v>12800</v>
       </c>
       <c r="F9" s="14">
-        <f>+[6]Main!$I$4*FX!C2</f>
+        <f>+[15]Main!$I$4*FX!C2</f>
         <v>106388.6848</v>
       </c>
       <c r="G9" s="14">
-        <f>+([6]Main!$I$6-[6]Main!$I$5)*FX!C2</f>
+        <f>+([15]Main!$I$6-[15]Main!$I$5)*FX!C2</f>
         <v>-10152.16</v>
       </c>
       <c r="H9" s="14">
@@ -4573,15 +4573,15 @@
         <v>25</v>
       </c>
       <c r="E10" s="13">
-        <f>+[7]Main!$I$2</f>
+        <f>+[16]Main!$I$2</f>
         <v>141.63</v>
       </c>
       <c r="F10" s="14">
-        <f>+[7]Main!$I$4</f>
+        <f>+[16]Main!$I$4</f>
         <v>82151.979704910002</v>
       </c>
       <c r="G10" s="14">
-        <f>+[7]Main!$I$6-[7]Main!$I$5</f>
+        <f>+[16]Main!$I$6-[16]Main!$I$5</f>
         <v>1013.5080000000007</v>
       </c>
       <c r="H10" s="14">
@@ -4867,15 +4867,15 @@
         <v>22</v>
       </c>
       <c r="E15" s="13">
-        <f>+[8]Main!$I$2</f>
+        <f>+[17]Main!$I$2</f>
         <v>202.53</v>
       </c>
       <c r="F15" s="14">
-        <f>+[8]Main!$I$4</f>
+        <f>+[17]Main!$I$4</f>
         <v>50674.485076589997</v>
       </c>
       <c r="G15" s="14">
-        <f>+[8]Main!$I$6-[8]Main!$I$5</f>
+        <f>+[17]Main!$I$6-[17]Main!$I$5</f>
         <v>-1230</v>
       </c>
       <c r="H15" s="14">
@@ -4941,15 +4941,15 @@
         <v>22</v>
       </c>
       <c r="E16" s="13">
-        <f>+[9]Main!$H$2</f>
+        <f>+[18]Main!$H$2</f>
         <v>127.88</v>
       </c>
       <c r="F16" s="14">
-        <f>+[9]Main!$H$4</f>
+        <f>+[18]Main!$H$4</f>
         <v>82486.819144840003</v>
       </c>
       <c r="G16" s="14">
-        <f>+[9]Main!$H$6-[9]Main!$H$5</f>
+        <f>+[18]Main!$H$6-[18]Main!$H$5</f>
         <v>-1634.819</v>
       </c>
       <c r="H16" s="14">
@@ -5013,15 +5013,15 @@
         <v>22</v>
       </c>
       <c r="E17" s="13">
-        <f>+[10]Main!$G$2</f>
+        <f>+[19]Main!$G$2</f>
         <v>51.15</v>
       </c>
       <c r="F17" s="14">
-        <f>+[10]Main!$G$4</f>
+        <f>+[19]Main!$G$4</f>
         <v>37085.089004699999</v>
       </c>
       <c r="G17" s="14">
-        <f>+[10]Main!$G$6-[10]Main!$G$5</f>
+        <f>+[19]Main!$G$6-[19]Main!$G$5</f>
         <v>9804</v>
       </c>
       <c r="H17" s="14">
@@ -5085,15 +5085,15 @@
         <v>26</v>
       </c>
       <c r="E18" s="3">
-        <f>+[11]Main!$I$2</f>
+        <f>+[20]Main!$I$2</f>
         <v>266.8</v>
       </c>
       <c r="F18" s="21">
-        <f>+[11]Main!$I$4*FX!C6</f>
+        <f>+[20]Main!$I$4*FX!C6</f>
         <v>49644.39379200001</v>
       </c>
       <c r="G18" s="14">
-        <f>+([11]Main!$I$6-[11]Main!$I$5)*FX!C6</f>
+        <f>+([20]Main!$I$6-[20]Main!$I$5)*FX!C6</f>
         <v>-1927.1995400000001</v>
       </c>
       <c r="H18" s="14">
@@ -5211,15 +5211,15 @@
         <v>22</v>
       </c>
       <c r="E20" s="3">
-        <f>+[12]Main!$L$3</f>
+        <f>+[21]Main!$L$3</f>
         <v>228.01</v>
       </c>
       <c r="F20" s="14">
-        <f>+[12]Main!$L$5</f>
+        <f>+[21]Main!$L$5</f>
         <v>42061.053038120001</v>
       </c>
       <c r="G20" s="14">
-        <f>+[12]Main!$L$7-[12]Main!$L$6</f>
+        <f>+[21]Main!$L$7-[21]Main!$L$6</f>
         <v>1030</v>
       </c>
       <c r="H20" s="14">
@@ -5283,15 +5283,15 @@
         <v>22</v>
       </c>
       <c r="E21" s="18">
-        <f>+[13]Main!$H$2</f>
+        <f>+[22]Main!$H$2</f>
         <v>134.9</v>
       </c>
       <c r="F21" s="14">
-        <f>+[13]Main!$H$4</f>
+        <f>+[22]Main!$H$4</f>
         <v>31344.512106500002</v>
       </c>
       <c r="G21" s="14">
-        <f>+[13]Main!$H$6-[13]Main!$H$5</f>
+        <f>+[22]Main!$H$6-[22]Main!$H$5</f>
         <v>764.97299999999996</v>
       </c>
       <c r="H21" s="14">
@@ -5355,15 +5355,15 @@
         <v>50</v>
       </c>
       <c r="E22" s="3">
-        <f>+[14]Main!$I$2</f>
+        <f>+[23]Main!$I$2</f>
         <v>66.67</v>
       </c>
       <c r="F22" s="14">
-        <f>+[14]Main!$I$4*FX!C5</f>
+        <f>+[23]Main!$I$4*FX!C5</f>
         <v>26732.303286336904</v>
       </c>
       <c r="G22" s="14">
-        <f>+([14]Main!$I$6-[14]Main!$I$5)*FX!C5</f>
+        <f>+([23]Main!$I$6-[23]Main!$I$5)*FX!C5</f>
         <v>718.45199999999988</v>
       </c>
       <c r="H22" s="14">
@@ -5427,15 +5427,15 @@
         <v>22</v>
       </c>
       <c r="E23" s="3">
-        <f>+[15]Main!$H$2</f>
+        <f>+[2]Main!$H$2</f>
         <v>25.88</v>
       </c>
       <c r="F23" s="14">
-        <f>+[15]Main!$H$4</f>
+        <f>+[2]Main!$H$4</f>
         <v>64072.986658159993</v>
       </c>
       <c r="G23" s="14">
-        <f>+[15]Main!$H$6-[15]Main!$H$5</f>
+        <f>+[2]Main!$H$6-[2]Main!$H$5</f>
         <v>29744</v>
       </c>
       <c r="H23" s="14">
@@ -5501,15 +5501,15 @@
         <v>22</v>
       </c>
       <c r="E24" s="3">
-        <f>+[16]Main!$G$3</f>
+        <f>+[24]Main!$G$3</f>
         <v>95</v>
       </c>
       <c r="F24" s="14">
-        <f>+[16]Main!$G$5</f>
+        <f>+[24]Main!$G$5</f>
         <v>23679.881450000001</v>
       </c>
       <c r="G24" s="14">
-        <f>+[16]Main!$G$7-[16]Main!$G$6</f>
+        <f>+[24]Main!$G$7-[24]Main!$G$6</f>
         <v>1592</v>
       </c>
       <c r="H24" s="14">
@@ -5629,15 +5629,15 @@
         <v>22</v>
       </c>
       <c r="E26" s="3">
-        <f>+[17]Main!$G$2</f>
+        <f>+[25]Main!$G$2</f>
         <v>45.96</v>
       </c>
       <c r="F26" s="14">
-        <f>+[17]Main!$G$4</f>
+        <f>+[25]Main!$G$4</f>
         <v>22817.764463160001</v>
       </c>
       <c r="G26" s="14">
-        <f>+[17]Main!$G$6-[17]Main!$G$5</f>
+        <f>+[25]Main!$G$6-[25]Main!$G$5</f>
         <v>-669.26499999999999</v>
       </c>
       <c r="H26" s="14">
@@ -5701,15 +5701,15 @@
         <v>22</v>
       </c>
       <c r="E27" s="3">
-        <f>+[18]Main!$H$2</f>
+        <f>+[26]Main!$H$2</f>
         <v>33.81</v>
       </c>
       <c r="F27" s="14">
-        <f>+[18]Main!$H$4</f>
+        <f>+[26]Main!$H$4</f>
         <v>17624.033178990001</v>
       </c>
       <c r="G27" s="14">
-        <f>+[18]Main!$H$6-[18]Main!$H$5</f>
+        <f>+[26]Main!$H$6-[26]Main!$H$5</f>
         <v>3836</v>
       </c>
       <c r="H27" s="14">
@@ -5829,15 +5829,15 @@
         <v>23</v>
       </c>
       <c r="E29" s="19">
-        <f>+[19]Main!$I$2</f>
+        <f>+[27]Main!$I$2</f>
         <v>5241</v>
       </c>
       <c r="F29" s="14">
-        <f>+[19]Main!$I$4*FX!C2</f>
+        <f>+[27]Main!$I$4*FX!C2</f>
         <v>21944.563863571202</v>
       </c>
       <c r="G29" s="14">
-        <f>+([19]Main!$I$6-[19]Main!$I$5)*FX!C2</f>
+        <f>+([27]Main!$I$6-[27]Main!$I$5)*FX!C2</f>
         <v>-2059.9551999999999</v>
       </c>
       <c r="H29" s="14">
@@ -5897,15 +5897,15 @@
         <v>23</v>
       </c>
       <c r="E30" s="19">
-        <f>+[20]Main!$I$2</f>
+        <f>+[28]Main!$I$2</f>
         <v>16735</v>
       </c>
       <c r="F30" s="14">
-        <f>+[20]Main!$I$4*FX!C2</f>
+        <f>+[28]Main!$I$4*FX!C2</f>
         <v>14518.749837375999</v>
       </c>
       <c r="G30" s="14">
-        <f>+([20]Main!$I$6-[20]Main!$I$5)*FX!C2</f>
+        <f>+([28]Main!$I$6-[28]Main!$I$5)*FX!C2</f>
         <v>-1445.152</v>
       </c>
       <c r="H30" s="14">
@@ -6023,15 +6023,15 @@
         <v>22</v>
       </c>
       <c r="E32" s="3">
-        <f>+[21]Main!$J$2</f>
+        <f>+[29]Main!$J$2</f>
         <v>184.82</v>
       </c>
       <c r="F32" s="14">
-        <f>+[21]Main!$J$4</f>
+        <f>+[29]Main!$J$4</f>
         <v>15180.539270520001</v>
       </c>
       <c r="G32" s="14">
-        <f>+[21]Main!$J$6-[21]Main!$J$5</f>
+        <f>+[29]Main!$J$6-[29]Main!$J$5</f>
         <v>2214.2530000000002</v>
       </c>
       <c r="H32" s="14">
@@ -6429,15 +6429,15 @@
         <v>22</v>
       </c>
       <c r="E39" s="3">
-        <f>+[22]Main!$H$2</f>
+        <f>+[30]Main!$H$2</f>
         <v>65.319999999999993</v>
       </c>
       <c r="F39" s="14">
-        <f>+[22]Main!$H$4</f>
+        <f>+[30]Main!$H$4</f>
         <v>9114.1865409199982</v>
       </c>
       <c r="G39" s="14">
-        <f>+[22]Main!$H$6-[22]Main!$H$5</f>
+        <f>+[30]Main!$H$6-[30]Main!$H$5</f>
         <v>2685.8</v>
       </c>
       <c r="H39" s="14">
@@ -6557,15 +6557,15 @@
         <v>22</v>
       </c>
       <c r="E41" s="3">
-        <f>+[23]Main!$I$2</f>
+        <f>+[7]Main!$I$2</f>
         <v>13.8</v>
       </c>
       <c r="F41" s="14">
-        <f>+[23]Main!$I$4</f>
+        <f>+[7]Main!$I$4</f>
         <v>9315</v>
       </c>
       <c r="G41" s="14">
-        <f>+[23]Main!$I$6-[23]Main!$I$5</f>
+        <f>+[7]Main!$I$6-[7]Main!$I$5</f>
         <v>11775</v>
       </c>
       <c r="H41" s="14">
@@ -6909,15 +6909,15 @@
         <v>22</v>
       </c>
       <c r="E47" s="3">
-        <f>+[24]Main!$I$2</f>
+        <f>+[31]Main!$I$2</f>
         <v>77.77</v>
       </c>
       <c r="F47" s="14">
-        <f>+[24]Main!$I$4</f>
+        <f>+[31]Main!$I$4</f>
         <v>6330.7175316000003</v>
       </c>
       <c r="G47" s="14">
-        <f>+[24]Main!$I$6-[24]Main!$I$5</f>
+        <f>+[31]Main!$I$6-[31]Main!$I$5</f>
         <v>3205.0709999999999</v>
       </c>
       <c r="H47" s="14">
@@ -7091,15 +7091,15 @@
         <v>22</v>
       </c>
       <c r="E50" s="3">
-        <f>+[25]Main!$G$2</f>
+        <f>+[32]Main!$G$2</f>
         <v>17.309999999999999</v>
       </c>
       <c r="F50" s="14">
-        <f>+[25]Main!$G$4</f>
+        <f>+[32]Main!$G$4</f>
         <v>5750.3819999999996</v>
       </c>
       <c r="G50" s="14">
-        <f>+[25]Main!$G$6-[25]Main!$G$5</f>
+        <f>+[32]Main!$G$6-[32]Main!$G$5</f>
         <v>1466.0810000000004</v>
       </c>
       <c r="H50" s="14">
@@ -7499,15 +7499,15 @@
         <v>22</v>
       </c>
       <c r="E57" s="3">
-        <f>+[26]Main!$I$2</f>
+        <f>+[33]Main!$I$2</f>
         <v>183.2</v>
       </c>
       <c r="F57" s="14">
-        <f>+[26]Main!$I$4</f>
+        <f>+[33]Main!$I$4</f>
         <v>5589.2865391999994</v>
       </c>
       <c r="G57" s="14">
-        <f>+[26]Main!$I$6-[26]Main!$I$5</f>
+        <f>+[33]Main!$I$6-[33]Main!$I$5</f>
         <v>6379</v>
       </c>
       <c r="H57" s="14">
@@ -9025,15 +9025,15 @@
         <v>23</v>
       </c>
       <c r="E84" s="34">
-        <f>+[27]Main!$J$2</f>
+        <f>+[34]Main!$J$2</f>
         <v>3555</v>
       </c>
       <c r="F84" s="14">
-        <f>+[27]Main!$J$4*FX!C2</f>
+        <f>+[34]Main!$J$4*FX!C2</f>
         <v>3334.2666713280005</v>
       </c>
       <c r="G84" s="14">
-        <f>+([27]Main!$J$6-[27]Main!$J$5)*FX!C2</f>
+        <f>+([34]Main!$J$6-[34]Main!$J$5)*FX!C2</f>
         <v>-683.66079999999999</v>
       </c>
       <c r="H84" s="14">
@@ -9543,15 +9543,15 @@
         <v>23</v>
       </c>
       <c r="E93" s="3">
-        <f>+[28]Main!$I$2</f>
+        <f>+[35]Main!$I$2</f>
         <v>5310</v>
       </c>
       <c r="F93" s="14">
-        <f>+[28]Main!$I$4*FX!C2</f>
+        <f>+[35]Main!$I$4*FX!C2</f>
         <v>2103.4388983680001</v>
       </c>
       <c r="G93" s="14">
-        <f>+([28]Main!$I$6-[28]Main!$I$5)*FX!C2</f>
+        <f>+([35]Main!$I$6-[35]Main!$I$5)*FX!C2</f>
         <v>-590.64960000000008</v>
       </c>
       <c r="H93" s="14">
@@ -10229,15 +10229,15 @@
         <v>22</v>
       </c>
       <c r="E105" s="3">
-        <f>+[29]Main!$I$2</f>
+        <f>+[36]Main!$I$2</f>
         <v>33.76</v>
       </c>
       <c r="F105" s="14">
-        <f>+[29]Main!$I$4</f>
+        <f>+[36]Main!$I$4</f>
         <v>1615.1327198399999</v>
       </c>
       <c r="G105" s="14">
-        <f>+[29]Main!$I$6-[29]Main!$I$5</f>
+        <f>+[36]Main!$I$6-[36]Main!$I$5</f>
         <v>553.85699999999997</v>
       </c>
       <c r="H105" s="14">
@@ -10411,15 +10411,15 @@
         <v>153</v>
       </c>
       <c r="E108" s="3">
-        <f>+[30]Main!$H$2</f>
+        <f>+[37]Main!$H$2</f>
         <v>15.92</v>
       </c>
       <c r="F108" s="14">
-        <f>+[30]Main!$H$5*FX!C4</f>
+        <f>+[37]Main!$H$5*FX!C4</f>
         <v>2707.3869572160002</v>
       </c>
       <c r="G108" s="14">
-        <f>+([30]Main!$H$7-[30]Main!$H$6)*FX!C4</f>
+        <f>+([37]Main!$H$7-[37]Main!$H$6)*FX!C4</f>
         <v>699.94651999999996</v>
       </c>
       <c r="H108" s="14">
@@ -10539,15 +10539,15 @@
         <v>85</v>
       </c>
       <c r="E110" s="3">
-        <f>+[31]Main!$I$2</f>
+        <f>+[38]Main!$I$2</f>
         <v>3.28</v>
       </c>
       <c r="F110" s="14">
-        <f>+[31]Main!$I$4*FX!C3</f>
+        <f>+[38]Main!$I$4*FX!C3</f>
         <v>372.96258964800001</v>
       </c>
       <c r="G110" s="14">
-        <f>+([31]Main!$I$6-[31]Main!$I$5)*FX!C3</f>
+        <f>+([38]Main!$I$6-[38]Main!$I$5)*FX!C3</f>
         <v>50.842859999999995</v>
       </c>
       <c r="H110" s="14">
@@ -17122,15 +17122,15 @@
         <v>22</v>
       </c>
       <c r="E5" s="26">
-        <f>+[32]Main!$H$2</f>
+        <f>+[39]Main!$H$2</f>
         <v>432.32</v>
       </c>
       <c r="F5" s="26">
-        <f>+[32]Main!$H$4</f>
+        <f>+[39]Main!$H$4</f>
         <v>3210247.9621363198</v>
       </c>
       <c r="G5" s="26">
-        <f>+[32]Main!$H$6-[32]Main!$H$5</f>
+        <f>+[39]Main!$H$6-[39]Main!$H$5</f>
         <v>-49200</v>
       </c>
       <c r="H5" s="26">
@@ -17217,15 +17217,15 @@
         <v>26</v>
       </c>
       <c r="E6" s="26">
-        <f>+[33]Main!$G$2</f>
+        <f>+[40]Main!$G$2</f>
         <v>617.5</v>
       </c>
       <c r="F6" s="26">
-        <f>+[33]Main!$G$4*FX!C6</f>
+        <f>+[40]Main!$G$4*FX!C6</f>
         <v>1271.3400000000001</v>
       </c>
       <c r="G6" s="26">
-        <f>+([33]Main!$G$6-[33]Main!$G$5)*FX!C6</f>
+        <f>+([40]Main!$G$6-[40]Main!$G$5)*FX!C6</f>
         <v>-668190.33400000015</v>
       </c>
       <c r="H6" s="26">
@@ -17312,15 +17312,15 @@
         <v>23</v>
       </c>
       <c r="E7" s="26">
-        <f>+[4]Main!$H$2</f>
+        <f>+[13]Main!$H$2</f>
         <v>3214</v>
       </c>
       <c r="F7" s="26">
-        <f>+[4]Main!$H$4*FX!C2</f>
+        <f>+[13]Main!$H$4*FX!C2</f>
         <v>124966.1644815872</v>
       </c>
       <c r="G7" s="26">
-        <f>+([4]Main!$H$6-[4]Main!$H$5)*FX!C2</f>
+        <f>+([13]Main!$H$6-[13]Main!$H$5)*FX!C2</f>
         <v>12550.617600000001</v>
       </c>
       <c r="H7" s="26">
@@ -17407,15 +17407,15 @@
         <v>23</v>
       </c>
       <c r="E8" s="26">
-        <f>+[6]Main!$I$2</f>
+        <f>+[15]Main!$I$2</f>
         <v>12800</v>
       </c>
       <c r="F8" s="26">
-        <f>+[6]Main!$I$4*FX!C2</f>
+        <f>+[15]Main!$I$4*FX!C2</f>
         <v>106388.6848</v>
       </c>
       <c r="G8" s="26">
-        <f>+([6]Main!$I$6-[6]Main!$I$5)*FX!C2</f>
+        <f>+([15]Main!$I$6-[15]Main!$I$5)*FX!C2</f>
         <v>-10152.16</v>
       </c>
       <c r="H8" s="26">
@@ -17502,15 +17502,15 @@
         <v>26</v>
       </c>
       <c r="E9" s="26">
-        <f>+[34]Main!$I$2</f>
+        <f>+[41]Main!$I$2</f>
         <v>2123</v>
       </c>
       <c r="F9" s="26">
-        <f>+[35]Main!$H$5*FX!C6</f>
+        <f>+[42]Main!$H$5*FX!C6</f>
         <v>65131.275185760009</v>
       </c>
       <c r="G9" s="26">
-        <f>+([35]Main!$H$7-[35]Main!$H$6)*FX!C6</f>
+        <f>+([42]Main!$H$7-[42]Main!$H$6)*FX!C6</f>
         <v>-16042.82638</v>
       </c>
       <c r="H9" s="26">
@@ -17597,15 +17597,15 @@
         <v>25</v>
       </c>
       <c r="E10" s="26">
-        <f>+[7]Main!$I$2</f>
+        <f>+[16]Main!$I$2</f>
         <v>141.63</v>
       </c>
       <c r="F10" s="26">
-        <f>+[7]Main!$I$4</f>
+        <f>+[16]Main!$I$4</f>
         <v>82151.979704910002</v>
       </c>
       <c r="G10" s="26">
-        <f>+[7]Main!$I$6-[7]Main!$I$5</f>
+        <f>+[16]Main!$I$6-[16]Main!$I$5</f>
         <v>1013.5080000000007</v>
       </c>
       <c r="H10" s="26">
@@ -17692,15 +17692,15 @@
         <v>22</v>
       </c>
       <c r="E11" s="26">
-        <f>+[8]Main!$I$2</f>
+        <f>+[17]Main!$I$2</f>
         <v>202.53</v>
       </c>
       <c r="F11" s="26">
-        <f>+[8]Main!$I$4</f>
+        <f>+[17]Main!$I$4</f>
         <v>50674.485076589997</v>
       </c>
       <c r="G11" s="26">
-        <f>+[8]Main!$I$6-[8]Main!$I$5</f>
+        <f>+[17]Main!$I$6-[17]Main!$I$5</f>
         <v>-1230</v>
       </c>
       <c r="H11" s="26">
@@ -17787,15 +17787,15 @@
         <v>22</v>
       </c>
       <c r="E12" s="26">
-        <f>+[12]Main!$L$3</f>
+        <f>+[21]Main!$L$3</f>
         <v>228.01</v>
       </c>
       <c r="F12" s="26">
-        <f>+[12]Main!$L$5</f>
+        <f>+[21]Main!$L$5</f>
         <v>42061.053038120001</v>
       </c>
       <c r="G12" s="26">
-        <f>+[12]Main!$L$7-[12]Main!$L$6</f>
+        <f>+[21]Main!$L$7-[21]Main!$L$6</f>
         <v>1030</v>
       </c>
       <c r="H12" s="26">
@@ -17882,15 +17882,15 @@
         <v>22</v>
       </c>
       <c r="E13" s="26">
-        <f>+[9]Main!$H$2</f>
+        <f>+[18]Main!$H$2</f>
         <v>127.88</v>
       </c>
       <c r="F13" s="26">
-        <f>+[9]Main!$H$4</f>
+        <f>+[18]Main!$H$4</f>
         <v>82486.819144840003</v>
       </c>
       <c r="G13" s="26">
-        <f>+[9]Main!$H$6-[9]Main!$H$5</f>
+        <f>+[18]Main!$H$6-[18]Main!$H$5</f>
         <v>-1634.819</v>
       </c>
       <c r="H13" s="26">
@@ -17977,15 +17977,15 @@
         <v>50</v>
       </c>
       <c r="E14" s="26">
-        <f>+[14]Main!$I$2</f>
+        <f>+[23]Main!$I$2</f>
         <v>66.67</v>
       </c>
       <c r="F14" s="26">
-        <f>+[14]Main!$I$4*FX!C5</f>
+        <f>+[23]Main!$I$4*FX!C5</f>
         <v>26732.303286336904</v>
       </c>
       <c r="G14" s="26">
-        <f>+([14]Main!$I$6-[14]Main!$I$5)*FX!C5</f>
+        <f>+([23]Main!$I$6-[23]Main!$I$5)*FX!C5</f>
         <v>718.45199999999988</v>
       </c>
       <c r="H14" s="26">
@@ -18072,15 +18072,15 @@
         <v>23</v>
       </c>
       <c r="E15" s="26">
-        <f>+[34]Main!$I$2</f>
+        <f>+[41]Main!$I$2</f>
         <v>2123</v>
       </c>
       <c r="F15" s="26">
-        <f>+[34]Main!$I$4*FX!C2</f>
+        <f>+[41]Main!$I$4*FX!C2</f>
         <v>11429.0165977856</v>
       </c>
       <c r="G15" s="26">
-        <f>+([34]Main!$I$6-[34]Main!$I$5)*FX!C2</f>
+        <f>+([41]Main!$I$6-[41]Main!$I$5)*FX!C2</f>
         <v>-2117.3888000000002</v>
       </c>
       <c r="H15" s="26">
@@ -18167,15 +18167,15 @@
         <v>23</v>
       </c>
       <c r="E16" s="26">
-        <f>+[19]Main!$I$2</f>
+        <f>+[27]Main!$I$2</f>
         <v>5241</v>
       </c>
       <c r="F16" s="26">
-        <f>+[19]Main!$I$4*FX!C2</f>
+        <f>+[27]Main!$I$4*FX!C2</f>
         <v>21944.563863571202</v>
       </c>
       <c r="G16" s="26">
-        <f>+([19]Main!$I$6-[19]Main!$I$5)*FX!C2</f>
+        <f>+([27]Main!$I$6-[27]Main!$I$5)*FX!C2</f>
         <v>-2059.9551999999999</v>
       </c>
       <c r="H16" s="26">
@@ -18262,15 +18262,15 @@
         <v>23</v>
       </c>
       <c r="E17" s="26">
-        <f>+[20]Main!$I$2</f>
+        <f>+[28]Main!$I$2</f>
         <v>16735</v>
       </c>
       <c r="F17" s="26">
-        <f>+[20]Main!$I$4*FX!C2</f>
+        <f>+[28]Main!$I$4*FX!C2</f>
         <v>14518.749837375999</v>
       </c>
       <c r="G17" s="26">
-        <f>+([20]Main!$I$6-[20]Main!$I$5)*FX!C2</f>
+        <f>+([28]Main!$I$6-[28]Main!$I$5)*FX!C2</f>
         <v>-1445.152</v>
       </c>
       <c r="H17" s="26">
@@ -18357,15 +18357,15 @@
         <v>94</v>
       </c>
       <c r="E18" s="26">
-        <f>+[36]Main!$H$2</f>
+        <f>+[43]Main!$H$2</f>
         <v>12.11</v>
       </c>
       <c r="F18" s="26">
-        <f>+[36]Main!$H$4*FX!C3</f>
+        <f>+[43]Main!$H$4*FX!C3</f>
         <v>1601.5717199999999</v>
       </c>
       <c r="G18" s="26">
-        <f>+([36]Main!$H$6-[36]Main!$H$5)*FX!C3</f>
+        <f>+([43]Main!$H$6-[43]Main!$H$5)*FX!C3</f>
         <v>1343.7380000000003</v>
       </c>
       <c r="H18" s="26">
@@ -18595,15 +18595,15 @@
         <v>22</v>
       </c>
       <c r="E21" s="26">
-        <f>+[37]Main!$J$2</f>
+        <f>+[44]Main!$J$2</f>
         <v>21.7</v>
       </c>
       <c r="F21" s="26">
-        <f>+[37]Main!$J$4</f>
+        <f>+[44]Main!$J$4</f>
         <v>9701.7223876999997</v>
       </c>
       <c r="G21" s="26">
-        <f>+[37]Main!$J$6-[37]Main!$J$5</f>
+        <f>+[44]Main!$J$6-[44]Main!$J$5</f>
         <v>-4758</v>
       </c>
       <c r="H21" s="26">
@@ -27898,15 +27898,15 @@
         <v>22</v>
       </c>
       <c r="E4" s="14">
-        <f>+[3]Main!$I$2</f>
+        <f>+[1]Main!$I$2</f>
         <v>29.6</v>
       </c>
       <c r="F4" s="14">
-        <f>+[3]Main!$I$4</f>
+        <f>+[1]Main!$I$4</f>
         <v>107859.27734800002</v>
       </c>
       <c r="G4" s="14">
-        <f>+[3]Main!$I$6-[3]Main!$I$5</f>
+        <f>+[1]Main!$I$6-[1]Main!$I$5</f>
         <v>89738</v>
       </c>
       <c r="H4" s="14">
@@ -28020,15 +28020,15 @@
         <v>22</v>
       </c>
       <c r="E7" s="14">
-        <f>+[15]Main!$H$2</f>
+        <f>+[2]Main!$H$2</f>
         <v>25.88</v>
       </c>
       <c r="F7" s="14">
-        <f>+[15]Main!$H$4</f>
+        <f>+[2]Main!$H$4</f>
         <v>64072.986658159993</v>
       </c>
       <c r="G7" s="14">
-        <f>+[15]Main!$H$6-[15]Main!$H$5</f>
+        <f>+[2]Main!$H$6-[2]Main!$H$5</f>
         <v>29744</v>
       </c>
       <c r="H7" s="14">
@@ -28070,15 +28070,15 @@
         <v>22</v>
       </c>
       <c r="E8" s="14">
-        <f>+[38]Main!$I$2</f>
+        <f>+[3]Main!$I$2</f>
         <v>50.5</v>
       </c>
       <c r="F8" s="14">
-        <f>+[38]Main!$I$4</f>
+        <f>+[3]Main!$I$4</f>
         <v>22898.106829</v>
       </c>
       <c r="G8" s="14">
-        <f>+[38]Main!$I$6-[38]Main!$I$5</f>
+        <f>+[3]Main!$I$6-[3]Main!$I$5</f>
         <v>3878</v>
       </c>
       <c r="H8" s="14">
@@ -28192,15 +28192,15 @@
         <v>22</v>
       </c>
       <c r="E11" s="14">
-        <f>+[39]Main!$I$2</f>
+        <f>+[4]Main!$I$2</f>
         <v>30.44</v>
       </c>
       <c r="F11" s="14">
-        <f>+[39]Main!$I$4</f>
+        <f>+[4]Main!$I$4</f>
         <v>17310.539416759999</v>
       </c>
       <c r="G11" s="14">
-        <f>+[39]Main!$I$6-[39]Main!$I$5</f>
+        <f>+[4]Main!$I$6-[4]Main!$I$5</f>
         <v>1122</v>
       </c>
       <c r="H11" s="14">
@@ -28278,15 +28278,15 @@
         <v>22</v>
       </c>
       <c r="E13" s="14">
-        <f>+[40]Main!$H$2</f>
+        <f>+[5]Main!$H$2</f>
         <v>41.21</v>
       </c>
       <c r="F13" s="14">
-        <f>+[40]Main!$H$4</f>
+        <f>+[5]Main!$H$4</f>
         <v>8939.4565020800001</v>
       </c>
       <c r="G13" s="14">
-        <f>+[40]Main!$H$6-[40]Main!$H$5</f>
+        <f>+[5]Main!$H$6-[5]Main!$H$5</f>
         <v>-663.44470000000001</v>
       </c>
       <c r="H13" s="14">
@@ -28328,20 +28328,20 @@
         <v>22</v>
       </c>
       <c r="E14" s="14">
-        <f>+[41]Main!$H$2</f>
-        <v>69.87</v>
+        <f>+[6]Main!$H$2</f>
+        <v>80.5</v>
       </c>
       <c r="F14" s="14">
-        <f>+[41]Main!$H$4</f>
-        <v>11343.32525883</v>
+        <f>+[6]Main!$H$4</f>
+        <v>12979.714142500001</v>
       </c>
       <c r="G14" s="14">
-        <f>+[41]Main!$H$6-[41]Main!$H$5</f>
-        <v>-617.35199999999998</v>
+        <f>+[6]Main!$H$6-[6]Main!$H$5</f>
+        <v>-642.15699999999993</v>
       </c>
       <c r="H14" s="14">
         <f>+F14+G14</f>
-        <v>10725.973258829999</v>
+        <v>12337.557142500002</v>
       </c>
       <c r="I14" s="36" t="s">
         <v>295</v>
@@ -28378,15 +28378,15 @@
         <v>22</v>
       </c>
       <c r="E15" s="14">
-        <f>+[23]Main!$I$2</f>
+        <f>+[7]Main!$I$2</f>
         <v>13.8</v>
       </c>
       <c r="F15" s="14">
-        <f>+[23]Main!$I$4</f>
+        <f>+[7]Main!$I$4</f>
         <v>9315</v>
       </c>
       <c r="G15" s="14">
-        <f>+[23]Main!$I$6-[23]Main!$I$5</f>
+        <f>+[7]Main!$I$6-[7]Main!$I$5</f>
         <v>11775</v>
       </c>
       <c r="H15" s="14">
@@ -28464,15 +28464,15 @@
         <v>22</v>
       </c>
       <c r="E17" s="14">
-        <f>+[42]Main!$K$2</f>
+        <f>+[8]Main!$K$2</f>
         <v>78.55</v>
       </c>
       <c r="F17" s="14">
-        <f>+[42]Main!$K$4</f>
+        <f>+[8]Main!$K$4</f>
         <v>7215.2325581999994</v>
       </c>
       <c r="G17" s="14">
-        <f>+[42]Main!$K$6-[42]Main!$K$5</f>
+        <f>+[8]Main!$K$6-[8]Main!$K$5</f>
         <v>1417</v>
       </c>
       <c r="H17" s="14">
@@ -30670,15 +30670,15 @@
         <v>22</v>
       </c>
       <c r="E78" s="14">
-        <f>+[43]Main!$H$2</f>
+        <f>+[9]Main!$H$2</f>
         <v>1.7</v>
       </c>
       <c r="F78" s="14">
-        <f>+[43]Main!$H$4</f>
+        <f>+[9]Main!$H$4</f>
         <v>183.18753240000001</v>
       </c>
       <c r="G78" s="14">
-        <f>+[43]Main!$H$6-[43]Main!$H$5</f>
+        <f>+[9]Main!$H$6-[9]Main!$H$5</f>
         <v>149.33199999999999</v>
       </c>
       <c r="H78" s="14">
@@ -31112,15 +31112,15 @@
         <v>85</v>
       </c>
       <c r="E90" s="14">
-        <f>+[44]Main!$K$2</f>
+        <f>+[10]Main!$K$2</f>
         <v>17.72</v>
       </c>
       <c r="F90" s="14">
-        <f>+[44]Main!$K$4*FX!C3</f>
+        <f>+[10]Main!$K$4*FX!C3</f>
         <v>3630.2432399999998</v>
       </c>
       <c r="G90" s="14">
-        <f>+([44]Main!$K$6-[44]Main!$K$5)*FX!C3</f>
+        <f>+([10]Main!$K$6-[10]Main!$K$5)*FX!C3</f>
         <v>1191.607</v>
       </c>
       <c r="H90" s="14">

--- a/Entertainment.xlsx
+++ b/Entertainment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6EC6EC6-4507-435B-A959-83FE01A41A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B7833E-9FB5-4F52-8504-DE3B5E493F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="2730" windowWidth="38175" windowHeight="15240" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
+    <workbookView xWindow="225" yWindow="3120" windowWidth="38175" windowHeight="15240" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -63,6 +63,7 @@
     <externalReference r:id="rId46"/>
     <externalReference r:id="rId47"/>
     <externalReference r:id="rId48"/>
+    <externalReference r:id="rId49"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Main!$A$1:$J$113</definedName>
@@ -88,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="488">
   <si>
     <t>Name</t>
   </si>
@@ -1563,13 +1564,19 @@
     <numFmt numFmtId="165" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1760,78 +1767,82 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="16" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="16" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1867,31 +1878,33 @@
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
+      <sheetName val="Streaming"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>29.6</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>107859.27734800002</v>
+        <row r="3">
+          <cell r="I3">
+            <v>97.5</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>9325</v>
+            <v>411721.73250000004</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>99063</v>
+            <v>12288.45</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="I7">
+            <v>14360.516</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1911,23 +1924,23 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
-          <cell r="K2">
-            <v>17.72</v>
+          <cell r="G2">
+            <v>51.15</v>
           </cell>
         </row>
         <row r="4">
-          <cell r="K4">
-            <v>3524.5079999999998</v>
+          <cell r="G4">
+            <v>37085.089004699999</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="K5">
-            <v>269.7</v>
+          <cell r="G5">
+            <v>4208</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="K6">
-            <v>1426.6</v>
+          <cell r="G6">
+            <v>14012</v>
           </cell>
         </row>
       </sheetData>
@@ -1947,39 +1960,357 @@
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
-      <sheetName val="Streaming"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="3">
-          <cell r="I3">
-            <v>97.5</v>
+        <row r="2">
+          <cell r="I2">
+            <v>154.19999999999999</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>204946.60319999998</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>411660.80962499999</v>
+            <v>13765.710999999999</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>9062.3590000000004</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="I7">
-            <v>14462.835999999999</v>
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/externalLinks/externalLink12.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Financials"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="L3">
+            <v>228.01</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="L5">
+            <v>42061.053038120001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="L6">
+            <v>2035.1</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="L7">
+            <v>3065.1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>134.9</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>31344.512106500002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>5489.9189999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>6254.8919999999998</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>66.67</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>42432.227438630005</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>943.8</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>2084.1999999999998</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>25.88</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>64072.986658159993</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>4888</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>34632</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="G3">
+            <v>95</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="G5">
+            <v>23679.881450000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="G6">
+            <v>2956</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="G7">
+            <v>4548</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="G2">
+            <v>45.96</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="G4">
+            <v>22817.764463160001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="G5">
+            <v>1261.9690000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="G6">
+            <v>592.70400000000006</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>33.81</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>17624.033178990001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>527</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>4363</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>5241</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>3428838.103683</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>321868</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2033,7 +2364,844 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>16735</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>2268554.6620899998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>285700</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>59895</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>184.82</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>15180.539270520001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>535.06100000000004</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>2749.3140000000003</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>65.319999999999993</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>9114.1865409199982</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>695</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>3380.8</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>13.8</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>9315</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>2739</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>14514</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>77.77</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>6330.7175316000003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>311.50299999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>3516.5740000000001</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="G2">
+            <v>17.309999999999999</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="G4">
+            <v>5750.3819999999996</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="G5">
+            <v>870.452</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="G6">
+            <v>2336.5330000000004</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>183.2</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>5589.2865391999994</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>144</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>6523</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>3555</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>520979.16739500005</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>133399</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>26577</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>5310</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>328662.32786999998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>104775</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>12486</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>33.76</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>1615.1327198399999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>55.219000000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>609.07600000000002</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>29.6</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>107859.27734800002</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>9325</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>99063</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>15.92</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>2183.3765784000002</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>149.55799999999999</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="H7">
+            <v>714.03099999999995</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>3.28</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>362.09960159999997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>4.45</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>53.811999999999998</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Ratios"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>405.1</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>3009258.8985904003</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>78272</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>40262</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="G2">
+            <v>617.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="G4">
+            <v>9081</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="G5">
+            <v>5158916.1000000006</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="G6">
+            <v>386128</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>2123</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>1785783.8434039999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>331931</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>1089</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="5">
+          <cell r="H5">
+            <v>465223.39418400003</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>126824.66499999999</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="H7">
+            <v>12233.047999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>12.11</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>1554.924</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>1205.2</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>2509.8000000000002</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="J2">
+            <v>21.7</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="J4">
+            <v>9701.7223876999997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>4774.8999999999996</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>16.899999999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>50.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>22898.106829</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>3322</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>7200</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>30.44</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>17310.539416759999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1778</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>2900</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2073,7 +3241,245 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>41.21</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>8939.4565020800001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>672.87819999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>9.4335000000000004</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>80.5</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>12979.714142500001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>642.15699999999993</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>78.55</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="K4">
+            <v>7215.2325581999994</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="K5">
+            <v>3147</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="K6">
+            <v>4564</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="H2">
+            <v>1.7</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="H4">
+            <v>183.18753240000001</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>27.463000000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>176.79499999999999</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="K2">
+            <v>17.72</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="K4">
+            <v>3524.5079999999998</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="K5">
+            <v>269.7</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="K6">
+            <v>1426.6</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="I2">
+            <v>84.96</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>5921.4493036799986</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>200</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>1846</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2113,7 +3519,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2153,7 +3559,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2193,7 +3599,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2233,7 +3639,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2264,1361 +3670,6 @@
         <row r="6">
           <cell r="H6">
             <v>992.37699999999995</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="G2">
-            <v>51.15</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="G4">
-            <v>37085.089004699999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="G5">
-            <v>4208</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="G6">
-            <v>14012</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>25.88</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>64072.986658159993</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>4888</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>34632</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>266.8</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>354602.81280000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>13765.710999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Financials"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="L3">
-            <v>228.01</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="L5">
-            <v>42061.053038120001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="L6">
-            <v>2035.1</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="L7">
-            <v>3065.1</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>134.9</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>31344.512106500002</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>5489.9189999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>6254.8919999999998</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>66.67</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>42432.227438630005</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>943.8</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>2084.1999999999998</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="G3">
-            <v>95</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="G5">
-            <v>23679.881450000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="G6">
-            <v>2956</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="G7">
-            <v>4548</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="G2">
-            <v>45.96</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="G4">
-            <v>22817.764463160001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="G5">
-            <v>1261.9690000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="G6">
-            <v>592.70400000000006</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>33.81</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>17624.033178990001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>527</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>4363</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>5241</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>3428838.103683</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>321868</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>16735</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>2268554.6620899998</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>285700</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>59895</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>184.82</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>15180.539270520001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>535.06100000000004</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>2749.3140000000003</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>50.5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>22898.106829</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>3322</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>7200</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink30.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>65.319999999999993</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>9114.1865409199982</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>695</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>3380.8</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>77.77</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>6330.7175316000003</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>311.50299999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>3516.5740000000001</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="G2">
-            <v>17.309999999999999</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="G4">
-            <v>5750.3819999999996</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="G5">
-            <v>870.452</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="G6">
-            <v>2336.5330000000004</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>183.2</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>5589.2865391999994</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>144</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>6523</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>3555</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>520979.16739500005</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>133399</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>26577</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>5310</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>328662.32786999998</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>104775</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>12486</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>33.76</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>1615.1327198399999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>55.219000000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>609.07600000000002</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>15.92</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>2183.3765784000002</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>149.55799999999999</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="H7">
-            <v>714.03099999999995</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>3.28</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>362.09960159999997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>4.45</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>53.811999999999998</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-      <sheetName val="Ratios"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>432.32</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>3210247.9621363198</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>89462</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>40262</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>30.44</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>17310.539416759999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1778</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>2900</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink40.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="G2">
-            <v>617.5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="G4">
-            <v>9081</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="G5">
-            <v>5158916.1000000006</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="G6">
-            <v>386128</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>2123</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>1785783.8434039999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>331931</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>1089</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="5">
-          <cell r="H5">
-            <v>465223.39418400003</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>126824.66499999999</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="H7">
-            <v>12233.047999999999</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>12.11</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>1554.924</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>1205.2</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>2509.8000000000002</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="J2">
-            <v>21.7</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="J4">
-            <v>9701.7223876999997</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>4774.8999999999996</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>16.899999999999999</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>41.21</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>8939.4565020800001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>672.87819999999999</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>9.4335000000000004</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>80.5</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>12979.714142500001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>642.15699999999993</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>13.8</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>9315</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>2739</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>14514</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="K2">
-            <v>78.55</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="K4">
-            <v>7215.2325581999994</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="K5">
-            <v>3147</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="K6">
-            <v>4564</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="H2">
-            <v>1.7</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="H4">
-            <v>183.18753240000001</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="H5">
-            <v>27.463000000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="H6">
-            <v>176.79499999999999</v>
           </cell>
         </row>
       </sheetData>
@@ -3945,7 +3996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B1669C-2C43-405D-A4FE-FB3FBD95AFDE}">
-  <dimension ref="A1:AS240"/>
+  <dimension ref="A1:AS241"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="23" customWidth="1"/>
@@ -4139,20 +4190,20 @@
         <v>22</v>
       </c>
       <c r="E4" s="13">
-        <f>+[11]Main!$I$3</f>
+        <f>+[1]Main!$I$3</f>
         <v>97.5</v>
       </c>
       <c r="F4" s="14">
-        <f>+[11]Main!$I$5</f>
-        <v>411660.80962499999</v>
+        <f>+[1]Main!$I$5</f>
+        <v>411721.73250000004</v>
       </c>
       <c r="G4" s="14">
-        <f>+[11]Main!$I$7-[11]Main!$I$6</f>
-        <v>5400.476999999999</v>
+        <f>+[1]Main!$I$7-[1]Main!$I$6</f>
+        <v>2072.0659999999989</v>
       </c>
       <c r="H4" s="14">
         <f>+F4+G4</f>
-        <v>417061.28662500001</v>
+        <v>413793.79850000003</v>
       </c>
       <c r="I4" s="39" t="s">
         <v>485</v>
@@ -4211,15 +4262,15 @@
         <v>22</v>
       </c>
       <c r="E5" s="13">
-        <f>+[12]Main!$K$2</f>
+        <f>+[2]Main!$K$2</f>
         <v>115.68</v>
       </c>
       <c r="F5" s="14">
-        <f>+[12]Main!$K$4</f>
+        <f>+[2]Main!$K$4</f>
         <v>207984.98580144002</v>
       </c>
       <c r="G5" s="14">
-        <f>+[12]Main!$K$6-[12]Main!$K$5</f>
+        <f>+[2]Main!$K$6-[2]Main!$K$5</f>
         <v>31164</v>
       </c>
       <c r="H5" s="14">
@@ -4285,15 +4336,15 @@
         <v>22</v>
       </c>
       <c r="E6" s="13">
-        <f>+[1]Main!$I$2</f>
+        <f>+[3]Main!$I$2</f>
         <v>29.6</v>
       </c>
       <c r="F6" s="14">
-        <f>+[1]Main!$I$4</f>
+        <f>+[3]Main!$I$4</f>
         <v>107859.27734800002</v>
       </c>
       <c r="G6" s="14">
-        <f>+[1]Main!$I$6-[1]Main!$I$5</f>
+        <f>+[3]Main!$I$6-[3]Main!$I$5</f>
         <v>89738</v>
       </c>
       <c r="H6" s="14">
@@ -4357,15 +4408,15 @@
         <v>23</v>
       </c>
       <c r="E7" s="13">
-        <f>+[13]Main!$H$2</f>
+        <f>+[4]Main!$H$2</f>
         <v>3214</v>
       </c>
       <c r="F7" s="14">
-        <f>+[13]Main!$H$4*FX!C2</f>
+        <f>+[4]Main!$H$4*FX!C2</f>
         <v>124966.1644815872</v>
       </c>
       <c r="G7" s="14">
-        <f>+([13]Main!$H$6-[13]Main!$H$5)*FX!C2</f>
+        <f>+([4]Main!$H$6-[4]Main!$H$5)*FX!C2</f>
         <v>12550.617600000001</v>
       </c>
       <c r="H7" s="14">
@@ -4429,15 +4480,15 @@
         <v>24</v>
       </c>
       <c r="E8" s="13">
-        <f>+[14]Main!$H$2</f>
+        <f>+[5]Main!$H$2</f>
         <v>627.5</v>
       </c>
       <c r="F8" s="14">
-        <f>+[14]Main!$H$5*FX!C3</f>
+        <f>+[5]Main!$H$5*FX!C3</f>
         <v>132772.605128675</v>
       </c>
       <c r="G8" s="14">
-        <f>+([14]Main!$H$7-[14]Main!$H$6)*FX!C3</f>
+        <f>+([5]Main!$H$7-[5]Main!$H$6)*FX!C3</f>
         <v>-8594.32</v>
       </c>
       <c r="H8" s="14">
@@ -4501,15 +4552,15 @@
         <v>23</v>
       </c>
       <c r="E9" s="13">
-        <f>+[15]Main!$I$2</f>
+        <f>+[6]Main!$I$2</f>
         <v>12800</v>
       </c>
       <c r="F9" s="14">
-        <f>+[15]Main!$I$4*FX!C2</f>
+        <f>+[6]Main!$I$4*FX!C2</f>
         <v>106388.6848</v>
       </c>
       <c r="G9" s="14">
-        <f>+([15]Main!$I$6-[15]Main!$I$5)*FX!C2</f>
+        <f>+([6]Main!$I$6-[6]Main!$I$5)*FX!C2</f>
         <v>-10152.16</v>
       </c>
       <c r="H9" s="14">
@@ -4573,15 +4624,15 @@
         <v>25</v>
       </c>
       <c r="E10" s="13">
-        <f>+[16]Main!$I$2</f>
+        <f>+[7]Main!$I$2</f>
         <v>141.63</v>
       </c>
       <c r="F10" s="14">
-        <f>+[16]Main!$I$4</f>
+        <f>+[7]Main!$I$4</f>
         <v>82151.979704910002</v>
       </c>
       <c r="G10" s="14">
-        <f>+[16]Main!$I$6-[16]Main!$I$5</f>
+        <f>+[7]Main!$I$6-[7]Main!$I$5</f>
         <v>1013.5080000000007</v>
       </c>
       <c r="H10" s="14">
@@ -4867,15 +4918,15 @@
         <v>22</v>
       </c>
       <c r="E15" s="13">
-        <f>+[17]Main!$I$2</f>
+        <f>+[8]Main!$I$2</f>
         <v>202.53</v>
       </c>
       <c r="F15" s="14">
-        <f>+[17]Main!$I$4</f>
+        <f>+[8]Main!$I$4</f>
         <v>50674.485076589997</v>
       </c>
       <c r="G15" s="14">
-        <f>+[17]Main!$I$6-[17]Main!$I$5</f>
+        <f>+[8]Main!$I$6-[8]Main!$I$5</f>
         <v>-1230</v>
       </c>
       <c r="H15" s="14">
@@ -4941,15 +4992,15 @@
         <v>22</v>
       </c>
       <c r="E16" s="13">
-        <f>+[18]Main!$H$2</f>
+        <f>+[9]Main!$H$2</f>
         <v>127.88</v>
       </c>
       <c r="F16" s="14">
-        <f>+[18]Main!$H$4</f>
+        <f>+[9]Main!$H$4</f>
         <v>82486.819144840003</v>
       </c>
       <c r="G16" s="14">
-        <f>+[18]Main!$H$6-[18]Main!$H$5</f>
+        <f>+[9]Main!$H$6-[9]Main!$H$5</f>
         <v>-1634.819</v>
       </c>
       <c r="H16" s="14">
@@ -5013,15 +5064,15 @@
         <v>22</v>
       </c>
       <c r="E17" s="13">
-        <f>+[19]Main!$G$2</f>
+        <f>+[10]Main!$G$2</f>
         <v>51.15</v>
       </c>
       <c r="F17" s="14">
-        <f>+[19]Main!$G$4</f>
+        <f>+[10]Main!$G$4</f>
         <v>37085.089004699999</v>
       </c>
       <c r="G17" s="14">
-        <f>+[19]Main!$G$6-[19]Main!$G$5</f>
+        <f>+[10]Main!$G$6-[10]Main!$G$5</f>
         <v>9804</v>
       </c>
       <c r="H17" s="14">
@@ -5085,20 +5136,20 @@
         <v>26</v>
       </c>
       <c r="E18" s="3">
-        <f>+[20]Main!$I$2</f>
-        <v>266.8</v>
+        <f>+[11]Main!$I$2</f>
+        <v>154.19999999999999</v>
       </c>
       <c r="F18" s="21">
-        <f>+[20]Main!$I$4*FX!C6</f>
-        <v>49644.39379200001</v>
+        <f>+[11]Main!$I$4*FX!C6</f>
+        <v>28692.524448</v>
       </c>
       <c r="G18" s="14">
-        <f>+([20]Main!$I$6-[20]Main!$I$5)*FX!C6</f>
+        <f>+([11]Main!$I$6-[11]Main!$I$5)*FX!C6</f>
         <v>-1927.1995400000001</v>
       </c>
       <c r="H18" s="14">
         <f>+F18+G18</f>
-        <v>47717.194252000008</v>
+        <v>26765.324907999999</v>
       </c>
       <c r="I18" s="32" t="s">
         <v>473</v>
@@ -5211,15 +5262,15 @@
         <v>22</v>
       </c>
       <c r="E20" s="3">
-        <f>+[21]Main!$L$3</f>
+        <f>+[12]Main!$L$3</f>
         <v>228.01</v>
       </c>
       <c r="F20" s="14">
-        <f>+[21]Main!$L$5</f>
+        <f>+[12]Main!$L$5</f>
         <v>42061.053038120001</v>
       </c>
       <c r="G20" s="14">
-        <f>+[21]Main!$L$7-[21]Main!$L$6</f>
+        <f>+[12]Main!$L$7-[12]Main!$L$6</f>
         <v>1030</v>
       </c>
       <c r="H20" s="14">
@@ -5283,15 +5334,15 @@
         <v>22</v>
       </c>
       <c r="E21" s="18">
-        <f>+[22]Main!$H$2</f>
+        <f>+[13]Main!$H$2</f>
         <v>134.9</v>
       </c>
       <c r="F21" s="14">
-        <f>+[22]Main!$H$4</f>
+        <f>+[13]Main!$H$4</f>
         <v>31344.512106500002</v>
       </c>
       <c r="G21" s="14">
-        <f>+[22]Main!$H$6-[22]Main!$H$5</f>
+        <f>+[13]Main!$H$6-[13]Main!$H$5</f>
         <v>764.97299999999996</v>
       </c>
       <c r="H21" s="14">
@@ -5355,15 +5406,15 @@
         <v>50</v>
       </c>
       <c r="E22" s="3">
-        <f>+[23]Main!$I$2</f>
+        <f>+[14]Main!$I$2</f>
         <v>66.67</v>
       </c>
       <c r="F22" s="14">
-        <f>+[23]Main!$I$4*FX!C5</f>
+        <f>+[14]Main!$I$4*FX!C5</f>
         <v>26732.303286336904</v>
       </c>
       <c r="G22" s="14">
-        <f>+([23]Main!$I$6-[23]Main!$I$5)*FX!C5</f>
+        <f>+([14]Main!$I$6-[14]Main!$I$5)*FX!C5</f>
         <v>718.45199999999988</v>
       </c>
       <c r="H22" s="14">
@@ -5427,15 +5478,15 @@
         <v>22</v>
       </c>
       <c r="E23" s="3">
-        <f>+[2]Main!$H$2</f>
+        <f>+[15]Main!$H$2</f>
         <v>25.88</v>
       </c>
       <c r="F23" s="14">
-        <f>+[2]Main!$H$4</f>
+        <f>+[15]Main!$H$4</f>
         <v>64072.986658159993</v>
       </c>
       <c r="G23" s="14">
-        <f>+[2]Main!$H$6-[2]Main!$H$5</f>
+        <f>+[15]Main!$H$6-[15]Main!$H$5</f>
         <v>29744</v>
       </c>
       <c r="H23" s="14">
@@ -5501,15 +5552,15 @@
         <v>22</v>
       </c>
       <c r="E24" s="3">
-        <f>+[24]Main!$G$3</f>
+        <f>+[16]Main!$G$3</f>
         <v>95</v>
       </c>
       <c r="F24" s="14">
-        <f>+[24]Main!$G$5</f>
+        <f>+[16]Main!$G$5</f>
         <v>23679.881450000001</v>
       </c>
       <c r="G24" s="14">
-        <f>+[24]Main!$G$7-[24]Main!$G$6</f>
+        <f>+[16]Main!$G$7-[16]Main!$G$6</f>
         <v>1592</v>
       </c>
       <c r="H24" s="14">
@@ -5629,15 +5680,15 @@
         <v>22</v>
       </c>
       <c r="E26" s="3">
-        <f>+[25]Main!$G$2</f>
+        <f>+[17]Main!$G$2</f>
         <v>45.96</v>
       </c>
       <c r="F26" s="14">
-        <f>+[25]Main!$G$4</f>
+        <f>+[17]Main!$G$4</f>
         <v>22817.764463160001</v>
       </c>
       <c r="G26" s="14">
-        <f>+[25]Main!$G$6-[25]Main!$G$5</f>
+        <f>+[17]Main!$G$6-[17]Main!$G$5</f>
         <v>-669.26499999999999</v>
       </c>
       <c r="H26" s="14">
@@ -5701,15 +5752,15 @@
         <v>22</v>
       </c>
       <c r="E27" s="3">
-        <f>+[26]Main!$H$2</f>
+        <f>+[18]Main!$H$2</f>
         <v>33.81</v>
       </c>
       <c r="F27" s="14">
-        <f>+[26]Main!$H$4</f>
+        <f>+[18]Main!$H$4</f>
         <v>17624.033178990001</v>
       </c>
       <c r="G27" s="14">
-        <f>+[26]Main!$H$6-[26]Main!$H$5</f>
+        <f>+[18]Main!$H$6-[18]Main!$H$5</f>
         <v>3836</v>
       </c>
       <c r="H27" s="14">
@@ -5829,15 +5880,15 @@
         <v>23</v>
       </c>
       <c r="E29" s="19">
-        <f>+[27]Main!$I$2</f>
+        <f>+[19]Main!$I$2</f>
         <v>5241</v>
       </c>
       <c r="F29" s="14">
-        <f>+[27]Main!$I$4*FX!C2</f>
+        <f>+[19]Main!$I$4*FX!C2</f>
         <v>21944.563863571202</v>
       </c>
       <c r="G29" s="14">
-        <f>+([27]Main!$I$6-[27]Main!$I$5)*FX!C2</f>
+        <f>+([19]Main!$I$6-[19]Main!$I$5)*FX!C2</f>
         <v>-2059.9551999999999</v>
       </c>
       <c r="H29" s="14">
@@ -5897,15 +5948,15 @@
         <v>23</v>
       </c>
       <c r="E30" s="19">
-        <f>+[28]Main!$I$2</f>
+        <f>+[20]Main!$I$2</f>
         <v>16735</v>
       </c>
       <c r="F30" s="14">
-        <f>+[28]Main!$I$4*FX!C2</f>
+        <f>+[20]Main!$I$4*FX!C2</f>
         <v>14518.749837375999</v>
       </c>
       <c r="G30" s="14">
-        <f>+([28]Main!$I$6-[28]Main!$I$5)*FX!C2</f>
+        <f>+([20]Main!$I$6-[20]Main!$I$5)*FX!C2</f>
         <v>-1445.152</v>
       </c>
       <c r="H30" s="14">
@@ -6023,15 +6074,15 @@
         <v>22</v>
       </c>
       <c r="E32" s="3">
-        <f>+[29]Main!$J$2</f>
+        <f>+[21]Main!$J$2</f>
         <v>184.82</v>
       </c>
       <c r="F32" s="14">
-        <f>+[29]Main!$J$4</f>
+        <f>+[21]Main!$J$4</f>
         <v>15180.539270520001</v>
       </c>
       <c r="G32" s="14">
-        <f>+[29]Main!$J$6-[29]Main!$J$5</f>
+        <f>+[21]Main!$J$6-[21]Main!$J$5</f>
         <v>2214.2530000000002</v>
       </c>
       <c r="H32" s="14">
@@ -6139,7 +6190,7 @@
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="12" t="s">
         <v>74</v>
       </c>
       <c r="C34" s="3" t="s">
@@ -6148,11 +6199,25 @@
       <c r="D34" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15"/>
+      <c r="E34" s="42">
+        <f>+[45]Main!$I$2</f>
+        <v>84.96</v>
+      </c>
+      <c r="F34" s="14">
+        <f>+[45]Main!$I$4</f>
+        <v>5921.4493036799986</v>
+      </c>
+      <c r="G34" s="14">
+        <f>+[45]Main!$I$6-[45]Main!$I$5</f>
+        <v>1646</v>
+      </c>
+      <c r="H34" s="14">
+        <f>+F34+G34</f>
+        <v>7567.4493036799986</v>
+      </c>
+      <c r="I34" s="43" t="s">
+        <v>480</v>
+      </c>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
@@ -6429,15 +6494,15 @@
         <v>22</v>
       </c>
       <c r="E39" s="3">
-        <f>+[30]Main!$H$2</f>
+        <f>+[22]Main!$H$2</f>
         <v>65.319999999999993</v>
       </c>
       <c r="F39" s="14">
-        <f>+[30]Main!$H$4</f>
+        <f>+[22]Main!$H$4</f>
         <v>9114.1865409199982</v>
       </c>
       <c r="G39" s="14">
-        <f>+[30]Main!$H$6-[30]Main!$H$5</f>
+        <f>+[22]Main!$H$6-[22]Main!$H$5</f>
         <v>2685.8</v>
       </c>
       <c r="H39" s="14">
@@ -6557,15 +6622,15 @@
         <v>22</v>
       </c>
       <c r="E41" s="3">
-        <f>+[7]Main!$I$2</f>
+        <f>+[23]Main!$I$2</f>
         <v>13.8</v>
       </c>
       <c r="F41" s="14">
-        <f>+[7]Main!$I$4</f>
+        <f>+[23]Main!$I$4</f>
         <v>9315</v>
       </c>
       <c r="G41" s="14">
-        <f>+[7]Main!$I$6-[7]Main!$I$5</f>
+        <f>+[23]Main!$I$6-[23]Main!$I$5</f>
         <v>11775</v>
       </c>
       <c r="H41" s="14">
@@ -6909,15 +6974,15 @@
         <v>22</v>
       </c>
       <c r="E47" s="3">
-        <f>+[31]Main!$I$2</f>
+        <f>+[24]Main!$I$2</f>
         <v>77.77</v>
       </c>
       <c r="F47" s="14">
-        <f>+[31]Main!$I$4</f>
+        <f>+[24]Main!$I$4</f>
         <v>6330.7175316000003</v>
       </c>
       <c r="G47" s="14">
-        <f>+[31]Main!$I$6-[31]Main!$I$5</f>
+        <f>+[24]Main!$I$6-[24]Main!$I$5</f>
         <v>3205.0709999999999</v>
       </c>
       <c r="H47" s="14">
@@ -7091,15 +7156,15 @@
         <v>22</v>
       </c>
       <c r="E50" s="3">
-        <f>+[32]Main!$G$2</f>
+        <f>+[25]Main!$G$2</f>
         <v>17.309999999999999</v>
       </c>
       <c r="F50" s="14">
-        <f>+[32]Main!$G$4</f>
+        <f>+[25]Main!$G$4</f>
         <v>5750.3819999999996</v>
       </c>
       <c r="G50" s="14">
-        <f>+[32]Main!$G$6-[32]Main!$G$5</f>
+        <f>+[25]Main!$G$6-[25]Main!$G$5</f>
         <v>1466.0810000000004</v>
       </c>
       <c r="H50" s="14">
@@ -7499,15 +7564,15 @@
         <v>22</v>
       </c>
       <c r="E57" s="3">
-        <f>+[33]Main!$I$2</f>
+        <f>+[26]Main!$I$2</f>
         <v>183.2</v>
       </c>
       <c r="F57" s="14">
-        <f>+[33]Main!$I$4</f>
+        <f>+[26]Main!$I$4</f>
         <v>5589.2865391999994</v>
       </c>
       <c r="G57" s="14">
-        <f>+[33]Main!$I$6-[33]Main!$I$5</f>
+        <f>+[26]Main!$I$6-[26]Main!$I$5</f>
         <v>6379</v>
       </c>
       <c r="H57" s="14">
@@ -8284,7 +8349,7 @@
     </row>
     <row r="71" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A71" s="11">
-        <f t="shared" ref="A71:A113" si="2">+A70+1</f>
+        <f t="shared" ref="A71:A114" si="2">+A70+1</f>
         <v>68</v>
       </c>
       <c r="B71" s="3" t="s">
@@ -9025,15 +9090,15 @@
         <v>23</v>
       </c>
       <c r="E84" s="34">
-        <f>+[34]Main!$J$2</f>
+        <f>+[27]Main!$J$2</f>
         <v>3555</v>
       </c>
       <c r="F84" s="14">
-        <f>+[34]Main!$J$4*FX!C2</f>
+        <f>+[27]Main!$J$4*FX!C2</f>
         <v>3334.2666713280005</v>
       </c>
       <c r="G84" s="14">
-        <f>+([34]Main!$J$6-[34]Main!$J$5)*FX!C2</f>
+        <f>+([27]Main!$J$6-[27]Main!$J$5)*FX!C2</f>
         <v>-683.66079999999999</v>
       </c>
       <c r="H84" s="14">
@@ -9543,15 +9608,15 @@
         <v>23</v>
       </c>
       <c r="E93" s="3">
-        <f>+[35]Main!$I$2</f>
+        <f>+[28]Main!$I$2</f>
         <v>5310</v>
       </c>
       <c r="F93" s="14">
-        <f>+[35]Main!$I$4*FX!C2</f>
+        <f>+[28]Main!$I$4*FX!C2</f>
         <v>2103.4388983680001</v>
       </c>
       <c r="G93" s="14">
-        <f>+([35]Main!$I$6-[35]Main!$I$5)*FX!C2</f>
+        <f>+([28]Main!$I$6-[28]Main!$I$5)*FX!C2</f>
         <v>-590.64960000000008</v>
       </c>
       <c r="H93" s="14">
@@ -10229,15 +10294,15 @@
         <v>22</v>
       </c>
       <c r="E105" s="3">
-        <f>+[36]Main!$I$2</f>
+        <f>+[29]Main!$I$2</f>
         <v>33.76</v>
       </c>
       <c r="F105" s="14">
-        <f>+[36]Main!$I$4</f>
+        <f>+[29]Main!$I$4</f>
         <v>1615.1327198399999</v>
       </c>
       <c r="G105" s="14">
-        <f>+[36]Main!$I$6-[36]Main!$I$5</f>
+        <f>+[29]Main!$I$6-[29]Main!$I$5</f>
         <v>553.85699999999997</v>
       </c>
       <c r="H105" s="14">
@@ -10411,15 +10476,15 @@
         <v>153</v>
       </c>
       <c r="E108" s="3">
-        <f>+[37]Main!$H$2</f>
+        <f>+[30]Main!$H$2</f>
         <v>15.92</v>
       </c>
       <c r="F108" s="14">
-        <f>+[37]Main!$H$5*FX!C4</f>
+        <f>+[30]Main!$H$5*FX!C4</f>
         <v>2707.3869572160002</v>
       </c>
       <c r="G108" s="14">
-        <f>+([37]Main!$H$7-[37]Main!$H$6)*FX!C4</f>
+        <f>+([30]Main!$H$7-[30]Main!$H$6)*FX!C4</f>
         <v>699.94651999999996</v>
       </c>
       <c r="H108" s="14">
@@ -10539,15 +10604,15 @@
         <v>85</v>
       </c>
       <c r="E110" s="3">
-        <f>+[38]Main!$I$2</f>
+        <f>+[31]Main!$I$2</f>
         <v>3.28</v>
       </c>
       <c r="F110" s="14">
-        <f>+[38]Main!$I$4*FX!C3</f>
+        <f>+[31]Main!$I$4*FX!C3</f>
         <v>372.96258964800001</v>
       </c>
       <c r="G110" s="14">
-        <f>+([38]Main!$I$6-[38]Main!$I$5)*FX!C3</f>
+        <f>+([31]Main!$I$6-[31]Main!$I$5)*FX!C3</f>
         <v>50.842859999999995</v>
       </c>
       <c r="H110" s="14">
@@ -10813,9 +10878,7 @@
     </row>
     <row r="115" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A115" s="11"/>
-      <c r="B115" s="22" t="s">
-        <v>476</v>
-      </c>
+      <c r="B115" s="3"/>
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
@@ -10862,15 +10925,11 @@
     </row>
     <row r="116" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A116" s="11"/>
-      <c r="B116" s="12" t="s">
-        <v>477</v>
-      </c>
-      <c r="C116" s="35" t="s">
-        <v>481</v>
-      </c>
-      <c r="D116" s="35" t="s">
-        <v>482</v>
-      </c>
+      <c r="B116" s="22" t="s">
+        <v>476</v>
+      </c>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
       <c r="E116" s="3"/>
       <c r="F116" s="21"/>
       <c r="G116" s="21"/>
@@ -10915,9 +10974,15 @@
     </row>
     <row r="117" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A117" s="11"/>
-      <c r="B117" s="3"/>
-      <c r="C117" s="3"/>
-      <c r="D117" s="3"/>
+      <c r="B117" s="12" t="s">
+        <v>477</v>
+      </c>
+      <c r="C117" s="35" t="s">
+        <v>481</v>
+      </c>
+      <c r="D117" s="35" t="s">
+        <v>482</v>
+      </c>
       <c r="E117" s="3"/>
       <c r="F117" s="21"/>
       <c r="G117" s="21"/>
@@ -15995,9 +16060,9 @@
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
       <c r="E225" s="3"/>
-      <c r="F225" s="3"/>
-      <c r="G225" s="3"/>
-      <c r="H225" s="3"/>
+      <c r="F225" s="21"/>
+      <c r="G225" s="21"/>
+      <c r="H225" s="21"/>
       <c r="I225" s="3"/>
       <c r="J225" s="3"/>
       <c r="K225" s="3"/>
@@ -16741,6 +16806,53 @@
       <c r="AR240" s="3"/>
       <c r="AS240" s="3"/>
     </row>
+    <row r="241" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A241" s="11"/>
+      <c r="B241" s="3"/>
+      <c r="C241" s="3"/>
+      <c r="D241" s="3"/>
+      <c r="E241" s="3"/>
+      <c r="F241" s="3"/>
+      <c r="G241" s="3"/>
+      <c r="H241" s="3"/>
+      <c r="I241" s="3"/>
+      <c r="J241" s="3"/>
+      <c r="K241" s="3"/>
+      <c r="L241" s="3"/>
+      <c r="M241" s="3"/>
+      <c r="N241" s="3"/>
+      <c r="O241" s="3"/>
+      <c r="P241" s="3"/>
+      <c r="Q241" s="3"/>
+      <c r="R241" s="3"/>
+      <c r="S241" s="3"/>
+      <c r="T241" s="3"/>
+      <c r="U241" s="3"/>
+      <c r="V241" s="3"/>
+      <c r="W241" s="3"/>
+      <c r="X241" s="3"/>
+      <c r="Y241" s="3"/>
+      <c r="Z241" s="3"/>
+      <c r="AA241" s="3"/>
+      <c r="AB241" s="3"/>
+      <c r="AC241" s="3"/>
+      <c r="AD241" s="3"/>
+      <c r="AE241" s="3"/>
+      <c r="AF241" s="3"/>
+      <c r="AG241" s="3"/>
+      <c r="AH241" s="3"/>
+      <c r="AI241" s="3"/>
+      <c r="AJ241" s="3"/>
+      <c r="AK241" s="3"/>
+      <c r="AL241" s="3"/>
+      <c r="AM241" s="3"/>
+      <c r="AN241" s="3"/>
+      <c r="AO241" s="3"/>
+      <c r="AP241" s="3"/>
+      <c r="AQ241" s="3"/>
+      <c r="AR241" s="3"/>
+      <c r="AS241" s="3"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B5" r:id="rId1" xr:uid="{28DCB031-FE72-4DDD-A270-8F54C33B0D07}"/>
@@ -16775,7 +16887,8 @@
     <hyperlink ref="B103" r:id="rId30" xr:uid="{99A434BF-F5F7-467F-AB02-447D8D64F5FB}"/>
     <hyperlink ref="B93" r:id="rId31" xr:uid="{04B6A34E-7F7B-490D-8880-75C12621EECA}"/>
     <hyperlink ref="B84" r:id="rId32" xr:uid="{56024696-67B2-4803-B0DF-95A89BDC0A77}"/>
-    <hyperlink ref="B116" r:id="rId33" xr:uid="{165C2902-BD53-4337-94C5-A6EDD7D0D481}"/>
+    <hyperlink ref="B117" r:id="rId33" xr:uid="{165C2902-BD53-4337-94C5-A6EDD7D0D481}"/>
+    <hyperlink ref="B34" r:id="rId34" xr:uid="{1F0370C2-260F-41D8-88F8-175FEE03B53D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17122,20 +17235,20 @@
         <v>22</v>
       </c>
       <c r="E5" s="26">
-        <f>+[39]Main!$H$2</f>
-        <v>432.32</v>
+        <f>+[32]Main!$H$2</f>
+        <v>405.1</v>
       </c>
       <c r="F5" s="26">
-        <f>+[39]Main!$H$4</f>
-        <v>3210247.9621363198</v>
+        <f>+[32]Main!$H$4</f>
+        <v>3009258.8985904003</v>
       </c>
       <c r="G5" s="26">
-        <f>+[39]Main!$H$6-[39]Main!$H$5</f>
-        <v>-49200</v>
+        <f>+[32]Main!$H$6-[32]Main!$H$5</f>
+        <v>-38010</v>
       </c>
       <c r="H5" s="26">
         <f t="shared" ref="H5:H18" si="0">+F5+G5</f>
-        <v>3161047.9621363198</v>
+        <v>2971248.8985904003</v>
       </c>
       <c r="I5" s="27" t="s">
         <v>240</v>
@@ -17217,15 +17330,15 @@
         <v>26</v>
       </c>
       <c r="E6" s="26">
-        <f>+[40]Main!$G$2</f>
+        <f>+[33]Main!$G$2</f>
         <v>617.5</v>
       </c>
       <c r="F6" s="26">
-        <f>+[40]Main!$G$4*FX!C6</f>
+        <f>+[33]Main!$G$4*FX!C6</f>
         <v>1271.3400000000001</v>
       </c>
       <c r="G6" s="26">
-        <f>+([40]Main!$G$6-[40]Main!$G$5)*FX!C6</f>
+        <f>+([33]Main!$G$6-[33]Main!$G$5)*FX!C6</f>
         <v>-668190.33400000015</v>
       </c>
       <c r="H6" s="26">
@@ -17312,15 +17425,15 @@
         <v>23</v>
       </c>
       <c r="E7" s="26">
-        <f>+[13]Main!$H$2</f>
+        <f>+[4]Main!$H$2</f>
         <v>3214</v>
       </c>
       <c r="F7" s="26">
-        <f>+[13]Main!$H$4*FX!C2</f>
+        <f>+[4]Main!$H$4*FX!C2</f>
         <v>124966.1644815872</v>
       </c>
       <c r="G7" s="26">
-        <f>+([13]Main!$H$6-[13]Main!$H$5)*FX!C2</f>
+        <f>+([4]Main!$H$6-[4]Main!$H$5)*FX!C2</f>
         <v>12550.617600000001</v>
       </c>
       <c r="H7" s="26">
@@ -17407,15 +17520,15 @@
         <v>23</v>
       </c>
       <c r="E8" s="26">
-        <f>+[15]Main!$I$2</f>
+        <f>+[6]Main!$I$2</f>
         <v>12800</v>
       </c>
       <c r="F8" s="26">
-        <f>+[15]Main!$I$4*FX!C2</f>
+        <f>+[6]Main!$I$4*FX!C2</f>
         <v>106388.6848</v>
       </c>
       <c r="G8" s="26">
-        <f>+([15]Main!$I$6-[15]Main!$I$5)*FX!C2</f>
+        <f>+([6]Main!$I$6-[6]Main!$I$5)*FX!C2</f>
         <v>-10152.16</v>
       </c>
       <c r="H8" s="26">
@@ -17502,15 +17615,15 @@
         <v>26</v>
       </c>
       <c r="E9" s="26">
-        <f>+[41]Main!$I$2</f>
+        <f>+[34]Main!$I$2</f>
         <v>2123</v>
       </c>
       <c r="F9" s="26">
-        <f>+[42]Main!$H$5*FX!C6</f>
+        <f>+[35]Main!$H$5*FX!C6</f>
         <v>65131.275185760009</v>
       </c>
       <c r="G9" s="26">
-        <f>+([42]Main!$H$7-[42]Main!$H$6)*FX!C6</f>
+        <f>+([35]Main!$H$7-[35]Main!$H$6)*FX!C6</f>
         <v>-16042.82638</v>
       </c>
       <c r="H9" s="26">
@@ -17597,15 +17710,15 @@
         <v>25</v>
       </c>
       <c r="E10" s="26">
-        <f>+[16]Main!$I$2</f>
+        <f>+[7]Main!$I$2</f>
         <v>141.63</v>
       </c>
       <c r="F10" s="26">
-        <f>+[16]Main!$I$4</f>
+        <f>+[7]Main!$I$4</f>
         <v>82151.979704910002</v>
       </c>
       <c r="G10" s="26">
-        <f>+[16]Main!$I$6-[16]Main!$I$5</f>
+        <f>+[7]Main!$I$6-[7]Main!$I$5</f>
         <v>1013.5080000000007</v>
       </c>
       <c r="H10" s="26">
@@ -17692,15 +17805,15 @@
         <v>22</v>
       </c>
       <c r="E11" s="26">
-        <f>+[17]Main!$I$2</f>
+        <f>+[8]Main!$I$2</f>
         <v>202.53</v>
       </c>
       <c r="F11" s="26">
-        <f>+[17]Main!$I$4</f>
+        <f>+[8]Main!$I$4</f>
         <v>50674.485076589997</v>
       </c>
       <c r="G11" s="26">
-        <f>+[17]Main!$I$6-[17]Main!$I$5</f>
+        <f>+[8]Main!$I$6-[8]Main!$I$5</f>
         <v>-1230</v>
       </c>
       <c r="H11" s="26">
@@ -17787,15 +17900,15 @@
         <v>22</v>
       </c>
       <c r="E12" s="26">
-        <f>+[21]Main!$L$3</f>
+        <f>+[12]Main!$L$3</f>
         <v>228.01</v>
       </c>
       <c r="F12" s="26">
-        <f>+[21]Main!$L$5</f>
+        <f>+[12]Main!$L$5</f>
         <v>42061.053038120001</v>
       </c>
       <c r="G12" s="26">
-        <f>+[21]Main!$L$7-[21]Main!$L$6</f>
+        <f>+[12]Main!$L$7-[12]Main!$L$6</f>
         <v>1030</v>
       </c>
       <c r="H12" s="26">
@@ -17882,15 +17995,15 @@
         <v>22</v>
       </c>
       <c r="E13" s="26">
-        <f>+[18]Main!$H$2</f>
+        <f>+[9]Main!$H$2</f>
         <v>127.88</v>
       </c>
       <c r="F13" s="26">
-        <f>+[18]Main!$H$4</f>
+        <f>+[9]Main!$H$4</f>
         <v>82486.819144840003</v>
       </c>
       <c r="G13" s="26">
-        <f>+[18]Main!$H$6-[18]Main!$H$5</f>
+        <f>+[9]Main!$H$6-[9]Main!$H$5</f>
         <v>-1634.819</v>
       </c>
       <c r="H13" s="26">
@@ -17977,15 +18090,15 @@
         <v>50</v>
       </c>
       <c r="E14" s="26">
-        <f>+[23]Main!$I$2</f>
+        <f>+[14]Main!$I$2</f>
         <v>66.67</v>
       </c>
       <c r="F14" s="26">
-        <f>+[23]Main!$I$4*FX!C5</f>
+        <f>+[14]Main!$I$4*FX!C5</f>
         <v>26732.303286336904</v>
       </c>
       <c r="G14" s="26">
-        <f>+([23]Main!$I$6-[23]Main!$I$5)*FX!C5</f>
+        <f>+([14]Main!$I$6-[14]Main!$I$5)*FX!C5</f>
         <v>718.45199999999988</v>
       </c>
       <c r="H14" s="26">
@@ -18072,15 +18185,15 @@
         <v>23</v>
       </c>
       <c r="E15" s="26">
-        <f>+[41]Main!$I$2</f>
+        <f>+[34]Main!$I$2</f>
         <v>2123</v>
       </c>
       <c r="F15" s="26">
-        <f>+[41]Main!$I$4*FX!C2</f>
+        <f>+[34]Main!$I$4*FX!C2</f>
         <v>11429.0165977856</v>
       </c>
       <c r="G15" s="26">
-        <f>+([41]Main!$I$6-[41]Main!$I$5)*FX!C2</f>
+        <f>+([34]Main!$I$6-[34]Main!$I$5)*FX!C2</f>
         <v>-2117.3888000000002</v>
       </c>
       <c r="H15" s="26">
@@ -18167,15 +18280,15 @@
         <v>23</v>
       </c>
       <c r="E16" s="26">
-        <f>+[27]Main!$I$2</f>
+        <f>+[19]Main!$I$2</f>
         <v>5241</v>
       </c>
       <c r="F16" s="26">
-        <f>+[27]Main!$I$4*FX!C2</f>
+        <f>+[19]Main!$I$4*FX!C2</f>
         <v>21944.563863571202</v>
       </c>
       <c r="G16" s="26">
-        <f>+([27]Main!$I$6-[27]Main!$I$5)*FX!C2</f>
+        <f>+([19]Main!$I$6-[19]Main!$I$5)*FX!C2</f>
         <v>-2059.9551999999999</v>
       </c>
       <c r="H16" s="26">
@@ -18262,15 +18375,15 @@
         <v>23</v>
       </c>
       <c r="E17" s="26">
-        <f>+[28]Main!$I$2</f>
+        <f>+[20]Main!$I$2</f>
         <v>16735</v>
       </c>
       <c r="F17" s="26">
-        <f>+[28]Main!$I$4*FX!C2</f>
+        <f>+[20]Main!$I$4*FX!C2</f>
         <v>14518.749837375999</v>
       </c>
       <c r="G17" s="26">
-        <f>+([28]Main!$I$6-[28]Main!$I$5)*FX!C2</f>
+        <f>+([20]Main!$I$6-[20]Main!$I$5)*FX!C2</f>
         <v>-1445.152</v>
       </c>
       <c r="H17" s="26">
@@ -18357,15 +18470,15 @@
         <v>94</v>
       </c>
       <c r="E18" s="26">
-        <f>+[43]Main!$H$2</f>
+        <f>+[36]Main!$H$2</f>
         <v>12.11</v>
       </c>
       <c r="F18" s="26">
-        <f>+[43]Main!$H$4*FX!C3</f>
+        <f>+[36]Main!$H$4*FX!C3</f>
         <v>1601.5717199999999</v>
       </c>
       <c r="G18" s="26">
-        <f>+([43]Main!$H$6-[43]Main!$H$5)*FX!C3</f>
+        <f>+([36]Main!$H$6-[36]Main!$H$5)*FX!C3</f>
         <v>1343.7380000000003</v>
       </c>
       <c r="H18" s="26">
@@ -18595,15 +18708,15 @@
         <v>22</v>
       </c>
       <c r="E21" s="26">
-        <f>+[44]Main!$J$2</f>
+        <f>+[37]Main!$J$2</f>
         <v>21.7</v>
       </c>
       <c r="F21" s="26">
-        <f>+[44]Main!$J$4</f>
+        <f>+[37]Main!$J$4</f>
         <v>9701.7223876999997</v>
       </c>
       <c r="G21" s="26">
-        <f>+[44]Main!$J$6-[44]Main!$J$5</f>
+        <f>+[37]Main!$J$6-[37]Main!$J$5</f>
         <v>-4758</v>
       </c>
       <c r="H21" s="26">
@@ -27898,15 +28011,15 @@
         <v>22</v>
       </c>
       <c r="E4" s="14">
-        <f>+[1]Main!$I$2</f>
+        <f>+[3]Main!$I$2</f>
         <v>29.6</v>
       </c>
       <c r="F4" s="14">
-        <f>+[1]Main!$I$4</f>
+        <f>+[3]Main!$I$4</f>
         <v>107859.27734800002</v>
       </c>
       <c r="G4" s="14">
-        <f>+[1]Main!$I$6-[1]Main!$I$5</f>
+        <f>+[3]Main!$I$6-[3]Main!$I$5</f>
         <v>89738</v>
       </c>
       <c r="H4" s="14">
@@ -28020,15 +28133,15 @@
         <v>22</v>
       </c>
       <c r="E7" s="14">
-        <f>+[2]Main!$H$2</f>
+        <f>+[15]Main!$H$2</f>
         <v>25.88</v>
       </c>
       <c r="F7" s="14">
-        <f>+[2]Main!$H$4</f>
+        <f>+[15]Main!$H$4</f>
         <v>64072.986658159993</v>
       </c>
       <c r="G7" s="14">
-        <f>+[2]Main!$H$6-[2]Main!$H$5</f>
+        <f>+[15]Main!$H$6-[15]Main!$H$5</f>
         <v>29744</v>
       </c>
       <c r="H7" s="14">
@@ -28070,15 +28183,15 @@
         <v>22</v>
       </c>
       <c r="E8" s="14">
-        <f>+[3]Main!$I$2</f>
+        <f>+[38]Main!$I$2</f>
         <v>50.5</v>
       </c>
       <c r="F8" s="14">
-        <f>+[3]Main!$I$4</f>
+        <f>+[38]Main!$I$4</f>
         <v>22898.106829</v>
       </c>
       <c r="G8" s="14">
-        <f>+[3]Main!$I$6-[3]Main!$I$5</f>
+        <f>+[38]Main!$I$6-[38]Main!$I$5</f>
         <v>3878</v>
       </c>
       <c r="H8" s="14">
@@ -28192,15 +28305,15 @@
         <v>22</v>
       </c>
       <c r="E11" s="14">
-        <f>+[4]Main!$I$2</f>
+        <f>+[39]Main!$I$2</f>
         <v>30.44</v>
       </c>
       <c r="F11" s="14">
-        <f>+[4]Main!$I$4</f>
+        <f>+[39]Main!$I$4</f>
         <v>17310.539416759999</v>
       </c>
       <c r="G11" s="14">
-        <f>+[4]Main!$I$6-[4]Main!$I$5</f>
+        <f>+[39]Main!$I$6-[39]Main!$I$5</f>
         <v>1122</v>
       </c>
       <c r="H11" s="14">
@@ -28278,15 +28391,15 @@
         <v>22</v>
       </c>
       <c r="E13" s="14">
-        <f>+[5]Main!$H$2</f>
+        <f>+[40]Main!$H$2</f>
         <v>41.21</v>
       </c>
       <c r="F13" s="14">
-        <f>+[5]Main!$H$4</f>
+        <f>+[40]Main!$H$4</f>
         <v>8939.4565020800001</v>
       </c>
       <c r="G13" s="14">
-        <f>+[5]Main!$H$6-[5]Main!$H$5</f>
+        <f>+[40]Main!$H$6-[40]Main!$H$5</f>
         <v>-663.44470000000001</v>
       </c>
       <c r="H13" s="14">
@@ -28328,15 +28441,15 @@
         <v>22</v>
       </c>
       <c r="E14" s="14">
-        <f>+[6]Main!$H$2</f>
+        <f>+[41]Main!$H$2</f>
         <v>80.5</v>
       </c>
       <c r="F14" s="14">
-        <f>+[6]Main!$H$4</f>
+        <f>+[41]Main!$H$4</f>
         <v>12979.714142500001</v>
       </c>
       <c r="G14" s="14">
-        <f>+[6]Main!$H$6-[6]Main!$H$5</f>
+        <f>+[41]Main!$H$6-[41]Main!$H$5</f>
         <v>-642.15699999999993</v>
       </c>
       <c r="H14" s="14">
@@ -28378,15 +28491,15 @@
         <v>22</v>
       </c>
       <c r="E15" s="14">
-        <f>+[7]Main!$I$2</f>
+        <f>+[23]Main!$I$2</f>
         <v>13.8</v>
       </c>
       <c r="F15" s="14">
-        <f>+[7]Main!$I$4</f>
+        <f>+[23]Main!$I$4</f>
         <v>9315</v>
       </c>
       <c r="G15" s="14">
-        <f>+[7]Main!$I$6-[7]Main!$I$5</f>
+        <f>+[23]Main!$I$6-[23]Main!$I$5</f>
         <v>11775</v>
       </c>
       <c r="H15" s="14">
@@ -28464,15 +28577,15 @@
         <v>22</v>
       </c>
       <c r="E17" s="14">
-        <f>+[8]Main!$K$2</f>
+        <f>+[42]Main!$K$2</f>
         <v>78.55</v>
       </c>
       <c r="F17" s="14">
-        <f>+[8]Main!$K$4</f>
+        <f>+[42]Main!$K$4</f>
         <v>7215.2325581999994</v>
       </c>
       <c r="G17" s="14">
-        <f>+[8]Main!$K$6-[8]Main!$K$5</f>
+        <f>+[42]Main!$K$6-[42]Main!$K$5</f>
         <v>1417</v>
       </c>
       <c r="H17" s="14">
@@ -30670,15 +30783,15 @@
         <v>22</v>
       </c>
       <c r="E78" s="14">
-        <f>+[9]Main!$H$2</f>
+        <f>+[43]Main!$H$2</f>
         <v>1.7</v>
       </c>
       <c r="F78" s="14">
-        <f>+[9]Main!$H$4</f>
+        <f>+[43]Main!$H$4</f>
         <v>183.18753240000001</v>
       </c>
       <c r="G78" s="14">
-        <f>+[9]Main!$H$6-[9]Main!$H$5</f>
+        <f>+[43]Main!$H$6-[43]Main!$H$5</f>
         <v>149.33199999999999</v>
       </c>
       <c r="H78" s="14">
@@ -31112,15 +31225,15 @@
         <v>85</v>
       </c>
       <c r="E90" s="14">
-        <f>+[10]Main!$K$2</f>
+        <f>+[44]Main!$K$2</f>
         <v>17.72</v>
       </c>
       <c r="F90" s="14">
-        <f>+[10]Main!$K$4*FX!C3</f>
+        <f>+[44]Main!$K$4*FX!C3</f>
         <v>3630.2432399999998</v>
       </c>
       <c r="G90" s="14">
-        <f>+([10]Main!$K$6-[10]Main!$K$5)*FX!C3</f>
+        <f>+([44]Main!$K$6-[44]Main!$K$5)*FX!C3</f>
         <v>1191.607</v>
       </c>
       <c r="H90" s="14">

--- a/Entertainment.xlsx
+++ b/Entertainment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B7833E-9FB5-4F52-8504-DE3B5E493F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB71FCF1-669E-411B-AB03-FFFC607D59AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="3120" windowWidth="38175" windowHeight="15240" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{E414CA5C-78F9-4930-AC5C-325CFFA496F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1884,22 +1884,22 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="I3">
-            <v>97.5</v>
+            <v>69.17</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>411721.73250000004</v>
+            <v>288019.70738892001</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>12288.45</v>
+            <v>9127.91</v>
           </cell>
         </row>
         <row r="7">
           <cell r="I7">
-            <v>14360.516</v>
+            <v>14309.306</v>
           </cell>
         </row>
       </sheetData>
@@ -2458,6 +2458,46 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
+          <cell r="I2">
+            <v>84.96</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>5921.4493036799986</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>200</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>1846</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
           <cell r="H2">
             <v>65.319999999999993</v>
           </cell>
@@ -2478,13 +2518,13 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2524,7 +2564,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2564,7 +2604,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2604,7 +2644,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2644,7 +2684,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2684,7 +2724,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2715,46 +2755,6 @@
         <row r="6">
           <cell r="I6">
             <v>12486</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>33.76</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>1615.1327198399999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>55.219000000000001</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>609.07600000000002</v>
           </cell>
         </row>
       </sheetData>
@@ -2818,6 +2818,46 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
+          <cell r="I2">
+            <v>33.76</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>1615.1327198399999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>55.219000000000001</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>609.07600000000002</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
           <cell r="H2">
             <v>15.92</v>
           </cell>
@@ -2844,7 +2884,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2884,7 +2924,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2926,7 +2966,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -2966,7 +3006,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3006,7 +3046,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3041,7 +3081,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3081,7 +3121,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3121,7 +3161,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3152,46 +3192,6 @@
         <row r="6">
           <cell r="I6">
             <v>7200</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink39.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>30.44</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>17310.539416759999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>1778</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>2900</v>
           </cell>
         </row>
       </sheetData>
@@ -3255,6 +3255,46 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="2">
+          <cell r="I2">
+            <v>30.44</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="I4">
+            <v>17310.539416759999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>1778</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>2900</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
           <cell r="H2">
             <v>41.21</v>
           </cell>
@@ -3281,7 +3321,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3321,7 +3361,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3359,7 +3399,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3399,7 +3439,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -3430,46 +3470,6 @@
         <row r="6">
           <cell r="K6">
             <v>1426.6</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink45.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="I2">
-            <v>84.96</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="I4">
-            <v>5921.4493036799986</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>200</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>1846</v>
           </cell>
         </row>
       </sheetData>
@@ -4191,19 +4191,19 @@
       </c>
       <c r="E4" s="13">
         <f>+[1]Main!$I$3</f>
-        <v>97.5</v>
+        <v>69.17</v>
       </c>
       <c r="F4" s="14">
         <f>+[1]Main!$I$5</f>
-        <v>411721.73250000004</v>
+        <v>288019.70738892001</v>
       </c>
       <c r="G4" s="14">
         <f>+[1]Main!$I$7-[1]Main!$I$6</f>
-        <v>2072.0659999999989</v>
+        <v>5181.3960000000006</v>
       </c>
       <c r="H4" s="14">
         <f>+F4+G4</f>
-        <v>413793.79850000003</v>
+        <v>293201.10338892002</v>
       </c>
       <c r="I4" s="39" t="s">
         <v>485</v>
@@ -6200,15 +6200,15 @@
         <v>22</v>
       </c>
       <c r="E34" s="42">
-        <f>+[45]Main!$I$2</f>
+        <f>+[22]Main!$I$2</f>
         <v>84.96</v>
       </c>
       <c r="F34" s="14">
-        <f>+[45]Main!$I$4</f>
+        <f>+[22]Main!$I$4</f>
         <v>5921.4493036799986</v>
       </c>
       <c r="G34" s="14">
-        <f>+[45]Main!$I$6-[45]Main!$I$5</f>
+        <f>+[22]Main!$I$6-[22]Main!$I$5</f>
         <v>1646</v>
       </c>
       <c r="H34" s="14">
@@ -6494,15 +6494,15 @@
         <v>22</v>
       </c>
       <c r="E39" s="3">
-        <f>+[22]Main!$H$2</f>
+        <f>+[23]Main!$H$2</f>
         <v>65.319999999999993</v>
       </c>
       <c r="F39" s="14">
-        <f>+[22]Main!$H$4</f>
+        <f>+[23]Main!$H$4</f>
         <v>9114.1865409199982</v>
       </c>
       <c r="G39" s="14">
-        <f>+[22]Main!$H$6-[22]Main!$H$5</f>
+        <f>+[23]Main!$H$6-[23]Main!$H$5</f>
         <v>2685.8</v>
       </c>
       <c r="H39" s="14">
@@ -6622,15 +6622,15 @@
         <v>22</v>
       </c>
       <c r="E41" s="3">
-        <f>+[23]Main!$I$2</f>
+        <f>+[24]Main!$I$2</f>
         <v>13.8</v>
       </c>
       <c r="F41" s="14">
-        <f>+[23]Main!$I$4</f>
+        <f>+[24]Main!$I$4</f>
         <v>9315</v>
       </c>
       <c r="G41" s="14">
-        <f>+[23]Main!$I$6-[23]Main!$I$5</f>
+        <f>+[24]Main!$I$6-[24]Main!$I$5</f>
         <v>11775</v>
       </c>
       <c r="H41" s="14">
@@ -6974,15 +6974,15 @@
         <v>22</v>
       </c>
       <c r="E47" s="3">
-        <f>+[24]Main!$I$2</f>
+        <f>+[25]Main!$I$2</f>
         <v>77.77</v>
       </c>
       <c r="F47" s="14">
-        <f>+[24]Main!$I$4</f>
+        <f>+[25]Main!$I$4</f>
         <v>6330.7175316000003</v>
       </c>
       <c r="G47" s="14">
-        <f>+[24]Main!$I$6-[24]Main!$I$5</f>
+        <f>+[25]Main!$I$6-[25]Main!$I$5</f>
         <v>3205.0709999999999</v>
       </c>
       <c r="H47" s="14">
@@ -7156,15 +7156,15 @@
         <v>22</v>
       </c>
       <c r="E50" s="3">
-        <f>+[25]Main!$G$2</f>
+        <f>+[26]Main!$G$2</f>
         <v>17.309999999999999</v>
       </c>
       <c r="F50" s="14">
-        <f>+[25]Main!$G$4</f>
+        <f>+[26]Main!$G$4</f>
         <v>5750.3819999999996</v>
       </c>
       <c r="G50" s="14">
-        <f>+[25]Main!$G$6-[25]Main!$G$5</f>
+        <f>+[26]Main!$G$6-[26]Main!$G$5</f>
         <v>1466.0810000000004</v>
       </c>
       <c r="H50" s="14">
@@ -7564,15 +7564,15 @@
         <v>22</v>
       </c>
       <c r="E57" s="3">
-        <f>+[26]Main!$I$2</f>
+        <f>+[27]Main!$I$2</f>
         <v>183.2</v>
       </c>
       <c r="F57" s="14">
-        <f>+[26]Main!$I$4</f>
+        <f>+[27]Main!$I$4</f>
         <v>5589.2865391999994</v>
       </c>
       <c r="G57" s="14">
-        <f>+[26]Main!$I$6-[26]Main!$I$5</f>
+        <f>+[27]Main!$I$6-[27]Main!$I$5</f>
         <v>6379</v>
       </c>
       <c r="H57" s="14">
@@ -8349,7 +8349,7 @@
     </row>
     <row r="71" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A71" s="11">
-        <f t="shared" ref="A71:A114" si="2">+A70+1</f>
+        <f t="shared" ref="A71:A113" si="2">+A70+1</f>
         <v>68</v>
       </c>
       <c r="B71" s="3" t="s">
@@ -9090,15 +9090,15 @@
         <v>23</v>
       </c>
       <c r="E84" s="34">
-        <f>+[27]Main!$J$2</f>
+        <f>+[28]Main!$J$2</f>
         <v>3555</v>
       </c>
       <c r="F84" s="14">
-        <f>+[27]Main!$J$4*FX!C2</f>
+        <f>+[28]Main!$J$4*FX!C2</f>
         <v>3334.2666713280005</v>
       </c>
       <c r="G84" s="14">
-        <f>+([27]Main!$J$6-[27]Main!$J$5)*FX!C2</f>
+        <f>+([28]Main!$J$6-[28]Main!$J$5)*FX!C2</f>
         <v>-683.66079999999999</v>
       </c>
       <c r="H84" s="14">
@@ -9608,15 +9608,15 @@
         <v>23</v>
       </c>
       <c r="E93" s="3">
-        <f>+[28]Main!$I$2</f>
+        <f>+[29]Main!$I$2</f>
         <v>5310</v>
       </c>
       <c r="F93" s="14">
-        <f>+[28]Main!$I$4*FX!C2</f>
+        <f>+[29]Main!$I$4*FX!C2</f>
         <v>2103.4388983680001</v>
       </c>
       <c r="G93" s="14">
-        <f>+([28]Main!$I$6-[28]Main!$I$5)*FX!C2</f>
+        <f>+([29]Main!$I$6-[29]Main!$I$5)*FX!C2</f>
         <v>-590.64960000000008</v>
       </c>
       <c r="H93" s="14">
@@ -10294,15 +10294,15 @@
         <v>22</v>
       </c>
       <c r="E105" s="3">
-        <f>+[29]Main!$I$2</f>
+        <f>+[30]Main!$I$2</f>
         <v>33.76</v>
       </c>
       <c r="F105" s="14">
-        <f>+[29]Main!$I$4</f>
+        <f>+[30]Main!$I$4</f>
         <v>1615.1327198399999</v>
       </c>
       <c r="G105" s="14">
-        <f>+[29]Main!$I$6-[29]Main!$I$5</f>
+        <f>+[30]Main!$I$6-[30]Main!$I$5</f>
         <v>553.85699999999997</v>
       </c>
       <c r="H105" s="14">
@@ -10476,15 +10476,15 @@
         <v>153</v>
       </c>
       <c r="E108" s="3">
-        <f>+[30]Main!$H$2</f>
+        <f>+[31]Main!$H$2</f>
         <v>15.92</v>
       </c>
       <c r="F108" s="14">
-        <f>+[30]Main!$H$5*FX!C4</f>
+        <f>+[31]Main!$H$5*FX!C4</f>
         <v>2707.3869572160002</v>
       </c>
       <c r="G108" s="14">
-        <f>+([30]Main!$H$7-[30]Main!$H$6)*FX!C4</f>
+        <f>+([31]Main!$H$7-[31]Main!$H$6)*FX!C4</f>
         <v>699.94651999999996</v>
       </c>
       <c r="H108" s="14">
@@ -10604,15 +10604,15 @@
         <v>85</v>
       </c>
       <c r="E110" s="3">
-        <f>+[31]Main!$I$2</f>
+        <f>+[32]Main!$I$2</f>
         <v>3.28</v>
       </c>
       <c r="F110" s="14">
-        <f>+[31]Main!$I$4*FX!C3</f>
+        <f>+[32]Main!$I$4*FX!C3</f>
         <v>372.96258964800001</v>
       </c>
       <c r="G110" s="14">
-        <f>+([31]Main!$I$6-[31]Main!$I$5)*FX!C3</f>
+        <f>+([32]Main!$I$6-[32]Main!$I$5)*FX!C3</f>
         <v>50.842859999999995</v>
       </c>
       <c r="H110" s="14">
@@ -17235,15 +17235,15 @@
         <v>22</v>
       </c>
       <c r="E5" s="26">
-        <f>+[32]Main!$H$2</f>
+        <f>+[33]Main!$H$2</f>
         <v>405.1</v>
       </c>
       <c r="F5" s="26">
-        <f>+[32]Main!$H$4</f>
+        <f>+[33]Main!$H$4</f>
         <v>3009258.8985904003</v>
       </c>
       <c r="G5" s="26">
-        <f>+[32]Main!$H$6-[32]Main!$H$5</f>
+        <f>+[33]Main!$H$6-[33]Main!$H$5</f>
         <v>-38010</v>
       </c>
       <c r="H5" s="26">
@@ -17330,15 +17330,15 @@
         <v>26</v>
       </c>
       <c r="E6" s="26">
-        <f>+[33]Main!$G$2</f>
+        <f>+[34]Main!$G$2</f>
         <v>617.5</v>
       </c>
       <c r="F6" s="26">
-        <f>+[33]Main!$G$4*FX!C6</f>
+        <f>+[34]Main!$G$4*FX!C6</f>
         <v>1271.3400000000001</v>
       </c>
       <c r="G6" s="26">
-        <f>+([33]Main!$G$6-[33]Main!$G$5)*FX!C6</f>
+        <f>+([34]Main!$G$6-[34]Main!$G$5)*FX!C6</f>
         <v>-668190.33400000015</v>
       </c>
       <c r="H6" s="26">
@@ -17615,15 +17615,15 @@
         <v>26</v>
       </c>
       <c r="E9" s="26">
-        <f>+[34]Main!$I$2</f>
+        <f>+[35]Main!$I$2</f>
         <v>2123</v>
       </c>
       <c r="F9" s="26">
-        <f>+[35]Main!$H$5*FX!C6</f>
+        <f>+[36]Main!$H$5*FX!C6</f>
         <v>65131.275185760009</v>
       </c>
       <c r="G9" s="26">
-        <f>+([35]Main!$H$7-[35]Main!$H$6)*FX!C6</f>
+        <f>+([36]Main!$H$7-[36]Main!$H$6)*FX!C6</f>
         <v>-16042.82638</v>
       </c>
       <c r="H9" s="26">
@@ -18185,15 +18185,15 @@
         <v>23</v>
       </c>
       <c r="E15" s="26">
-        <f>+[34]Main!$I$2</f>
+        <f>+[35]Main!$I$2</f>
         <v>2123</v>
       </c>
       <c r="F15" s="26">
-        <f>+[34]Main!$I$4*FX!C2</f>
+        <f>+[35]Main!$I$4*FX!C2</f>
         <v>11429.0165977856</v>
       </c>
       <c r="G15" s="26">
-        <f>+([34]Main!$I$6-[34]Main!$I$5)*FX!C2</f>
+        <f>+([35]Main!$I$6-[35]Main!$I$5)*FX!C2</f>
         <v>-2117.3888000000002</v>
       </c>
       <c r="H15" s="26">
@@ -18470,15 +18470,15 @@
         <v>94</v>
       </c>
       <c r="E18" s="26">
-        <f>+[36]Main!$H$2</f>
+        <f>+[37]Main!$H$2</f>
         <v>12.11</v>
       </c>
       <c r="F18" s="26">
-        <f>+[36]Main!$H$4*FX!C3</f>
+        <f>+[37]Main!$H$4*FX!C3</f>
         <v>1601.5717199999999</v>
       </c>
       <c r="G18" s="26">
-        <f>+([36]Main!$H$6-[36]Main!$H$5)*FX!C3</f>
+        <f>+([37]Main!$H$6-[37]Main!$H$5)*FX!C3</f>
         <v>1343.7380000000003</v>
       </c>
       <c r="H18" s="26">
@@ -18708,15 +18708,15 @@
         <v>22</v>
       </c>
       <c r="E21" s="26">
-        <f>+[37]Main!$J$2</f>
+        <f>+[38]Main!$J$2</f>
         <v>21.7</v>
       </c>
       <c r="F21" s="26">
-        <f>+[37]Main!$J$4</f>
+        <f>+[38]Main!$J$4</f>
         <v>9701.7223876999997</v>
       </c>
       <c r="G21" s="26">
-        <f>+[37]Main!$J$6-[37]Main!$J$5</f>
+        <f>+[38]Main!$J$6-[38]Main!$J$5</f>
         <v>-4758</v>
       </c>
       <c r="H21" s="26">
@@ -28183,15 +28183,15 @@
         <v>22</v>
       </c>
       <c r="E8" s="14">
-        <f>+[38]Main!$I$2</f>
+        <f>+[39]Main!$I$2</f>
         <v>50.5</v>
       </c>
       <c r="F8" s="14">
-        <f>+[38]Main!$I$4</f>
+        <f>+[39]Main!$I$4</f>
         <v>22898.106829</v>
       </c>
       <c r="G8" s="14">
-        <f>+[38]Main!$I$6-[38]Main!$I$5</f>
+        <f>+[39]Main!$I$6-[39]Main!$I$5</f>
         <v>3878</v>
       </c>
       <c r="H8" s="14">
@@ -28305,15 +28305,15 @@
         <v>22</v>
       </c>
       <c r="E11" s="14">
-        <f>+[39]Main!$I$2</f>
+        <f>+[40]Main!$I$2</f>
         <v>30.44</v>
       </c>
       <c r="F11" s="14">
-        <f>+[39]Main!$I$4</f>
+        <f>+[40]Main!$I$4</f>
         <v>17310.539416759999</v>
       </c>
       <c r="G11" s="14">
-        <f>+[39]Main!$I$6-[39]Main!$I$5</f>
+        <f>+[40]Main!$I$6-[40]Main!$I$5</f>
         <v>1122</v>
       </c>
       <c r="H11" s="14">
@@ -28391,15 +28391,15 @@
         <v>22</v>
       </c>
       <c r="E13" s="14">
-        <f>+[40]Main!$H$2</f>
+        <f>+[41]Main!$H$2</f>
         <v>41.21</v>
       </c>
       <c r="F13" s="14">
-        <f>+[40]Main!$H$4</f>
+        <f>+[41]Main!$H$4</f>
         <v>8939.4565020800001</v>
       </c>
       <c r="G13" s="14">
-        <f>+[40]Main!$H$6-[40]Main!$H$5</f>
+        <f>+[41]Main!$H$6-[41]Main!$H$5</f>
         <v>-663.44470000000001</v>
       </c>
       <c r="H13" s="14">
@@ -28441,15 +28441,15 @@
         <v>22</v>
       </c>
       <c r="E14" s="14">
-        <f>+[41]Main!$H$2</f>
+        <f>+[42]Main!$H$2</f>
         <v>80.5</v>
       </c>
       <c r="F14" s="14">
-        <f>+[41]Main!$H$4</f>
+        <f>+[42]Main!$H$4</f>
         <v>12979.714142500001</v>
       </c>
       <c r="G14" s="14">
-        <f>+[41]Main!$H$6-[41]Main!$H$5</f>
+        <f>+[42]Main!$H$6-[42]Main!$H$5</f>
         <v>-642.15699999999993</v>
       </c>
       <c r="H14" s="14">
@@ -28491,15 +28491,15 @@
         <v>22</v>
       </c>
       <c r="E15" s="14">
-        <f>+[23]Main!$I$2</f>
+        <f>+[24]Main!$I$2</f>
         <v>13.8</v>
       </c>
       <c r="F15" s="14">
-        <f>+[23]Main!$I$4</f>
+        <f>+[24]Main!$I$4</f>
         <v>9315</v>
       </c>
       <c r="G15" s="14">
-        <f>+[23]Main!$I$6-[23]Main!$I$5</f>
+        <f>+[24]Main!$I$6-[24]Main!$I$5</f>
         <v>11775</v>
       </c>
       <c r="H15" s="14">
@@ -28577,15 +28577,15 @@
         <v>22</v>
       </c>
       <c r="E17" s="14">
-        <f>+[42]Main!$K$2</f>
+        <f>+[43]Main!$K$2</f>
         <v>78.55</v>
       </c>
       <c r="F17" s="14">
-        <f>+[42]Main!$K$4</f>
+        <f>+[43]Main!$K$4</f>
         <v>7215.2325581999994</v>
       </c>
       <c r="G17" s="14">
-        <f>+[42]Main!$K$6-[42]Main!$K$5</f>
+        <f>+[43]Main!$K$6-[43]Main!$K$5</f>
         <v>1417</v>
       </c>
       <c r="H17" s="14">
@@ -30783,15 +30783,15 @@
         <v>22</v>
       </c>
       <c r="E78" s="14">
-        <f>+[43]Main!$H$2</f>
+        <f>+[44]Main!$H$2</f>
         <v>1.7</v>
       </c>
       <c r="F78" s="14">
-        <f>+[43]Main!$H$4</f>
+        <f>+[44]Main!$H$4</f>
         <v>183.18753240000001</v>
       </c>
       <c r="G78" s="14">
-        <f>+[43]Main!$H$6-[43]Main!$H$5</f>
+        <f>+[44]Main!$H$6-[44]Main!$H$5</f>
         <v>149.33199999999999</v>
       </c>
       <c r="H78" s="14">
@@ -31225,15 +31225,15 @@
         <v>85</v>
       </c>
       <c r="E90" s="14">
-        <f>+[44]Main!$K$2</f>
+        <f>+[45]Main!$K$2</f>
         <v>17.72</v>
       </c>
       <c r="F90" s="14">
-        <f>+[44]Main!$K$4*FX!C3</f>
+        <f>+[45]Main!$K$4*FX!C3</f>
         <v>3630.2432399999998</v>
       </c>
       <c r="G90" s="14">
-        <f>+([44]Main!$K$6-[44]Main!$K$5)*FX!C3</f>
+        <f>+([45]Main!$K$6-[45]Main!$K$5)*FX!C3</f>
         <v>1191.607</v>
       </c>
       <c r="H90" s="14">
